--- a/artfynd/A 58895-2025 artfynd.xlsx
+++ b/artfynd/A 58895-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129846986</v>
       </c>
       <c r="B2" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 58895-2025 artfynd.xlsx
+++ b/artfynd/A 58895-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129846986</v>
       </c>
       <c r="B2" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 58895-2025 artfynd.xlsx
+++ b/artfynd/A 58895-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129846986</v>
       </c>
       <c r="B2" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 58895-2025 artfynd.xlsx
+++ b/artfynd/A 58895-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129846986</v>
       </c>
       <c r="B2" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 58895-2025 artfynd.xlsx
+++ b/artfynd/A 58895-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129846986</v>
       </c>
       <c r="B2" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 58895-2025 artfynd.xlsx
+++ b/artfynd/A 58895-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129846986</v>
       </c>
       <c r="B2" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 58895-2025 artfynd.xlsx
+++ b/artfynd/A 58895-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>129846986</v>
       </c>
       <c r="B2" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,6 +787,2802 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>130252584</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57900</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Bergtallstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>497202</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6826919</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Kajsa Larsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Kajsa Larsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>130252591</v>
+      </c>
+      <c r="B4" t="n">
+        <v>78852</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bergtallstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>496966</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6826906</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Kajsa Larsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Kajsa Larsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>130252592</v>
+      </c>
+      <c r="B5" t="n">
+        <v>78852</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bergtallstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>496950</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6827038</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Kajsa Larsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Kajsa Larsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>130252588</v>
+      </c>
+      <c r="B6" t="n">
+        <v>78852</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bergtallstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>497230</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6826961</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Kajsa Larsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Kajsa Larsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>130252115</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79127</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>185</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bergfallstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>496555</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6826991</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>130252594</v>
+      </c>
+      <c r="B8" t="n">
+        <v>78852</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bergtallstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>496874</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6827149</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Kajsa Larsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Kajsa Larsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>130252603</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79095</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bergtallstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>496694</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6827132</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Kajsa Larsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Kajsa Larsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>130252595</v>
+      </c>
+      <c r="B10" t="n">
+        <v>78852</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bergtallstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>496894</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6827123</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Kajsa Larsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Kajsa Larsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>130252600</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79095</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Bergtallstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>496948</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6827029</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Kajsa Larsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Kajsa Larsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>130252589</v>
+      </c>
+      <c r="B12" t="n">
+        <v>78852</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Bergtallstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>497211</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6826926</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Kajsa Larsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Kajsa Larsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>130252599</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79095</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Bergtallstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>496968</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6826958</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Kajsa Larsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Kajsa Larsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>130252604</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79095</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Bergtallstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>496679</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6827141</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Kajsa Larsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Kajsa Larsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>130252587</v>
+      </c>
+      <c r="B15" t="n">
+        <v>8451</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Bergtallstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>496719</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6827112</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Kajsa Larsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Kajsa Larsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>130252605</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79095</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Bergtallstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>496676</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6827143</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Kajsa Larsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Kajsa Larsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>130252585</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57738</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Bergtallstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>496635</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6827130</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Kajsa Larsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Kajsa Larsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>130252607</v>
+      </c>
+      <c r="B18" t="n">
+        <v>92923</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Bergtallstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>496598</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6827085</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Kajsa Larsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Kajsa Larsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>130252590</v>
+      </c>
+      <c r="B19" t="n">
+        <v>78852</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Bergtallstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>496995</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6826923</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Kajsa Larsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Kajsa Larsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>130252609</v>
+      </c>
+      <c r="B20" t="n">
+        <v>92923</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Bergtallstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>496549</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6826988</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Kajsa Larsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Kajsa Larsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>130252602</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79095</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Bergtallstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>496722</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6827107</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Kajsa Larsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Kajsa Larsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>130252598</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79095</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Bergtallstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>497202</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6826911</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Kajsa Larsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Kajsa Larsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>130252596</v>
+      </c>
+      <c r="B23" t="n">
+        <v>78852</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Bergtallstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>496771</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6827069</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Kajsa Larsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Kajsa Larsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>130252606</v>
+      </c>
+      <c r="B24" t="n">
+        <v>92923</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Bergtallstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>496618</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6827114</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Kajsa Larsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Kajsa Larsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>130252601</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79095</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Bergtallstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>496911</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6827100</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Kajsa Larsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Kajsa Larsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>130252597</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79095</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Bergtallstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>496922</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6826906</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Kajsa Larsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Kajsa Larsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>130252608</v>
+      </c>
+      <c r="B27" t="n">
+        <v>92923</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Bergtallstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>496576</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6826998</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Kajsa Larsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Kajsa Larsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>130252114</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79127</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>185</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Bergfallstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>496880</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6827051</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 58895-2025 artfynd.xlsx
+++ b/artfynd/A 58895-2025 artfynd.xlsx
@@ -2075,32 +2075,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130252119</v>
+        <v>130252122</v>
       </c>
       <c r="B15" t="n">
-        <v>57985</v>
+        <v>8451</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2110,10 +2110,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>496602</v>
+        <v>496640</v>
       </c>
       <c r="R15" t="n">
-        <v>6827039</v>
+        <v>6827137</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2145,7 +2145,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2289,32 +2289,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130252122</v>
+        <v>130252119</v>
       </c>
       <c r="B17" t="n">
-        <v>8451</v>
+        <v>57985</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2324,10 +2324,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>496640</v>
+        <v>496602</v>
       </c>
       <c r="R17" t="n">
-        <v>6827137</v>
+        <v>6827039</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2931,10 +2931,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130252124</v>
+        <v>130252142</v>
       </c>
       <c r="B23" t="n">
-        <v>78937</v>
+        <v>79180</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2942,21 +2942,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2966,10 +2966,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>497192</v>
+        <v>496939</v>
       </c>
       <c r="R23" t="n">
-        <v>6826651</v>
+        <v>6827036</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3011,7 +3011,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3038,10 +3038,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130252142</v>
+        <v>130252124</v>
       </c>
       <c r="B24" t="n">
-        <v>79180</v>
+        <v>78937</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3049,21 +3049,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3073,10 +3073,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>496939</v>
+        <v>497192</v>
       </c>
       <c r="R24" t="n">
-        <v>6827036</v>
+        <v>6826651</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3118,7 +3118,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -6044,10 +6044,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130252118</v>
+        <v>130252150</v>
       </c>
       <c r="B52" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6055,42 +6055,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>496923</v>
+        <v>496701</v>
       </c>
       <c r="R52" t="n">
-        <v>6826913</v>
+        <v>6827080</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6122,7 +6114,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6132,12 +6124,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:50</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6164,45 +6151,54 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130252150</v>
+        <v>130252130</v>
       </c>
       <c r="B53" t="n">
-        <v>79180</v>
+        <v>44080</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>101735</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>496701</v>
+        <v>497225</v>
       </c>
       <c r="R53" t="n">
-        <v>6827080</v>
+        <v>6826804</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6234,7 +6230,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6244,7 +6240,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6253,6 +6249,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6271,41 +6268,40 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130252130</v>
+        <v>130252118</v>
       </c>
       <c r="B54" t="n">
-        <v>44080</v>
+        <v>57826</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>101735</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
@@ -6315,10 +6311,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>497225</v>
+        <v>496923</v>
       </c>
       <c r="R54" t="n">
-        <v>6826804</v>
+        <v>6826913</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6350,7 +6346,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6360,7 +6356,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6369,7 +6370,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -7352,10 +7352,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130252114</v>
+        <v>130252597</v>
       </c>
       <c r="B64" t="n">
-        <v>79212</v>
+        <v>79180</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7363,34 +7363,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>496880</v>
+        <v>496922</v>
       </c>
       <c r="R64" t="n">
-        <v>6827051</v>
+        <v>6826906</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7422,7 +7422,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7432,7 +7432,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7441,26 +7441,25 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130252597</v>
+        <v>130252139</v>
       </c>
       <c r="B65" t="n">
         <v>79180</v>
@@ -7491,14 +7490,14 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>496922</v>
+        <v>497225</v>
       </c>
       <c r="R65" t="n">
-        <v>6826906</v>
+        <v>6826804</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7530,7 +7529,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7540,7 +7539,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7555,19 +7554,19 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130252139</v>
+        <v>130252151</v>
       </c>
       <c r="B66" t="n">
         <v>79180</v>
@@ -7602,10 +7601,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>497225</v>
+        <v>496704</v>
       </c>
       <c r="R66" t="n">
-        <v>6826804</v>
+        <v>6827086</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7637,7 +7636,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7647,7 +7646,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7674,10 +7673,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130252151</v>
+        <v>130252114</v>
       </c>
       <c r="B67" t="n">
-        <v>79180</v>
+        <v>79212</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7685,21 +7684,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7709,10 +7708,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>496704</v>
+        <v>496880</v>
       </c>
       <c r="R67" t="n">
-        <v>6827086</v>
+        <v>6827051</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7744,7 +7743,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7754,7 +7753,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7763,6 +7762,7 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -9311,10 +9311,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>130255837</v>
+        <v>130256346</v>
       </c>
       <c r="B83" t="n">
-        <v>79180</v>
+        <v>78938</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9322,21 +9322,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9346,10 +9346,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>497191</v>
+        <v>496652</v>
       </c>
       <c r="R83" t="n">
-        <v>6826771</v>
+        <v>6827164</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9379,19 +9379,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>12:00</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9406,22 +9396,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>130256346</v>
+        <v>130255837</v>
       </c>
       <c r="B84" t="n">
-        <v>78938</v>
+        <v>79180</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9429,21 +9419,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9453,10 +9443,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>496652</v>
+        <v>497191</v>
       </c>
       <c r="R84" t="n">
-        <v>6827164</v>
+        <v>6826771</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9486,9 +9476,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9503,12 +9503,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
@@ -10749,10 +10749,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>130255827</v>
+        <v>130256350</v>
       </c>
       <c r="B97" t="n">
-        <v>79180</v>
+        <v>78937</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10760,21 +10760,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10784,10 +10784,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>496658</v>
+        <v>496962</v>
       </c>
       <c r="R97" t="n">
-        <v>6827164</v>
+        <v>6826909</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10817,19 +10817,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>10:27</t>
-        </is>
-      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>10:27</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10844,19 +10834,19 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>130255812</v>
+        <v>130256375</v>
       </c>
       <c r="B98" t="n">
         <v>79180</v>
@@ -10891,10 +10881,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>497186</v>
+        <v>496859</v>
       </c>
       <c r="R98" t="n">
-        <v>6826839</v>
+        <v>6827052</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10924,19 +10914,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z98" t="inlineStr">
-        <is>
-          <t>11:52</t>
-        </is>
-      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t>11:52</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10951,19 +10931,19 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>130255825</v>
+        <v>130255827</v>
       </c>
       <c r="B99" t="n">
         <v>79180</v>
@@ -10998,10 +10978,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>496759</v>
+        <v>496658</v>
       </c>
       <c r="R99" t="n">
-        <v>6827133</v>
+        <v>6827164</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11033,7 +11013,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11043,7 +11023,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11070,7 +11050,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>130255807</v>
+        <v>130255825</v>
       </c>
       <c r="B100" t="n">
         <v>79180</v>
@@ -11105,10 +11085,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>497130</v>
+        <v>496759</v>
       </c>
       <c r="R100" t="n">
-        <v>6826601</v>
+        <v>6827133</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11140,7 +11120,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11150,7 +11130,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11177,10 +11157,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>130256350</v>
+        <v>130255807</v>
       </c>
       <c r="B101" t="n">
-        <v>78937</v>
+        <v>79180</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11188,21 +11168,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11212,10 +11192,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>496962</v>
+        <v>497130</v>
       </c>
       <c r="R101" t="n">
-        <v>6826909</v>
+        <v>6826601</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11245,9 +11225,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11262,12 +11252,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
@@ -11371,7 +11361,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>130256375</v>
+        <v>130255812</v>
       </c>
       <c r="B103" t="n">
         <v>79180</v>
@@ -11406,10 +11396,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>496859</v>
+        <v>497186</v>
       </c>
       <c r="R103" t="n">
-        <v>6827052</v>
+        <v>6826839</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11439,9 +11429,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11456,19 +11456,19 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>130256353</v>
+        <v>130256351</v>
       </c>
       <c r="B104" t="n">
         <v>78937</v>
@@ -11503,10 +11503,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>496827</v>
+        <v>496898</v>
       </c>
       <c r="R104" t="n">
-        <v>6827089</v>
+        <v>6827000</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11565,10 +11565,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>130255833</v>
+        <v>130256353</v>
       </c>
       <c r="B105" t="n">
-        <v>79180</v>
+        <v>78937</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11576,21 +11576,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11600,10 +11600,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>496579</v>
+        <v>496827</v>
       </c>
       <c r="R105" t="n">
-        <v>6827030</v>
+        <v>6827089</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11633,19 +11633,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z105" t="inlineStr">
-        <is>
-          <t>10:11</t>
-        </is>
-      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB105" t="inlineStr">
-        <is>
-          <t>10:11</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11660,19 +11650,19 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>130255804</v>
+        <v>130255833</v>
       </c>
       <c r="B106" t="n">
         <v>79180</v>
@@ -11707,10 +11697,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>497012</v>
+        <v>496579</v>
       </c>
       <c r="R106" t="n">
-        <v>6826898</v>
+        <v>6827030</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11742,7 +11732,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11752,7 +11742,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11779,7 +11769,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>130255826</v>
+        <v>130255804</v>
       </c>
       <c r="B107" t="n">
         <v>79180</v>
@@ -11814,10 +11804,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>496694</v>
+        <v>497012</v>
       </c>
       <c r="R107" t="n">
-        <v>6827122</v>
+        <v>6826898</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11849,7 +11839,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -11859,7 +11849,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11886,10 +11876,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>130256351</v>
+        <v>130255826</v>
       </c>
       <c r="B108" t="n">
-        <v>78937</v>
+        <v>79180</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11897,21 +11887,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11921,10 +11911,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>496898</v>
+        <v>496694</v>
       </c>
       <c r="R108" t="n">
-        <v>6827000</v>
+        <v>6827122</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11954,9 +11944,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11971,12 +11971,12 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
@@ -12588,7 +12588,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>130256357</v>
+        <v>130256380</v>
       </c>
       <c r="B115" t="n">
         <v>79180</v>
@@ -12623,10 +12623,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>496964</v>
+        <v>496852</v>
       </c>
       <c r="R115" t="n">
-        <v>6826912</v>
+        <v>6827074</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12685,7 +12685,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>130256380</v>
+        <v>130255802</v>
       </c>
       <c r="B116" t="n">
         <v>79180</v>
@@ -12720,10 +12720,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>496852</v>
+        <v>496785</v>
       </c>
       <c r="R116" t="n">
-        <v>6827074</v>
+        <v>6827060</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12753,9 +12753,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12770,19 +12780,19 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>130255802</v>
+        <v>130256357</v>
       </c>
       <c r="B117" t="n">
         <v>79180</v>
@@ -12817,10 +12827,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>496785</v>
+        <v>496964</v>
       </c>
       <c r="R117" t="n">
-        <v>6827060</v>
+        <v>6826912</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12850,19 +12860,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z117" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB117" t="inlineStr">
-        <is>
-          <t>12:47</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12877,12 +12877,12 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
@@ -13792,32 +13792,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>130256392</v>
+        <v>130256343</v>
       </c>
       <c r="B127" t="n">
-        <v>93010</v>
+        <v>79180</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13827,10 +13827,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>496581</v>
+        <v>496851</v>
       </c>
       <c r="R127" t="n">
-        <v>6827082</v>
+        <v>6827066</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13871,7 +13871,6 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
-      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
@@ -13890,45 +13889,54 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>130256343</v>
+        <v>130255793</v>
       </c>
       <c r="B128" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>496851</v>
+        <v>496670</v>
       </c>
       <c r="R128" t="n">
-        <v>6827066</v>
+        <v>6827136</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13958,74 +13966,94 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AD128" t="b">
         <v>0</v>
       </c>
       <c r="AE128" t="b">
         <v>0</v>
       </c>
+      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>130255834</v>
+        <v>130256349</v>
       </c>
       <c r="B129" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>496582</v>
+        <v>496714</v>
       </c>
       <c r="R129" t="n">
-        <v>6827040</v>
+        <v>6827127</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14055,84 +14083,84 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z129" t="inlineStr">
-        <is>
-          <t>10:10</t>
-        </is>
-      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="AB129" t="inlineStr">
-        <is>
-          <t>10:10</t>
-        </is>
-      </c>
       <c r="AD129" t="b">
         <v>0</v>
       </c>
       <c r="AE129" t="b">
         <v>0</v>
       </c>
+      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>130255805</v>
+        <v>130256347</v>
       </c>
       <c r="B130" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>497139</v>
+        <v>496941</v>
       </c>
       <c r="R130" t="n">
-        <v>6826719</v>
+        <v>6826899</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14162,46 +14190,37 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z130" t="inlineStr">
-        <is>
-          <t>12:17</t>
-        </is>
-      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="AB130" t="inlineStr">
-        <is>
-          <t>12:17</t>
-        </is>
-      </c>
       <c r="AD130" t="b">
         <v>0</v>
       </c>
       <c r="AE130" t="b">
         <v>0</v>
       </c>
+      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>130255836</v>
+        <v>130255834</v>
       </c>
       <c r="B131" t="n">
         <v>79180</v>
@@ -14236,10 +14255,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>497183</v>
+        <v>496582</v>
       </c>
       <c r="R131" t="n">
-        <v>6826662</v>
+        <v>6827040</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14271,7 +14290,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -14281,7 +14300,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14308,54 +14327,45 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>130255793</v>
+        <v>130255805</v>
       </c>
       <c r="B132" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr"/>
-      <c r="K132" t="inlineStr"/>
-      <c r="L132" t="inlineStr"/>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>496670</v>
+        <v>497139</v>
       </c>
       <c r="R132" t="n">
-        <v>6827136</v>
+        <v>6826719</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14387,7 +14397,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14397,7 +14407,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14406,7 +14416,6 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
-      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
@@ -14425,54 +14434,45 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>130256349</v>
+        <v>130255836</v>
       </c>
       <c r="B133" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
-      <c r="L133" t="inlineStr"/>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>496714</v>
+        <v>497183</v>
       </c>
       <c r="R133" t="n">
-        <v>6827127</v>
+        <v>6826662</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14502,40 +14502,49 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z133" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AA133" t="inlineStr">
         <is>
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="AB133" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AD133" t="b">
         <v>0</v>
       </c>
       <c r="AE133" t="b">
         <v>0</v>
       </c>
-      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>130256347</v>
+        <v>130256392</v>
       </c>
       <c r="B134" t="n">
-        <v>8451</v>
+        <v>93010</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14543,43 +14552,34 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
-      <c r="J134" t="inlineStr"/>
-      <c r="K134" t="inlineStr"/>
-      <c r="L134" t="inlineStr"/>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>496941</v>
+        <v>496581</v>
       </c>
       <c r="R134" t="n">
-        <v>6826899</v>
+        <v>6827082</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>

--- a/artfynd/A 58895-2025 artfynd.xlsx
+++ b/artfynd/A 58895-2025 artfynd.xlsx
@@ -790,45 +790,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130252591</v>
+        <v>130252120</v>
       </c>
       <c r="B3" t="n">
-        <v>78937</v>
+        <v>8451</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>496966</v>
+        <v>496653</v>
       </c>
       <c r="R3" t="n">
-        <v>6826906</v>
+        <v>6827111</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,44 +885,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130252116</v>
+        <v>130252155</v>
       </c>
       <c r="B4" t="n">
-        <v>79799</v>
+        <v>93010</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>496721</v>
+        <v>496725</v>
       </c>
       <c r="R4" t="n">
-        <v>6827083</v>
+        <v>6827084</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -967,7 +967,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,45 +1004,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130252155</v>
+        <v>130252591</v>
       </c>
       <c r="B5" t="n">
-        <v>93010</v>
+        <v>78937</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>496725</v>
+        <v>496966</v>
       </c>
       <c r="R5" t="n">
-        <v>6827084</v>
+        <v>6826906</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1099,22 +1099,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130252584</v>
+        <v>130252116</v>
       </c>
       <c r="B6" t="n">
-        <v>57985</v>
+        <v>79799</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1122,34 +1122,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497202</v>
+        <v>496721</v>
       </c>
       <c r="R6" t="n">
-        <v>6826919</v>
+        <v>6827083</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1206,57 +1206,57 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130252120</v>
+        <v>130252584</v>
       </c>
       <c r="B7" t="n">
-        <v>8451</v>
+        <v>57985</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>496653</v>
+        <v>497202</v>
       </c>
       <c r="R7" t="n">
-        <v>6827111</v>
+        <v>6826919</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1313,12 +1313,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1432,10 +1432,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130252126</v>
+        <v>130252115</v>
       </c>
       <c r="B9" t="n">
-        <v>78937</v>
+        <v>79212</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1443,21 +1443,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>496737</v>
+        <v>496555</v>
       </c>
       <c r="R9" t="n">
-        <v>6827071</v>
+        <v>6826991</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1512,7 +1512,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,6 +1521,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1539,7 +1540,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130252592</v>
+        <v>130252126</v>
       </c>
       <c r="B10" t="n">
         <v>78937</v>
@@ -1570,14 +1571,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>496950</v>
+        <v>496737</v>
       </c>
       <c r="R10" t="n">
-        <v>6827038</v>
+        <v>6827071</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1609,7 +1610,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1619,7 +1620,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1634,19 +1635,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130252588</v>
+        <v>130252592</v>
       </c>
       <c r="B11" t="n">
         <v>78937</v>
@@ -1681,10 +1682,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497230</v>
+        <v>496950</v>
       </c>
       <c r="R11" t="n">
-        <v>6826961</v>
+        <v>6827038</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1716,7 +1717,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1726,7 +1727,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1753,45 +1754,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130252156</v>
+        <v>130252588</v>
       </c>
       <c r="B12" t="n">
-        <v>93010</v>
+        <v>78937</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>496675</v>
+        <v>497230</v>
       </c>
       <c r="R12" t="n">
-        <v>6827138</v>
+        <v>6826961</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1823,7 +1824,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1833,7 +1834,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1848,22 +1849,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130252115</v>
+        <v>130252138</v>
       </c>
       <c r="B13" t="n">
-        <v>79212</v>
+        <v>79180</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1871,21 +1872,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1895,10 +1896,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>496555</v>
+        <v>497207</v>
       </c>
       <c r="R13" t="n">
-        <v>6826991</v>
+        <v>6826726</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1930,7 +1931,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1940,7 +1941,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1949,7 +1950,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1968,32 +1968,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130252138</v>
+        <v>130252156</v>
       </c>
       <c r="B14" t="n">
-        <v>79180</v>
+        <v>93010</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2003,10 +2003,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>497207</v>
+        <v>496675</v>
       </c>
       <c r="R14" t="n">
-        <v>6826726</v>
+        <v>6827138</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2038,7 +2038,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2075,32 +2075,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130252122</v>
+        <v>130252119</v>
       </c>
       <c r="B15" t="n">
-        <v>8451</v>
+        <v>57985</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2110,10 +2110,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>496640</v>
+        <v>496602</v>
       </c>
       <c r="R15" t="n">
-        <v>6827137</v>
+        <v>6827039</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2145,7 +2145,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2289,32 +2289,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130252119</v>
+        <v>130252122</v>
       </c>
       <c r="B17" t="n">
-        <v>57985</v>
+        <v>8451</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2324,10 +2324,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>496602</v>
+        <v>496640</v>
       </c>
       <c r="R17" t="n">
-        <v>6827039</v>
+        <v>6827137</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2931,10 +2931,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130252142</v>
+        <v>130252124</v>
       </c>
       <c r="B23" t="n">
-        <v>79180</v>
+        <v>78937</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2942,21 +2942,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2966,10 +2966,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>496939</v>
+        <v>497192</v>
       </c>
       <c r="R23" t="n">
-        <v>6827036</v>
+        <v>6826651</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3011,7 +3011,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3038,10 +3038,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130252124</v>
+        <v>130252142</v>
       </c>
       <c r="B24" t="n">
-        <v>78937</v>
+        <v>79180</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3049,21 +3049,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3073,10 +3073,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>497192</v>
+        <v>496939</v>
       </c>
       <c r="R24" t="n">
-        <v>6826651</v>
+        <v>6827036</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3118,7 +3118,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3573,10 +3573,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130252141</v>
+        <v>130252129</v>
       </c>
       <c r="B29" t="n">
-        <v>79180</v>
+        <v>78937</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3584,21 +3584,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3608,10 +3608,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>496956</v>
+        <v>496646</v>
       </c>
       <c r="R29" t="n">
-        <v>6827088</v>
+        <v>6827139</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3643,7 +3643,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3680,45 +3680,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130252157</v>
+        <v>130252589</v>
       </c>
       <c r="B30" t="n">
-        <v>93010</v>
+        <v>78937</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>496628</v>
+        <v>497211</v>
       </c>
       <c r="R30" t="n">
-        <v>6827124</v>
+        <v>6826926</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3750,7 +3750,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3760,7 +3760,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3775,22 +3775,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130252129</v>
+        <v>130252141</v>
       </c>
       <c r="B31" t="n">
-        <v>78937</v>
+        <v>79180</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3798,21 +3798,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3822,10 +3822,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>496646</v>
+        <v>496956</v>
       </c>
       <c r="R31" t="n">
-        <v>6827139</v>
+        <v>6827088</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3857,7 +3857,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3867,7 +3867,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3894,45 +3894,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130252589</v>
+        <v>130252157</v>
       </c>
       <c r="B32" t="n">
-        <v>78937</v>
+        <v>93010</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>497211</v>
+        <v>496628</v>
       </c>
       <c r="R32" t="n">
-        <v>6826926</v>
+        <v>6827124</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3964,7 +3964,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3974,7 +3974,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3989,12 +3989,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -7352,10 +7352,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130252597</v>
+        <v>130252114</v>
       </c>
       <c r="B64" t="n">
-        <v>79180</v>
+        <v>79212</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7363,34 +7363,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>496922</v>
+        <v>496880</v>
       </c>
       <c r="R64" t="n">
-        <v>6826906</v>
+        <v>6827051</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7422,7 +7422,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7432,7 +7432,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7441,25 +7441,26 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130252139</v>
+        <v>130252597</v>
       </c>
       <c r="B65" t="n">
         <v>79180</v>
@@ -7490,14 +7491,14 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>497225</v>
+        <v>496922</v>
       </c>
       <c r="R65" t="n">
-        <v>6826804</v>
+        <v>6826906</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7529,7 +7530,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7539,7 +7540,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7554,19 +7555,19 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130252151</v>
+        <v>130252139</v>
       </c>
       <c r="B66" t="n">
         <v>79180</v>
@@ -7601,10 +7602,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>496704</v>
+        <v>497225</v>
       </c>
       <c r="R66" t="n">
-        <v>6827086</v>
+        <v>6826804</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7636,7 +7637,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7646,7 +7647,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7673,10 +7674,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130252114</v>
+        <v>130252151</v>
       </c>
       <c r="B67" t="n">
-        <v>79212</v>
+        <v>79180</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7684,21 +7685,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7708,10 +7709,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>496880</v>
+        <v>496704</v>
       </c>
       <c r="R67" t="n">
-        <v>6827051</v>
+        <v>6827086</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7743,7 +7744,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7753,7 +7754,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7762,7 +7763,6 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -9311,10 +9311,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>130256346</v>
+        <v>130255837</v>
       </c>
       <c r="B83" t="n">
-        <v>78938</v>
+        <v>79180</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9322,21 +9322,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9346,10 +9346,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>496652</v>
+        <v>497191</v>
       </c>
       <c r="R83" t="n">
-        <v>6827164</v>
+        <v>6826771</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9379,9 +9379,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9396,22 +9406,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>130255837</v>
+        <v>130256346</v>
       </c>
       <c r="B84" t="n">
-        <v>79180</v>
+        <v>78938</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9419,21 +9429,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9443,10 +9453,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>497191</v>
+        <v>496652</v>
       </c>
       <c r="R84" t="n">
-        <v>6826771</v>
+        <v>6827164</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9476,19 +9486,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>12:00</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9503,12 +9503,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>

--- a/artfynd/A 58895-2025 artfynd.xlsx
+++ b/artfynd/A 58895-2025 artfynd.xlsx
@@ -790,45 +790,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130252120</v>
+        <v>130252591</v>
       </c>
       <c r="B3" t="n">
-        <v>8451</v>
+        <v>78937</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>496653</v>
+        <v>496966</v>
       </c>
       <c r="R3" t="n">
-        <v>6827111</v>
+        <v>6826906</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,44 +885,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130252155</v>
+        <v>130252116</v>
       </c>
       <c r="B4" t="n">
-        <v>93010</v>
+        <v>79799</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>496725</v>
+        <v>496721</v>
       </c>
       <c r="R4" t="n">
-        <v>6827084</v>
+        <v>6827083</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -967,7 +967,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,45 +1004,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130252591</v>
+        <v>130252155</v>
       </c>
       <c r="B5" t="n">
-        <v>78937</v>
+        <v>93010</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>496966</v>
+        <v>496725</v>
       </c>
       <c r="R5" t="n">
-        <v>6826906</v>
+        <v>6827084</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1099,22 +1099,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130252116</v>
+        <v>130252584</v>
       </c>
       <c r="B6" t="n">
-        <v>79799</v>
+        <v>57985</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1122,34 +1122,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>496721</v>
+        <v>497202</v>
       </c>
       <c r="R6" t="n">
-        <v>6827083</v>
+        <v>6826919</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1206,57 +1206,57 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130252584</v>
+        <v>130252120</v>
       </c>
       <c r="B7" t="n">
-        <v>57985</v>
+        <v>8451</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>497202</v>
+        <v>496653</v>
       </c>
       <c r="R7" t="n">
-        <v>6826919</v>
+        <v>6827111</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1313,12 +1313,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1432,10 +1432,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130252115</v>
+        <v>130252126</v>
       </c>
       <c r="B9" t="n">
-        <v>79212</v>
+        <v>78937</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1443,21 +1443,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>496555</v>
+        <v>496737</v>
       </c>
       <c r="R9" t="n">
-        <v>6826991</v>
+        <v>6827071</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1512,7 +1512,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,7 +1521,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1540,7 +1539,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130252126</v>
+        <v>130252592</v>
       </c>
       <c r="B10" t="n">
         <v>78937</v>
@@ -1571,14 +1570,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>496737</v>
+        <v>496950</v>
       </c>
       <c r="R10" t="n">
-        <v>6827071</v>
+        <v>6827038</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1610,7 +1609,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1620,7 +1619,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1635,19 +1634,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130252592</v>
+        <v>130252588</v>
       </c>
       <c r="B11" t="n">
         <v>78937</v>
@@ -1682,10 +1681,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>496950</v>
+        <v>497230</v>
       </c>
       <c r="R11" t="n">
-        <v>6827038</v>
+        <v>6826961</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1717,7 +1716,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1727,7 +1726,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1754,45 +1753,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130252588</v>
+        <v>130252156</v>
       </c>
       <c r="B12" t="n">
-        <v>78937</v>
+        <v>93010</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497230</v>
+        <v>496675</v>
       </c>
       <c r="R12" t="n">
-        <v>6826961</v>
+        <v>6827138</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1824,7 +1823,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1834,7 +1833,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1849,22 +1848,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130252138</v>
+        <v>130252115</v>
       </c>
       <c r="B13" t="n">
-        <v>79180</v>
+        <v>79212</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1872,21 +1871,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1896,10 +1895,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>497207</v>
+        <v>496555</v>
       </c>
       <c r="R13" t="n">
-        <v>6826726</v>
+        <v>6826991</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1931,7 +1930,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1941,7 +1940,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1950,6 +1949,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1968,32 +1968,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130252156</v>
+        <v>130252138</v>
       </c>
       <c r="B14" t="n">
-        <v>93010</v>
+        <v>79180</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2003,10 +2003,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>496675</v>
+        <v>497207</v>
       </c>
       <c r="R14" t="n">
-        <v>6827138</v>
+        <v>6826726</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2038,7 +2038,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2075,32 +2075,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130252119</v>
+        <v>130252122</v>
       </c>
       <c r="B15" t="n">
-        <v>57985</v>
+        <v>8451</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2110,10 +2110,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>496602</v>
+        <v>496640</v>
       </c>
       <c r="R15" t="n">
-        <v>6827039</v>
+        <v>6827137</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2145,7 +2145,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2289,32 +2289,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130252122</v>
+        <v>130252119</v>
       </c>
       <c r="B17" t="n">
-        <v>8451</v>
+        <v>57985</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2324,10 +2324,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>496640</v>
+        <v>496602</v>
       </c>
       <c r="R17" t="n">
-        <v>6827137</v>
+        <v>6827039</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -3573,10 +3573,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130252129</v>
+        <v>130252141</v>
       </c>
       <c r="B29" t="n">
-        <v>78937</v>
+        <v>79180</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3584,21 +3584,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3608,10 +3608,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>496646</v>
+        <v>496956</v>
       </c>
       <c r="R29" t="n">
-        <v>6827139</v>
+        <v>6827088</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3643,7 +3643,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3680,45 +3680,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130252589</v>
+        <v>130252157</v>
       </c>
       <c r="B30" t="n">
-        <v>78937</v>
+        <v>93010</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>497211</v>
+        <v>496628</v>
       </c>
       <c r="R30" t="n">
-        <v>6826926</v>
+        <v>6827124</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3750,7 +3750,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3760,7 +3760,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3775,22 +3775,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130252141</v>
+        <v>130252129</v>
       </c>
       <c r="B31" t="n">
-        <v>79180</v>
+        <v>78937</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3798,21 +3798,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3822,10 +3822,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>496956</v>
+        <v>496646</v>
       </c>
       <c r="R31" t="n">
-        <v>6827088</v>
+        <v>6827139</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3857,7 +3857,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3867,7 +3867,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3894,45 +3894,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130252157</v>
+        <v>130252589</v>
       </c>
       <c r="B32" t="n">
-        <v>93010</v>
+        <v>78937</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>496628</v>
+        <v>497211</v>
       </c>
       <c r="R32" t="n">
-        <v>6827124</v>
+        <v>6826926</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3964,7 +3964,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3974,7 +3974,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3989,12 +3989,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4750,10 +4750,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130252136</v>
+        <v>130252590</v>
       </c>
       <c r="B40" t="n">
-        <v>79180</v>
+        <v>78937</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4761,34 +4761,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>497002</v>
+        <v>496995</v>
       </c>
       <c r="R40" t="n">
-        <v>6826879</v>
+        <v>6826923</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4820,7 +4820,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4845,19 +4845,19 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130252590</v>
+        <v>130252128</v>
       </c>
       <c r="B41" t="n">
         <v>78937</v>
@@ -4888,14 +4888,14 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>496995</v>
+        <v>496684</v>
       </c>
       <c r="R41" t="n">
-        <v>6826923</v>
+        <v>6827129</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4927,7 +4927,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4937,7 +4937,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4952,22 +4952,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130252128</v>
+        <v>130252136</v>
       </c>
       <c r="B42" t="n">
-        <v>78937</v>
+        <v>79180</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4975,21 +4975,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4999,10 +4999,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>496684</v>
+        <v>497002</v>
       </c>
       <c r="R42" t="n">
-        <v>6827129</v>
+        <v>6826879</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5034,7 +5034,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5044,7 +5044,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -7352,10 +7352,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130252114</v>
+        <v>130252597</v>
       </c>
       <c r="B64" t="n">
-        <v>79212</v>
+        <v>79180</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7363,34 +7363,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>496880</v>
+        <v>496922</v>
       </c>
       <c r="R64" t="n">
-        <v>6827051</v>
+        <v>6826906</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7422,7 +7422,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7432,7 +7432,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7441,26 +7441,25 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130252597</v>
+        <v>130252139</v>
       </c>
       <c r="B65" t="n">
         <v>79180</v>
@@ -7491,14 +7490,14 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>496922</v>
+        <v>497225</v>
       </c>
       <c r="R65" t="n">
-        <v>6826906</v>
+        <v>6826804</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7530,7 +7529,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7540,7 +7539,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7555,19 +7554,19 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130252139</v>
+        <v>130252151</v>
       </c>
       <c r="B66" t="n">
         <v>79180</v>
@@ -7602,10 +7601,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>497225</v>
+        <v>496704</v>
       </c>
       <c r="R66" t="n">
-        <v>6826804</v>
+        <v>6827086</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7637,7 +7636,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7647,7 +7646,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7674,10 +7673,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130252151</v>
+        <v>130252114</v>
       </c>
       <c r="B67" t="n">
-        <v>79180</v>
+        <v>79212</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7685,21 +7684,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7709,10 +7708,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>496704</v>
+        <v>496880</v>
       </c>
       <c r="R67" t="n">
-        <v>6827086</v>
+        <v>6827051</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7744,7 +7743,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7754,7 +7753,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7763,6 +7762,7 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -11983,10 +11983,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>130256360</v>
+        <v>130256342</v>
       </c>
       <c r="B109" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11994,34 +11994,42 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>496972</v>
+        <v>496940</v>
       </c>
       <c r="R109" t="n">
-        <v>6826953</v>
+        <v>6826899</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12054,6 +12062,11 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12080,10 +12093,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>130256354</v>
+        <v>130256360</v>
       </c>
       <c r="B110" t="n">
-        <v>78937</v>
+        <v>79180</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12091,21 +12104,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12115,10 +12128,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>496654</v>
+        <v>496972</v>
       </c>
       <c r="R110" t="n">
-        <v>6827171</v>
+        <v>6826953</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12177,10 +12190,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>130256386</v>
+        <v>130256354</v>
       </c>
       <c r="B111" t="n">
-        <v>79180</v>
+        <v>78937</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12188,21 +12201,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12212,10 +12225,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>496723</v>
+        <v>496654</v>
       </c>
       <c r="R111" t="n">
-        <v>6827125</v>
+        <v>6827171</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12274,7 +12287,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>130255819</v>
+        <v>130256386</v>
       </c>
       <c r="B112" t="n">
         <v>79180</v>
@@ -12309,10 +12322,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>496850</v>
+        <v>496723</v>
       </c>
       <c r="R112" t="n">
-        <v>6827090</v>
+        <v>6827125</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12342,19 +12355,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>11:05</t>
-        </is>
-      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>11:05</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12369,19 +12372,19 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>130256374</v>
+        <v>130255819</v>
       </c>
       <c r="B113" t="n">
         <v>79180</v>
@@ -12416,10 +12419,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>496863</v>
+        <v>496850</v>
       </c>
       <c r="R113" t="n">
-        <v>6827047</v>
+        <v>6827090</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12449,9 +12452,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12466,22 +12479,22 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>130256342</v>
+        <v>130256374</v>
       </c>
       <c r="B114" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12489,42 +12502,34 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>496940</v>
+        <v>496863</v>
       </c>
       <c r="R114" t="n">
-        <v>6826899</v>
+        <v>6827047</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12557,11 +12562,6 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -15445,10 +15445,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>130256340</v>
+        <v>130256364</v>
       </c>
       <c r="B143" t="n">
-        <v>79770</v>
+        <v>79180</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15456,21 +15456,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15480,10 +15480,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>496774</v>
+        <v>496909</v>
       </c>
       <c r="R143" t="n">
-        <v>6827067</v>
+        <v>6827002</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15542,7 +15542,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>130256364</v>
+        <v>130256355</v>
       </c>
       <c r="B144" t="n">
         <v>79180</v>
@@ -15577,10 +15577,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>496909</v>
+        <v>496940</v>
       </c>
       <c r="R144" t="n">
-        <v>6827002</v>
+        <v>6826898</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15639,7 +15639,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>130256355</v>
+        <v>130256362</v>
       </c>
       <c r="B145" t="n">
         <v>79180</v>
@@ -15674,10 +15674,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>496940</v>
+        <v>496893</v>
       </c>
       <c r="R145" t="n">
-        <v>6826898</v>
+        <v>6826998</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15736,7 +15736,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>130256362</v>
+        <v>130256371</v>
       </c>
       <c r="B146" t="n">
         <v>79180</v>
@@ -15771,10 +15771,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>496893</v>
+        <v>496880</v>
       </c>
       <c r="R146" t="n">
-        <v>6826998</v>
+        <v>6827036</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15833,7 +15833,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>130256371</v>
+        <v>130255828</v>
       </c>
       <c r="B147" t="n">
         <v>79180</v>
@@ -15868,10 +15868,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>496880</v>
+        <v>496658</v>
       </c>
       <c r="R147" t="n">
-        <v>6827036</v>
+        <v>6827133</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15901,9 +15901,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z147" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA147" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB147" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15918,19 +15928,19 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>130255828</v>
+        <v>130255821</v>
       </c>
       <c r="B148" t="n">
         <v>79180</v>
@@ -15965,10 +15975,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>496658</v>
+        <v>496839</v>
       </c>
       <c r="R148" t="n">
-        <v>6827133</v>
+        <v>6827082</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16000,7 +16010,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -16010,7 +16020,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16037,45 +16047,56 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>130255821</v>
+        <v>130256394</v>
       </c>
       <c r="B149" t="n">
-        <v>79180</v>
+        <v>93010</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr"/>
+      <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
           <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>496839</v>
+        <v>496581</v>
       </c>
       <c r="R149" t="n">
-        <v>6827082</v>
+        <v>6827079</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16105,95 +16126,75 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z149" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AA149" t="inlineStr">
         <is>
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="AB149" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AD149" t="b">
         <v>0</v>
       </c>
       <c r="AE149" t="b">
         <v>0</v>
       </c>
+      <c r="AF149" t="inlineStr"/>
       <c r="AG149" t="b">
         <v>0</v>
       </c>
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>130256394</v>
+        <v>130256340</v>
       </c>
       <c r="B150" t="n">
-        <v>93010</v>
+        <v>79770</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J150" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K150" t="inlineStr"/>
-      <c r="N150" t="inlineStr"/>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
           <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>496581</v>
+        <v>496774</v>
       </c>
       <c r="R150" t="n">
-        <v>6827079</v>
+        <v>6827067</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16234,7 +16235,6 @@
       <c r="AE150" t="b">
         <v>0</v>
       </c>
-      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 58895-2025 artfynd.xlsx
+++ b/artfynd/A 58895-2025 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>130252591</v>
       </c>
       <c r="B3" t="n">
-        <v>78937</v>
+        <v>78940</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>130252116</v>
       </c>
       <c r="B4" t="n">
-        <v>79799</v>
+        <v>79802</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>130252155</v>
       </c>
       <c r="B5" t="n">
-        <v>93010</v>
+        <v>93013</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>130252132</v>
       </c>
       <c r="B8" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,32 +1432,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130252126</v>
+        <v>130252156</v>
       </c>
       <c r="B9" t="n">
-        <v>78937</v>
+        <v>93013</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>496737</v>
+        <v>496675</v>
       </c>
       <c r="R9" t="n">
-        <v>6827071</v>
+        <v>6827138</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1512,7 +1512,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1539,10 +1539,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130252592</v>
+        <v>130252115</v>
       </c>
       <c r="B10" t="n">
-        <v>78937</v>
+        <v>79215</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1550,34 +1550,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>496950</v>
+        <v>496555</v>
       </c>
       <c r="R10" t="n">
-        <v>6827038</v>
+        <v>6826991</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1628,28 +1628,29 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130252588</v>
+        <v>130252138</v>
       </c>
       <c r="B11" t="n">
-        <v>78937</v>
+        <v>79183</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1657,34 +1658,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497230</v>
+        <v>497207</v>
       </c>
       <c r="R11" t="n">
-        <v>6826961</v>
+        <v>6826726</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1716,7 +1717,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1726,7 +1727,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1741,44 +1742,44 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130252156</v>
+        <v>130252126</v>
       </c>
       <c r="B12" t="n">
-        <v>93010</v>
+        <v>78940</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1788,10 +1789,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>496675</v>
+        <v>496737</v>
       </c>
       <c r="R12" t="n">
-        <v>6827138</v>
+        <v>6827071</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1823,7 +1824,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1833,7 +1834,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1860,10 +1861,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130252115</v>
+        <v>130252592</v>
       </c>
       <c r="B13" t="n">
-        <v>79212</v>
+        <v>78940</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1871,34 +1872,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>496555</v>
+        <v>496950</v>
       </c>
       <c r="R13" t="n">
-        <v>6826991</v>
+        <v>6827038</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1930,7 +1931,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1940,7 +1941,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1949,29 +1950,28 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130252138</v>
+        <v>130252588</v>
       </c>
       <c r="B14" t="n">
-        <v>79180</v>
+        <v>78940</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1979,34 +1979,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>497207</v>
+        <v>497230</v>
       </c>
       <c r="R14" t="n">
-        <v>6826726</v>
+        <v>6826961</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2038,7 +2038,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2063,22 +2063,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130252122</v>
+        <v>130252154</v>
       </c>
       <c r="B15" t="n">
-        <v>8451</v>
+        <v>93013</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2086,21 +2086,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2110,10 +2110,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>496640</v>
+        <v>496692</v>
       </c>
       <c r="R15" t="n">
-        <v>6827137</v>
+        <v>6827092</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2145,7 +2145,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2182,32 +2182,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130252154</v>
+        <v>130252119</v>
       </c>
       <c r="B16" t="n">
-        <v>93010</v>
+        <v>57985</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2217,10 +2217,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>496692</v>
+        <v>496602</v>
       </c>
       <c r="R16" t="n">
-        <v>6827092</v>
+        <v>6827039</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2289,32 +2289,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130252119</v>
+        <v>130252122</v>
       </c>
       <c r="B17" t="n">
-        <v>57985</v>
+        <v>8451</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2324,10 +2324,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>496602</v>
+        <v>496640</v>
       </c>
       <c r="R17" t="n">
-        <v>6827039</v>
+        <v>6827137</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2396,32 +2396,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130252125</v>
+        <v>130252123</v>
       </c>
       <c r="B18" t="n">
-        <v>78937</v>
+        <v>8451</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2431,10 +2431,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>497154</v>
+        <v>496581</v>
       </c>
       <c r="R18" t="n">
-        <v>6826854</v>
+        <v>6827019</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2476,7 +2476,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2503,10 +2503,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130252594</v>
+        <v>130252125</v>
       </c>
       <c r="B19" t="n">
-        <v>78937</v>
+        <v>78940</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2534,14 +2534,14 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>496874</v>
+        <v>497154</v>
       </c>
       <c r="R19" t="n">
-        <v>6827149</v>
+        <v>6826854</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2598,22 +2598,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130252145</v>
+        <v>130252603</v>
       </c>
       <c r="B20" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2641,14 +2641,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>496870</v>
+        <v>496694</v>
       </c>
       <c r="R20" t="n">
-        <v>6827056</v>
+        <v>6827132</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2705,22 +2705,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130252603</v>
+        <v>130252145</v>
       </c>
       <c r="B21" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2748,14 +2748,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>496694</v>
+        <v>496870</v>
       </c>
       <c r="R21" t="n">
-        <v>6827132</v>
+        <v>6827056</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2812,57 +2812,57 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130252123</v>
+        <v>130252594</v>
       </c>
       <c r="B22" t="n">
-        <v>8451</v>
+        <v>78940</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>496581</v>
+        <v>496874</v>
       </c>
       <c r="R22" t="n">
-        <v>6827019</v>
+        <v>6827149</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2904,7 +2904,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2919,22 +2919,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130252124</v>
+        <v>130252142</v>
       </c>
       <c r="B23" t="n">
-        <v>78937</v>
+        <v>79183</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2942,21 +2942,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2966,10 +2966,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>497192</v>
+        <v>496939</v>
       </c>
       <c r="R23" t="n">
-        <v>6826651</v>
+        <v>6827036</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3011,7 +3011,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3038,10 +3038,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130252142</v>
+        <v>130252124</v>
       </c>
       <c r="B24" t="n">
-        <v>79180</v>
+        <v>78940</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3049,21 +3049,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3073,10 +3073,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>496939</v>
+        <v>497192</v>
       </c>
       <c r="R24" t="n">
-        <v>6827036</v>
+        <v>6826651</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3118,7 +3118,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3255,7 +3255,7 @@
         <v>130252595</v>
       </c>
       <c r="B26" t="n">
-        <v>78937</v>
+        <v>78940</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3362,7 +3362,7 @@
         <v>130252127</v>
       </c>
       <c r="B27" t="n">
-        <v>78937</v>
+        <v>78940</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>130252600</v>
       </c>
       <c r="B28" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3573,32 +3573,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130252141</v>
+        <v>130252157</v>
       </c>
       <c r="B29" t="n">
-        <v>79180</v>
+        <v>93013</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3608,10 +3608,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>496956</v>
+        <v>496628</v>
       </c>
       <c r="R29" t="n">
-        <v>6827088</v>
+        <v>6827124</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3643,7 +3643,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3680,32 +3680,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130252157</v>
+        <v>130252129</v>
       </c>
       <c r="B30" t="n">
-        <v>93010</v>
+        <v>78940</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3715,10 +3715,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>496628</v>
+        <v>496646</v>
       </c>
       <c r="R30" t="n">
-        <v>6827124</v>
+        <v>6827139</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3750,7 +3750,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3760,7 +3760,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3787,10 +3787,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130252129</v>
+        <v>130252589</v>
       </c>
       <c r="B31" t="n">
-        <v>78937</v>
+        <v>78940</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3818,14 +3818,14 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>496646</v>
+        <v>497211</v>
       </c>
       <c r="R31" t="n">
-        <v>6827139</v>
+        <v>6826926</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3857,7 +3857,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3867,7 +3867,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3882,22 +3882,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130252589</v>
+        <v>130252141</v>
       </c>
       <c r="B32" t="n">
-        <v>78937</v>
+        <v>79183</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3905,34 +3905,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>497211</v>
+        <v>496956</v>
       </c>
       <c r="R32" t="n">
-        <v>6826926</v>
+        <v>6827088</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3964,7 +3964,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3974,7 +3974,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3989,12 +3989,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4004,7 +4004,7 @@
         <v>130252599</v>
       </c>
       <c r="B33" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4108,10 +4108,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130252604</v>
+        <v>130252135</v>
       </c>
       <c r="B34" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4139,14 +4139,14 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>496679</v>
+        <v>496915</v>
       </c>
       <c r="R34" t="n">
-        <v>6827141</v>
+        <v>6826903</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4203,22 +4203,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130252605</v>
+        <v>130252604</v>
       </c>
       <c r="B35" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4250,10 +4250,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>496676</v>
+        <v>496679</v>
       </c>
       <c r="R35" t="n">
-        <v>6827143</v>
+        <v>6827141</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4322,10 +4322,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130252143</v>
+        <v>130252146</v>
       </c>
       <c r="B36" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4357,10 +4357,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>496877</v>
+        <v>496864</v>
       </c>
       <c r="R36" t="n">
-        <v>6827056</v>
+        <v>6827053</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4429,10 +4429,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130252146</v>
+        <v>130252143</v>
       </c>
       <c r="B37" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4464,10 +4464,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>496864</v>
+        <v>496877</v>
       </c>
       <c r="R37" t="n">
-        <v>6827053</v>
+        <v>6827056</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4509,7 +4509,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4536,10 +4536,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130252135</v>
+        <v>130252605</v>
       </c>
       <c r="B38" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4567,14 +4567,14 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>496915</v>
+        <v>496676</v>
       </c>
       <c r="R38" t="n">
-        <v>6826903</v>
+        <v>6827143</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4631,12 +4631,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4753,7 +4753,7 @@
         <v>130252590</v>
       </c>
       <c r="B40" t="n">
-        <v>78937</v>
+        <v>78940</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4857,10 +4857,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130252128</v>
+        <v>130252136</v>
       </c>
       <c r="B41" t="n">
-        <v>78937</v>
+        <v>79183</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4868,21 +4868,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4892,10 +4892,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>496684</v>
+        <v>497002</v>
       </c>
       <c r="R41" t="n">
-        <v>6827129</v>
+        <v>6826879</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4927,7 +4927,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4937,7 +4937,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4964,10 +4964,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130252136</v>
+        <v>130252128</v>
       </c>
       <c r="B42" t="n">
-        <v>79180</v>
+        <v>78940</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4975,21 +4975,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4999,10 +4999,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>497002</v>
+        <v>496684</v>
       </c>
       <c r="R42" t="n">
-        <v>6826879</v>
+        <v>6827129</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5034,7 +5034,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5044,7 +5044,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5071,45 +5071,53 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130252158</v>
+        <v>130252585</v>
       </c>
       <c r="B43" t="n">
-        <v>93010</v>
+        <v>57823</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>496629</v>
+        <v>496635</v>
       </c>
       <c r="R43" t="n">
-        <v>6827128</v>
+        <v>6827130</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5141,7 +5149,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5151,7 +5159,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5166,22 +5174,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130252607</v>
+        <v>130252158</v>
       </c>
       <c r="B44" t="n">
-        <v>93010</v>
+        <v>93013</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5209,14 +5217,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>496598</v>
+        <v>496629</v>
       </c>
       <c r="R44" t="n">
-        <v>6827085</v>
+        <v>6827128</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5248,7 +5256,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5258,7 +5266,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5267,72 +5275,63 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130252585</v>
+        <v>130252607</v>
       </c>
       <c r="B45" t="n">
-        <v>57823</v>
+        <v>93013</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>496635</v>
+        <v>496598</v>
       </c>
       <c r="R45" t="n">
-        <v>6827130</v>
+        <v>6827085</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5364,7 +5363,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5374,7 +5373,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5383,6 +5382,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5401,32 +5401,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130252609</v>
+        <v>130252598</v>
       </c>
       <c r="B46" t="n">
-        <v>93010</v>
+        <v>79183</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5436,10 +5436,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>496549</v>
+        <v>497202</v>
       </c>
       <c r="R46" t="n">
-        <v>6826988</v>
+        <v>6826911</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5471,7 +5471,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5490,7 +5490,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5509,10 +5508,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130252153</v>
+        <v>130252602</v>
       </c>
       <c r="B47" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5540,14 +5539,14 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>496564</v>
+        <v>496722</v>
       </c>
       <c r="R47" t="n">
-        <v>6827012</v>
+        <v>6827107</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5579,7 +5578,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5589,7 +5588,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5604,22 +5603,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130252602</v>
+        <v>130252153</v>
       </c>
       <c r="B48" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5647,14 +5646,14 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>496722</v>
+        <v>496564</v>
       </c>
       <c r="R48" t="n">
-        <v>6827107</v>
+        <v>6827012</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5686,7 +5685,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5696,7 +5695,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5711,44 +5710,44 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130252598</v>
+        <v>130252609</v>
       </c>
       <c r="B49" t="n">
-        <v>79180</v>
+        <v>93013</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5758,10 +5757,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>497202</v>
+        <v>496549</v>
       </c>
       <c r="R49" t="n">
-        <v>6826911</v>
+        <v>6826988</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5793,7 +5792,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5803,7 +5802,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5812,6 +5811,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5833,7 +5833,7 @@
         <v>130252147</v>
       </c>
       <c r="B50" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5940,7 +5940,7 @@
         <v>130252140</v>
       </c>
       <c r="B51" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6044,10 +6044,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130252150</v>
+        <v>130252118</v>
       </c>
       <c r="B52" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6055,34 +6055,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>496701</v>
+        <v>496923</v>
       </c>
       <c r="R52" t="n">
-        <v>6827080</v>
+        <v>6826913</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6114,7 +6122,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6124,7 +6132,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6268,10 +6281,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130252118</v>
+        <v>130252150</v>
       </c>
       <c r="B54" t="n">
-        <v>57826</v>
+        <v>79183</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6279,42 +6292,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>496923</v>
+        <v>496701</v>
       </c>
       <c r="R54" t="n">
-        <v>6826913</v>
+        <v>6827080</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6346,7 +6351,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6356,12 +6361,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:50</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6388,10 +6388,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130252596</v>
+        <v>130252117</v>
       </c>
       <c r="B55" t="n">
-        <v>78937</v>
+        <v>79773</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6399,34 +6399,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>496771</v>
+        <v>497155</v>
       </c>
       <c r="R55" t="n">
-        <v>6827069</v>
+        <v>6826856</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6458,7 +6458,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6468,7 +6468,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6483,57 +6483,57 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130252137</v>
+        <v>130252606</v>
       </c>
       <c r="B56" t="n">
-        <v>79180</v>
+        <v>93013</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>497206</v>
+        <v>496618</v>
       </c>
       <c r="R56" t="n">
-        <v>6826638</v>
+        <v>6827114</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6565,7 +6565,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6575,7 +6575,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6584,50 +6584,51 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130252606</v>
+        <v>130252596</v>
       </c>
       <c r="B57" t="n">
-        <v>93010</v>
+        <v>78940</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6637,10 +6638,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>496618</v>
+        <v>496771</v>
       </c>
       <c r="R57" t="n">
-        <v>6827114</v>
+        <v>6827069</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6672,7 +6673,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6682,7 +6683,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6691,7 +6692,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6710,10 +6710,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130252117</v>
+        <v>130252137</v>
       </c>
       <c r="B58" t="n">
-        <v>79770</v>
+        <v>79183</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6721,21 +6721,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6745,10 +6745,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>497155</v>
+        <v>497206</v>
       </c>
       <c r="R58" t="n">
-        <v>6826856</v>
+        <v>6826638</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6780,7 +6780,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6790,7 +6790,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6820,7 +6820,7 @@
         <v>130252601</v>
       </c>
       <c r="B59" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6927,7 +6927,7 @@
         <v>130252144</v>
       </c>
       <c r="B60" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7034,7 +7034,7 @@
         <v>130252131</v>
       </c>
       <c r="B61" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         <v>130252152</v>
       </c>
       <c r="B62" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7248,7 +7248,7 @@
         <v>130252133</v>
       </c>
       <c r="B63" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7352,10 +7352,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130252597</v>
+        <v>130252114</v>
       </c>
       <c r="B64" t="n">
-        <v>79180</v>
+        <v>79215</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7363,34 +7363,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>496922</v>
+        <v>496880</v>
       </c>
       <c r="R64" t="n">
-        <v>6826906</v>
+        <v>6827051</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7422,7 +7422,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7432,7 +7432,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7441,63 +7441,64 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130252139</v>
+        <v>130252608</v>
       </c>
       <c r="B65" t="n">
-        <v>79180</v>
+        <v>93013</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>497225</v>
+        <v>496576</v>
       </c>
       <c r="R65" t="n">
-        <v>6826804</v>
+        <v>6826998</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7529,7 +7530,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7539,7 +7540,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7548,28 +7549,29 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130252151</v>
+        <v>130252139</v>
       </c>
       <c r="B66" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7601,10 +7603,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>496704</v>
+        <v>497225</v>
       </c>
       <c r="R66" t="n">
-        <v>6827086</v>
+        <v>6826804</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7636,7 +7638,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7646,7 +7648,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7673,10 +7675,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130252114</v>
+        <v>130252151</v>
       </c>
       <c r="B67" t="n">
-        <v>79212</v>
+        <v>79183</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7684,21 +7686,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7708,10 +7710,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>496880</v>
+        <v>496704</v>
       </c>
       <c r="R67" t="n">
-        <v>6827051</v>
+        <v>6827086</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7743,7 +7745,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7753,7 +7755,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7762,7 +7764,6 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7781,32 +7782,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130252608</v>
+        <v>130252597</v>
       </c>
       <c r="B68" t="n">
-        <v>93010</v>
+        <v>79183</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7816,10 +7817,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>496576</v>
+        <v>496922</v>
       </c>
       <c r="R68" t="n">
-        <v>6826998</v>
+        <v>6826906</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7851,7 +7852,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7861,7 +7862,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7870,7 +7871,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7892,7 +7892,7 @@
         <v>130256388</v>
       </c>
       <c r="B69" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7986,10 +7986,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130256379</v>
+        <v>130252149</v>
       </c>
       <c r="B70" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8015,16 +8015,19 @@
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>496857</v>
+        <v>496745</v>
       </c>
       <c r="R70" t="n">
-        <v>6827067</v>
+        <v>6827070</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8054,39 +8057,50 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130256356</v>
+        <v>130256379</v>
       </c>
       <c r="B71" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8118,10 +8132,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>496957</v>
+        <v>496857</v>
       </c>
       <c r="R71" t="n">
-        <v>6826898</v>
+        <v>6827067</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8180,10 +8194,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130252149</v>
+        <v>130256356</v>
       </c>
       <c r="B72" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8209,19 +8223,16 @@
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>496745</v>
+        <v>496957</v>
       </c>
       <c r="R72" t="n">
-        <v>6827070</v>
+        <v>6826898</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8251,50 +8262,39 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130256369</v>
+        <v>130255817</v>
       </c>
       <c r="B73" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8326,10 +8326,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>496893</v>
+        <v>496872</v>
       </c>
       <c r="R73" t="n">
-        <v>6827043</v>
+        <v>6827052</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8359,9 +8359,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8376,22 +8386,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130255830</v>
+        <v>130255832</v>
       </c>
       <c r="B74" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8423,10 +8433,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>496649</v>
+        <v>496578</v>
       </c>
       <c r="R74" t="n">
-        <v>6827117</v>
+        <v>6827044</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8458,7 +8468,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8468,7 +8478,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8495,10 +8505,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130255820</v>
+        <v>130256369</v>
       </c>
       <c r="B75" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8530,10 +8540,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>496838</v>
+        <v>496893</v>
       </c>
       <c r="R75" t="n">
-        <v>6827085</v>
+        <v>6827043</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8563,19 +8573,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>11:04</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8590,22 +8590,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>130255817</v>
+        <v>130255830</v>
       </c>
       <c r="B76" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8637,10 +8637,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>496872</v>
+        <v>496649</v>
       </c>
       <c r="R76" t="n">
-        <v>6827052</v>
+        <v>6827117</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8672,7 +8672,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8682,7 +8682,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8709,10 +8709,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>130255832</v>
+        <v>130255820</v>
       </c>
       <c r="B77" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8744,10 +8744,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>496578</v>
+        <v>496838</v>
       </c>
       <c r="R77" t="n">
-        <v>6827044</v>
+        <v>6827085</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8779,7 +8779,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8789,7 +8789,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8819,7 +8819,7 @@
         <v>130256383</v>
       </c>
       <c r="B78" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8916,7 +8916,7 @@
         <v>130256365</v>
       </c>
       <c r="B79" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9013,7 +9013,7 @@
         <v>130255797</v>
       </c>
       <c r="B80" t="n">
-        <v>78937</v>
+        <v>78940</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9120,7 +9120,7 @@
         <v>130256376</v>
       </c>
       <c r="B81" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9217,7 +9217,7 @@
         <v>130256368</v>
       </c>
       <c r="B82" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9311,10 +9311,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>130255837</v>
+        <v>130256346</v>
       </c>
       <c r="B83" t="n">
-        <v>79180</v>
+        <v>78941</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9322,21 +9322,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9346,10 +9346,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>497191</v>
+        <v>496652</v>
       </c>
       <c r="R83" t="n">
-        <v>6826771</v>
+        <v>6827164</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9379,19 +9379,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>12:00</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9406,22 +9396,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>130256346</v>
+        <v>130255837</v>
       </c>
       <c r="B84" t="n">
-        <v>78938</v>
+        <v>79183</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9429,21 +9419,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9453,10 +9443,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>496652</v>
+        <v>497191</v>
       </c>
       <c r="R84" t="n">
-        <v>6827164</v>
+        <v>6826771</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9486,9 +9476,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9503,44 +9503,44 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>130256352</v>
+        <v>130255839</v>
       </c>
       <c r="B85" t="n">
-        <v>78937</v>
+        <v>93013</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9550,10 +9550,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>496837</v>
+        <v>496787</v>
       </c>
       <c r="R85" t="n">
-        <v>6827069</v>
+        <v>6827052</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9583,9 +9583,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9600,44 +9610,44 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>130255839</v>
+        <v>130256352</v>
       </c>
       <c r="B86" t="n">
-        <v>93010</v>
+        <v>78940</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9647,10 +9657,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>496787</v>
+        <v>496837</v>
       </c>
       <c r="R86" t="n">
-        <v>6827052</v>
+        <v>6827069</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9680,19 +9690,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9707,22 +9707,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>130256387</v>
+        <v>130255823</v>
       </c>
       <c r="B87" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9754,10 +9754,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>496715</v>
+        <v>496757</v>
       </c>
       <c r="R87" t="n">
-        <v>6827126</v>
+        <v>6827109</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9787,9 +9787,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9804,22 +9814,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>130255818</v>
+        <v>130255803</v>
       </c>
       <c r="B88" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9851,10 +9861,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>496862</v>
+        <v>497148</v>
       </c>
       <c r="R88" t="n">
-        <v>6827065</v>
+        <v>6826907</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9886,7 +9896,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -9896,7 +9906,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9923,10 +9933,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>130255823</v>
+        <v>130255818</v>
       </c>
       <c r="B89" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9958,10 +9968,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>496757</v>
+        <v>496862</v>
       </c>
       <c r="R89" t="n">
-        <v>6827109</v>
+        <v>6827065</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9993,7 +10003,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10003,7 +10013,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10030,10 +10040,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>130255803</v>
+        <v>130256387</v>
       </c>
       <c r="B90" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10065,10 +10075,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>497148</v>
+        <v>496715</v>
       </c>
       <c r="R90" t="n">
-        <v>6826907</v>
+        <v>6827126</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10098,19 +10108,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>12:33</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>12:33</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10125,12 +10125,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
@@ -10140,7 +10140,7 @@
         <v>130255814</v>
       </c>
       <c r="B91" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10244,10 +10244,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>130256370</v>
+        <v>130255798</v>
       </c>
       <c r="B92" t="n">
-        <v>79180</v>
+        <v>78940</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10255,21 +10255,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10279,10 +10279,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>496894</v>
+        <v>496740</v>
       </c>
       <c r="R92" t="n">
-        <v>6827030</v>
+        <v>6827145</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10312,9 +10312,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10329,22 +10339,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>130255798</v>
+        <v>130256370</v>
       </c>
       <c r="B93" t="n">
-        <v>78937</v>
+        <v>79183</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10352,21 +10362,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10376,10 +10386,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>496740</v>
+        <v>496894</v>
       </c>
       <c r="R93" t="n">
-        <v>6827145</v>
+        <v>6827030</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10409,19 +10419,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>10:45</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>10:45</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10436,12 +10436,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
@@ -10451,7 +10451,7 @@
         <v>130255808</v>
       </c>
       <c r="B94" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10558,7 +10558,7 @@
         <v>130256367</v>
       </c>
       <c r="B95" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10655,7 +10655,7 @@
         <v>130256373</v>
       </c>
       <c r="B96" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10749,10 +10749,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>130256350</v>
+        <v>130255827</v>
       </c>
       <c r="B97" t="n">
-        <v>78937</v>
+        <v>79183</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10760,21 +10760,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10784,10 +10784,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>496962</v>
+        <v>496658</v>
       </c>
       <c r="R97" t="n">
-        <v>6826909</v>
+        <v>6827164</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10817,9 +10817,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10834,22 +10844,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>130256375</v>
+        <v>130256350</v>
       </c>
       <c r="B98" t="n">
-        <v>79180</v>
+        <v>78940</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10857,21 +10867,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10881,10 +10891,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>496859</v>
+        <v>496962</v>
       </c>
       <c r="R98" t="n">
-        <v>6827052</v>
+        <v>6826909</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10943,10 +10953,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>130255827</v>
+        <v>130255807</v>
       </c>
       <c r="B99" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10978,10 +10988,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>496658</v>
+        <v>497130</v>
       </c>
       <c r="R99" t="n">
-        <v>6827164</v>
+        <v>6826601</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11013,7 +11023,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11023,7 +11033,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11050,10 +11060,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>130255825</v>
+        <v>130255812</v>
       </c>
       <c r="B100" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11085,10 +11095,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>496759</v>
+        <v>497186</v>
       </c>
       <c r="R100" t="n">
-        <v>6827133</v>
+        <v>6826839</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11120,7 +11130,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11130,7 +11140,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11157,10 +11167,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>130255807</v>
+        <v>130256391</v>
       </c>
       <c r="B101" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11192,10 +11202,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>497130</v>
+        <v>496588</v>
       </c>
       <c r="R101" t="n">
-        <v>6826601</v>
+        <v>6827066</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11225,19 +11235,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z101" t="inlineStr">
-        <is>
-          <t>12:11</t>
-        </is>
-      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB101" t="inlineStr">
-        <is>
-          <t>12:11</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11252,22 +11252,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>130256391</v>
+        <v>130256375</v>
       </c>
       <c r="B102" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11299,10 +11299,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>496588</v>
+        <v>496859</v>
       </c>
       <c r="R102" t="n">
-        <v>6827066</v>
+        <v>6827052</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11361,10 +11361,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>130255812</v>
+        <v>130255825</v>
       </c>
       <c r="B103" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11396,10 +11396,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>497186</v>
+        <v>496759</v>
       </c>
       <c r="R103" t="n">
-        <v>6826839</v>
+        <v>6827133</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11431,7 +11431,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11441,7 +11441,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11468,10 +11468,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>130256351</v>
+        <v>130255833</v>
       </c>
       <c r="B104" t="n">
-        <v>78937</v>
+        <v>79183</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11479,21 +11479,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11503,10 +11503,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>496898</v>
+        <v>496579</v>
       </c>
       <c r="R104" t="n">
-        <v>6827000</v>
+        <v>6827030</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11536,9 +11536,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11553,22 +11563,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>130256353</v>
+        <v>130256351</v>
       </c>
       <c r="B105" t="n">
-        <v>78937</v>
+        <v>78940</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11600,10 +11610,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>496827</v>
+        <v>496898</v>
       </c>
       <c r="R105" t="n">
-        <v>6827089</v>
+        <v>6827000</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11662,10 +11672,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>130255833</v>
+        <v>130255826</v>
       </c>
       <c r="B106" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11697,10 +11707,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>496579</v>
+        <v>496694</v>
       </c>
       <c r="R106" t="n">
-        <v>6827030</v>
+        <v>6827122</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11732,7 +11742,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11742,7 +11752,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11769,10 +11779,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>130255804</v>
+        <v>130256353</v>
       </c>
       <c r="B107" t="n">
-        <v>79180</v>
+        <v>78940</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11780,21 +11790,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11804,10 +11814,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>497012</v>
+        <v>496827</v>
       </c>
       <c r="R107" t="n">
-        <v>6826898</v>
+        <v>6827089</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11837,19 +11847,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z107" t="inlineStr">
-        <is>
-          <t>12:22</t>
-        </is>
-      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB107" t="inlineStr">
-        <is>
-          <t>12:22</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11864,22 +11864,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>130255826</v>
+        <v>130255804</v>
       </c>
       <c r="B108" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11911,10 +11911,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>496694</v>
+        <v>497012</v>
       </c>
       <c r="R108" t="n">
-        <v>6827122</v>
+        <v>6826898</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11946,7 +11946,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -11956,7 +11956,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11983,10 +11983,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>130256342</v>
+        <v>130256374</v>
       </c>
       <c r="B109" t="n">
-        <v>57826</v>
+        <v>79183</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11994,42 +11994,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>496940</v>
+        <v>496863</v>
       </c>
       <c r="R109" t="n">
-        <v>6826899</v>
+        <v>6827047</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12062,11 +12054,6 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12096,7 +12083,7 @@
         <v>130256360</v>
       </c>
       <c r="B110" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12193,7 +12180,7 @@
         <v>130256354</v>
       </c>
       <c r="B111" t="n">
-        <v>78937</v>
+        <v>78940</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12287,10 +12274,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>130256386</v>
+        <v>130255819</v>
       </c>
       <c r="B112" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12322,10 +12309,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>496723</v>
+        <v>496850</v>
       </c>
       <c r="R112" t="n">
-        <v>6827125</v>
+        <v>6827090</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12355,9 +12342,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12372,22 +12369,22 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>130255819</v>
+        <v>130256386</v>
       </c>
       <c r="B113" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12419,10 +12416,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>496850</v>
+        <v>496723</v>
       </c>
       <c r="R113" t="n">
-        <v>6827090</v>
+        <v>6827125</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12452,19 +12449,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z113" t="inlineStr">
-        <is>
-          <t>11:05</t>
-        </is>
-      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB113" t="inlineStr">
-        <is>
-          <t>11:05</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12479,22 +12466,22 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>130256374</v>
+        <v>130256342</v>
       </c>
       <c r="B114" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12502,34 +12489,42 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>496863</v>
+        <v>496940</v>
       </c>
       <c r="R114" t="n">
-        <v>6827047</v>
+        <v>6826899</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12562,6 +12557,11 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12591,7 +12591,7 @@
         <v>130256380</v>
       </c>
       <c r="B115" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12688,7 +12688,7 @@
         <v>130255802</v>
       </c>
       <c r="B116" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12795,7 +12795,7 @@
         <v>130256357</v>
       </c>
       <c r="B117" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12892,7 +12892,7 @@
         <v>130256390</v>
       </c>
       <c r="B118" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12989,7 +12989,7 @@
         <v>130256363</v>
       </c>
       <c r="B119" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13086,7 +13086,7 @@
         <v>130256381</v>
       </c>
       <c r="B120" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13183,7 +13183,7 @@
         <v>130255796</v>
       </c>
       <c r="B121" t="n">
-        <v>78937</v>
+        <v>78940</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13287,10 +13287,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>130256378</v>
+        <v>130256359</v>
       </c>
       <c r="B122" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13322,10 +13322,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>496862</v>
+        <v>496963</v>
       </c>
       <c r="R122" t="n">
-        <v>6827064</v>
+        <v>6826942</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13384,10 +13384,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>130256382</v>
+        <v>130255801</v>
       </c>
       <c r="B123" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>496831</v>
+        <v>496702</v>
       </c>
       <c r="R123" t="n">
-        <v>6827081</v>
+        <v>6827131</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13452,9 +13452,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13469,57 +13479,66 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>130256359</v>
+        <v>130256348</v>
       </c>
       <c r="B124" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>496963</v>
+        <v>496864</v>
       </c>
       <c r="R124" t="n">
-        <v>6826942</v>
+        <v>6827043</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13560,6 +13579,7 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
+      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
@@ -13578,10 +13598,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>130255801</v>
+        <v>130256378</v>
       </c>
       <c r="B125" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13613,10 +13633,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>496702</v>
+        <v>496862</v>
       </c>
       <c r="R125" t="n">
-        <v>6827131</v>
+        <v>6827064</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13646,19 +13666,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z125" t="inlineStr">
-        <is>
-          <t>10:39</t>
-        </is>
-      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB125" t="inlineStr">
-        <is>
-          <t>10:39</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13673,66 +13683,57 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>130256348</v>
+        <v>130256382</v>
       </c>
       <c r="B126" t="n">
-        <v>8451</v>
+        <v>79183</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr"/>
-      <c r="K126" t="inlineStr"/>
-      <c r="L126" t="inlineStr"/>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>496864</v>
+        <v>496831</v>
       </c>
       <c r="R126" t="n">
-        <v>6827043</v>
+        <v>6827081</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13773,7 +13774,6 @@
       <c r="AE126" t="b">
         <v>0</v>
       </c>
-      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
@@ -13792,32 +13792,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>130256343</v>
+        <v>130256392</v>
       </c>
       <c r="B127" t="n">
-        <v>79180</v>
+        <v>93013</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13827,10 +13827,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>496851</v>
+        <v>496581</v>
       </c>
       <c r="R127" t="n">
-        <v>6827066</v>
+        <v>6827082</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13871,6 +13871,7 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
+      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
@@ -13889,54 +13890,45 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>130255793</v>
+        <v>130255834</v>
       </c>
       <c r="B128" t="n">
-        <v>8451</v>
+        <v>79183</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
-      <c r="L128" t="inlineStr"/>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>496670</v>
+        <v>496582</v>
       </c>
       <c r="R128" t="n">
-        <v>6827136</v>
+        <v>6827040</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13968,7 +13960,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -13978,7 +13970,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13987,7 +13979,6 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
-      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
@@ -14006,54 +13997,45 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>130256349</v>
+        <v>130255836</v>
       </c>
       <c r="B129" t="n">
-        <v>8451</v>
+        <v>79183</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
-      <c r="K129" t="inlineStr"/>
-      <c r="L129" t="inlineStr"/>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>496714</v>
+        <v>497183</v>
       </c>
       <c r="R129" t="n">
-        <v>6827127</v>
+        <v>6826662</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14083,84 +14065,84 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AD129" t="b">
         <v>0</v>
       </c>
       <c r="AE129" t="b">
         <v>0</v>
       </c>
-      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>130256347</v>
+        <v>130255805</v>
       </c>
       <c r="B130" t="n">
-        <v>8451</v>
+        <v>79183</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="J130" t="inlineStr"/>
-      <c r="K130" t="inlineStr"/>
-      <c r="L130" t="inlineStr"/>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>496941</v>
+        <v>497139</v>
       </c>
       <c r="R130" t="n">
-        <v>6826899</v>
+        <v>6826719</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14190,40 +14172,49 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
       <c r="AD130" t="b">
         <v>0</v>
       </c>
       <c r="AE130" t="b">
         <v>0</v>
       </c>
-      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>130255834</v>
+        <v>130256343</v>
       </c>
       <c r="B131" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14255,10 +14246,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>496582</v>
+        <v>496851</v>
       </c>
       <c r="R131" t="n">
-        <v>6827040</v>
+        <v>6827066</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14288,19 +14279,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z131" t="inlineStr">
-        <is>
-          <t>10:10</t>
-        </is>
-      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB131" t="inlineStr">
-        <is>
-          <t>10:10</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14315,57 +14296,66 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>130255805</v>
+        <v>130255793</v>
       </c>
       <c r="B132" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>497139</v>
+        <v>496670</v>
       </c>
       <c r="R132" t="n">
-        <v>6826719</v>
+        <v>6827136</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14397,7 +14387,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14407,7 +14397,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14416,6 +14406,7 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
+      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
@@ -14434,45 +14425,54 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>130255836</v>
+        <v>130256349</v>
       </c>
       <c r="B133" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>497183</v>
+        <v>496714</v>
       </c>
       <c r="R133" t="n">
-        <v>6826662</v>
+        <v>6827127</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14502,49 +14502,40 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z133" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AA133" t="inlineStr">
         <is>
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="AB133" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AD133" t="b">
         <v>0</v>
       </c>
       <c r="AE133" t="b">
         <v>0</v>
       </c>
+      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>130256392</v>
+        <v>130256347</v>
       </c>
       <c r="B134" t="n">
-        <v>93010</v>
+        <v>8451</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14552,34 +14543,43 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>496581</v>
+        <v>496941</v>
       </c>
       <c r="R134" t="n">
-        <v>6827082</v>
+        <v>6826899</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14639,10 +14639,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>130255806</v>
+        <v>130256345</v>
       </c>
       <c r="B135" t="n">
-        <v>79180</v>
+        <v>78941</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14650,21 +14650,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14674,10 +14674,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>497147</v>
+        <v>496837</v>
       </c>
       <c r="R135" t="n">
-        <v>6826725</v>
+        <v>6827069</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14707,19 +14707,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z135" t="inlineStr">
-        <is>
-          <t>12:17</t>
-        </is>
-      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB135" t="inlineStr">
-        <is>
-          <t>12:17</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14734,22 +14724,22 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>130255813</v>
+        <v>130256344</v>
       </c>
       <c r="B136" t="n">
-        <v>79180</v>
+        <v>78941</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14757,21 +14747,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14781,10 +14771,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>497093</v>
+        <v>496869</v>
       </c>
       <c r="R136" t="n">
-        <v>6827168</v>
+        <v>6827038</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14814,19 +14804,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z136" t="inlineStr">
-        <is>
-          <t>11:31</t>
-        </is>
-      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB136" t="inlineStr">
-        <is>
-          <t>11:31</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14841,22 +14821,22 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>130255810</v>
+        <v>130255806</v>
       </c>
       <c r="B137" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14888,10 +14868,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>497191</v>
+        <v>497147</v>
       </c>
       <c r="R137" t="n">
-        <v>6826663</v>
+        <v>6826725</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14923,7 +14903,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -14933,7 +14913,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14960,10 +14940,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>130256345</v>
+        <v>130255810</v>
       </c>
       <c r="B138" t="n">
-        <v>78938</v>
+        <v>79183</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14971,21 +14951,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14995,10 +14975,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>496837</v>
+        <v>497191</v>
       </c>
       <c r="R138" t="n">
-        <v>6827069</v>
+        <v>6826663</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15028,9 +15008,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z138" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AA138" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB138" t="inlineStr">
+        <is>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15045,22 +15035,22 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>130256344</v>
+        <v>130255813</v>
       </c>
       <c r="B139" t="n">
-        <v>78938</v>
+        <v>79183</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15068,21 +15058,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15092,10 +15082,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>496869</v>
+        <v>497093</v>
       </c>
       <c r="R139" t="n">
-        <v>6827038</v>
+        <v>6827168</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15125,9 +15115,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB139" t="inlineStr">
+        <is>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15142,12 +15142,12 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
@@ -15157,7 +15157,7 @@
         <v>130256358</v>
       </c>
       <c r="B140" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15251,10 +15251,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>130256389</v>
+        <v>130256361</v>
       </c>
       <c r="B141" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15286,10 +15286,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>496578</v>
+        <v>496893</v>
       </c>
       <c r="R141" t="n">
-        <v>6827076</v>
+        <v>6826989</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15348,10 +15348,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>130256361</v>
+        <v>130256389</v>
       </c>
       <c r="B142" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15383,10 +15383,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>496893</v>
+        <v>496578</v>
       </c>
       <c r="R142" t="n">
-        <v>6826989</v>
+        <v>6827076</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15445,45 +15445,56 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>130256364</v>
+        <v>130256394</v>
       </c>
       <c r="B143" t="n">
-        <v>79180</v>
+        <v>93013</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr"/>
+      <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
           <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>496909</v>
+        <v>496581</v>
       </c>
       <c r="R143" t="n">
-        <v>6827002</v>
+        <v>6827079</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15524,6 +15535,7 @@
       <c r="AE143" t="b">
         <v>0</v>
       </c>
+      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>
@@ -15542,10 +15554,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>130256355</v>
+        <v>130256364</v>
       </c>
       <c r="B144" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15577,10 +15589,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>496940</v>
+        <v>496909</v>
       </c>
       <c r="R144" t="n">
-        <v>6826898</v>
+        <v>6827002</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15639,10 +15651,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>130256362</v>
+        <v>130256355</v>
       </c>
       <c r="B145" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15674,10 +15686,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>496893</v>
+        <v>496940</v>
       </c>
       <c r="R145" t="n">
-        <v>6826998</v>
+        <v>6826898</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15739,7 +15751,7 @@
         <v>130256371</v>
       </c>
       <c r="B146" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15836,7 +15848,7 @@
         <v>130255828</v>
       </c>
       <c r="B147" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15943,7 +15955,7 @@
         <v>130255821</v>
       </c>
       <c r="B148" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16047,56 +16059,45 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>130256394</v>
+        <v>130256362</v>
       </c>
       <c r="B149" t="n">
-        <v>93010</v>
+        <v>79183</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J149" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K149" t="inlineStr"/>
-      <c r="N149" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
           <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>496581</v>
+        <v>496893</v>
       </c>
       <c r="R149" t="n">
-        <v>6827079</v>
+        <v>6826998</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16137,7 +16138,6 @@
       <c r="AE149" t="b">
         <v>0</v>
       </c>
-      <c r="AF149" t="inlineStr"/>
       <c r="AG149" t="b">
         <v>0</v>
       </c>
@@ -16159,7 +16159,7 @@
         <v>130256340</v>
       </c>
       <c r="B150" t="n">
-        <v>79770</v>
+        <v>79773</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16253,10 +16253,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>130256372</v>
+        <v>130255811</v>
       </c>
       <c r="B151" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16288,10 +16288,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>496867</v>
+        <v>497200</v>
       </c>
       <c r="R151" t="n">
-        <v>6827035</v>
+        <v>6826832</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16321,9 +16321,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z151" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB151" t="inlineStr">
+        <is>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16338,22 +16348,22 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>130255811</v>
+        <v>130255831</v>
       </c>
       <c r="B152" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16385,10 +16395,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>497200</v>
+        <v>496599</v>
       </c>
       <c r="R152" t="n">
-        <v>6826832</v>
+        <v>6827121</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16420,7 +16430,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -16430,7 +16440,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16457,10 +16467,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>130255824</v>
+        <v>130256372</v>
       </c>
       <c r="B153" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16492,10 +16502,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>496752</v>
+        <v>496867</v>
       </c>
       <c r="R153" t="n">
-        <v>6827114</v>
+        <v>6827035</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16525,19 +16535,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z153" t="inlineStr">
-        <is>
-          <t>10:49</t>
-        </is>
-      </c>
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB153" t="inlineStr">
-        <is>
-          <t>10:49</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16552,22 +16552,22 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>130255831</v>
+        <v>130255824</v>
       </c>
       <c r="B154" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16599,10 +16599,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>496599</v>
+        <v>496752</v>
       </c>
       <c r="R154" t="n">
-        <v>6827121</v>
+        <v>6827114</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16634,7 +16634,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -16644,7 +16644,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16671,32 +16671,32 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>130256385</v>
+        <v>130255838</v>
       </c>
       <c r="B155" t="n">
-        <v>79180</v>
+        <v>93013</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16706,10 +16706,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>496747</v>
+        <v>496571</v>
       </c>
       <c r="R155" t="n">
-        <v>6827065</v>
+        <v>6827076</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16739,9 +16739,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z155" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
       <c r="AA155" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB155" t="inlineStr">
+        <is>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16756,44 +16766,44 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>130255838</v>
+        <v>130256385</v>
       </c>
       <c r="B156" t="n">
-        <v>93010</v>
+        <v>79183</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16803,10 +16813,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>496571</v>
+        <v>496747</v>
       </c>
       <c r="R156" t="n">
-        <v>6827076</v>
+        <v>6827065</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16836,19 +16846,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z156" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB156" t="inlineStr">
-        <is>
-          <t>10:13</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16863,44 +16863,44 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>130255816</v>
+        <v>130256393</v>
       </c>
       <c r="B157" t="n">
-        <v>79180</v>
+        <v>93013</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16910,10 +16910,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>496954</v>
+        <v>496647</v>
       </c>
       <c r="R157" t="n">
-        <v>6827096</v>
+        <v>6827158</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16943,19 +16943,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z157" t="inlineStr">
-        <is>
-          <t>11:22</t>
-        </is>
-      </c>
       <c r="AA157" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB157" t="inlineStr">
-        <is>
-          <t>11:22</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16970,12 +16960,12 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
@@ -16985,7 +16975,7 @@
         <v>130255809</v>
       </c>
       <c r="B158" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17089,10 +17079,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>130255829</v>
+        <v>130255816</v>
       </c>
       <c r="B159" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17124,10 +17114,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>496643</v>
+        <v>496954</v>
       </c>
       <c r="R159" t="n">
-        <v>6827146</v>
+        <v>6827096</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17159,7 +17149,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -17169,7 +17159,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17196,32 +17186,32 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>130256393</v>
+        <v>130255829</v>
       </c>
       <c r="B160" t="n">
-        <v>93010</v>
+        <v>79183</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17231,10 +17221,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>496647</v>
+        <v>496643</v>
       </c>
       <c r="R160" t="n">
-        <v>6827158</v>
+        <v>6827146</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17264,9 +17254,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z160" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB160" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17281,12 +17281,12 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>

--- a/artfynd/A 58895-2025 artfynd.xlsx
+++ b/artfynd/A 58895-2025 artfynd.xlsx
@@ -790,45 +790,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130252591</v>
+        <v>130252155</v>
       </c>
       <c r="B3" t="n">
-        <v>78940</v>
+        <v>93039</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>496966</v>
+        <v>496725</v>
       </c>
       <c r="R3" t="n">
-        <v>6826906</v>
+        <v>6827084</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,22 +885,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130252116</v>
+        <v>130252591</v>
       </c>
       <c r="B4" t="n">
-        <v>79802</v>
+        <v>78966</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,34 +908,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>496721</v>
+        <v>496966</v>
       </c>
       <c r="R4" t="n">
-        <v>6827083</v>
+        <v>6826906</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -967,7 +967,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -992,44 +992,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130252155</v>
+        <v>130252116</v>
       </c>
       <c r="B5" t="n">
-        <v>93013</v>
+        <v>79828</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>496725</v>
+        <v>496721</v>
       </c>
       <c r="R5" t="n">
-        <v>6827084</v>
+        <v>6827083</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1114,7 +1114,7 @@
         <v>130252584</v>
       </c>
       <c r="B6" t="n">
-        <v>57985</v>
+        <v>58011</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>130252132</v>
       </c>
       <c r="B8" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,32 +1432,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130252156</v>
+        <v>130252115</v>
       </c>
       <c r="B9" t="n">
-        <v>93013</v>
+        <v>79241</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>185</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>496675</v>
+        <v>496555</v>
       </c>
       <c r="R9" t="n">
-        <v>6827138</v>
+        <v>6826991</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1512,7 +1512,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,6 +1521,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1539,32 +1540,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130252115</v>
+        <v>130252156</v>
       </c>
       <c r="B10" t="n">
-        <v>79215</v>
+        <v>93039</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1574,10 +1575,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>496555</v>
+        <v>496675</v>
       </c>
       <c r="R10" t="n">
-        <v>6826991</v>
+        <v>6827138</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1609,7 +1610,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1619,7 +1620,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1628,7 +1629,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1650,7 +1650,7 @@
         <v>130252138</v>
       </c>
       <c r="B11" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1754,10 +1754,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130252126</v>
+        <v>130252592</v>
       </c>
       <c r="B12" t="n">
-        <v>78940</v>
+        <v>78966</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1785,14 +1785,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>496737</v>
+        <v>496950</v>
       </c>
       <c r="R12" t="n">
-        <v>6827071</v>
+        <v>6827038</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1849,22 +1849,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130252592</v>
+        <v>130252126</v>
       </c>
       <c r="B13" t="n">
-        <v>78940</v>
+        <v>78966</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1892,14 +1892,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>496950</v>
+        <v>496737</v>
       </c>
       <c r="R13" t="n">
-        <v>6827038</v>
+        <v>6827071</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1931,7 +1931,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1956,12 +1956,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1971,7 +1971,7 @@
         <v>130252588</v>
       </c>
       <c r="B14" t="n">
-        <v>78940</v>
+        <v>78966</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>130252154</v>
       </c>
       <c r="B15" t="n">
-        <v>93013</v>
+        <v>93039</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>130252119</v>
       </c>
       <c r="B16" t="n">
-        <v>57985</v>
+        <v>58011</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2396,32 +2396,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130252123</v>
+        <v>130252125</v>
       </c>
       <c r="B18" t="n">
-        <v>8451</v>
+        <v>78966</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2431,10 +2431,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>496581</v>
+        <v>497154</v>
       </c>
       <c r="R18" t="n">
-        <v>6827019</v>
+        <v>6826854</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2476,7 +2476,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2503,10 +2503,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130252125</v>
+        <v>130252145</v>
       </c>
       <c r="B19" t="n">
-        <v>78940</v>
+        <v>79209</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2514,21 +2514,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2538,10 +2538,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>497154</v>
+        <v>496870</v>
       </c>
       <c r="R19" t="n">
-        <v>6826854</v>
+        <v>6827056</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2610,10 +2610,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130252603</v>
+        <v>130252594</v>
       </c>
       <c r="B20" t="n">
-        <v>79183</v>
+        <v>78966</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,21 +2621,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2645,10 +2645,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>496694</v>
+        <v>496874</v>
       </c>
       <c r="R20" t="n">
-        <v>6827132</v>
+        <v>6827149</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2717,10 +2717,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130252145</v>
+        <v>130252603</v>
       </c>
       <c r="B21" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2748,14 +2748,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>496870</v>
+        <v>496694</v>
       </c>
       <c r="R21" t="n">
-        <v>6827056</v>
+        <v>6827132</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2812,57 +2812,57 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130252594</v>
+        <v>130252123</v>
       </c>
       <c r="B22" t="n">
-        <v>78940</v>
+        <v>8451</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>496874</v>
+        <v>496581</v>
       </c>
       <c r="R22" t="n">
-        <v>6827149</v>
+        <v>6827019</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2904,7 +2904,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2919,22 +2919,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130252142</v>
+        <v>130252124</v>
       </c>
       <c r="B23" t="n">
-        <v>79183</v>
+        <v>78966</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2942,21 +2942,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2966,10 +2966,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>496939</v>
+        <v>497192</v>
       </c>
       <c r="R23" t="n">
-        <v>6827036</v>
+        <v>6826651</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3011,7 +3011,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3038,10 +3038,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130252124</v>
+        <v>130252142</v>
       </c>
       <c r="B24" t="n">
-        <v>78940</v>
+        <v>79209</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3049,21 +3049,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3073,10 +3073,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>497192</v>
+        <v>496939</v>
       </c>
       <c r="R24" t="n">
-        <v>6826651</v>
+        <v>6827036</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3118,7 +3118,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3252,10 +3252,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130252595</v>
+        <v>130252600</v>
       </c>
       <c r="B26" t="n">
-        <v>78940</v>
+        <v>79209</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3263,21 +3263,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3287,10 +3287,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>496894</v>
+        <v>496948</v>
       </c>
       <c r="R26" t="n">
-        <v>6827123</v>
+        <v>6827029</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3322,7 +3322,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3362,7 +3362,7 @@
         <v>130252127</v>
       </c>
       <c r="B27" t="n">
-        <v>78940</v>
+        <v>78966</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3466,10 +3466,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130252600</v>
+        <v>130252595</v>
       </c>
       <c r="B28" t="n">
-        <v>79183</v>
+        <v>78966</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3477,21 +3477,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3501,10 +3501,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>496948</v>
+        <v>496894</v>
       </c>
       <c r="R28" t="n">
-        <v>6827029</v>
+        <v>6827123</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3536,7 +3536,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3546,7 +3546,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3573,32 +3573,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130252157</v>
+        <v>130252141</v>
       </c>
       <c r="B29" t="n">
-        <v>93013</v>
+        <v>79209</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3608,10 +3608,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>496628</v>
+        <v>496956</v>
       </c>
       <c r="R29" t="n">
-        <v>6827124</v>
+        <v>6827088</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3643,7 +3643,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3680,10 +3680,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130252129</v>
+        <v>130252589</v>
       </c>
       <c r="B30" t="n">
-        <v>78940</v>
+        <v>78966</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3711,14 +3711,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>496646</v>
+        <v>497211</v>
       </c>
       <c r="R30" t="n">
-        <v>6827139</v>
+        <v>6826926</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3750,7 +3750,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3760,7 +3760,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3775,22 +3775,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130252589</v>
+        <v>130252129</v>
       </c>
       <c r="B31" t="n">
-        <v>78940</v>
+        <v>78966</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3818,14 +3818,14 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>497211</v>
+        <v>496646</v>
       </c>
       <c r="R31" t="n">
-        <v>6826926</v>
+        <v>6827139</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3857,7 +3857,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3867,7 +3867,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3882,44 +3882,44 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130252141</v>
+        <v>130252157</v>
       </c>
       <c r="B32" t="n">
-        <v>79183</v>
+        <v>93039</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3929,10 +3929,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>496956</v>
+        <v>496628</v>
       </c>
       <c r="R32" t="n">
-        <v>6827088</v>
+        <v>6827124</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3964,7 +3964,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3974,7 +3974,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4004,7 +4004,7 @@
         <v>130252599</v>
       </c>
       <c r="B33" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4108,10 +4108,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130252135</v>
+        <v>130252143</v>
       </c>
       <c r="B34" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4143,10 +4143,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>496915</v>
+        <v>496877</v>
       </c>
       <c r="R34" t="n">
-        <v>6826903</v>
+        <v>6827056</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4218,7 +4218,7 @@
         <v>130252604</v>
       </c>
       <c r="B35" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4322,10 +4322,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130252146</v>
+        <v>130252135</v>
       </c>
       <c r="B36" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4357,10 +4357,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>496864</v>
+        <v>496915</v>
       </c>
       <c r="R36" t="n">
-        <v>6827053</v>
+        <v>6826903</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4429,10 +4429,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130252143</v>
+        <v>130252605</v>
       </c>
       <c r="B37" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4460,14 +4460,14 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>496877</v>
+        <v>496676</v>
       </c>
       <c r="R37" t="n">
-        <v>6827056</v>
+        <v>6827143</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4509,7 +4509,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4524,22 +4524,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130252605</v>
+        <v>130252146</v>
       </c>
       <c r="B38" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4567,14 +4567,14 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>496676</v>
+        <v>496864</v>
       </c>
       <c r="R38" t="n">
-        <v>6827143</v>
+        <v>6827053</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4631,12 +4631,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4750,45 +4750,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130252590</v>
+        <v>130252158</v>
       </c>
       <c r="B40" t="n">
-        <v>78940</v>
+        <v>93039</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>496995</v>
+        <v>496629</v>
       </c>
       <c r="R40" t="n">
-        <v>6826923</v>
+        <v>6827128</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4820,7 +4820,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4845,57 +4845,57 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130252136</v>
+        <v>130252607</v>
       </c>
       <c r="B41" t="n">
-        <v>79183</v>
+        <v>93039</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>497002</v>
+        <v>496598</v>
       </c>
       <c r="R41" t="n">
-        <v>6826879</v>
+        <v>6827085</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4927,7 +4927,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4937,7 +4937,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4946,18 +4946,19 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -4967,7 +4968,7 @@
         <v>130252128</v>
       </c>
       <c r="B42" t="n">
-        <v>78940</v>
+        <v>78966</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5071,10 +5072,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130252585</v>
+        <v>130252136</v>
       </c>
       <c r="B43" t="n">
-        <v>57823</v>
+        <v>79209</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5082,42 +5083,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>496635</v>
+        <v>497002</v>
       </c>
       <c r="R43" t="n">
-        <v>6827130</v>
+        <v>6826879</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5149,7 +5142,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5159,7 +5152,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5174,57 +5167,57 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130252158</v>
+        <v>130252590</v>
       </c>
       <c r="B44" t="n">
-        <v>93013</v>
+        <v>78966</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>496629</v>
+        <v>496995</v>
       </c>
       <c r="R44" t="n">
-        <v>6827128</v>
+        <v>6826923</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5256,7 +5249,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5266,7 +5259,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5281,57 +5274,65 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130252607</v>
+        <v>130252585</v>
       </c>
       <c r="B45" t="n">
-        <v>93013</v>
+        <v>57849</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>496598</v>
+        <v>496635</v>
       </c>
       <c r="R45" t="n">
-        <v>6827085</v>
+        <v>6827130</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5363,7 +5364,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5373,7 +5374,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5382,7 +5383,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5404,7 +5404,7 @@
         <v>130252598</v>
       </c>
       <c r="B46" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5508,10 +5508,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130252602</v>
+        <v>130252153</v>
       </c>
       <c r="B47" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5539,14 +5539,14 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>496722</v>
+        <v>496564</v>
       </c>
       <c r="R47" t="n">
-        <v>6827107</v>
+        <v>6827012</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5578,7 +5578,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5603,22 +5603,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130252153</v>
+        <v>130252602</v>
       </c>
       <c r="B48" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5646,14 +5646,14 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>496564</v>
+        <v>496722</v>
       </c>
       <c r="R48" t="n">
-        <v>6827012</v>
+        <v>6827107</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5685,7 +5685,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5695,7 +5695,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5710,12 +5710,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5725,7 +5725,7 @@
         <v>130252609</v>
       </c>
       <c r="B49" t="n">
-        <v>93013</v>
+        <v>93039</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5833,7 +5833,7 @@
         <v>130252147</v>
       </c>
       <c r="B50" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5940,7 +5940,7 @@
         <v>130252140</v>
       </c>
       <c r="B51" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6047,7 +6047,7 @@
         <v>130252118</v>
       </c>
       <c r="B52" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6164,54 +6164,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130252130</v>
+        <v>130252150</v>
       </c>
       <c r="B53" t="n">
-        <v>44080</v>
+        <v>79209</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>101735</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>497225</v>
+        <v>496701</v>
       </c>
       <c r="R53" t="n">
-        <v>6826804</v>
+        <v>6827080</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6243,7 +6234,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6253,7 +6244,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6262,7 +6253,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6281,45 +6271,54 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130252150</v>
+        <v>130252130</v>
       </c>
       <c r="B54" t="n">
-        <v>79183</v>
+        <v>44106</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>101735</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>496701</v>
+        <v>497225</v>
       </c>
       <c r="R54" t="n">
-        <v>6827080</v>
+        <v>6826804</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6351,7 +6350,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6361,7 +6360,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6370,6 +6369,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6388,10 +6388,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130252117</v>
+        <v>130252596</v>
       </c>
       <c r="B55" t="n">
-        <v>79773</v>
+        <v>78966</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6399,34 +6399,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>497155</v>
+        <v>496771</v>
       </c>
       <c r="R55" t="n">
-        <v>6826856</v>
+        <v>6827069</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6458,7 +6458,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6468,7 +6468,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6483,57 +6483,57 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130252606</v>
+        <v>130252137</v>
       </c>
       <c r="B56" t="n">
-        <v>93013</v>
+        <v>79209</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>496618</v>
+        <v>497206</v>
       </c>
       <c r="R56" t="n">
-        <v>6827114</v>
+        <v>6826638</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6565,7 +6565,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6575,7 +6575,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6584,29 +6584,28 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130252596</v>
+        <v>130252117</v>
       </c>
       <c r="B57" t="n">
-        <v>78940</v>
+        <v>79799</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6614,34 +6613,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>496771</v>
+        <v>497155</v>
       </c>
       <c r="R57" t="n">
-        <v>6827069</v>
+        <v>6826856</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6673,7 +6672,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6683,7 +6682,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6698,57 +6697,57 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130252137</v>
+        <v>130252606</v>
       </c>
       <c r="B58" t="n">
-        <v>79183</v>
+        <v>93039</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>497206</v>
+        <v>496618</v>
       </c>
       <c r="R58" t="n">
-        <v>6826638</v>
+        <v>6827114</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6780,7 +6779,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6790,7 +6789,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6799,18 +6798,19 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -6820,7 +6820,7 @@
         <v>130252601</v>
       </c>
       <c r="B59" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6927,7 +6927,7 @@
         <v>130252144</v>
       </c>
       <c r="B60" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7031,10 +7031,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130252131</v>
+        <v>130252152</v>
       </c>
       <c r="B61" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7066,10 +7066,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>496656</v>
+        <v>496591</v>
       </c>
       <c r="R61" t="n">
-        <v>6827109</v>
+        <v>6827054</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7101,7 +7101,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7111,7 +7111,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7138,10 +7138,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130252152</v>
+        <v>130252131</v>
       </c>
       <c r="B62" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7173,10 +7173,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>496591</v>
+        <v>496656</v>
       </c>
       <c r="R62" t="n">
-        <v>6827054</v>
+        <v>6827109</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7208,7 +7208,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7218,7 +7218,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7248,7 +7248,7 @@
         <v>130252133</v>
       </c>
       <c r="B63" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7355,7 +7355,7 @@
         <v>130252114</v>
       </c>
       <c r="B64" t="n">
-        <v>79215</v>
+        <v>79241</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         <v>130252608</v>
       </c>
       <c r="B65" t="n">
-        <v>93013</v>
+        <v>93039</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7568,10 +7568,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130252139</v>
+        <v>130252597</v>
       </c>
       <c r="B66" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7599,14 +7599,14 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>497225</v>
+        <v>496922</v>
       </c>
       <c r="R66" t="n">
-        <v>6826804</v>
+        <v>6826906</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7638,7 +7638,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7663,22 +7663,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130252151</v>
+        <v>130252139</v>
       </c>
       <c r="B67" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7710,10 +7710,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>496704</v>
+        <v>497225</v>
       </c>
       <c r="R67" t="n">
-        <v>6827086</v>
+        <v>6826804</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7745,7 +7745,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7755,7 +7755,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7782,10 +7782,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130252597</v>
+        <v>130252151</v>
       </c>
       <c r="B68" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7813,14 +7813,14 @@
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>496922</v>
+        <v>496704</v>
       </c>
       <c r="R68" t="n">
-        <v>6826906</v>
+        <v>6827086</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7852,7 +7852,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7862,7 +7862,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7877,22 +7877,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130256388</v>
+        <v>130252149</v>
       </c>
       <c r="B69" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7918,16 +7918,19 @@
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>496665</v>
+        <v>496745</v>
       </c>
       <c r="R69" t="n">
-        <v>6827143</v>
+        <v>6827070</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7957,39 +7960,50 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130252149</v>
+        <v>130256388</v>
       </c>
       <c r="B70" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8015,19 +8029,16 @@
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>496745</v>
+        <v>496665</v>
       </c>
       <c r="R70" t="n">
-        <v>6827070</v>
+        <v>6827143</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8057,50 +8068,39 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130256379</v>
+        <v>130256356</v>
       </c>
       <c r="B71" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8132,10 +8132,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>496857</v>
+        <v>496957</v>
       </c>
       <c r="R71" t="n">
-        <v>6827067</v>
+        <v>6826898</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8194,10 +8194,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130256356</v>
+        <v>130256379</v>
       </c>
       <c r="B72" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8229,10 +8229,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>496957</v>
+        <v>496857</v>
       </c>
       <c r="R72" t="n">
-        <v>6826898</v>
+        <v>6827067</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8294,7 +8294,7 @@
         <v>130255817</v>
       </c>
       <c r="B73" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8398,10 +8398,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130255832</v>
+        <v>130256369</v>
       </c>
       <c r="B74" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8433,10 +8433,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>496578</v>
+        <v>496893</v>
       </c>
       <c r="R74" t="n">
-        <v>6827044</v>
+        <v>6827043</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8466,19 +8466,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>10:11</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>10:11</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8493,22 +8483,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130256369</v>
+        <v>130255820</v>
       </c>
       <c r="B75" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8540,10 +8530,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>496893</v>
+        <v>496838</v>
       </c>
       <c r="R75" t="n">
-        <v>6827043</v>
+        <v>6827085</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8573,9 +8563,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8590,12 +8590,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
@@ -8605,7 +8605,7 @@
         <v>130255830</v>
       </c>
       <c r="B76" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8709,10 +8709,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>130255820</v>
+        <v>130255832</v>
       </c>
       <c r="B77" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8744,10 +8744,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>496838</v>
+        <v>496578</v>
       </c>
       <c r="R77" t="n">
-        <v>6827085</v>
+        <v>6827044</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8779,7 +8779,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8789,7 +8789,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8816,10 +8816,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>130256383</v>
+        <v>130256368</v>
       </c>
       <c r="B78" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8851,10 +8851,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>496821</v>
+        <v>496902</v>
       </c>
       <c r="R78" t="n">
-        <v>6827087</v>
+        <v>6827030</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8913,10 +8913,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>130256365</v>
+        <v>130256383</v>
       </c>
       <c r="B79" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8948,10 +8948,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>496920</v>
+        <v>496821</v>
       </c>
       <c r="R79" t="n">
-        <v>6827003</v>
+        <v>6827087</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9013,7 +9013,7 @@
         <v>130255797</v>
       </c>
       <c r="B80" t="n">
-        <v>78940</v>
+        <v>78966</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9117,10 +9117,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>130256376</v>
+        <v>130256365</v>
       </c>
       <c r="B81" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9152,10 +9152,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>496855</v>
+        <v>496920</v>
       </c>
       <c r="R81" t="n">
-        <v>6827052</v>
+        <v>6827003</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9214,10 +9214,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>130256368</v>
+        <v>130256376</v>
       </c>
       <c r="B82" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9249,10 +9249,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>496902</v>
+        <v>496855</v>
       </c>
       <c r="R82" t="n">
-        <v>6827030</v>
+        <v>6827052</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9314,7 +9314,7 @@
         <v>130256346</v>
       </c>
       <c r="B83" t="n">
-        <v>78941</v>
+        <v>78967</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9411,7 +9411,7 @@
         <v>130255837</v>
       </c>
       <c r="B84" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9515,32 +9515,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>130255839</v>
+        <v>130256352</v>
       </c>
       <c r="B85" t="n">
-        <v>93013</v>
+        <v>78966</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9550,10 +9550,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>496787</v>
+        <v>496837</v>
       </c>
       <c r="R85" t="n">
-        <v>6827052</v>
+        <v>6827069</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9583,19 +9583,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9610,44 +9600,44 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>130256352</v>
+        <v>130255839</v>
       </c>
       <c r="B86" t="n">
-        <v>78940</v>
+        <v>93039</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9657,10 +9647,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>496837</v>
+        <v>496787</v>
       </c>
       <c r="R86" t="n">
-        <v>6827069</v>
+        <v>6827052</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9690,9 +9680,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9707,12 +9707,12 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
@@ -9722,7 +9722,7 @@
         <v>130255823</v>
       </c>
       <c r="B87" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9829,7 +9829,7 @@
         <v>130255803</v>
       </c>
       <c r="B88" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9933,10 +9933,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>130255818</v>
+        <v>130255814</v>
       </c>
       <c r="B89" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9968,10 +9968,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>496862</v>
+        <v>497073</v>
       </c>
       <c r="R89" t="n">
-        <v>6827065</v>
+        <v>6827132</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10003,7 +10003,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10040,10 +10040,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>130256387</v>
+        <v>130255818</v>
       </c>
       <c r="B90" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10075,10 +10075,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>496715</v>
+        <v>496862</v>
       </c>
       <c r="R90" t="n">
-        <v>6827126</v>
+        <v>6827065</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10108,9 +10108,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10125,22 +10135,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>130255814</v>
+        <v>130256387</v>
       </c>
       <c r="B91" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10172,10 +10182,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>497073</v>
+        <v>496715</v>
       </c>
       <c r="R91" t="n">
-        <v>6827132</v>
+        <v>6827126</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10205,19 +10215,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>11:27</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>11:27</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10232,12 +10232,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
@@ -10247,7 +10247,7 @@
         <v>130255798</v>
       </c>
       <c r="B92" t="n">
-        <v>78940</v>
+        <v>78966</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10351,10 +10351,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>130256370</v>
+        <v>130255808</v>
       </c>
       <c r="B93" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10386,10 +10386,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>496894</v>
+        <v>497167</v>
       </c>
       <c r="R93" t="n">
-        <v>6827030</v>
+        <v>6826594</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10419,9 +10419,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10436,22 +10446,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>130255808</v>
+        <v>130256370</v>
       </c>
       <c r="B94" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10483,10 +10493,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>497167</v>
+        <v>496894</v>
       </c>
       <c r="R94" t="n">
-        <v>6826594</v>
+        <v>6827030</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10516,19 +10526,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>12:09</t>
-        </is>
-      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>12:09</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10543,22 +10543,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>130256367</v>
+        <v>130256373</v>
       </c>
       <c r="B95" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10590,10 +10590,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>496908</v>
+        <v>496864</v>
       </c>
       <c r="R95" t="n">
-        <v>6827027</v>
+        <v>6827047</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10652,10 +10652,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>130256373</v>
+        <v>130256367</v>
       </c>
       <c r="B96" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10687,10 +10687,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>496864</v>
+        <v>496908</v>
       </c>
       <c r="R96" t="n">
-        <v>6827047</v>
+        <v>6827027</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10749,10 +10749,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>130255827</v>
+        <v>130255812</v>
       </c>
       <c r="B97" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10784,10 +10784,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>496658</v>
+        <v>497186</v>
       </c>
       <c r="R97" t="n">
-        <v>6827164</v>
+        <v>6826839</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10819,7 +10819,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10829,7 +10829,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10856,10 +10856,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>130256350</v>
+        <v>130255825</v>
       </c>
       <c r="B98" t="n">
-        <v>78940</v>
+        <v>79209</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10867,21 +10867,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10891,10 +10891,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>496962</v>
+        <v>496759</v>
       </c>
       <c r="R98" t="n">
-        <v>6826909</v>
+        <v>6827133</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10924,9 +10924,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10941,22 +10951,22 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>130255807</v>
+        <v>130256375</v>
       </c>
       <c r="B99" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10988,10 +10998,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>497130</v>
+        <v>496859</v>
       </c>
       <c r="R99" t="n">
-        <v>6826601</v>
+        <v>6827052</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11021,19 +11031,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>12:11</t>
-        </is>
-      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>12:11</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11048,22 +11048,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>130255812</v>
+        <v>130256350</v>
       </c>
       <c r="B100" t="n">
-        <v>79183</v>
+        <v>78966</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11071,21 +11071,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11095,10 +11095,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>497186</v>
+        <v>496962</v>
       </c>
       <c r="R100" t="n">
-        <v>6826839</v>
+        <v>6826909</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11128,19 +11128,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>11:52</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>11:52</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11155,12 +11145,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
@@ -11170,7 +11160,7 @@
         <v>130256391</v>
       </c>
       <c r="B101" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11264,10 +11254,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>130256375</v>
+        <v>130255827</v>
       </c>
       <c r="B102" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11299,10 +11289,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>496859</v>
+        <v>496658</v>
       </c>
       <c r="R102" t="n">
-        <v>6827052</v>
+        <v>6827164</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11332,9 +11322,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11349,22 +11349,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>130255825</v>
+        <v>130255807</v>
       </c>
       <c r="B103" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11396,10 +11396,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>496759</v>
+        <v>497130</v>
       </c>
       <c r="R103" t="n">
-        <v>6827133</v>
+        <v>6826601</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11431,7 +11431,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11441,7 +11441,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11468,10 +11468,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>130255833</v>
+        <v>130255804</v>
       </c>
       <c r="B104" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11503,10 +11503,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>496579</v>
+        <v>497012</v>
       </c>
       <c r="R104" t="n">
-        <v>6827030</v>
+        <v>6826898</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11538,7 +11538,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11575,10 +11575,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>130256351</v>
+        <v>130255833</v>
       </c>
       <c r="B105" t="n">
-        <v>78940</v>
+        <v>79209</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11586,21 +11586,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11610,10 +11610,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>496898</v>
+        <v>496579</v>
       </c>
       <c r="R105" t="n">
-        <v>6827000</v>
+        <v>6827030</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11643,9 +11643,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11660,12 +11670,12 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
@@ -11675,7 +11685,7 @@
         <v>130255826</v>
       </c>
       <c r="B106" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11782,7 +11792,7 @@
         <v>130256353</v>
       </c>
       <c r="B107" t="n">
-        <v>78940</v>
+        <v>78966</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11876,10 +11886,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>130255804</v>
+        <v>130256351</v>
       </c>
       <c r="B108" t="n">
-        <v>79183</v>
+        <v>78966</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11887,21 +11897,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11911,10 +11921,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>497012</v>
+        <v>496898</v>
       </c>
       <c r="R108" t="n">
-        <v>6826898</v>
+        <v>6827000</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11944,19 +11954,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z108" t="inlineStr">
-        <is>
-          <t>12:22</t>
-        </is>
-      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB108" t="inlineStr">
-        <is>
-          <t>12:22</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11971,22 +11971,22 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>130256374</v>
+        <v>130255819</v>
       </c>
       <c r="B109" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12018,10 +12018,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>496863</v>
+        <v>496850</v>
       </c>
       <c r="R109" t="n">
-        <v>6827047</v>
+        <v>6827090</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12051,9 +12051,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12068,22 +12078,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>130256360</v>
+        <v>130256374</v>
       </c>
       <c r="B110" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12115,10 +12125,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>496972</v>
+        <v>496863</v>
       </c>
       <c r="R110" t="n">
-        <v>6826953</v>
+        <v>6827047</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12177,10 +12187,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>130256354</v>
+        <v>130256386</v>
       </c>
       <c r="B111" t="n">
-        <v>78940</v>
+        <v>79209</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12188,21 +12198,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12212,10 +12222,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>496654</v>
+        <v>496723</v>
       </c>
       <c r="R111" t="n">
-        <v>6827171</v>
+        <v>6827125</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12274,10 +12284,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>130255819</v>
+        <v>130256354</v>
       </c>
       <c r="B112" t="n">
-        <v>79183</v>
+        <v>78966</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12285,21 +12295,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12309,10 +12319,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>496850</v>
+        <v>496654</v>
       </c>
       <c r="R112" t="n">
-        <v>6827090</v>
+        <v>6827171</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12342,19 +12352,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>11:05</t>
-        </is>
-      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>11:05</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12369,22 +12369,22 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>130256386</v>
+        <v>130256360</v>
       </c>
       <c r="B113" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12416,10 +12416,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>496723</v>
+        <v>496972</v>
       </c>
       <c r="R113" t="n">
-        <v>6827125</v>
+        <v>6826953</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12481,7 +12481,7 @@
         <v>130256342</v>
       </c>
       <c r="B114" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12588,10 +12588,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>130256380</v>
+        <v>130255802</v>
       </c>
       <c r="B115" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12623,10 +12623,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>496852</v>
+        <v>496785</v>
       </c>
       <c r="R115" t="n">
-        <v>6827074</v>
+        <v>6827060</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12656,9 +12656,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12673,22 +12683,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>130255802</v>
+        <v>130256380</v>
       </c>
       <c r="B116" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12720,10 +12730,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>496785</v>
+        <v>496852</v>
       </c>
       <c r="R116" t="n">
-        <v>6827060</v>
+        <v>6827074</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12753,19 +12763,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z116" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB116" t="inlineStr">
-        <is>
-          <t>12:47</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12780,12 +12780,12 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
@@ -12795,7 +12795,7 @@
         <v>130256357</v>
       </c>
       <c r="B117" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12889,10 +12889,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>130256390</v>
+        <v>130256359</v>
       </c>
       <c r="B118" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12924,10 +12924,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>496581</v>
+        <v>496963</v>
       </c>
       <c r="R118" t="n">
-        <v>6827049</v>
+        <v>6826942</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12986,10 +12986,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>130256363</v>
+        <v>130255796</v>
       </c>
       <c r="B119" t="n">
-        <v>79183</v>
+        <v>78966</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12997,21 +12997,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13021,10 +13021,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>496897</v>
+        <v>497111</v>
       </c>
       <c r="R119" t="n">
-        <v>6827002</v>
+        <v>6826644</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13054,9 +13054,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13071,22 +13081,22 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>130256381</v>
+        <v>130255801</v>
       </c>
       <c r="B120" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13118,10 +13128,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>496852</v>
+        <v>496702</v>
       </c>
       <c r="R120" t="n">
-        <v>6827066</v>
+        <v>6827131</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13151,9 +13161,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13168,22 +13188,22 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>130255796</v>
+        <v>130256382</v>
       </c>
       <c r="B121" t="n">
-        <v>78940</v>
+        <v>79209</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13191,21 +13211,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13215,10 +13235,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>497111</v>
+        <v>496831</v>
       </c>
       <c r="R121" t="n">
-        <v>6826644</v>
+        <v>6827081</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13248,19 +13268,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z121" t="inlineStr">
-        <is>
-          <t>12:13</t>
-        </is>
-      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB121" t="inlineStr">
-        <is>
-          <t>12:13</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13275,22 +13285,22 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>130256359</v>
+        <v>130256378</v>
       </c>
       <c r="B122" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13322,10 +13332,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>496963</v>
+        <v>496862</v>
       </c>
       <c r="R122" t="n">
-        <v>6826942</v>
+        <v>6827064</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13384,10 +13394,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>130255801</v>
+        <v>130256363</v>
       </c>
       <c r="B123" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13419,10 +13429,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>496702</v>
+        <v>496897</v>
       </c>
       <c r="R123" t="n">
-        <v>6827131</v>
+        <v>6827002</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13452,19 +13462,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z123" t="inlineStr">
-        <is>
-          <t>10:39</t>
-        </is>
-      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB123" t="inlineStr">
-        <is>
-          <t>10:39</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13479,66 +13479,57 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>130256348</v>
+        <v>130256381</v>
       </c>
       <c r="B124" t="n">
-        <v>8451</v>
+        <v>79209</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
-      <c r="L124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>496864</v>
+        <v>496852</v>
       </c>
       <c r="R124" t="n">
-        <v>6827043</v>
+        <v>6827066</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13579,7 +13570,6 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
-      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
@@ -13598,10 +13588,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>130256378</v>
+        <v>130256390</v>
       </c>
       <c r="B125" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13633,10 +13623,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>496862</v>
+        <v>496581</v>
       </c>
       <c r="R125" t="n">
-        <v>6827064</v>
+        <v>6827049</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13695,45 +13685,54 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>130256382</v>
+        <v>130256348</v>
       </c>
       <c r="B126" t="n">
-        <v>79183</v>
+        <v>8451</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>496831</v>
+        <v>496864</v>
       </c>
       <c r="R126" t="n">
-        <v>6827081</v>
+        <v>6827043</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13774,6 +13773,7 @@
       <c r="AE126" t="b">
         <v>0</v>
       </c>
+      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
@@ -13792,32 +13792,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>130256392</v>
+        <v>130255834</v>
       </c>
       <c r="B127" t="n">
-        <v>93013</v>
+        <v>79209</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13827,10 +13827,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>496581</v>
+        <v>496582</v>
       </c>
       <c r="R127" t="n">
-        <v>6827082</v>
+        <v>6827040</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13860,40 +13860,49 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
       <c r="AD127" t="b">
         <v>0</v>
       </c>
       <c r="AE127" t="b">
         <v>0</v>
       </c>
-      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>130255834</v>
+        <v>130255836</v>
       </c>
       <c r="B128" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13925,10 +13934,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>496582</v>
+        <v>497183</v>
       </c>
       <c r="R128" t="n">
-        <v>6827040</v>
+        <v>6826662</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13960,7 +13969,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -13970,7 +13979,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13997,10 +14006,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>130255836</v>
+        <v>130256343</v>
       </c>
       <c r="B129" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14032,10 +14041,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>497183</v>
+        <v>496851</v>
       </c>
       <c r="R129" t="n">
-        <v>6826662</v>
+        <v>6827066</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14065,19 +14074,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z129" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB129" t="inlineStr">
-        <is>
-          <t>12:06</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14092,12 +14091,12 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
@@ -14107,7 +14106,7 @@
         <v>130255805</v>
       </c>
       <c r="B130" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14211,32 +14210,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>130256343</v>
+        <v>130256392</v>
       </c>
       <c r="B131" t="n">
-        <v>79183</v>
+        <v>93039</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14246,10 +14245,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>496851</v>
+        <v>496581</v>
       </c>
       <c r="R131" t="n">
-        <v>6827066</v>
+        <v>6827082</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14290,6 +14289,7 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
+      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
@@ -14642,7 +14642,7 @@
         <v>130256345</v>
       </c>
       <c r="B135" t="n">
-        <v>78941</v>
+        <v>78967</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14739,7 +14739,7 @@
         <v>130256344</v>
       </c>
       <c r="B136" t="n">
-        <v>78941</v>
+        <v>78967</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14833,10 +14833,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>130255806</v>
+        <v>130255813</v>
       </c>
       <c r="B137" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14868,10 +14868,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>497147</v>
+        <v>497093</v>
       </c>
       <c r="R137" t="n">
-        <v>6826725</v>
+        <v>6827168</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -14913,7 +14913,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14940,10 +14940,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>130255810</v>
+        <v>130255806</v>
       </c>
       <c r="B138" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14975,10 +14975,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>497191</v>
+        <v>497147</v>
       </c>
       <c r="R138" t="n">
-        <v>6826663</v>
+        <v>6826725</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15010,7 +15010,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -15020,7 +15020,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15047,10 +15047,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>130255813</v>
+        <v>130255810</v>
       </c>
       <c r="B139" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15082,10 +15082,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>497093</v>
+        <v>497191</v>
       </c>
       <c r="R139" t="n">
-        <v>6827168</v>
+        <v>6826663</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15117,7 +15117,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -15127,7 +15127,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15157,7 +15157,7 @@
         <v>130256358</v>
       </c>
       <c r="B140" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15254,7 +15254,7 @@
         <v>130256361</v>
       </c>
       <c r="B141" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15351,7 +15351,7 @@
         <v>130256389</v>
       </c>
       <c r="B142" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15448,7 +15448,7 @@
         <v>130256394</v>
       </c>
       <c r="B143" t="n">
-        <v>93013</v>
+        <v>93039</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15554,10 +15554,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>130256364</v>
+        <v>130256355</v>
       </c>
       <c r="B144" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15589,10 +15589,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>496909</v>
+        <v>496940</v>
       </c>
       <c r="R144" t="n">
-        <v>6827002</v>
+        <v>6826898</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15651,10 +15651,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>130256355</v>
+        <v>130256364</v>
       </c>
       <c r="B145" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15686,10 +15686,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>496940</v>
+        <v>496909</v>
       </c>
       <c r="R145" t="n">
-        <v>6826898</v>
+        <v>6827002</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15751,7 +15751,7 @@
         <v>130256371</v>
       </c>
       <c r="B146" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15848,7 +15848,7 @@
         <v>130255828</v>
       </c>
       <c r="B147" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15952,10 +15952,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>130255821</v>
+        <v>130256362</v>
       </c>
       <c r="B148" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15987,10 +15987,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>496839</v>
+        <v>496893</v>
       </c>
       <c r="R148" t="n">
-        <v>6827082</v>
+        <v>6826998</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16020,19 +16020,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z148" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB148" t="inlineStr">
-        <is>
-          <t>11:04</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16047,22 +16037,22 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>130256362</v>
+        <v>130255821</v>
       </c>
       <c r="B149" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16094,10 +16084,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>496893</v>
+        <v>496839</v>
       </c>
       <c r="R149" t="n">
-        <v>6826998</v>
+        <v>6827082</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16127,9 +16117,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z149" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AA149" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB149" t="inlineStr">
+        <is>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16144,12 +16144,12 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
@@ -16159,7 +16159,7 @@
         <v>130256340</v>
       </c>
       <c r="B150" t="n">
-        <v>79773</v>
+        <v>79799</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16256,7 +16256,7 @@
         <v>130255811</v>
       </c>
       <c r="B151" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16363,7 +16363,7 @@
         <v>130255831</v>
       </c>
       <c r="B152" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16467,10 +16467,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>130256372</v>
+        <v>130255824</v>
       </c>
       <c r="B153" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16502,10 +16502,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>496867</v>
+        <v>496752</v>
       </c>
       <c r="R153" t="n">
-        <v>6827035</v>
+        <v>6827114</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16535,9 +16535,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z153" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB153" t="inlineStr">
+        <is>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16552,22 +16562,22 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>130255824</v>
+        <v>130256372</v>
       </c>
       <c r="B154" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16599,10 +16609,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>496752</v>
+        <v>496867</v>
       </c>
       <c r="R154" t="n">
-        <v>6827114</v>
+        <v>6827035</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16632,19 +16642,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z154" t="inlineStr">
-        <is>
-          <t>10:49</t>
-        </is>
-      </c>
       <c r="AA154" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB154" t="inlineStr">
-        <is>
-          <t>10:49</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16659,12 +16659,12 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
@@ -16674,7 +16674,7 @@
         <v>130255838</v>
       </c>
       <c r="B155" t="n">
-        <v>93013</v>
+        <v>93039</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16781,7 +16781,7 @@
         <v>130256385</v>
       </c>
       <c r="B156" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16878,7 +16878,7 @@
         <v>130256393</v>
       </c>
       <c r="B157" t="n">
-        <v>93013</v>
+        <v>93039</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16972,10 +16972,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>130255809</v>
+        <v>130255829</v>
       </c>
       <c r="B158" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17007,10 +17007,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>497168</v>
+        <v>496643</v>
       </c>
       <c r="R158" t="n">
-        <v>6826596</v>
+        <v>6827146</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17042,7 +17042,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -17052,7 +17052,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17082,7 +17082,7 @@
         <v>130255816</v>
       </c>
       <c r="B159" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17186,10 +17186,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>130255829</v>
+        <v>130255809</v>
       </c>
       <c r="B160" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17221,10 +17221,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>496643</v>
+        <v>497168</v>
       </c>
       <c r="R160" t="n">
-        <v>6827146</v>
+        <v>6826596</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17256,7 +17256,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -17266,7 +17266,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD160" t="b">

--- a/artfynd/A 58895-2025 artfynd.xlsx
+++ b/artfynd/A 58895-2025 artfynd.xlsx
@@ -2075,32 +2075,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130252154</v>
+        <v>130252119</v>
       </c>
       <c r="B15" t="n">
-        <v>93039</v>
+        <v>58011</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2110,10 +2110,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>496692</v>
+        <v>496602</v>
       </c>
       <c r="R15" t="n">
-        <v>6827092</v>
+        <v>6827039</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2145,7 +2145,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2182,32 +2182,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130252119</v>
+        <v>130252122</v>
       </c>
       <c r="B16" t="n">
-        <v>58011</v>
+        <v>8451</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2217,10 +2217,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>496602</v>
+        <v>496640</v>
       </c>
       <c r="R16" t="n">
-        <v>6827039</v>
+        <v>6827137</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2289,10 +2289,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130252122</v>
+        <v>130252154</v>
       </c>
       <c r="B17" t="n">
-        <v>8451</v>
+        <v>93039</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2300,21 +2300,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2324,10 +2324,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>496640</v>
+        <v>496692</v>
       </c>
       <c r="R17" t="n">
-        <v>6827137</v>
+        <v>6827092</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -5401,32 +5401,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130252598</v>
+        <v>130252609</v>
       </c>
       <c r="B46" t="n">
-        <v>79209</v>
+        <v>93039</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5436,10 +5436,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>497202</v>
+        <v>496549</v>
       </c>
       <c r="R46" t="n">
-        <v>6826911</v>
+        <v>6826988</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5471,7 +5471,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5490,6 +5490,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5508,7 +5509,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130252153</v>
+        <v>130252598</v>
       </c>
       <c r="B47" t="n">
         <v>79209</v>
@@ -5539,14 +5540,14 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>496564</v>
+        <v>497202</v>
       </c>
       <c r="R47" t="n">
-        <v>6827012</v>
+        <v>6826911</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5578,7 +5579,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5588,7 +5589,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5603,19 +5604,19 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130252602</v>
+        <v>130252153</v>
       </c>
       <c r="B48" t="n">
         <v>79209</v>
@@ -5646,14 +5647,14 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>496722</v>
+        <v>496564</v>
       </c>
       <c r="R48" t="n">
-        <v>6827107</v>
+        <v>6827012</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5685,7 +5686,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5695,7 +5696,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5710,44 +5711,44 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130252609</v>
+        <v>130252602</v>
       </c>
       <c r="B49" t="n">
-        <v>93039</v>
+        <v>79209</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5757,10 +5758,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>496549</v>
+        <v>496722</v>
       </c>
       <c r="R49" t="n">
-        <v>6826988</v>
+        <v>6827107</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5792,7 +5793,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5802,7 +5803,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5811,7 +5812,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -9311,10 +9311,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>130256346</v>
+        <v>130255837</v>
       </c>
       <c r="B83" t="n">
-        <v>78967</v>
+        <v>79209</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9322,21 +9322,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9346,10 +9346,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>496652</v>
+        <v>497191</v>
       </c>
       <c r="R83" t="n">
-        <v>6827164</v>
+        <v>6826771</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9379,9 +9379,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9396,22 +9406,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>130255837</v>
+        <v>130256346</v>
       </c>
       <c r="B84" t="n">
-        <v>79209</v>
+        <v>78967</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9419,21 +9429,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9443,10 +9453,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>497191</v>
+        <v>496652</v>
       </c>
       <c r="R84" t="n">
-        <v>6826771</v>
+        <v>6827164</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9476,19 +9486,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>12:00</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9503,44 +9503,44 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>130256352</v>
+        <v>130255839</v>
       </c>
       <c r="B85" t="n">
-        <v>78966</v>
+        <v>93039</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9550,10 +9550,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>496837</v>
+        <v>496787</v>
       </c>
       <c r="R85" t="n">
-        <v>6827069</v>
+        <v>6827052</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9583,9 +9583,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9600,44 +9610,44 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>130255839</v>
+        <v>130256352</v>
       </c>
       <c r="B86" t="n">
-        <v>93039</v>
+        <v>78966</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9647,10 +9657,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>496787</v>
+        <v>496837</v>
       </c>
       <c r="R86" t="n">
-        <v>6827052</v>
+        <v>6827069</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9680,19 +9690,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9707,12 +9707,12 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
@@ -14210,10 +14210,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>130256392</v>
+        <v>130255793</v>
       </c>
       <c r="B131" t="n">
-        <v>93039</v>
+        <v>8451</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14221,34 +14221,43 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>496581</v>
+        <v>496670</v>
       </c>
       <c r="R131" t="n">
-        <v>6827082</v>
+        <v>6827136</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14278,9 +14287,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14296,19 +14315,19 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>130255793</v>
+        <v>130256349</v>
       </c>
       <c r="B132" t="n">
         <v>8451</v>
@@ -14352,10 +14371,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>496670</v>
+        <v>496714</v>
       </c>
       <c r="R132" t="n">
-        <v>6827136</v>
+        <v>6827127</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14385,19 +14404,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z132" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB132" t="inlineStr">
-        <is>
-          <t>10:30</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14413,19 +14422,19 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>130256349</v>
+        <v>130256347</v>
       </c>
       <c r="B133" t="n">
         <v>8451</v>
@@ -14469,10 +14478,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>496714</v>
+        <v>496941</v>
       </c>
       <c r="R133" t="n">
-        <v>6827127</v>
+        <v>6826899</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14532,10 +14541,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>130256347</v>
+        <v>130256392</v>
       </c>
       <c r="B134" t="n">
-        <v>8451</v>
+        <v>93039</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14543,43 +14552,34 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
-      <c r="J134" t="inlineStr"/>
-      <c r="K134" t="inlineStr"/>
-      <c r="L134" t="inlineStr"/>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>496941</v>
+        <v>496581</v>
       </c>
       <c r="R134" t="n">
-        <v>6826899</v>
+        <v>6827082</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -16875,32 +16875,32 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>130256393</v>
+        <v>130255829</v>
       </c>
       <c r="B157" t="n">
-        <v>93039</v>
+        <v>79209</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16910,10 +16910,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>496647</v>
+        <v>496643</v>
       </c>
       <c r="R157" t="n">
-        <v>6827158</v>
+        <v>6827146</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16943,9 +16943,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA157" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB157" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16960,19 +16970,19 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>130255829</v>
+        <v>130255816</v>
       </c>
       <c r="B158" t="n">
         <v>79209</v>
@@ -17007,10 +17017,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>496643</v>
+        <v>496954</v>
       </c>
       <c r="R158" t="n">
-        <v>6827146</v>
+        <v>6827096</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17042,7 +17052,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -17052,7 +17062,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17079,7 +17089,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>130255816</v>
+        <v>130255809</v>
       </c>
       <c r="B159" t="n">
         <v>79209</v>
@@ -17114,10 +17124,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>496954</v>
+        <v>497168</v>
       </c>
       <c r="R159" t="n">
-        <v>6827096</v>
+        <v>6826596</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17149,7 +17159,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -17159,7 +17169,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17186,32 +17196,32 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>130255809</v>
+        <v>130256393</v>
       </c>
       <c r="B160" t="n">
-        <v>79209</v>
+        <v>93039</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17221,10 +17231,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>497168</v>
+        <v>496647</v>
       </c>
       <c r="R160" t="n">
-        <v>6826596</v>
+        <v>6827158</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17254,19 +17264,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z160" t="inlineStr">
-        <is>
-          <t>12:09</t>
-        </is>
-      </c>
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB160" t="inlineStr">
-        <is>
-          <t>12:09</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17281,12 +17281,12 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>

--- a/artfynd/A 58895-2025 artfynd.xlsx
+++ b/artfynd/A 58895-2025 artfynd.xlsx
@@ -790,45 +790,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130252155</v>
+        <v>130252584</v>
       </c>
       <c r="B3" t="n">
-        <v>93039</v>
+        <v>58011</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>496725</v>
+        <v>497202</v>
       </c>
       <c r="R3" t="n">
-        <v>6827084</v>
+        <v>6826919</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,57 +885,57 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130252591</v>
+        <v>130252120</v>
       </c>
       <c r="B4" t="n">
-        <v>78966</v>
+        <v>8451</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>496966</v>
+        <v>496653</v>
       </c>
       <c r="R4" t="n">
-        <v>6826906</v>
+        <v>6827111</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -967,7 +967,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -992,44 +992,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130252116</v>
+        <v>130252155</v>
       </c>
       <c r="B5" t="n">
-        <v>79828</v>
+        <v>93040</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>496721</v>
+        <v>496725</v>
       </c>
       <c r="R5" t="n">
-        <v>6827083</v>
+        <v>6827084</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,10 +1111,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130252584</v>
+        <v>130252116</v>
       </c>
       <c r="B6" t="n">
-        <v>58011</v>
+        <v>79828</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1122,34 +1122,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497202</v>
+        <v>496721</v>
       </c>
       <c r="R6" t="n">
-        <v>6826919</v>
+        <v>6827083</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1206,57 +1206,57 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130252120</v>
+        <v>130252591</v>
       </c>
       <c r="B7" t="n">
-        <v>8451</v>
+        <v>78966</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>496653</v>
+        <v>496966</v>
       </c>
       <c r="R7" t="n">
-        <v>6827111</v>
+        <v>6826906</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1313,12 +1313,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1543,7 +1543,7 @@
         <v>130252156</v>
       </c>
       <c r="B10" t="n">
-        <v>93039</v>
+        <v>93040</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1647,10 +1647,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130252138</v>
+        <v>130252126</v>
       </c>
       <c r="B11" t="n">
-        <v>79209</v>
+        <v>78966</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1658,21 +1658,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1682,10 +1682,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>497207</v>
+        <v>496737</v>
       </c>
       <c r="R11" t="n">
-        <v>6826726</v>
+        <v>6827071</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1717,7 +1717,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1727,7 +1727,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1861,7 +1861,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130252126</v>
+        <v>130252588</v>
       </c>
       <c r="B13" t="n">
         <v>78966</v>
@@ -1892,14 +1892,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>496737</v>
+        <v>497230</v>
       </c>
       <c r="R13" t="n">
-        <v>6827071</v>
+        <v>6826961</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1931,7 +1931,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1956,22 +1956,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130252588</v>
+        <v>130252138</v>
       </c>
       <c r="B14" t="n">
-        <v>78966</v>
+        <v>79209</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1979,34 +1979,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>497230</v>
+        <v>497207</v>
       </c>
       <c r="R14" t="n">
-        <v>6826961</v>
+        <v>6826726</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2038,7 +2038,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2063,44 +2063,44 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130252119</v>
+        <v>130252154</v>
       </c>
       <c r="B15" t="n">
-        <v>58011</v>
+        <v>93040</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2110,10 +2110,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>496602</v>
+        <v>496692</v>
       </c>
       <c r="R15" t="n">
-        <v>6827039</v>
+        <v>6827092</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2145,7 +2145,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2182,32 +2182,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130252122</v>
+        <v>130252119</v>
       </c>
       <c r="B16" t="n">
-        <v>8451</v>
+        <v>58011</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2217,10 +2217,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>496640</v>
+        <v>496602</v>
       </c>
       <c r="R16" t="n">
-        <v>6827137</v>
+        <v>6827039</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2289,10 +2289,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130252154</v>
+        <v>130252122</v>
       </c>
       <c r="B17" t="n">
-        <v>93039</v>
+        <v>8451</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2300,21 +2300,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2324,10 +2324,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>496692</v>
+        <v>496640</v>
       </c>
       <c r="R17" t="n">
-        <v>6827092</v>
+        <v>6827137</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2396,32 +2396,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130252125</v>
+        <v>130252123</v>
       </c>
       <c r="B18" t="n">
-        <v>78966</v>
+        <v>8451</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2431,10 +2431,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>497154</v>
+        <v>496581</v>
       </c>
       <c r="R18" t="n">
-        <v>6826854</v>
+        <v>6827019</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2476,7 +2476,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2503,10 +2503,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130252145</v>
+        <v>130252594</v>
       </c>
       <c r="B19" t="n">
-        <v>79209</v>
+        <v>78966</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2514,34 +2514,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>496870</v>
+        <v>496874</v>
       </c>
       <c r="R19" t="n">
-        <v>6827056</v>
+        <v>6827149</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2598,19 +2598,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130252594</v>
+        <v>130252125</v>
       </c>
       <c r="B20" t="n">
         <v>78966</v>
@@ -2641,14 +2641,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>496874</v>
+        <v>497154</v>
       </c>
       <c r="R20" t="n">
-        <v>6827149</v>
+        <v>6826854</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2705,12 +2705,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2824,32 +2824,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130252123</v>
+        <v>130252145</v>
       </c>
       <c r="B22" t="n">
-        <v>8451</v>
+        <v>79209</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2859,10 +2859,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>496581</v>
+        <v>496870</v>
       </c>
       <c r="R22" t="n">
-        <v>6827019</v>
+        <v>6827056</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2904,7 +2904,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3252,10 +3252,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130252600</v>
+        <v>130252127</v>
       </c>
       <c r="B26" t="n">
-        <v>79209</v>
+        <v>78966</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3263,34 +3263,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>496948</v>
+        <v>496719</v>
       </c>
       <c r="R26" t="n">
-        <v>6827029</v>
+        <v>6827076</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3322,7 +3322,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3347,19 +3347,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130252127</v>
+        <v>130252595</v>
       </c>
       <c r="B27" t="n">
         <v>78966</v>
@@ -3390,14 +3390,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>496719</v>
+        <v>496894</v>
       </c>
       <c r="R27" t="n">
-        <v>6827076</v>
+        <v>6827123</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3429,7 +3429,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3439,7 +3439,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3454,22 +3454,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130252595</v>
+        <v>130252600</v>
       </c>
       <c r="B28" t="n">
-        <v>78966</v>
+        <v>79209</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3477,21 +3477,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3501,10 +3501,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>496894</v>
+        <v>496948</v>
       </c>
       <c r="R28" t="n">
-        <v>6827123</v>
+        <v>6827029</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3536,7 +3536,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3546,7 +3546,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3573,32 +3573,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130252141</v>
+        <v>130252157</v>
       </c>
       <c r="B29" t="n">
-        <v>79209</v>
+        <v>93040</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3608,10 +3608,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>496956</v>
+        <v>496628</v>
       </c>
       <c r="R29" t="n">
-        <v>6827088</v>
+        <v>6827124</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3643,7 +3643,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3680,10 +3680,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130252589</v>
+        <v>130252141</v>
       </c>
       <c r="B30" t="n">
-        <v>78966</v>
+        <v>79209</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3691,34 +3691,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>497211</v>
+        <v>496956</v>
       </c>
       <c r="R30" t="n">
-        <v>6826926</v>
+        <v>6827088</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3750,7 +3750,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3760,7 +3760,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3775,12 +3775,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -3894,45 +3894,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130252157</v>
+        <v>130252589</v>
       </c>
       <c r="B32" t="n">
-        <v>93039</v>
+        <v>78966</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>496628</v>
+        <v>497211</v>
       </c>
       <c r="R32" t="n">
-        <v>6827124</v>
+        <v>6826926</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3964,7 +3964,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3974,7 +3974,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3989,12 +3989,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4108,7 +4108,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130252143</v>
+        <v>130252135</v>
       </c>
       <c r="B34" t="n">
         <v>79209</v>
@@ -4143,10 +4143,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>496877</v>
+        <v>496915</v>
       </c>
       <c r="R34" t="n">
-        <v>6827056</v>
+        <v>6826903</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4322,7 +4322,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130252135</v>
+        <v>130252146</v>
       </c>
       <c r="B36" t="n">
         <v>79209</v>
@@ -4357,10 +4357,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>496915</v>
+        <v>496864</v>
       </c>
       <c r="R36" t="n">
-        <v>6826903</v>
+        <v>6827053</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4429,7 +4429,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130252605</v>
+        <v>130252143</v>
       </c>
       <c r="B37" t="n">
         <v>79209</v>
@@ -4460,14 +4460,14 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>496676</v>
+        <v>496877</v>
       </c>
       <c r="R37" t="n">
-        <v>6827143</v>
+        <v>6827056</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4509,7 +4509,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4524,19 +4524,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130252146</v>
+        <v>130252605</v>
       </c>
       <c r="B38" t="n">
         <v>79209</v>
@@ -4567,14 +4567,14 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>496864</v>
+        <v>496676</v>
       </c>
       <c r="R38" t="n">
-        <v>6827053</v>
+        <v>6827143</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4631,12 +4631,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4753,7 +4753,7 @@
         <v>130252158</v>
       </c>
       <c r="B40" t="n">
-        <v>93039</v>
+        <v>93040</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4860,7 +4860,7 @@
         <v>130252607</v>
       </c>
       <c r="B41" t="n">
-        <v>93039</v>
+        <v>93040</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5072,10 +5072,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130252136</v>
+        <v>130252590</v>
       </c>
       <c r="B43" t="n">
-        <v>79209</v>
+        <v>78966</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5083,34 +5083,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>497002</v>
+        <v>496995</v>
       </c>
       <c r="R43" t="n">
-        <v>6826879</v>
+        <v>6826923</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5142,7 +5142,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5152,7 +5152,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5167,22 +5167,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130252590</v>
+        <v>130252136</v>
       </c>
       <c r="B44" t="n">
-        <v>78966</v>
+        <v>79209</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5190,34 +5190,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>496995</v>
+        <v>497002</v>
       </c>
       <c r="R44" t="n">
-        <v>6826923</v>
+        <v>6826879</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5249,7 +5249,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5274,12 +5274,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5401,32 +5401,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130252609</v>
+        <v>130252598</v>
       </c>
       <c r="B46" t="n">
-        <v>93039</v>
+        <v>79209</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5436,10 +5436,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>496549</v>
+        <v>497202</v>
       </c>
       <c r="R46" t="n">
-        <v>6826988</v>
+        <v>6826911</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5471,7 +5471,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5490,7 +5490,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5509,7 +5508,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130252598</v>
+        <v>130252602</v>
       </c>
       <c r="B47" t="n">
         <v>79209</v>
@@ -5544,10 +5543,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>497202</v>
+        <v>496722</v>
       </c>
       <c r="R47" t="n">
-        <v>6826911</v>
+        <v>6827107</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5579,7 +5578,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5589,7 +5588,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5723,32 +5722,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130252602</v>
+        <v>130252609</v>
       </c>
       <c r="B49" t="n">
-        <v>79209</v>
+        <v>93040</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5758,10 +5757,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>496722</v>
+        <v>496549</v>
       </c>
       <c r="R49" t="n">
-        <v>6827107</v>
+        <v>6826988</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5793,7 +5792,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5803,7 +5802,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5812,6 +5811,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6044,10 +6044,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130252118</v>
+        <v>130252150</v>
       </c>
       <c r="B52" t="n">
-        <v>57852</v>
+        <v>79209</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6055,42 +6055,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>496923</v>
+        <v>496701</v>
       </c>
       <c r="R52" t="n">
-        <v>6826913</v>
+        <v>6827080</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6122,7 +6114,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6132,12 +6124,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:50</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6164,10 +6151,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130252150</v>
+        <v>130252118</v>
       </c>
       <c r="B53" t="n">
-        <v>79209</v>
+        <v>57852</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6175,34 +6162,42 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>496701</v>
+        <v>496923</v>
       </c>
       <c r="R53" t="n">
-        <v>6827080</v>
+        <v>6826913</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6234,7 +6229,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6244,7 +6239,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6388,32 +6388,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130252596</v>
+        <v>130252606</v>
       </c>
       <c r="B55" t="n">
-        <v>78966</v>
+        <v>93040</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6423,10 +6423,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>496771</v>
+        <v>496618</v>
       </c>
       <c r="R55" t="n">
-        <v>6827069</v>
+        <v>6827114</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6458,7 +6458,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6468,7 +6468,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6477,6 +6477,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6495,10 +6496,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130252137</v>
+        <v>130252596</v>
       </c>
       <c r="B56" t="n">
-        <v>79209</v>
+        <v>78966</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6506,34 +6507,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>497206</v>
+        <v>496771</v>
       </c>
       <c r="R56" t="n">
-        <v>6826638</v>
+        <v>6827069</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6565,7 +6566,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6575,7 +6576,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6590,12 +6591,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -6709,45 +6710,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130252606</v>
+        <v>130252137</v>
       </c>
       <c r="B58" t="n">
-        <v>93039</v>
+        <v>79209</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>496618</v>
+        <v>497206</v>
       </c>
       <c r="R58" t="n">
-        <v>6827114</v>
+        <v>6826638</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6779,7 +6780,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6789,7 +6790,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6798,19 +6799,18 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -7031,7 +7031,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130252152</v>
+        <v>130252131</v>
       </c>
       <c r="B61" t="n">
         <v>79209</v>
@@ -7066,10 +7066,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>496591</v>
+        <v>496656</v>
       </c>
       <c r="R61" t="n">
-        <v>6827054</v>
+        <v>6827109</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7101,7 +7101,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7111,7 +7111,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7138,7 +7138,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130252131</v>
+        <v>130252152</v>
       </c>
       <c r="B62" t="n">
         <v>79209</v>
@@ -7173,10 +7173,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>496656</v>
+        <v>496591</v>
       </c>
       <c r="R62" t="n">
-        <v>6827109</v>
+        <v>6827054</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7208,7 +7208,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7218,7 +7218,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7463,7 +7463,7 @@
         <v>130252608</v>
       </c>
       <c r="B65" t="n">
-        <v>93039</v>
+        <v>93040</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130252597</v>
+        <v>130252139</v>
       </c>
       <c r="B66" t="n">
         <v>79209</v>
@@ -7599,14 +7599,14 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>496922</v>
+        <v>497225</v>
       </c>
       <c r="R66" t="n">
-        <v>6826906</v>
+        <v>6826804</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7638,7 +7638,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7663,19 +7663,19 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130252139</v>
+        <v>130252151</v>
       </c>
       <c r="B67" t="n">
         <v>79209</v>
@@ -7710,10 +7710,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>497225</v>
+        <v>496704</v>
       </c>
       <c r="R67" t="n">
-        <v>6826804</v>
+        <v>6827086</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7745,7 +7745,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7755,7 +7755,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7782,7 +7782,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130252151</v>
+        <v>130252597</v>
       </c>
       <c r="B68" t="n">
         <v>79209</v>
@@ -7813,14 +7813,14 @@
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>496704</v>
+        <v>496922</v>
       </c>
       <c r="R68" t="n">
-        <v>6827086</v>
+        <v>6826906</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7852,7 +7852,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7862,7 +7862,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7877,19 +7877,19 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130252149</v>
+        <v>130256388</v>
       </c>
       <c r="B69" t="n">
         <v>79209</v>
@@ -7918,19 +7918,16 @@
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>496745</v>
+        <v>496665</v>
       </c>
       <c r="R69" t="n">
-        <v>6827070</v>
+        <v>6827143</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7960,47 +7957,36 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130256388</v>
+        <v>130252149</v>
       </c>
       <c r="B70" t="n">
         <v>79209</v>
@@ -8029,16 +8015,19 @@
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>496665</v>
+        <v>496745</v>
       </c>
       <c r="R70" t="n">
-        <v>6827143</v>
+        <v>6827070</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8068,36 +8057,47 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130256356</v>
+        <v>130256379</v>
       </c>
       <c r="B71" t="n">
         <v>79209</v>
@@ -8132,10 +8132,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>496957</v>
+        <v>496857</v>
       </c>
       <c r="R71" t="n">
-        <v>6826898</v>
+        <v>6827067</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8194,7 +8194,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130256379</v>
+        <v>130256356</v>
       </c>
       <c r="B72" t="n">
         <v>79209</v>
@@ -8229,10 +8229,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>496857</v>
+        <v>496957</v>
       </c>
       <c r="R72" t="n">
-        <v>6827067</v>
+        <v>6826898</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8398,7 +8398,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130256369</v>
+        <v>130255832</v>
       </c>
       <c r="B74" t="n">
         <v>79209</v>
@@ -8433,10 +8433,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>496893</v>
+        <v>496578</v>
       </c>
       <c r="R74" t="n">
-        <v>6827043</v>
+        <v>6827044</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8466,9 +8466,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8483,19 +8493,19 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130255820</v>
+        <v>130256369</v>
       </c>
       <c r="B75" t="n">
         <v>79209</v>
@@ -8530,10 +8540,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>496838</v>
+        <v>496893</v>
       </c>
       <c r="R75" t="n">
-        <v>6827085</v>
+        <v>6827043</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8563,19 +8573,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>11:04</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8590,12 +8590,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
@@ -8709,7 +8709,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>130255832</v>
+        <v>130255820</v>
       </c>
       <c r="B77" t="n">
         <v>79209</v>
@@ -8744,10 +8744,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>496578</v>
+        <v>496838</v>
       </c>
       <c r="R77" t="n">
-        <v>6827044</v>
+        <v>6827085</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8779,7 +8779,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8789,7 +8789,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8816,10 +8816,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>130256368</v>
+        <v>130255797</v>
       </c>
       <c r="B78" t="n">
-        <v>79209</v>
+        <v>78966</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8827,21 +8827,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8851,10 +8851,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>496902</v>
+        <v>497218</v>
       </c>
       <c r="R78" t="n">
-        <v>6827030</v>
+        <v>6826761</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8884,9 +8884,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8901,12 +8911,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -9010,10 +9020,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>130255797</v>
+        <v>130256365</v>
       </c>
       <c r="B80" t="n">
-        <v>78966</v>
+        <v>79209</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9021,21 +9031,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9045,10 +9055,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>497218</v>
+        <v>496920</v>
       </c>
       <c r="R80" t="n">
-        <v>6826761</v>
+        <v>6827003</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9078,19 +9088,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>11:59</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>11:59</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9105,19 +9105,19 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>130256365</v>
+        <v>130256376</v>
       </c>
       <c r="B81" t="n">
         <v>79209</v>
@@ -9152,10 +9152,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>496920</v>
+        <v>496855</v>
       </c>
       <c r="R81" t="n">
-        <v>6827003</v>
+        <v>6827052</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9214,7 +9214,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>130256376</v>
+        <v>130256368</v>
       </c>
       <c r="B82" t="n">
         <v>79209</v>
@@ -9249,10 +9249,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>496855</v>
+        <v>496902</v>
       </c>
       <c r="R82" t="n">
-        <v>6827052</v>
+        <v>6827030</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9518,7 +9518,7 @@
         <v>130255839</v>
       </c>
       <c r="B85" t="n">
-        <v>93039</v>
+        <v>93040</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9933,7 +9933,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>130255814</v>
+        <v>130255818</v>
       </c>
       <c r="B89" t="n">
         <v>79209</v>
@@ -9968,10 +9968,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>497073</v>
+        <v>496862</v>
       </c>
       <c r="R89" t="n">
-        <v>6827132</v>
+        <v>6827065</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10003,7 +10003,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10040,7 +10040,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>130255818</v>
+        <v>130256387</v>
       </c>
       <c r="B90" t="n">
         <v>79209</v>
@@ -10075,10 +10075,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>496862</v>
+        <v>496715</v>
       </c>
       <c r="R90" t="n">
-        <v>6827065</v>
+        <v>6827126</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10108,19 +10108,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>11:06</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>11:06</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10135,19 +10125,19 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>130256387</v>
+        <v>130255814</v>
       </c>
       <c r="B91" t="n">
         <v>79209</v>
@@ -10182,10 +10172,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>496715</v>
+        <v>497073</v>
       </c>
       <c r="R91" t="n">
-        <v>6827126</v>
+        <v>6827132</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10215,9 +10205,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10232,12 +10232,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
@@ -10351,7 +10351,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>130255808</v>
+        <v>130256370</v>
       </c>
       <c r="B93" t="n">
         <v>79209</v>
@@ -10386,10 +10386,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>497167</v>
+        <v>496894</v>
       </c>
       <c r="R93" t="n">
-        <v>6826594</v>
+        <v>6827030</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10419,19 +10419,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>12:09</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>12:09</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10446,19 +10436,19 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>130256370</v>
+        <v>130255808</v>
       </c>
       <c r="B94" t="n">
         <v>79209</v>
@@ -10493,10 +10483,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>496894</v>
+        <v>497167</v>
       </c>
       <c r="R94" t="n">
-        <v>6827030</v>
+        <v>6826594</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10526,9 +10516,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10543,19 +10543,19 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>130256373</v>
+        <v>130256367</v>
       </c>
       <c r="B95" t="n">
         <v>79209</v>
@@ -10590,10 +10590,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>496864</v>
+        <v>496908</v>
       </c>
       <c r="R95" t="n">
-        <v>6827047</v>
+        <v>6827027</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10652,7 +10652,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>130256367</v>
+        <v>130256373</v>
       </c>
       <c r="B96" t="n">
         <v>79209</v>
@@ -10687,10 +10687,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>496908</v>
+        <v>496864</v>
       </c>
       <c r="R96" t="n">
-        <v>6827027</v>
+        <v>6827047</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10749,7 +10749,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>130255812</v>
+        <v>130255827</v>
       </c>
       <c r="B97" t="n">
         <v>79209</v>
@@ -10784,10 +10784,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>497186</v>
+        <v>496658</v>
       </c>
       <c r="R97" t="n">
-        <v>6826839</v>
+        <v>6827164</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10819,7 +10819,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10829,7 +10829,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10856,7 +10856,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>130255825</v>
+        <v>130255807</v>
       </c>
       <c r="B98" t="n">
         <v>79209</v>
@@ -10891,10 +10891,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>496759</v>
+        <v>497130</v>
       </c>
       <c r="R98" t="n">
-        <v>6827133</v>
+        <v>6826601</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10926,7 +10926,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -10936,7 +10936,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10963,7 +10963,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>130256375</v>
+        <v>130255812</v>
       </c>
       <c r="B99" t="n">
         <v>79209</v>
@@ -10998,10 +10998,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>496859</v>
+        <v>497186</v>
       </c>
       <c r="R99" t="n">
-        <v>6827052</v>
+        <v>6826839</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11031,9 +11031,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11048,22 +11058,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>130256350</v>
+        <v>130256391</v>
       </c>
       <c r="B100" t="n">
-        <v>78966</v>
+        <v>79209</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11071,21 +11081,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11095,10 +11105,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>496962</v>
+        <v>496588</v>
       </c>
       <c r="R100" t="n">
-        <v>6826909</v>
+        <v>6827066</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11157,7 +11167,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>130256391</v>
+        <v>130256375</v>
       </c>
       <c r="B101" t="n">
         <v>79209</v>
@@ -11192,10 +11202,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>496588</v>
+        <v>496859</v>
       </c>
       <c r="R101" t="n">
-        <v>6827066</v>
+        <v>6827052</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11254,7 +11264,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>130255827</v>
+        <v>130255825</v>
       </c>
       <c r="B102" t="n">
         <v>79209</v>
@@ -11289,10 +11299,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>496658</v>
+        <v>496759</v>
       </c>
       <c r="R102" t="n">
-        <v>6827164</v>
+        <v>6827133</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11324,7 +11334,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11334,7 +11344,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11361,10 +11371,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>130255807</v>
+        <v>130256350</v>
       </c>
       <c r="B103" t="n">
-        <v>79209</v>
+        <v>78966</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11372,21 +11382,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11396,10 +11406,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>497130</v>
+        <v>496962</v>
       </c>
       <c r="R103" t="n">
-        <v>6826601</v>
+        <v>6826909</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11429,19 +11439,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z103" t="inlineStr">
-        <is>
-          <t>12:11</t>
-        </is>
-      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB103" t="inlineStr">
-        <is>
-          <t>12:11</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11456,19 +11456,19 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>130255804</v>
+        <v>130255833</v>
       </c>
       <c r="B104" t="n">
         <v>79209</v>
@@ -11503,10 +11503,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>497012</v>
+        <v>496579</v>
       </c>
       <c r="R104" t="n">
-        <v>6826898</v>
+        <v>6827030</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11538,7 +11538,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11575,10 +11575,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>130255833</v>
+        <v>130256351</v>
       </c>
       <c r="B105" t="n">
-        <v>79209</v>
+        <v>78966</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11586,21 +11586,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11610,10 +11610,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>496579</v>
+        <v>496898</v>
       </c>
       <c r="R105" t="n">
-        <v>6827030</v>
+        <v>6827000</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11643,19 +11643,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z105" t="inlineStr">
-        <is>
-          <t>10:11</t>
-        </is>
-      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB105" t="inlineStr">
-        <is>
-          <t>10:11</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11670,22 +11660,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>130255826</v>
+        <v>130256353</v>
       </c>
       <c r="B106" t="n">
-        <v>79209</v>
+        <v>78966</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11693,21 +11683,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11717,10 +11707,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>496694</v>
+        <v>496827</v>
       </c>
       <c r="R106" t="n">
-        <v>6827122</v>
+        <v>6827089</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11750,19 +11740,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z106" t="inlineStr">
-        <is>
-          <t>10:34</t>
-        </is>
-      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB106" t="inlineStr">
-        <is>
-          <t>10:34</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11777,22 +11757,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>130256353</v>
+        <v>130255826</v>
       </c>
       <c r="B107" t="n">
-        <v>78966</v>
+        <v>79209</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11800,21 +11780,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11824,10 +11804,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>496827</v>
+        <v>496694</v>
       </c>
       <c r="R107" t="n">
-        <v>6827089</v>
+        <v>6827122</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11857,9 +11837,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11874,22 +11864,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>130256351</v>
+        <v>130255804</v>
       </c>
       <c r="B108" t="n">
-        <v>78966</v>
+        <v>79209</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11897,21 +11887,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11921,10 +11911,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>496898</v>
+        <v>497012</v>
       </c>
       <c r="R108" t="n">
-        <v>6827000</v>
+        <v>6826898</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11954,9 +11944,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11971,19 +11971,19 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>130255819</v>
+        <v>130256374</v>
       </c>
       <c r="B109" t="n">
         <v>79209</v>
@@ -12018,10 +12018,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>496850</v>
+        <v>496863</v>
       </c>
       <c r="R109" t="n">
-        <v>6827090</v>
+        <v>6827047</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12051,19 +12051,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z109" t="inlineStr">
-        <is>
-          <t>11:05</t>
-        </is>
-      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB109" t="inlineStr">
-        <is>
-          <t>11:05</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12078,19 +12068,19 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>130256374</v>
+        <v>130256360</v>
       </c>
       <c r="B110" t="n">
         <v>79209</v>
@@ -12125,10 +12115,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>496863</v>
+        <v>496972</v>
       </c>
       <c r="R110" t="n">
-        <v>6827047</v>
+        <v>6826953</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12187,7 +12177,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>130256386</v>
+        <v>130255819</v>
       </c>
       <c r="B111" t="n">
         <v>79209</v>
@@ -12222,10 +12212,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>496723</v>
+        <v>496850</v>
       </c>
       <c r="R111" t="n">
-        <v>6827125</v>
+        <v>6827090</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12255,9 +12245,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12272,22 +12272,22 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>130256354</v>
+        <v>130256386</v>
       </c>
       <c r="B112" t="n">
-        <v>78966</v>
+        <v>79209</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12295,21 +12295,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12319,10 +12319,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>496654</v>
+        <v>496723</v>
       </c>
       <c r="R112" t="n">
-        <v>6827171</v>
+        <v>6827125</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12381,10 +12381,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>130256360</v>
+        <v>130256354</v>
       </c>
       <c r="B113" t="n">
-        <v>79209</v>
+        <v>78966</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12392,21 +12392,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12416,10 +12416,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>496972</v>
+        <v>496654</v>
       </c>
       <c r="R113" t="n">
-        <v>6826953</v>
+        <v>6827171</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12588,7 +12588,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>130255802</v>
+        <v>130256380</v>
       </c>
       <c r="B115" t="n">
         <v>79209</v>
@@ -12623,10 +12623,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>496785</v>
+        <v>496852</v>
       </c>
       <c r="R115" t="n">
-        <v>6827060</v>
+        <v>6827074</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12656,19 +12656,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z115" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB115" t="inlineStr">
-        <is>
-          <t>12:47</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12683,19 +12673,19 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>130256380</v>
+        <v>130255802</v>
       </c>
       <c r="B116" t="n">
         <v>79209</v>
@@ -12730,10 +12720,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>496852</v>
+        <v>496785</v>
       </c>
       <c r="R116" t="n">
-        <v>6827074</v>
+        <v>6827060</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12763,9 +12753,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12780,12 +12780,12 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
@@ -12889,45 +12889,54 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>130256359</v>
+        <v>130256348</v>
       </c>
       <c r="B118" t="n">
-        <v>79209</v>
+        <v>8451</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>496963</v>
+        <v>496864</v>
       </c>
       <c r="R118" t="n">
-        <v>6826942</v>
+        <v>6827043</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12968,6 +12977,7 @@
       <c r="AE118" t="b">
         <v>0</v>
       </c>
+      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
@@ -12986,10 +12996,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>130255796</v>
+        <v>130256390</v>
       </c>
       <c r="B119" t="n">
-        <v>78966</v>
+        <v>79209</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12997,21 +13007,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13021,10 +13031,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>497111</v>
+        <v>496581</v>
       </c>
       <c r="R119" t="n">
-        <v>6826644</v>
+        <v>6827049</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13054,19 +13064,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z119" t="inlineStr">
-        <is>
-          <t>12:13</t>
-        </is>
-      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB119" t="inlineStr">
-        <is>
-          <t>12:13</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13081,19 +13081,19 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>130255801</v>
+        <v>130256363</v>
       </c>
       <c r="B120" t="n">
         <v>79209</v>
@@ -13128,10 +13128,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>496702</v>
+        <v>496897</v>
       </c>
       <c r="R120" t="n">
-        <v>6827131</v>
+        <v>6827002</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13161,19 +13161,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z120" t="inlineStr">
-        <is>
-          <t>10:39</t>
-        </is>
-      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB120" t="inlineStr">
-        <is>
-          <t>10:39</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13188,19 +13178,19 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>130256382</v>
+        <v>130256381</v>
       </c>
       <c r="B121" t="n">
         <v>79209</v>
@@ -13235,10 +13225,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>496831</v>
+        <v>496852</v>
       </c>
       <c r="R121" t="n">
-        <v>6827081</v>
+        <v>6827066</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13394,7 +13384,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>130256363</v>
+        <v>130256382</v>
       </c>
       <c r="B123" t="n">
         <v>79209</v>
@@ -13429,10 +13419,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>496897</v>
+        <v>496831</v>
       </c>
       <c r="R123" t="n">
-        <v>6827002</v>
+        <v>6827081</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13491,7 +13481,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>130256381</v>
+        <v>130256359</v>
       </c>
       <c r="B124" t="n">
         <v>79209</v>
@@ -13526,10 +13516,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>496852</v>
+        <v>496963</v>
       </c>
       <c r="R124" t="n">
-        <v>6827066</v>
+        <v>6826942</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13588,7 +13578,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>130256390</v>
+        <v>130255801</v>
       </c>
       <c r="B125" t="n">
         <v>79209</v>
@@ -13623,10 +13613,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>496581</v>
+        <v>496702</v>
       </c>
       <c r="R125" t="n">
-        <v>6827049</v>
+        <v>6827131</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13656,9 +13646,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13673,66 +13673,57 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>130256348</v>
+        <v>130255796</v>
       </c>
       <c r="B126" t="n">
-        <v>8451</v>
+        <v>78966</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr"/>
-      <c r="K126" t="inlineStr"/>
-      <c r="L126" t="inlineStr"/>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>496864</v>
+        <v>497111</v>
       </c>
       <c r="R126" t="n">
-        <v>6827043</v>
+        <v>6826644</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13762,30 +13753,39 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
       <c r="AD126" t="b">
         <v>0</v>
       </c>
       <c r="AE126" t="b">
         <v>0</v>
       </c>
-      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
@@ -14006,7 +14006,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>130256343</v>
+        <v>130255805</v>
       </c>
       <c r="B129" t="n">
         <v>79209</v>
@@ -14041,10 +14041,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>496851</v>
+        <v>497139</v>
       </c>
       <c r="R129" t="n">
-        <v>6827066</v>
+        <v>6826719</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14074,9 +14074,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14091,19 +14101,19 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>130255805</v>
+        <v>130256343</v>
       </c>
       <c r="B130" t="n">
         <v>79209</v>
@@ -14138,10 +14148,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>497139</v>
+        <v>496851</v>
       </c>
       <c r="R130" t="n">
-        <v>6826719</v>
+        <v>6827066</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14171,19 +14181,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z130" t="inlineStr">
-        <is>
-          <t>12:17</t>
-        </is>
-      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB130" t="inlineStr">
-        <is>
-          <t>12:17</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14198,22 +14198,22 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>130255793</v>
+        <v>130256392</v>
       </c>
       <c r="B131" t="n">
-        <v>8451</v>
+        <v>93040</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14221,43 +14221,34 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="J131" t="inlineStr"/>
-      <c r="K131" t="inlineStr"/>
-      <c r="L131" t="inlineStr"/>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>496670</v>
+        <v>496581</v>
       </c>
       <c r="R131" t="n">
-        <v>6827136</v>
+        <v>6827082</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14287,19 +14278,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z131" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB131" t="inlineStr">
-        <is>
-          <t>10:30</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14315,19 +14296,19 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>130256349</v>
+        <v>130255793</v>
       </c>
       <c r="B132" t="n">
         <v>8451</v>
@@ -14371,10 +14352,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>496714</v>
+        <v>496670</v>
       </c>
       <c r="R132" t="n">
-        <v>6827127</v>
+        <v>6827136</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14404,9 +14385,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB132" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14422,19 +14413,19 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>130256347</v>
+        <v>130256349</v>
       </c>
       <c r="B133" t="n">
         <v>8451</v>
@@ -14478,10 +14469,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>496941</v>
+        <v>496714</v>
       </c>
       <c r="R133" t="n">
-        <v>6826899</v>
+        <v>6827127</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14541,10 +14532,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>130256392</v>
+        <v>130256347</v>
       </c>
       <c r="B134" t="n">
-        <v>93039</v>
+        <v>8451</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14552,34 +14543,43 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>496581</v>
+        <v>496941</v>
       </c>
       <c r="R134" t="n">
-        <v>6827082</v>
+        <v>6826899</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14639,10 +14639,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>130256345</v>
+        <v>130255806</v>
       </c>
       <c r="B135" t="n">
-        <v>78967</v>
+        <v>79209</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14650,21 +14650,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14674,10 +14674,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>496837</v>
+        <v>497147</v>
       </c>
       <c r="R135" t="n">
-        <v>6827069</v>
+        <v>6826725</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14707,9 +14707,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB135" t="inlineStr">
+        <is>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14724,22 +14734,22 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>130256344</v>
+        <v>130255810</v>
       </c>
       <c r="B136" t="n">
-        <v>78967</v>
+        <v>79209</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14747,21 +14757,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14771,10 +14781,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>496869</v>
+        <v>497191</v>
       </c>
       <c r="R136" t="n">
-        <v>6827038</v>
+        <v>6826663</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14804,9 +14814,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB136" t="inlineStr">
+        <is>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14821,12 +14841,12 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
@@ -14940,10 +14960,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>130255806</v>
+        <v>130256345</v>
       </c>
       <c r="B138" t="n">
-        <v>79209</v>
+        <v>78967</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14951,21 +14971,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14975,10 +14995,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>497147</v>
+        <v>496837</v>
       </c>
       <c r="R138" t="n">
-        <v>6826725</v>
+        <v>6827069</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15008,19 +15028,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z138" t="inlineStr">
-        <is>
-          <t>12:17</t>
-        </is>
-      </c>
       <c r="AA138" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB138" t="inlineStr">
-        <is>
-          <t>12:17</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15035,22 +15045,22 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>130255810</v>
+        <v>130256344</v>
       </c>
       <c r="B139" t="n">
-        <v>79209</v>
+        <v>78967</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15058,21 +15068,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15082,10 +15092,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>497191</v>
+        <v>496869</v>
       </c>
       <c r="R139" t="n">
-        <v>6826663</v>
+        <v>6827038</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15115,19 +15125,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z139" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB139" t="inlineStr">
-        <is>
-          <t>12:06</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15142,12 +15142,12 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
@@ -15448,7 +15448,7 @@
         <v>130256394</v>
       </c>
       <c r="B143" t="n">
-        <v>93039</v>
+        <v>93040</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15554,7 +15554,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>130256355</v>
+        <v>130256364</v>
       </c>
       <c r="B144" t="n">
         <v>79209</v>
@@ -15589,10 +15589,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>496940</v>
+        <v>496909</v>
       </c>
       <c r="R144" t="n">
-        <v>6826898</v>
+        <v>6827002</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15651,7 +15651,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>130256364</v>
+        <v>130256355</v>
       </c>
       <c r="B145" t="n">
         <v>79209</v>
@@ -15686,10 +15686,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>496909</v>
+        <v>496940</v>
       </c>
       <c r="R145" t="n">
-        <v>6827002</v>
+        <v>6826898</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15952,7 +15952,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>130256362</v>
+        <v>130255821</v>
       </c>
       <c r="B148" t="n">
         <v>79209</v>
@@ -15987,10 +15987,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>496893</v>
+        <v>496839</v>
       </c>
       <c r="R148" t="n">
-        <v>6826998</v>
+        <v>6827082</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16020,9 +16020,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z148" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB148" t="inlineStr">
+        <is>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16037,19 +16047,19 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>130255821</v>
+        <v>130256362</v>
       </c>
       <c r="B149" t="n">
         <v>79209</v>
@@ -16084,10 +16094,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>496839</v>
+        <v>496893</v>
       </c>
       <c r="R149" t="n">
-        <v>6827082</v>
+        <v>6826998</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16117,19 +16127,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z149" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AA149" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB149" t="inlineStr">
-        <is>
-          <t>11:04</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16144,12 +16144,12 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
@@ -16467,7 +16467,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>130255824</v>
+        <v>130256372</v>
       </c>
       <c r="B153" t="n">
         <v>79209</v>
@@ -16502,10 +16502,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>496752</v>
+        <v>496867</v>
       </c>
       <c r="R153" t="n">
-        <v>6827114</v>
+        <v>6827035</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16535,19 +16535,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z153" t="inlineStr">
-        <is>
-          <t>10:49</t>
-        </is>
-      </c>
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB153" t="inlineStr">
-        <is>
-          <t>10:49</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16562,19 +16552,19 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>130256372</v>
+        <v>130255824</v>
       </c>
       <c r="B154" t="n">
         <v>79209</v>
@@ -16609,10 +16599,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>496867</v>
+        <v>496752</v>
       </c>
       <c r="R154" t="n">
-        <v>6827035</v>
+        <v>6827114</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16642,9 +16632,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z154" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
       <c r="AA154" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB154" t="inlineStr">
+        <is>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16659,12 +16659,12 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
@@ -16674,7 +16674,7 @@
         <v>130255838</v>
       </c>
       <c r="B155" t="n">
-        <v>93039</v>
+        <v>93040</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16875,32 +16875,32 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>130255829</v>
+        <v>130256393</v>
       </c>
       <c r="B157" t="n">
-        <v>79209</v>
+        <v>93040</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16910,10 +16910,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>496643</v>
+        <v>496647</v>
       </c>
       <c r="R157" t="n">
-        <v>6827146</v>
+        <v>6827158</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16943,19 +16943,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z157" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA157" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB157" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16970,19 +16960,19 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>130255816</v>
+        <v>130255809</v>
       </c>
       <c r="B158" t="n">
         <v>79209</v>
@@ -17017,10 +17007,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>496954</v>
+        <v>497168</v>
       </c>
       <c r="R158" t="n">
-        <v>6827096</v>
+        <v>6826596</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17052,7 +17042,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -17062,7 +17052,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17089,7 +17079,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>130255809</v>
+        <v>130255816</v>
       </c>
       <c r="B159" t="n">
         <v>79209</v>
@@ -17124,10 +17114,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>497168</v>
+        <v>496954</v>
       </c>
       <c r="R159" t="n">
-        <v>6826596</v>
+        <v>6827096</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17159,7 +17149,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -17169,7 +17159,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17196,32 +17186,32 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>130256393</v>
+        <v>130255829</v>
       </c>
       <c r="B160" t="n">
-        <v>93039</v>
+        <v>79209</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17231,10 +17221,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>496647</v>
+        <v>496643</v>
       </c>
       <c r="R160" t="n">
-        <v>6827158</v>
+        <v>6827146</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17264,9 +17254,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z160" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB160" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17281,12 +17281,12 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>

--- a/artfynd/A 58895-2025 artfynd.xlsx
+++ b/artfynd/A 58895-2025 artfynd.xlsx
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130252584</v>
+        <v>130252591</v>
       </c>
       <c r="B3" t="n">
-        <v>58011</v>
+        <v>78966</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,21 +801,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497202</v>
+        <v>496966</v>
       </c>
       <c r="R3" t="n">
-        <v>6826919</v>
+        <v>6826906</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,32 +897,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130252120</v>
+        <v>130252116</v>
       </c>
       <c r="B4" t="n">
-        <v>8451</v>
+        <v>79828</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>496653</v>
+        <v>496721</v>
       </c>
       <c r="R4" t="n">
-        <v>6827111</v>
+        <v>6827083</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -967,7 +967,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1007,7 +1007,7 @@
         <v>130252155</v>
       </c>
       <c r="B5" t="n">
-        <v>93040</v>
+        <v>93041</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,10 +1111,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130252116</v>
+        <v>130252584</v>
       </c>
       <c r="B6" t="n">
-        <v>79828</v>
+        <v>58011</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1122,34 +1122,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>496721</v>
+        <v>497202</v>
       </c>
       <c r="R6" t="n">
-        <v>6827083</v>
+        <v>6826919</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1206,57 +1206,57 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130252591</v>
+        <v>130252120</v>
       </c>
       <c r="B7" t="n">
-        <v>78966</v>
+        <v>8451</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>496966</v>
+        <v>496653</v>
       </c>
       <c r="R7" t="n">
-        <v>6826906</v>
+        <v>6827111</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1313,12 +1313,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1540,32 +1540,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130252156</v>
+        <v>130252138</v>
       </c>
       <c r="B10" t="n">
-        <v>93040</v>
+        <v>79209</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1575,10 +1575,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>496675</v>
+        <v>497207</v>
       </c>
       <c r="R10" t="n">
-        <v>6827138</v>
+        <v>6826726</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1968,32 +1968,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130252138</v>
+        <v>130252156</v>
       </c>
       <c r="B14" t="n">
-        <v>79209</v>
+        <v>93041</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2003,10 +2003,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>497207</v>
+        <v>496675</v>
       </c>
       <c r="R14" t="n">
-        <v>6826726</v>
+        <v>6827138</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2038,7 +2038,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2078,7 +2078,7 @@
         <v>130252154</v>
       </c>
       <c r="B15" t="n">
-        <v>93040</v>
+        <v>93041</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2396,32 +2396,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130252123</v>
+        <v>130252125</v>
       </c>
       <c r="B18" t="n">
-        <v>8451</v>
+        <v>78966</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2431,10 +2431,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>496581</v>
+        <v>497154</v>
       </c>
       <c r="R18" t="n">
-        <v>6827019</v>
+        <v>6826854</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2476,7 +2476,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2503,10 +2503,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130252594</v>
+        <v>130252603</v>
       </c>
       <c r="B19" t="n">
-        <v>78966</v>
+        <v>79209</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2514,21 +2514,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2538,10 +2538,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>496874</v>
+        <v>496694</v>
       </c>
       <c r="R19" t="n">
-        <v>6827149</v>
+        <v>6827132</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2610,10 +2610,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130252125</v>
+        <v>130252145</v>
       </c>
       <c r="B20" t="n">
-        <v>78966</v>
+        <v>79209</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,21 +2621,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2645,10 +2645,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>497154</v>
+        <v>496870</v>
       </c>
       <c r="R20" t="n">
-        <v>6826854</v>
+        <v>6827056</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2717,10 +2717,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130252603</v>
+        <v>130252594</v>
       </c>
       <c r="B21" t="n">
-        <v>79209</v>
+        <v>78966</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2728,21 +2728,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2752,10 +2752,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>496694</v>
+        <v>496874</v>
       </c>
       <c r="R21" t="n">
-        <v>6827132</v>
+        <v>6827149</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2824,32 +2824,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130252145</v>
+        <v>130252123</v>
       </c>
       <c r="B22" t="n">
-        <v>79209</v>
+        <v>8451</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2859,10 +2859,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>496870</v>
+        <v>496581</v>
       </c>
       <c r="R22" t="n">
-        <v>6827056</v>
+        <v>6827019</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2904,7 +2904,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2931,10 +2931,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130252124</v>
+        <v>130252142</v>
       </c>
       <c r="B23" t="n">
-        <v>78966</v>
+        <v>79209</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2942,21 +2942,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2966,10 +2966,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>497192</v>
+        <v>496939</v>
       </c>
       <c r="R23" t="n">
-        <v>6826651</v>
+        <v>6827036</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3011,7 +3011,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3038,10 +3038,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130252142</v>
+        <v>130252124</v>
       </c>
       <c r="B24" t="n">
-        <v>79209</v>
+        <v>78966</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3049,21 +3049,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3073,10 +3073,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>496939</v>
+        <v>497192</v>
       </c>
       <c r="R24" t="n">
-        <v>6827036</v>
+        <v>6826651</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3118,7 +3118,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3252,7 +3252,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130252127</v>
+        <v>130252595</v>
       </c>
       <c r="B26" t="n">
         <v>78966</v>
@@ -3283,14 +3283,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>496719</v>
+        <v>496894</v>
       </c>
       <c r="R26" t="n">
-        <v>6827076</v>
+        <v>6827123</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3322,7 +3322,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3347,19 +3347,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130252595</v>
+        <v>130252127</v>
       </c>
       <c r="B27" t="n">
         <v>78966</v>
@@ -3390,14 +3390,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>496894</v>
+        <v>496719</v>
       </c>
       <c r="R27" t="n">
-        <v>6827123</v>
+        <v>6827076</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3429,7 +3429,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3439,7 +3439,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3454,12 +3454,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3573,32 +3573,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130252157</v>
+        <v>130252129</v>
       </c>
       <c r="B29" t="n">
-        <v>93040</v>
+        <v>78966</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3608,10 +3608,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>496628</v>
+        <v>496646</v>
       </c>
       <c r="R29" t="n">
-        <v>6827124</v>
+        <v>6827139</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3643,7 +3643,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3680,10 +3680,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130252141</v>
+        <v>130252589</v>
       </c>
       <c r="B30" t="n">
-        <v>79209</v>
+        <v>78966</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3691,34 +3691,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>496956</v>
+        <v>497211</v>
       </c>
       <c r="R30" t="n">
-        <v>6827088</v>
+        <v>6826926</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3750,7 +3750,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3760,7 +3760,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3775,22 +3775,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130252129</v>
+        <v>130252141</v>
       </c>
       <c r="B31" t="n">
-        <v>78966</v>
+        <v>79209</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3798,21 +3798,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3822,10 +3822,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>496646</v>
+        <v>496956</v>
       </c>
       <c r="R31" t="n">
-        <v>6827139</v>
+        <v>6827088</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3857,7 +3857,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3867,7 +3867,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3894,45 +3894,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130252589</v>
+        <v>130252157</v>
       </c>
       <c r="B32" t="n">
-        <v>78966</v>
+        <v>93041</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>497211</v>
+        <v>496628</v>
       </c>
       <c r="R32" t="n">
-        <v>6826926</v>
+        <v>6827124</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3964,7 +3964,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3974,7 +3974,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3989,12 +3989,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4108,45 +4108,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130252135</v>
+        <v>130252587</v>
       </c>
       <c r="B34" t="n">
-        <v>79209</v>
+        <v>8451</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>496915</v>
+        <v>496719</v>
       </c>
       <c r="R34" t="n">
-        <v>6826903</v>
+        <v>6827112</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4203,19 +4203,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130252604</v>
+        <v>130252135</v>
       </c>
       <c r="B35" t="n">
         <v>79209</v>
@@ -4246,14 +4246,14 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>496679</v>
+        <v>496915</v>
       </c>
       <c r="R35" t="n">
-        <v>6827141</v>
+        <v>6826903</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4285,7 +4285,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4295,7 +4295,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4310,19 +4310,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130252146</v>
+        <v>130252604</v>
       </c>
       <c r="B36" t="n">
         <v>79209</v>
@@ -4353,14 +4353,14 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>496864</v>
+        <v>496679</v>
       </c>
       <c r="R36" t="n">
-        <v>6827053</v>
+        <v>6827141</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4417,19 +4417,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130252143</v>
+        <v>130252146</v>
       </c>
       <c r="B37" t="n">
         <v>79209</v>
@@ -4464,10 +4464,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>496877</v>
+        <v>496864</v>
       </c>
       <c r="R37" t="n">
-        <v>6827056</v>
+        <v>6827053</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4509,7 +4509,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4536,7 +4536,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130252605</v>
+        <v>130252143</v>
       </c>
       <c r="B38" t="n">
         <v>79209</v>
@@ -4567,14 +4567,14 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>496676</v>
+        <v>496877</v>
       </c>
       <c r="R38" t="n">
-        <v>6827143</v>
+        <v>6827056</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4631,44 +4631,44 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130252587</v>
+        <v>130252605</v>
       </c>
       <c r="B39" t="n">
-        <v>8451</v>
+        <v>79209</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4678,10 +4678,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>496719</v>
+        <v>496676</v>
       </c>
       <c r="R39" t="n">
-        <v>6827112</v>
+        <v>6827143</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4723,7 +4723,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4750,45 +4750,53 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130252158</v>
+        <v>130252585</v>
       </c>
       <c r="B40" t="n">
-        <v>93040</v>
+        <v>57849</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>496629</v>
+        <v>496635</v>
       </c>
       <c r="R40" t="n">
-        <v>6827128</v>
+        <v>6827130</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4820,7 +4828,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4830,7 +4838,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4845,44 +4853,44 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130252607</v>
+        <v>130252590</v>
       </c>
       <c r="B41" t="n">
-        <v>93040</v>
+        <v>78966</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4892,10 +4900,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>496598</v>
+        <v>496995</v>
       </c>
       <c r="R41" t="n">
-        <v>6827085</v>
+        <v>6826923</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4927,7 +4935,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4937,7 +4945,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4946,7 +4954,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4965,10 +4972,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130252128</v>
+        <v>130252136</v>
       </c>
       <c r="B42" t="n">
-        <v>78966</v>
+        <v>79209</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4976,21 +4983,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5000,10 +5007,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>496684</v>
+        <v>497002</v>
       </c>
       <c r="R42" t="n">
-        <v>6827129</v>
+        <v>6826879</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5035,7 +5042,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5045,7 +5052,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5072,7 +5079,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130252590</v>
+        <v>130252128</v>
       </c>
       <c r="B43" t="n">
         <v>78966</v>
@@ -5103,14 +5110,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>496995</v>
+        <v>496684</v>
       </c>
       <c r="R43" t="n">
-        <v>6826923</v>
+        <v>6827129</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5142,7 +5149,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5152,7 +5159,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5167,44 +5174,44 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130252136</v>
+        <v>130252158</v>
       </c>
       <c r="B44" t="n">
-        <v>79209</v>
+        <v>93041</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5214,10 +5221,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>497002</v>
+        <v>496629</v>
       </c>
       <c r="R44" t="n">
-        <v>6826879</v>
+        <v>6827128</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5249,7 +5256,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5259,7 +5266,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5286,53 +5293,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130252585</v>
+        <v>130252607</v>
       </c>
       <c r="B45" t="n">
-        <v>57849</v>
+        <v>93041</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>496635</v>
+        <v>496598</v>
       </c>
       <c r="R45" t="n">
-        <v>6827130</v>
+        <v>6827085</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5364,7 +5363,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5374,7 +5373,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5383,6 +5382,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5401,32 +5401,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130252598</v>
+        <v>130252609</v>
       </c>
       <c r="B46" t="n">
-        <v>79209</v>
+        <v>93041</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5436,10 +5436,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>497202</v>
+        <v>496549</v>
       </c>
       <c r="R46" t="n">
-        <v>6826911</v>
+        <v>6826988</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5471,7 +5471,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5490,6 +5490,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5508,7 +5509,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130252602</v>
+        <v>130252598</v>
       </c>
       <c r="B47" t="n">
         <v>79209</v>
@@ -5543,10 +5544,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>496722</v>
+        <v>497202</v>
       </c>
       <c r="R47" t="n">
-        <v>6827107</v>
+        <v>6826911</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5578,7 +5579,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5588,7 +5589,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5615,7 +5616,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130252153</v>
+        <v>130252602</v>
       </c>
       <c r="B48" t="n">
         <v>79209</v>
@@ -5646,14 +5647,14 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>496564</v>
+        <v>496722</v>
       </c>
       <c r="R48" t="n">
-        <v>6827012</v>
+        <v>6827107</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5685,7 +5686,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5695,7 +5696,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5710,57 +5711,57 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130252609</v>
+        <v>130252153</v>
       </c>
       <c r="B49" t="n">
-        <v>93040</v>
+        <v>79209</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>496549</v>
+        <v>496564</v>
       </c>
       <c r="R49" t="n">
-        <v>6826988</v>
+        <v>6827012</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5792,7 +5793,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5802,7 +5803,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5811,19 +5812,18 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -6388,45 +6388,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130252606</v>
+        <v>130252117</v>
       </c>
       <c r="B55" t="n">
-        <v>93040</v>
+        <v>79799</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>496618</v>
+        <v>497155</v>
       </c>
       <c r="R55" t="n">
-        <v>6827114</v>
+        <v>6826856</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6458,7 +6458,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6468,7 +6468,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6477,19 +6477,18 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6603,10 +6602,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130252117</v>
+        <v>130252137</v>
       </c>
       <c r="B57" t="n">
-        <v>79799</v>
+        <v>79209</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6614,21 +6613,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6638,10 +6637,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>497155</v>
+        <v>497206</v>
       </c>
       <c r="R57" t="n">
-        <v>6826856</v>
+        <v>6826638</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6673,7 +6672,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6683,7 +6682,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6710,45 +6709,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130252137</v>
+        <v>130252606</v>
       </c>
       <c r="B58" t="n">
-        <v>79209</v>
+        <v>93041</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>497206</v>
+        <v>496618</v>
       </c>
       <c r="R58" t="n">
-        <v>6826638</v>
+        <v>6827114</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6780,7 +6779,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6790,7 +6789,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6799,18 +6798,19 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -7460,45 +7460,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130252608</v>
+        <v>130252139</v>
       </c>
       <c r="B65" t="n">
-        <v>93040</v>
+        <v>79209</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>496576</v>
+        <v>497225</v>
       </c>
       <c r="R65" t="n">
-        <v>6826998</v>
+        <v>6826804</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7549,26 +7549,25 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130252139</v>
+        <v>130252151</v>
       </c>
       <c r="B66" t="n">
         <v>79209</v>
@@ -7603,10 +7602,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>497225</v>
+        <v>496704</v>
       </c>
       <c r="R66" t="n">
-        <v>6826804</v>
+        <v>6827086</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7638,7 +7637,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7648,7 +7647,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7675,7 +7674,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130252151</v>
+        <v>130252597</v>
       </c>
       <c r="B67" t="n">
         <v>79209</v>
@@ -7706,14 +7705,14 @@
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>496704</v>
+        <v>496922</v>
       </c>
       <c r="R67" t="n">
-        <v>6827086</v>
+        <v>6826906</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7745,7 +7744,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7755,7 +7754,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7770,44 +7769,44 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130252597</v>
+        <v>130252608</v>
       </c>
       <c r="B68" t="n">
-        <v>79209</v>
+        <v>93041</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7817,10 +7816,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>496922</v>
+        <v>496576</v>
       </c>
       <c r="R68" t="n">
-        <v>6826906</v>
+        <v>6826998</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7852,7 +7851,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7862,7 +7861,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7871,6 +7870,7 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8291,7 +8291,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130255817</v>
+        <v>130255830</v>
       </c>
       <c r="B73" t="n">
         <v>79209</v>
@@ -8326,10 +8326,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>496872</v>
+        <v>496649</v>
       </c>
       <c r="R73" t="n">
-        <v>6827052</v>
+        <v>6827117</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8361,7 +8361,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8371,7 +8371,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8398,7 +8398,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130255832</v>
+        <v>130255820</v>
       </c>
       <c r="B74" t="n">
         <v>79209</v>
@@ -8433,10 +8433,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>496578</v>
+        <v>496838</v>
       </c>
       <c r="R74" t="n">
-        <v>6827044</v>
+        <v>6827085</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8468,7 +8468,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8478,7 +8478,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8505,7 +8505,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130256369</v>
+        <v>130255817</v>
       </c>
       <c r="B75" t="n">
         <v>79209</v>
@@ -8540,10 +8540,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>496893</v>
+        <v>496872</v>
       </c>
       <c r="R75" t="n">
-        <v>6827043</v>
+        <v>6827052</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8573,9 +8573,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8590,19 +8600,19 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>130255830</v>
+        <v>130255832</v>
       </c>
       <c r="B76" t="n">
         <v>79209</v>
@@ -8637,10 +8647,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>496649</v>
+        <v>496578</v>
       </c>
       <c r="R76" t="n">
-        <v>6827117</v>
+        <v>6827044</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8672,7 +8682,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8682,7 +8692,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8709,7 +8719,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>130255820</v>
+        <v>130256369</v>
       </c>
       <c r="B77" t="n">
         <v>79209</v>
@@ -8744,10 +8754,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>496838</v>
+        <v>496893</v>
       </c>
       <c r="R77" t="n">
-        <v>6827085</v>
+        <v>6827043</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8777,19 +8787,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>11:04</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8804,22 +8804,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>130255797</v>
+        <v>130256383</v>
       </c>
       <c r="B78" t="n">
-        <v>78966</v>
+        <v>79209</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8827,21 +8827,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8851,10 +8851,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>497218</v>
+        <v>496821</v>
       </c>
       <c r="R78" t="n">
-        <v>6826761</v>
+        <v>6827087</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8884,19 +8884,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>11:59</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>11:59</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8911,19 +8901,19 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>130256383</v>
+        <v>130256365</v>
       </c>
       <c r="B79" t="n">
         <v>79209</v>
@@ -8958,10 +8948,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>496821</v>
+        <v>496920</v>
       </c>
       <c r="R79" t="n">
-        <v>6827087</v>
+        <v>6827003</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9020,10 +9010,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>130256365</v>
+        <v>130255797</v>
       </c>
       <c r="B80" t="n">
-        <v>79209</v>
+        <v>78966</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9031,21 +9021,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9055,10 +9045,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>496920</v>
+        <v>497218</v>
       </c>
       <c r="R80" t="n">
-        <v>6827003</v>
+        <v>6826761</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9088,9 +9078,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9105,12 +9105,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
@@ -9311,10 +9311,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>130255837</v>
+        <v>130256346</v>
       </c>
       <c r="B83" t="n">
-        <v>79209</v>
+        <v>78967</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9322,21 +9322,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9346,10 +9346,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>497191</v>
+        <v>496652</v>
       </c>
       <c r="R83" t="n">
-        <v>6826771</v>
+        <v>6827164</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9379,19 +9379,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>12:00</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9406,22 +9396,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>130256346</v>
+        <v>130255837</v>
       </c>
       <c r="B84" t="n">
-        <v>78967</v>
+        <v>79209</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9429,21 +9419,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9453,10 +9443,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>496652</v>
+        <v>497191</v>
       </c>
       <c r="R84" t="n">
-        <v>6827164</v>
+        <v>6826771</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9486,9 +9476,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9503,44 +9503,44 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>130255839</v>
+        <v>130256352</v>
       </c>
       <c r="B85" t="n">
-        <v>93040</v>
+        <v>78966</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9550,10 +9550,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>496787</v>
+        <v>496837</v>
       </c>
       <c r="R85" t="n">
-        <v>6827052</v>
+        <v>6827069</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9583,19 +9583,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9610,44 +9600,44 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>130256352</v>
+        <v>130255839</v>
       </c>
       <c r="B86" t="n">
-        <v>78966</v>
+        <v>93041</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9657,10 +9647,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>496837</v>
+        <v>496787</v>
       </c>
       <c r="R86" t="n">
-        <v>6827069</v>
+        <v>6827052</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9690,9 +9680,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9707,12 +9707,12 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
@@ -10244,10 +10244,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>130255798</v>
+        <v>130255808</v>
       </c>
       <c r="B92" t="n">
-        <v>78966</v>
+        <v>79209</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10255,21 +10255,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10279,10 +10279,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>496740</v>
+        <v>497167</v>
       </c>
       <c r="R92" t="n">
-        <v>6827145</v>
+        <v>6826594</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10314,7 +10314,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10324,7 +10324,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10448,10 +10448,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>130255808</v>
+        <v>130255798</v>
       </c>
       <c r="B94" t="n">
-        <v>79209</v>
+        <v>78966</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10459,21 +10459,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10483,10 +10483,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>497167</v>
+        <v>496740</v>
       </c>
       <c r="R94" t="n">
-        <v>6826594</v>
+        <v>6827145</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10518,7 +10518,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10528,7 +10528,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10856,10 +10856,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>130255807</v>
+        <v>130256350</v>
       </c>
       <c r="B98" t="n">
-        <v>79209</v>
+        <v>78966</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10867,21 +10867,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10891,10 +10891,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>497130</v>
+        <v>496962</v>
       </c>
       <c r="R98" t="n">
-        <v>6826601</v>
+        <v>6826909</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10924,19 +10924,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z98" t="inlineStr">
-        <is>
-          <t>12:11</t>
-        </is>
-      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t>12:11</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10951,19 +10941,19 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>130255812</v>
+        <v>130255807</v>
       </c>
       <c r="B99" t="n">
         <v>79209</v>
@@ -10998,10 +10988,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>497186</v>
+        <v>497130</v>
       </c>
       <c r="R99" t="n">
-        <v>6826839</v>
+        <v>6826601</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11033,7 +11023,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11043,7 +11033,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11070,7 +11060,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>130256391</v>
+        <v>130255812</v>
       </c>
       <c r="B100" t="n">
         <v>79209</v>
@@ -11105,10 +11095,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>496588</v>
+        <v>497186</v>
       </c>
       <c r="R100" t="n">
-        <v>6827066</v>
+        <v>6826839</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11138,9 +11128,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11155,19 +11155,19 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>130256375</v>
+        <v>130256391</v>
       </c>
       <c r="B101" t="n">
         <v>79209</v>
@@ -11202,10 +11202,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>496859</v>
+        <v>496588</v>
       </c>
       <c r="R101" t="n">
-        <v>6827052</v>
+        <v>6827066</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11264,7 +11264,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>130255825</v>
+        <v>130256375</v>
       </c>
       <c r="B102" t="n">
         <v>79209</v>
@@ -11299,10 +11299,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>496759</v>
+        <v>496859</v>
       </c>
       <c r="R102" t="n">
-        <v>6827133</v>
+        <v>6827052</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11332,19 +11332,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z102" t="inlineStr">
-        <is>
-          <t>10:48</t>
-        </is>
-      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB102" t="inlineStr">
-        <is>
-          <t>10:48</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11359,22 +11349,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>130256350</v>
+        <v>130255825</v>
       </c>
       <c r="B103" t="n">
-        <v>78966</v>
+        <v>79209</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11382,21 +11372,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11406,10 +11396,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>496962</v>
+        <v>496759</v>
       </c>
       <c r="R103" t="n">
-        <v>6826909</v>
+        <v>6827133</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11439,9 +11429,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11456,12 +11456,12 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
@@ -11672,10 +11672,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>130256353</v>
+        <v>130255826</v>
       </c>
       <c r="B106" t="n">
-        <v>78966</v>
+        <v>79209</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11683,21 +11683,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11707,10 +11707,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>496827</v>
+        <v>496694</v>
       </c>
       <c r="R106" t="n">
-        <v>6827089</v>
+        <v>6827122</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11740,9 +11740,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11757,22 +11767,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>130255826</v>
+        <v>130256353</v>
       </c>
       <c r="B107" t="n">
-        <v>79209</v>
+        <v>78966</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11780,21 +11790,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11804,10 +11814,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>496694</v>
+        <v>496827</v>
       </c>
       <c r="R107" t="n">
-        <v>6827122</v>
+        <v>6827089</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11837,19 +11847,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z107" t="inlineStr">
-        <is>
-          <t>10:34</t>
-        </is>
-      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB107" t="inlineStr">
-        <is>
-          <t>10:34</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11864,12 +11864,12 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
@@ -11983,10 +11983,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>130256374</v>
+        <v>130256342</v>
       </c>
       <c r="B109" t="n">
-        <v>79209</v>
+        <v>57852</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11994,34 +11994,42 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>496863</v>
+        <v>496940</v>
       </c>
       <c r="R109" t="n">
-        <v>6827047</v>
+        <v>6826899</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12054,6 +12062,11 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12080,7 +12093,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>130256360</v>
+        <v>130256374</v>
       </c>
       <c r="B110" t="n">
         <v>79209</v>
@@ -12115,10 +12128,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>496972</v>
+        <v>496863</v>
       </c>
       <c r="R110" t="n">
-        <v>6826953</v>
+        <v>6827047</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12177,7 +12190,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>130255819</v>
+        <v>130256360</v>
       </c>
       <c r="B111" t="n">
         <v>79209</v>
@@ -12212,10 +12225,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>496850</v>
+        <v>496972</v>
       </c>
       <c r="R111" t="n">
-        <v>6827090</v>
+        <v>6826953</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12245,19 +12258,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z111" t="inlineStr">
-        <is>
-          <t>11:05</t>
-        </is>
-      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB111" t="inlineStr">
-        <is>
-          <t>11:05</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12272,22 +12275,22 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>130256386</v>
+        <v>130256354</v>
       </c>
       <c r="B112" t="n">
-        <v>79209</v>
+        <v>78966</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12295,21 +12298,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12319,10 +12322,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>496723</v>
+        <v>496654</v>
       </c>
       <c r="R112" t="n">
-        <v>6827125</v>
+        <v>6827171</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12381,10 +12384,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>130256354</v>
+        <v>130255819</v>
       </c>
       <c r="B113" t="n">
-        <v>78966</v>
+        <v>79209</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12392,21 +12395,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12416,10 +12419,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>496654</v>
+        <v>496850</v>
       </c>
       <c r="R113" t="n">
-        <v>6827171</v>
+        <v>6827090</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12449,9 +12452,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12466,22 +12479,22 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>130256342</v>
+        <v>130256386</v>
       </c>
       <c r="B114" t="n">
-        <v>57852</v>
+        <v>79209</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12489,42 +12502,34 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>496940</v>
+        <v>496723</v>
       </c>
       <c r="R114" t="n">
-        <v>6826899</v>
+        <v>6827125</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12557,11 +12562,6 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12889,54 +12889,45 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>130256348</v>
+        <v>130255801</v>
       </c>
       <c r="B118" t="n">
-        <v>8451</v>
+        <v>79209</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="J118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>496864</v>
+        <v>496702</v>
       </c>
       <c r="R118" t="n">
-        <v>6827043</v>
+        <v>6827131</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12966,75 +12957,93 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
       <c r="AD118" t="b">
         <v>0</v>
       </c>
       <c r="AE118" t="b">
         <v>0</v>
       </c>
-      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>130256390</v>
+        <v>130256348</v>
       </c>
       <c r="B119" t="n">
-        <v>79209</v>
+        <v>8451</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>496581</v>
+        <v>496864</v>
       </c>
       <c r="R119" t="n">
-        <v>6827049</v>
+        <v>6827043</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13075,6 +13084,7 @@
       <c r="AE119" t="b">
         <v>0</v>
       </c>
+      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
       </c>
@@ -13093,7 +13103,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>130256363</v>
+        <v>130256390</v>
       </c>
       <c r="B120" t="n">
         <v>79209</v>
@@ -13128,10 +13138,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>496897</v>
+        <v>496581</v>
       </c>
       <c r="R120" t="n">
-        <v>6827002</v>
+        <v>6827049</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13190,7 +13200,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>130256381</v>
+        <v>130256363</v>
       </c>
       <c r="B121" t="n">
         <v>79209</v>
@@ -13225,10 +13235,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>496852</v>
+        <v>496897</v>
       </c>
       <c r="R121" t="n">
-        <v>6827066</v>
+        <v>6827002</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13287,7 +13297,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>130256378</v>
+        <v>130256381</v>
       </c>
       <c r="B122" t="n">
         <v>79209</v>
@@ -13322,10 +13332,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>496862</v>
+        <v>496852</v>
       </c>
       <c r="R122" t="n">
-        <v>6827064</v>
+        <v>6827066</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13384,10 +13394,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>130256382</v>
+        <v>130255796</v>
       </c>
       <c r="B123" t="n">
-        <v>79209</v>
+        <v>78966</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13395,21 +13405,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13419,10 +13429,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>496831</v>
+        <v>497111</v>
       </c>
       <c r="R123" t="n">
-        <v>6827081</v>
+        <v>6826644</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13452,9 +13462,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13469,19 +13489,19 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>130256359</v>
+        <v>130256378</v>
       </c>
       <c r="B124" t="n">
         <v>79209</v>
@@ -13516,10 +13536,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>496963</v>
+        <v>496862</v>
       </c>
       <c r="R124" t="n">
-        <v>6826942</v>
+        <v>6827064</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13578,7 +13598,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>130255801</v>
+        <v>130256382</v>
       </c>
       <c r="B125" t="n">
         <v>79209</v>
@@ -13613,10 +13633,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>496702</v>
+        <v>496831</v>
       </c>
       <c r="R125" t="n">
-        <v>6827131</v>
+        <v>6827081</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13646,19 +13666,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z125" t="inlineStr">
-        <is>
-          <t>10:39</t>
-        </is>
-      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB125" t="inlineStr">
-        <is>
-          <t>10:39</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13673,22 +13683,22 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>130255796</v>
+        <v>130256359</v>
       </c>
       <c r="B126" t="n">
-        <v>78966</v>
+        <v>79209</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13696,21 +13706,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13720,10 +13730,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>497111</v>
+        <v>496963</v>
       </c>
       <c r="R126" t="n">
-        <v>6826644</v>
+        <v>6826942</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13753,19 +13763,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z126" t="inlineStr">
-        <is>
-          <t>12:13</t>
-        </is>
-      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB126" t="inlineStr">
-        <is>
-          <t>12:13</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13780,44 +13780,44 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>130255834</v>
+        <v>130256392</v>
       </c>
       <c r="B127" t="n">
-        <v>79209</v>
+        <v>93041</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13827,10 +13827,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>496582</v>
+        <v>496581</v>
       </c>
       <c r="R127" t="n">
-        <v>6827040</v>
+        <v>6827082</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13860,46 +13860,37 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z127" t="inlineStr">
-        <is>
-          <t>10:10</t>
-        </is>
-      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="AB127" t="inlineStr">
-        <is>
-          <t>10:10</t>
-        </is>
-      </c>
       <c r="AD127" t="b">
         <v>0</v>
       </c>
       <c r="AE127" t="b">
         <v>0</v>
       </c>
+      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>130255836</v>
+        <v>130255834</v>
       </c>
       <c r="B128" t="n">
         <v>79209</v>
@@ -13934,10 +13925,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>497183</v>
+        <v>496582</v>
       </c>
       <c r="R128" t="n">
-        <v>6826662</v>
+        <v>6827040</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13969,7 +13960,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -13979,7 +13970,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14006,7 +13997,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>130255805</v>
+        <v>130255836</v>
       </c>
       <c r="B129" t="n">
         <v>79209</v>
@@ -14041,10 +14032,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>497139</v>
+        <v>497183</v>
       </c>
       <c r="R129" t="n">
-        <v>6826719</v>
+        <v>6826662</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14076,7 +14067,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -14086,7 +14077,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14113,7 +14104,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>130256343</v>
+        <v>130255805</v>
       </c>
       <c r="B130" t="n">
         <v>79209</v>
@@ -14148,10 +14139,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>496851</v>
+        <v>497139</v>
       </c>
       <c r="R130" t="n">
-        <v>6827066</v>
+        <v>6826719</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14181,9 +14172,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14198,44 +14199,44 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>130256392</v>
+        <v>130256343</v>
       </c>
       <c r="B131" t="n">
-        <v>93040</v>
+        <v>79209</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14245,10 +14246,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>496581</v>
+        <v>496851</v>
       </c>
       <c r="R131" t="n">
-        <v>6827082</v>
+        <v>6827066</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14289,7 +14290,6 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
-      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
@@ -15154,7 +15154,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>130256358</v>
+        <v>130256389</v>
       </c>
       <c r="B140" t="n">
         <v>79209</v>
@@ -15189,10 +15189,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>496962</v>
+        <v>496578</v>
       </c>
       <c r="R140" t="n">
-        <v>6826923</v>
+        <v>6827076</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15251,7 +15251,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>130256361</v>
+        <v>130256358</v>
       </c>
       <c r="B141" t="n">
         <v>79209</v>
@@ -15286,10 +15286,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>496893</v>
+        <v>496962</v>
       </c>
       <c r="R141" t="n">
-        <v>6826989</v>
+        <v>6826923</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15348,7 +15348,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>130256389</v>
+        <v>130256361</v>
       </c>
       <c r="B142" t="n">
         <v>79209</v>
@@ -15383,10 +15383,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>496578</v>
+        <v>496893</v>
       </c>
       <c r="R142" t="n">
-        <v>6827076</v>
+        <v>6826989</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15445,56 +15445,45 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>130256394</v>
+        <v>130256355</v>
       </c>
       <c r="B143" t="n">
-        <v>93040</v>
+        <v>79209</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J143" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K143" t="inlineStr"/>
-      <c r="N143" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
           <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>496581</v>
+        <v>496940</v>
       </c>
       <c r="R143" t="n">
-        <v>6827079</v>
+        <v>6826898</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15535,7 +15524,6 @@
       <c r="AE143" t="b">
         <v>0</v>
       </c>
-      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>
@@ -15554,45 +15542,56 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>130256364</v>
+        <v>130256394</v>
       </c>
       <c r="B144" t="n">
-        <v>79209</v>
+        <v>93041</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr"/>
+      <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
           <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>496909</v>
+        <v>496581</v>
       </c>
       <c r="R144" t="n">
-        <v>6827002</v>
+        <v>6827079</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15633,6 +15632,7 @@
       <c r="AE144" t="b">
         <v>0</v>
       </c>
+      <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="b">
         <v>0</v>
       </c>
@@ -15651,10 +15651,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>130256355</v>
+        <v>130256340</v>
       </c>
       <c r="B145" t="n">
-        <v>79209</v>
+        <v>79799</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15662,21 +15662,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15686,10 +15686,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>496940</v>
+        <v>496774</v>
       </c>
       <c r="R145" t="n">
-        <v>6826898</v>
+        <v>6827067</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15748,7 +15748,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>130256371</v>
+        <v>130256364</v>
       </c>
       <c r="B146" t="n">
         <v>79209</v>
@@ -15783,10 +15783,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>496880</v>
+        <v>496909</v>
       </c>
       <c r="R146" t="n">
-        <v>6827036</v>
+        <v>6827002</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15845,7 +15845,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>130255828</v>
+        <v>130256371</v>
       </c>
       <c r="B147" t="n">
         <v>79209</v>
@@ -15880,10 +15880,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>496658</v>
+        <v>496880</v>
       </c>
       <c r="R147" t="n">
-        <v>6827133</v>
+        <v>6827036</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15913,19 +15913,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z147" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA147" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB147" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15940,19 +15930,19 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>130255821</v>
+        <v>130255828</v>
       </c>
       <c r="B148" t="n">
         <v>79209</v>
@@ -15987,10 +15977,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>496839</v>
+        <v>496658</v>
       </c>
       <c r="R148" t="n">
-        <v>6827082</v>
+        <v>6827133</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16022,7 +16012,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -16032,7 +16022,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16059,7 +16049,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>130256362</v>
+        <v>130255821</v>
       </c>
       <c r="B149" t="n">
         <v>79209</v>
@@ -16094,10 +16084,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>496893</v>
+        <v>496839</v>
       </c>
       <c r="R149" t="n">
-        <v>6826998</v>
+        <v>6827082</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16127,9 +16117,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z149" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AA149" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB149" t="inlineStr">
+        <is>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16144,22 +16144,22 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>130256340</v>
+        <v>130256362</v>
       </c>
       <c r="B150" t="n">
-        <v>79799</v>
+        <v>79209</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16167,21 +16167,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16191,10 +16191,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>496774</v>
+        <v>496893</v>
       </c>
       <c r="R150" t="n">
-        <v>6827067</v>
+        <v>6826998</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16253,7 +16253,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>130255811</v>
+        <v>130255831</v>
       </c>
       <c r="B151" t="n">
         <v>79209</v>
@@ -16288,10 +16288,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>497200</v>
+        <v>496599</v>
       </c>
       <c r="R151" t="n">
-        <v>6826832</v>
+        <v>6827121</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16323,7 +16323,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -16333,7 +16333,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16360,7 +16360,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>130255831</v>
+        <v>130255824</v>
       </c>
       <c r="B152" t="n">
         <v>79209</v>
@@ -16395,10 +16395,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>496599</v>
+        <v>496752</v>
       </c>
       <c r="R152" t="n">
-        <v>6827121</v>
+        <v>6827114</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16430,7 +16430,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -16440,7 +16440,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16467,7 +16467,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>130256372</v>
+        <v>130255811</v>
       </c>
       <c r="B153" t="n">
         <v>79209</v>
@@ -16502,10 +16502,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>496867</v>
+        <v>497200</v>
       </c>
       <c r="R153" t="n">
-        <v>6827035</v>
+        <v>6826832</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16535,9 +16535,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z153" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB153" t="inlineStr">
+        <is>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16552,19 +16562,19 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>130255824</v>
+        <v>130256372</v>
       </c>
       <c r="B154" t="n">
         <v>79209</v>
@@ -16599,10 +16609,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>496752</v>
+        <v>496867</v>
       </c>
       <c r="R154" t="n">
-        <v>6827114</v>
+        <v>6827035</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16632,19 +16642,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z154" t="inlineStr">
-        <is>
-          <t>10:49</t>
-        </is>
-      </c>
       <c r="AA154" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB154" t="inlineStr">
-        <is>
-          <t>10:49</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16659,44 +16659,44 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>130255838</v>
+        <v>130256385</v>
       </c>
       <c r="B155" t="n">
-        <v>93040</v>
+        <v>79209</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16706,10 +16706,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>496571</v>
+        <v>496747</v>
       </c>
       <c r="R155" t="n">
-        <v>6827076</v>
+        <v>6827065</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16739,19 +16739,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z155" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
       <c r="AA155" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB155" t="inlineStr">
-        <is>
-          <t>10:13</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16766,44 +16756,44 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>130256385</v>
+        <v>130255838</v>
       </c>
       <c r="B156" t="n">
-        <v>79209</v>
+        <v>93041</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16813,10 +16803,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>496747</v>
+        <v>496571</v>
       </c>
       <c r="R156" t="n">
-        <v>6827065</v>
+        <v>6827076</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16846,9 +16836,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z156" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB156" t="inlineStr">
+        <is>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16863,44 +16863,44 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>130256393</v>
+        <v>130255809</v>
       </c>
       <c r="B157" t="n">
-        <v>93040</v>
+        <v>79209</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16910,10 +16910,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>496647</v>
+        <v>497168</v>
       </c>
       <c r="R157" t="n">
-        <v>6827158</v>
+        <v>6826596</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16943,9 +16943,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
       <c r="AA157" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB157" t="inlineStr">
+        <is>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16960,19 +16970,19 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>130255809</v>
+        <v>130255816</v>
       </c>
       <c r="B158" t="n">
         <v>79209</v>
@@ -17007,10 +17017,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>497168</v>
+        <v>496954</v>
       </c>
       <c r="R158" t="n">
-        <v>6826596</v>
+        <v>6827096</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17042,7 +17052,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -17052,7 +17062,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17079,7 +17089,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>130255816</v>
+        <v>130255829</v>
       </c>
       <c r="B159" t="n">
         <v>79209</v>
@@ -17114,10 +17124,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>496954</v>
+        <v>496643</v>
       </c>
       <c r="R159" t="n">
-        <v>6827096</v>
+        <v>6827146</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17149,7 +17159,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -17159,7 +17169,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17186,32 +17196,32 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>130255829</v>
+        <v>130256393</v>
       </c>
       <c r="B160" t="n">
-        <v>79209</v>
+        <v>93041</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17221,10 +17231,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>496643</v>
+        <v>496647</v>
       </c>
       <c r="R160" t="n">
-        <v>6827146</v>
+        <v>6827158</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17254,19 +17264,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z160" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB160" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17281,12 +17281,12 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>

--- a/artfynd/A 58895-2025 artfynd.xlsx
+++ b/artfynd/A 58895-2025 artfynd.xlsx
@@ -790,45 +790,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130252591</v>
+        <v>130252155</v>
       </c>
       <c r="B3" t="n">
-        <v>78966</v>
+        <v>93043</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>496966</v>
+        <v>496725</v>
       </c>
       <c r="R3" t="n">
-        <v>6826906</v>
+        <v>6827084</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,22 +885,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130252116</v>
+        <v>130252584</v>
       </c>
       <c r="B4" t="n">
-        <v>79828</v>
+        <v>58013</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,34 +908,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>496721</v>
+        <v>497202</v>
       </c>
       <c r="R4" t="n">
-        <v>6827083</v>
+        <v>6826919</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -967,7 +967,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -992,57 +992,57 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130252155</v>
+        <v>130252591</v>
       </c>
       <c r="B5" t="n">
-        <v>93041</v>
+        <v>78968</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>496725</v>
+        <v>496966</v>
       </c>
       <c r="R5" t="n">
-        <v>6827084</v>
+        <v>6826906</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1099,22 +1099,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130252584</v>
+        <v>130252116</v>
       </c>
       <c r="B6" t="n">
-        <v>58011</v>
+        <v>79830</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1122,34 +1122,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>497202</v>
+        <v>496721</v>
       </c>
       <c r="R6" t="n">
-        <v>6826919</v>
+        <v>6827083</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1206,12 +1206,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1328,7 +1328,7 @@
         <v>130252132</v>
       </c>
       <c r="B8" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,32 +1432,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130252115</v>
+        <v>130252156</v>
       </c>
       <c r="B9" t="n">
-        <v>79241</v>
+        <v>93043</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>185</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>496555</v>
+        <v>496675</v>
       </c>
       <c r="R9" t="n">
-        <v>6826991</v>
+        <v>6827138</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1512,7 +1512,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,7 +1521,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1543,7 +1542,7 @@
         <v>130252138</v>
       </c>
       <c r="B10" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1650,7 +1649,7 @@
         <v>130252126</v>
       </c>
       <c r="B11" t="n">
-        <v>78966</v>
+        <v>78968</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1757,7 +1756,7 @@
         <v>130252592</v>
       </c>
       <c r="B12" t="n">
-        <v>78966</v>
+        <v>78968</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1864,7 +1863,7 @@
         <v>130252588</v>
       </c>
       <c r="B13" t="n">
-        <v>78966</v>
+        <v>78968</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1968,32 +1967,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130252156</v>
+        <v>130252115</v>
       </c>
       <c r="B14" t="n">
-        <v>93041</v>
+        <v>79243</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>185</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2003,10 +2002,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>496675</v>
+        <v>496555</v>
       </c>
       <c r="R14" t="n">
-        <v>6827138</v>
+        <v>6826991</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2038,7 +2037,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2048,7 +2047,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2057,6 +2056,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2075,32 +2075,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130252154</v>
+        <v>130252119</v>
       </c>
       <c r="B15" t="n">
-        <v>93041</v>
+        <v>58013</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2110,10 +2110,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>496692</v>
+        <v>496602</v>
       </c>
       <c r="R15" t="n">
-        <v>6827092</v>
+        <v>6827039</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2145,7 +2145,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2182,32 +2182,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130252119</v>
+        <v>130252154</v>
       </c>
       <c r="B16" t="n">
-        <v>58011</v>
+        <v>93043</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2217,10 +2217,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>496602</v>
+        <v>496692</v>
       </c>
       <c r="R16" t="n">
-        <v>6827039</v>
+        <v>6827092</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2396,10 +2396,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130252125</v>
+        <v>130252145</v>
       </c>
       <c r="B18" t="n">
-        <v>78966</v>
+        <v>79211</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2407,21 +2407,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2431,10 +2431,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>497154</v>
+        <v>496870</v>
       </c>
       <c r="R18" t="n">
-        <v>6826854</v>
+        <v>6827056</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2476,7 +2476,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2506,7 +2506,7 @@
         <v>130252603</v>
       </c>
       <c r="B19" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2610,10 +2610,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130252145</v>
+        <v>130252125</v>
       </c>
       <c r="B20" t="n">
-        <v>79209</v>
+        <v>78968</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,21 +2621,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2645,10 +2645,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>496870</v>
+        <v>497154</v>
       </c>
       <c r="R20" t="n">
-        <v>6827056</v>
+        <v>6826854</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2720,7 +2720,7 @@
         <v>130252594</v>
       </c>
       <c r="B21" t="n">
-        <v>78966</v>
+        <v>78968</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2931,10 +2931,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130252142</v>
+        <v>130252124</v>
       </c>
       <c r="B23" t="n">
-        <v>79209</v>
+        <v>78968</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2942,21 +2942,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2966,10 +2966,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>496939</v>
+        <v>497192</v>
       </c>
       <c r="R23" t="n">
-        <v>6827036</v>
+        <v>6826651</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3011,7 +3011,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3038,10 +3038,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130252124</v>
+        <v>130252142</v>
       </c>
       <c r="B24" t="n">
-        <v>78966</v>
+        <v>79211</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3049,21 +3049,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3073,10 +3073,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>497192</v>
+        <v>496939</v>
       </c>
       <c r="R24" t="n">
-        <v>6826651</v>
+        <v>6827036</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3118,7 +3118,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3255,7 +3255,7 @@
         <v>130252595</v>
       </c>
       <c r="B26" t="n">
-        <v>78966</v>
+        <v>78968</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3362,7 +3362,7 @@
         <v>130252127</v>
       </c>
       <c r="B27" t="n">
-        <v>78966</v>
+        <v>78968</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>130252600</v>
       </c>
       <c r="B28" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3573,32 +3573,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130252129</v>
+        <v>130252157</v>
       </c>
       <c r="B29" t="n">
-        <v>78966</v>
+        <v>93043</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3608,10 +3608,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>496646</v>
+        <v>496628</v>
       </c>
       <c r="R29" t="n">
-        <v>6827139</v>
+        <v>6827124</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3643,7 +3643,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3680,10 +3680,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130252589</v>
+        <v>130252129</v>
       </c>
       <c r="B30" t="n">
-        <v>78966</v>
+        <v>78968</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3711,14 +3711,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>497211</v>
+        <v>496646</v>
       </c>
       <c r="R30" t="n">
-        <v>6826926</v>
+        <v>6827139</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3750,7 +3750,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3760,7 +3760,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3775,22 +3775,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130252141</v>
+        <v>130252589</v>
       </c>
       <c r="B31" t="n">
-        <v>79209</v>
+        <v>78968</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3798,34 +3798,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>496956</v>
+        <v>497211</v>
       </c>
       <c r="R31" t="n">
-        <v>6827088</v>
+        <v>6826926</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3857,7 +3857,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3867,7 +3867,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3882,44 +3882,44 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130252157</v>
+        <v>130252141</v>
       </c>
       <c r="B32" t="n">
-        <v>93041</v>
+        <v>79211</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3929,10 +3929,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>496628</v>
+        <v>496956</v>
       </c>
       <c r="R32" t="n">
-        <v>6827124</v>
+        <v>6827088</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3964,7 +3964,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3974,7 +3974,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4004,7 +4004,7 @@
         <v>130252599</v>
       </c>
       <c r="B33" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4215,10 +4215,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130252135</v>
+        <v>130252143</v>
       </c>
       <c r="B35" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4250,10 +4250,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>496915</v>
+        <v>496877</v>
       </c>
       <c r="R35" t="n">
-        <v>6826903</v>
+        <v>6827056</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4285,7 +4285,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4295,7 +4295,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4325,7 +4325,7 @@
         <v>130252604</v>
       </c>
       <c r="B36" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4432,7 +4432,7 @@
         <v>130252146</v>
       </c>
       <c r="B37" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4536,10 +4536,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130252143</v>
+        <v>130252135</v>
       </c>
       <c r="B38" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4571,10 +4571,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>496877</v>
+        <v>496915</v>
       </c>
       <c r="R38" t="n">
-        <v>6827056</v>
+        <v>6826903</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4646,7 +4646,7 @@
         <v>130252605</v>
       </c>
       <c r="B39" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4750,53 +4750,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130252585</v>
+        <v>130252158</v>
       </c>
       <c r="B40" t="n">
-        <v>57849</v>
+        <v>93043</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>496635</v>
+        <v>496629</v>
       </c>
       <c r="R40" t="n">
-        <v>6827130</v>
+        <v>6827128</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4828,7 +4820,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4838,7 +4830,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4853,44 +4845,44 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130252590</v>
+        <v>130252607</v>
       </c>
       <c r="B41" t="n">
-        <v>78966</v>
+        <v>93043</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4900,10 +4892,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>496995</v>
+        <v>496598</v>
       </c>
       <c r="R41" t="n">
-        <v>6826923</v>
+        <v>6827085</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4935,7 +4927,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4945,7 +4937,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4954,6 +4946,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4972,10 +4965,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130252136</v>
+        <v>130252590</v>
       </c>
       <c r="B42" t="n">
-        <v>79209</v>
+        <v>78968</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4983,34 +4976,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>497002</v>
+        <v>496995</v>
       </c>
       <c r="R42" t="n">
-        <v>6826879</v>
+        <v>6826923</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5042,7 +5035,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5052,7 +5045,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5067,22 +5060,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130252128</v>
+        <v>130252136</v>
       </c>
       <c r="B43" t="n">
-        <v>78966</v>
+        <v>79211</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5090,21 +5083,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5114,10 +5107,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>496684</v>
+        <v>497002</v>
       </c>
       <c r="R43" t="n">
-        <v>6827129</v>
+        <v>6826879</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5149,7 +5142,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5159,7 +5152,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5186,32 +5179,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130252158</v>
+        <v>130252128</v>
       </c>
       <c r="B44" t="n">
-        <v>93041</v>
+        <v>78968</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5221,10 +5214,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>496629</v>
+        <v>496684</v>
       </c>
       <c r="R44" t="n">
-        <v>6827128</v>
+        <v>6827129</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5256,7 +5249,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5266,7 +5259,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5293,45 +5286,53 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130252607</v>
+        <v>130252585</v>
       </c>
       <c r="B45" t="n">
-        <v>93041</v>
+        <v>57851</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>496598</v>
+        <v>496635</v>
       </c>
       <c r="R45" t="n">
-        <v>6827085</v>
+        <v>6827130</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5363,7 +5364,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5373,7 +5374,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5382,7 +5383,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5404,7 +5404,7 @@
         <v>130252609</v>
       </c>
       <c r="B46" t="n">
-        <v>93041</v>
+        <v>93043</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5509,10 +5509,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130252598</v>
+        <v>130252602</v>
       </c>
       <c r="B47" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5544,10 +5544,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>497202</v>
+        <v>496722</v>
       </c>
       <c r="R47" t="n">
-        <v>6826911</v>
+        <v>6827107</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5579,7 +5579,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5616,10 +5616,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130252602</v>
+        <v>130252598</v>
       </c>
       <c r="B48" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5651,10 +5651,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>496722</v>
+        <v>497202</v>
       </c>
       <c r="R48" t="n">
-        <v>6827107</v>
+        <v>6826911</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5686,7 +5686,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5696,7 +5696,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5726,7 +5726,7 @@
         <v>130252153</v>
       </c>
       <c r="B49" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5830,10 +5830,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130252147</v>
+        <v>130252140</v>
       </c>
       <c r="B50" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5865,10 +5865,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>496781</v>
+        <v>497211</v>
       </c>
       <c r="R50" t="n">
-        <v>6827069</v>
+        <v>6826809</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5900,7 +5900,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5910,7 +5910,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5937,10 +5937,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130252140</v>
+        <v>130252147</v>
       </c>
       <c r="B51" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5972,10 +5972,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>497211</v>
+        <v>496781</v>
       </c>
       <c r="R51" t="n">
-        <v>6826809</v>
+        <v>6827069</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6007,7 +6007,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6017,7 +6017,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6047,7 +6047,7 @@
         <v>130252150</v>
       </c>
       <c r="B52" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6151,40 +6151,41 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130252118</v>
+        <v>130252130</v>
       </c>
       <c r="B53" t="n">
-        <v>57852</v>
+        <v>44108</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>101735</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
@@ -6194,10 +6195,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>496923</v>
+        <v>497225</v>
       </c>
       <c r="R53" t="n">
-        <v>6826913</v>
+        <v>6826804</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6229,7 +6230,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6239,12 +6240,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:50</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6253,6 +6249,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6271,41 +6268,40 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130252130</v>
+        <v>130252118</v>
       </c>
       <c r="B54" t="n">
-        <v>44106</v>
+        <v>57854</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>101735</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
@@ -6315,10 +6311,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>497225</v>
+        <v>496923</v>
       </c>
       <c r="R54" t="n">
-        <v>6826804</v>
+        <v>6826913</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6350,7 +6346,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6360,7 +6356,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6369,7 +6370,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6388,45 +6388,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130252117</v>
+        <v>130252606</v>
       </c>
       <c r="B55" t="n">
-        <v>79799</v>
+        <v>93043</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>497155</v>
+        <v>496618</v>
       </c>
       <c r="R55" t="n">
-        <v>6826856</v>
+        <v>6827114</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6458,7 +6458,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6468,7 +6468,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6477,18 +6477,19 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6498,7 +6499,7 @@
         <v>130252596</v>
       </c>
       <c r="B56" t="n">
-        <v>78966</v>
+        <v>78968</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6605,7 +6606,7 @@
         <v>130252137</v>
       </c>
       <c r="B57" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6709,45 +6710,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130252606</v>
+        <v>130252117</v>
       </c>
       <c r="B58" t="n">
-        <v>93041</v>
+        <v>79801</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>496618</v>
+        <v>497155</v>
       </c>
       <c r="R58" t="n">
-        <v>6827114</v>
+        <v>6826856</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6779,7 +6780,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6789,7 +6790,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6798,19 +6799,18 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -6820,7 +6820,7 @@
         <v>130252601</v>
       </c>
       <c r="B59" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6927,7 +6927,7 @@
         <v>130252144</v>
       </c>
       <c r="B60" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7034,7 +7034,7 @@
         <v>130252131</v>
       </c>
       <c r="B61" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         <v>130252152</v>
       </c>
       <c r="B62" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7248,7 +7248,7 @@
         <v>130252133</v>
       </c>
       <c r="B63" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7355,7 +7355,7 @@
         <v>130252114</v>
       </c>
       <c r="B64" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7460,10 +7460,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130252139</v>
+        <v>130252151</v>
       </c>
       <c r="B65" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7495,10 +7495,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>497225</v>
+        <v>496704</v>
       </c>
       <c r="R65" t="n">
-        <v>6826804</v>
+        <v>6827086</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7567,10 +7567,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130252151</v>
+        <v>130252597</v>
       </c>
       <c r="B66" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7598,14 +7598,14 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>496704</v>
+        <v>496922</v>
       </c>
       <c r="R66" t="n">
-        <v>6827086</v>
+        <v>6826906</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7637,7 +7637,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7647,7 +7647,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7662,22 +7662,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130252597</v>
+        <v>130252139</v>
       </c>
       <c r="B67" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7705,14 +7705,14 @@
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>496922</v>
+        <v>497225</v>
       </c>
       <c r="R67" t="n">
-        <v>6826906</v>
+        <v>6826804</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7744,7 +7744,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7754,7 +7754,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7769,12 +7769,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -7784,7 +7784,7 @@
         <v>130252608</v>
       </c>
       <c r="B68" t="n">
-        <v>93041</v>
+        <v>93043</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7889,10 +7889,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130256388</v>
+        <v>130256379</v>
       </c>
       <c r="B69" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7924,10 +7924,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>496665</v>
+        <v>496857</v>
       </c>
       <c r="R69" t="n">
-        <v>6827143</v>
+        <v>6827067</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7986,10 +7986,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130252149</v>
+        <v>130256388</v>
       </c>
       <c r="B70" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8015,19 +8015,16 @@
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>496745</v>
+        <v>496665</v>
       </c>
       <c r="R70" t="n">
-        <v>6827070</v>
+        <v>6827143</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8057,50 +8054,39 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130256379</v>
+        <v>130256356</v>
       </c>
       <c r="B71" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8132,10 +8118,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>496857</v>
+        <v>496957</v>
       </c>
       <c r="R71" t="n">
-        <v>6827067</v>
+        <v>6826898</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8194,10 +8180,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130256356</v>
+        <v>130252149</v>
       </c>
       <c r="B72" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8223,16 +8209,19 @@
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>496957</v>
+        <v>496745</v>
       </c>
       <c r="R72" t="n">
-        <v>6826898</v>
+        <v>6827070</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8262,39 +8251,50 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130255830</v>
+        <v>130255817</v>
       </c>
       <c r="B73" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8326,10 +8326,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>496649</v>
+        <v>496872</v>
       </c>
       <c r="R73" t="n">
-        <v>6827117</v>
+        <v>6827052</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8361,7 +8361,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8371,7 +8371,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8398,10 +8398,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130255820</v>
+        <v>130255832</v>
       </c>
       <c r="B74" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8433,10 +8433,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>496838</v>
+        <v>496578</v>
       </c>
       <c r="R74" t="n">
-        <v>6827085</v>
+        <v>6827044</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8468,7 +8468,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8478,7 +8478,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8505,10 +8505,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130255817</v>
+        <v>130255830</v>
       </c>
       <c r="B75" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8540,10 +8540,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>496872</v>
+        <v>496649</v>
       </c>
       <c r="R75" t="n">
-        <v>6827052</v>
+        <v>6827117</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8575,7 +8575,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8585,7 +8585,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8612,10 +8612,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>130255832</v>
+        <v>130255820</v>
       </c>
       <c r="B76" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8647,10 +8647,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>496578</v>
+        <v>496838</v>
       </c>
       <c r="R76" t="n">
-        <v>6827044</v>
+        <v>6827085</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8682,7 +8682,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8692,7 +8692,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8722,7 +8722,7 @@
         <v>130256369</v>
       </c>
       <c r="B77" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8816,10 +8816,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>130256383</v>
+        <v>130256376</v>
       </c>
       <c r="B78" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8851,10 +8851,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>496821</v>
+        <v>496855</v>
       </c>
       <c r="R78" t="n">
-        <v>6827087</v>
+        <v>6827052</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8913,10 +8913,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>130256365</v>
+        <v>130256368</v>
       </c>
       <c r="B79" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8948,10 +8948,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>496920</v>
+        <v>496902</v>
       </c>
       <c r="R79" t="n">
-        <v>6827003</v>
+        <v>6827030</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9010,10 +9010,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>130255797</v>
+        <v>130256365</v>
       </c>
       <c r="B80" t="n">
-        <v>78966</v>
+        <v>79211</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9021,21 +9021,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9045,10 +9045,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>497218</v>
+        <v>496920</v>
       </c>
       <c r="R80" t="n">
-        <v>6826761</v>
+        <v>6827003</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9078,19 +9078,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>11:59</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>11:59</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9105,22 +9095,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>130256376</v>
+        <v>130256383</v>
       </c>
       <c r="B81" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9152,10 +9142,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>496855</v>
+        <v>496821</v>
       </c>
       <c r="R81" t="n">
-        <v>6827052</v>
+        <v>6827087</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9214,10 +9204,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>130256368</v>
+        <v>130255797</v>
       </c>
       <c r="B82" t="n">
-        <v>79209</v>
+        <v>78968</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9225,21 +9215,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9249,10 +9239,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>496902</v>
+        <v>497218</v>
       </c>
       <c r="R82" t="n">
-        <v>6827030</v>
+        <v>6826761</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9282,9 +9272,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9299,22 +9299,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>130256346</v>
+        <v>130255837</v>
       </c>
       <c r="B83" t="n">
-        <v>78967</v>
+        <v>79211</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9322,21 +9322,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9346,10 +9346,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>496652</v>
+        <v>497191</v>
       </c>
       <c r="R83" t="n">
-        <v>6827164</v>
+        <v>6826771</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9379,9 +9379,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9396,22 +9406,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>130255837</v>
+        <v>130256346</v>
       </c>
       <c r="B84" t="n">
-        <v>79209</v>
+        <v>78969</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9419,21 +9429,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9443,10 +9453,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>497191</v>
+        <v>496652</v>
       </c>
       <c r="R84" t="n">
-        <v>6826771</v>
+        <v>6827164</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9476,19 +9486,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>12:00</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9503,44 +9503,44 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>130256352</v>
+        <v>130255839</v>
       </c>
       <c r="B85" t="n">
-        <v>78966</v>
+        <v>93043</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9550,10 +9550,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>496837</v>
+        <v>496787</v>
       </c>
       <c r="R85" t="n">
-        <v>6827069</v>
+        <v>6827052</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9583,9 +9583,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9600,44 +9610,44 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>130255839</v>
+        <v>130256352</v>
       </c>
       <c r="B86" t="n">
-        <v>93041</v>
+        <v>78968</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9647,10 +9657,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>496787</v>
+        <v>496837</v>
       </c>
       <c r="R86" t="n">
-        <v>6827052</v>
+        <v>6827069</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9680,19 +9690,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9707,12 +9707,12 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
@@ -9722,7 +9722,7 @@
         <v>130255823</v>
       </c>
       <c r="B87" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9829,7 +9829,7 @@
         <v>130255803</v>
       </c>
       <c r="B88" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9936,7 +9936,7 @@
         <v>130255818</v>
       </c>
       <c r="B89" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10040,10 +10040,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>130256387</v>
+        <v>130255814</v>
       </c>
       <c r="B90" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10075,10 +10075,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>496715</v>
+        <v>497073</v>
       </c>
       <c r="R90" t="n">
-        <v>6827126</v>
+        <v>6827132</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10108,9 +10108,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10125,22 +10135,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>130255814</v>
+        <v>130256387</v>
       </c>
       <c r="B91" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10172,10 +10182,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>497073</v>
+        <v>496715</v>
       </c>
       <c r="R91" t="n">
-        <v>6827132</v>
+        <v>6827126</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10205,19 +10215,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>11:27</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>11:27</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10232,22 +10232,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>130255808</v>
+        <v>130255798</v>
       </c>
       <c r="B92" t="n">
-        <v>79209</v>
+        <v>78968</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10255,21 +10255,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10279,10 +10279,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>497167</v>
+        <v>496740</v>
       </c>
       <c r="R92" t="n">
-        <v>6826594</v>
+        <v>6827145</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10314,7 +10314,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10324,7 +10324,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10351,10 +10351,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>130256370</v>
+        <v>130255808</v>
       </c>
       <c r="B93" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10386,10 +10386,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>496894</v>
+        <v>497167</v>
       </c>
       <c r="R93" t="n">
-        <v>6827030</v>
+        <v>6826594</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10419,9 +10419,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10436,22 +10446,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>130255798</v>
+        <v>130256370</v>
       </c>
       <c r="B94" t="n">
-        <v>78966</v>
+        <v>79211</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10459,21 +10469,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10483,10 +10493,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>496740</v>
+        <v>496894</v>
       </c>
       <c r="R94" t="n">
-        <v>6827145</v>
+        <v>6827030</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10516,19 +10526,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>10:45</t>
-        </is>
-      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>10:45</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10543,12 +10543,12 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
@@ -10558,7 +10558,7 @@
         <v>130256367</v>
       </c>
       <c r="B95" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10655,7 +10655,7 @@
         <v>130256373</v>
       </c>
       <c r="B96" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10752,7 +10752,7 @@
         <v>130255827</v>
       </c>
       <c r="B97" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10859,7 +10859,7 @@
         <v>130256350</v>
       </c>
       <c r="B98" t="n">
-        <v>78966</v>
+        <v>78968</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10956,7 +10956,7 @@
         <v>130255807</v>
       </c>
       <c r="B99" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11063,7 +11063,7 @@
         <v>130255812</v>
       </c>
       <c r="B100" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11167,10 +11167,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>130256391</v>
+        <v>130255825</v>
       </c>
       <c r="B101" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11202,10 +11202,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>496588</v>
+        <v>496759</v>
       </c>
       <c r="R101" t="n">
-        <v>6827066</v>
+        <v>6827133</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11235,9 +11235,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11252,22 +11262,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>130256375</v>
+        <v>130256391</v>
       </c>
       <c r="B102" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11299,10 +11309,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>496859</v>
+        <v>496588</v>
       </c>
       <c r="R102" t="n">
-        <v>6827052</v>
+        <v>6827066</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11361,10 +11371,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>130255825</v>
+        <v>130256375</v>
       </c>
       <c r="B103" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11396,10 +11406,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>496759</v>
+        <v>496859</v>
       </c>
       <c r="R103" t="n">
-        <v>6827133</v>
+        <v>6827052</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11429,19 +11439,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z103" t="inlineStr">
-        <is>
-          <t>10:48</t>
-        </is>
-      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB103" t="inlineStr">
-        <is>
-          <t>10:48</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11456,12 +11456,12 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
@@ -11471,7 +11471,7 @@
         <v>130255833</v>
       </c>
       <c r="B104" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11578,7 +11578,7 @@
         <v>130256351</v>
       </c>
       <c r="B105" t="n">
-        <v>78966</v>
+        <v>78968</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11675,7 +11675,7 @@
         <v>130255826</v>
       </c>
       <c r="B106" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11782,7 +11782,7 @@
         <v>130256353</v>
       </c>
       <c r="B107" t="n">
-        <v>78966</v>
+        <v>78968</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11879,7 +11879,7 @@
         <v>130255804</v>
       </c>
       <c r="B108" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11983,10 +11983,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>130256342</v>
+        <v>130256386</v>
       </c>
       <c r="B109" t="n">
-        <v>57852</v>
+        <v>79211</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11994,42 +11994,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>496940</v>
+        <v>496723</v>
       </c>
       <c r="R109" t="n">
-        <v>6826899</v>
+        <v>6827125</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12062,11 +12054,6 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12093,10 +12080,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>130256374</v>
+        <v>130256360</v>
       </c>
       <c r="B110" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12128,10 +12115,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>496863</v>
+        <v>496972</v>
       </c>
       <c r="R110" t="n">
-        <v>6827047</v>
+        <v>6826953</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12190,10 +12177,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>130256360</v>
+        <v>130256374</v>
       </c>
       <c r="B111" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12225,10 +12212,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>496972</v>
+        <v>496863</v>
       </c>
       <c r="R111" t="n">
-        <v>6826953</v>
+        <v>6827047</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12290,7 +12277,7 @@
         <v>130256354</v>
       </c>
       <c r="B112" t="n">
-        <v>78966</v>
+        <v>78968</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12387,7 +12374,7 @@
         <v>130255819</v>
       </c>
       <c r="B113" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12491,10 +12478,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>130256386</v>
+        <v>130256342</v>
       </c>
       <c r="B114" t="n">
-        <v>79209</v>
+        <v>57854</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12502,34 +12489,42 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>496723</v>
+        <v>496940</v>
       </c>
       <c r="R114" t="n">
-        <v>6827125</v>
+        <v>6826899</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12562,6 +12557,11 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12588,10 +12588,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>130256380</v>
+        <v>130255802</v>
       </c>
       <c r="B115" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12623,10 +12623,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>496852</v>
+        <v>496785</v>
       </c>
       <c r="R115" t="n">
-        <v>6827074</v>
+        <v>6827060</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12656,9 +12656,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12673,22 +12683,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>130255802</v>
+        <v>130256380</v>
       </c>
       <c r="B116" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12720,10 +12730,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>496785</v>
+        <v>496852</v>
       </c>
       <c r="R116" t="n">
-        <v>6827060</v>
+        <v>6827074</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12753,19 +12763,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z116" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB116" t="inlineStr">
-        <is>
-          <t>12:47</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12780,12 +12780,12 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
@@ -12795,7 +12795,7 @@
         <v>130256357</v>
       </c>
       <c r="B117" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12889,45 +12889,54 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>130255801</v>
+        <v>130256348</v>
       </c>
       <c r="B118" t="n">
-        <v>79209</v>
+        <v>8451</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>496702</v>
+        <v>496864</v>
       </c>
       <c r="R118" t="n">
-        <v>6827131</v>
+        <v>6827043</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12957,93 +12966,75 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z118" t="inlineStr">
-        <is>
-          <t>10:39</t>
-        </is>
-      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="AB118" t="inlineStr">
-        <is>
-          <t>10:39</t>
-        </is>
-      </c>
       <c r="AD118" t="b">
         <v>0</v>
       </c>
       <c r="AE118" t="b">
         <v>0</v>
       </c>
+      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>130256348</v>
+        <v>130255796</v>
       </c>
       <c r="B119" t="n">
-        <v>8451</v>
+        <v>78968</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="J119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>496864</v>
+        <v>497111</v>
       </c>
       <c r="R119" t="n">
-        <v>6827043</v>
+        <v>6826644</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13073,40 +13064,49 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
       <c r="AD119" t="b">
         <v>0</v>
       </c>
       <c r="AE119" t="b">
         <v>0</v>
       </c>
-      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
       </c>
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>130256390</v>
+        <v>130255801</v>
       </c>
       <c r="B120" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13138,10 +13138,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>496581</v>
+        <v>496702</v>
       </c>
       <c r="R120" t="n">
-        <v>6827049</v>
+        <v>6827131</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13171,9 +13171,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13188,22 +13198,22 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>130256363</v>
+        <v>130256382</v>
       </c>
       <c r="B121" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13235,10 +13245,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>496897</v>
+        <v>496831</v>
       </c>
       <c r="R121" t="n">
-        <v>6827002</v>
+        <v>6827081</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13300,7 +13310,7 @@
         <v>130256381</v>
       </c>
       <c r="B122" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13394,10 +13404,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>130255796</v>
+        <v>130256378</v>
       </c>
       <c r="B123" t="n">
-        <v>78966</v>
+        <v>79211</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13405,21 +13415,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13429,10 +13439,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>497111</v>
+        <v>496862</v>
       </c>
       <c r="R123" t="n">
-        <v>6826644</v>
+        <v>6827064</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13462,19 +13472,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z123" t="inlineStr">
-        <is>
-          <t>12:13</t>
-        </is>
-      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB123" t="inlineStr">
-        <is>
-          <t>12:13</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13489,22 +13489,22 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>130256378</v>
+        <v>130256363</v>
       </c>
       <c r="B124" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13536,10 +13536,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>496862</v>
+        <v>496897</v>
       </c>
       <c r="R124" t="n">
-        <v>6827064</v>
+        <v>6827002</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13598,10 +13598,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>130256382</v>
+        <v>130256390</v>
       </c>
       <c r="B125" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13633,10 +13633,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>496831</v>
+        <v>496581</v>
       </c>
       <c r="R125" t="n">
-        <v>6827081</v>
+        <v>6827049</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13698,7 +13698,7 @@
         <v>130256359</v>
       </c>
       <c r="B126" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13792,32 +13792,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>130256392</v>
+        <v>130255834</v>
       </c>
       <c r="B127" t="n">
-        <v>93041</v>
+        <v>79211</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13827,10 +13827,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>496581</v>
+        <v>496582</v>
       </c>
       <c r="R127" t="n">
-        <v>6827082</v>
+        <v>6827040</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13860,40 +13860,49 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
       <c r="AD127" t="b">
         <v>0</v>
       </c>
       <c r="AE127" t="b">
         <v>0</v>
       </c>
-      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>130255834</v>
+        <v>130255836</v>
       </c>
       <c r="B128" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13925,10 +13934,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>496582</v>
+        <v>497183</v>
       </c>
       <c r="R128" t="n">
-        <v>6827040</v>
+        <v>6826662</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13960,7 +13969,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -13970,7 +13979,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13997,10 +14006,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>130255836</v>
+        <v>130255805</v>
       </c>
       <c r="B129" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14032,10 +14041,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>497183</v>
+        <v>497139</v>
       </c>
       <c r="R129" t="n">
-        <v>6826662</v>
+        <v>6826719</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14067,7 +14076,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -14077,7 +14086,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14104,10 +14113,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>130255805</v>
+        <v>130256343</v>
       </c>
       <c r="B130" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14139,10 +14148,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>497139</v>
+        <v>496851</v>
       </c>
       <c r="R130" t="n">
-        <v>6826719</v>
+        <v>6827066</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14172,19 +14181,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z130" t="inlineStr">
-        <is>
-          <t>12:17</t>
-        </is>
-      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB130" t="inlineStr">
-        <is>
-          <t>12:17</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14199,57 +14198,66 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>130256343</v>
+        <v>130255793</v>
       </c>
       <c r="B131" t="n">
-        <v>79209</v>
+        <v>8451</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>496851</v>
+        <v>496670</v>
       </c>
       <c r="R131" t="n">
-        <v>6827066</v>
+        <v>6827136</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14279,36 +14287,47 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AD131" t="b">
         <v>0</v>
       </c>
       <c r="AE131" t="b">
         <v>0</v>
       </c>
+      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>130255793</v>
+        <v>130256349</v>
       </c>
       <c r="B132" t="n">
         <v>8451</v>
@@ -14352,10 +14371,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>496670</v>
+        <v>496714</v>
       </c>
       <c r="R132" t="n">
-        <v>6827136</v>
+        <v>6827127</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14385,19 +14404,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z132" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB132" t="inlineStr">
-        <is>
-          <t>10:30</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14413,19 +14422,19 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>130256349</v>
+        <v>130256347</v>
       </c>
       <c r="B133" t="n">
         <v>8451</v>
@@ -14469,10 +14478,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>496714</v>
+        <v>496941</v>
       </c>
       <c r="R133" t="n">
-        <v>6827127</v>
+        <v>6826899</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14532,10 +14541,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>130256347</v>
+        <v>130256392</v>
       </c>
       <c r="B134" t="n">
-        <v>8451</v>
+        <v>93043</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14543,43 +14552,34 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
-      <c r="J134" t="inlineStr"/>
-      <c r="K134" t="inlineStr"/>
-      <c r="L134" t="inlineStr"/>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>496941</v>
+        <v>496581</v>
       </c>
       <c r="R134" t="n">
-        <v>6826899</v>
+        <v>6827082</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14642,7 +14642,7 @@
         <v>130255806</v>
       </c>
       <c r="B135" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14749,7 +14749,7 @@
         <v>130255810</v>
       </c>
       <c r="B136" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14856,7 +14856,7 @@
         <v>130255813</v>
       </c>
       <c r="B137" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14963,7 +14963,7 @@
         <v>130256345</v>
       </c>
       <c r="B138" t="n">
-        <v>78967</v>
+        <v>78969</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15060,7 +15060,7 @@
         <v>130256344</v>
       </c>
       <c r="B139" t="n">
-        <v>78967</v>
+        <v>78969</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15157,7 +15157,7 @@
         <v>130256389</v>
       </c>
       <c r="B140" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15251,10 +15251,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>130256358</v>
+        <v>130256361</v>
       </c>
       <c r="B141" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15286,10 +15286,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>496962</v>
+        <v>496893</v>
       </c>
       <c r="R141" t="n">
-        <v>6826923</v>
+        <v>6826989</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15348,10 +15348,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>130256361</v>
+        <v>130256358</v>
       </c>
       <c r="B142" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15383,10 +15383,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>496893</v>
+        <v>496962</v>
       </c>
       <c r="R142" t="n">
-        <v>6826989</v>
+        <v>6826923</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15445,10 +15445,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>130256355</v>
+        <v>130255828</v>
       </c>
       <c r="B143" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15480,10 +15480,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>496940</v>
+        <v>496658</v>
       </c>
       <c r="R143" t="n">
-        <v>6826898</v>
+        <v>6827133</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15513,9 +15513,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z143" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB143" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15530,68 +15540,57 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>130256394</v>
+        <v>130255821</v>
       </c>
       <c r="B144" t="n">
-        <v>93041</v>
+        <v>79211</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J144" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K144" t="inlineStr"/>
-      <c r="N144" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
           <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>496581</v>
+        <v>496839</v>
       </c>
       <c r="R144" t="n">
-        <v>6827079</v>
+        <v>6827082</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15621,40 +15620,49 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z144" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AA144" t="inlineStr">
         <is>
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="AB144" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AD144" t="b">
         <v>0</v>
       </c>
       <c r="AE144" t="b">
         <v>0</v>
       </c>
-      <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="b">
         <v>0</v>
       </c>
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>130256340</v>
+        <v>130256362</v>
       </c>
       <c r="B145" t="n">
-        <v>79799</v>
+        <v>79211</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15662,21 +15670,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15686,10 +15694,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>496774</v>
+        <v>496893</v>
       </c>
       <c r="R145" t="n">
-        <v>6827067</v>
+        <v>6826998</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15748,10 +15756,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>130256364</v>
+        <v>130256355</v>
       </c>
       <c r="B146" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15783,10 +15791,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>496909</v>
+        <v>496940</v>
       </c>
       <c r="R146" t="n">
-        <v>6827002</v>
+        <v>6826898</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15848,7 +15856,7 @@
         <v>130256371</v>
       </c>
       <c r="B147" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15942,10 +15950,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>130255828</v>
+        <v>130256364</v>
       </c>
       <c r="B148" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15977,10 +15985,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>496658</v>
+        <v>496909</v>
       </c>
       <c r="R148" t="n">
-        <v>6827133</v>
+        <v>6827002</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16010,19 +16018,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z148" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB148" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16037,22 +16035,22 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>130255821</v>
+        <v>130256340</v>
       </c>
       <c r="B149" t="n">
-        <v>79209</v>
+        <v>79801</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16060,21 +16058,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16084,10 +16082,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>496839</v>
+        <v>496774</v>
       </c>
       <c r="R149" t="n">
-        <v>6827082</v>
+        <v>6827067</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16117,19 +16115,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z149" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AA149" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB149" t="inlineStr">
-        <is>
-          <t>11:04</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16144,57 +16132,68 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>130256362</v>
+        <v>130256394</v>
       </c>
       <c r="B150" t="n">
-        <v>79209</v>
+        <v>93043</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr"/>
+      <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
           <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>496893</v>
+        <v>496581</v>
       </c>
       <c r="R150" t="n">
-        <v>6826998</v>
+        <v>6827079</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16235,6 +16234,7 @@
       <c r="AE150" t="b">
         <v>0</v>
       </c>
+      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
@@ -16253,10 +16253,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>130255831</v>
+        <v>130255811</v>
       </c>
       <c r="B151" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16288,10 +16288,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>496599</v>
+        <v>497200</v>
       </c>
       <c r="R151" t="n">
-        <v>6827121</v>
+        <v>6826832</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16323,7 +16323,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -16333,7 +16333,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16360,10 +16360,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>130255824</v>
+        <v>130255831</v>
       </c>
       <c r="B152" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16395,10 +16395,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>496752</v>
+        <v>496599</v>
       </c>
       <c r="R152" t="n">
-        <v>6827114</v>
+        <v>6827121</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16430,7 +16430,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -16440,7 +16440,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16467,10 +16467,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>130255811</v>
+        <v>130255824</v>
       </c>
       <c r="B153" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16502,10 +16502,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>497200</v>
+        <v>496752</v>
       </c>
       <c r="R153" t="n">
-        <v>6826832</v>
+        <v>6827114</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16537,7 +16537,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -16547,7 +16547,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16577,7 +16577,7 @@
         <v>130256372</v>
       </c>
       <c r="B154" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16674,7 +16674,7 @@
         <v>130256385</v>
       </c>
       <c r="B155" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16771,7 +16771,7 @@
         <v>130255838</v>
       </c>
       <c r="B156" t="n">
-        <v>93041</v>
+        <v>93043</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16878,7 +16878,7 @@
         <v>130255809</v>
       </c>
       <c r="B157" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16985,7 +16985,7 @@
         <v>130255816</v>
       </c>
       <c r="B158" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17092,7 +17092,7 @@
         <v>130255829</v>
       </c>
       <c r="B159" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17199,7 +17199,7 @@
         <v>130256393</v>
       </c>
       <c r="B160" t="n">
-        <v>93041</v>
+        <v>93043</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>

--- a/artfynd/A 58895-2025 artfynd.xlsx
+++ b/artfynd/A 58895-2025 artfynd.xlsx
@@ -790,45 +790,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130252155</v>
+        <v>130252591</v>
       </c>
       <c r="B3" t="n">
-        <v>93043</v>
+        <v>78968</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>496725</v>
+        <v>496966</v>
       </c>
       <c r="R3" t="n">
-        <v>6827084</v>
+        <v>6826906</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,22 +885,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130252584</v>
+        <v>130252116</v>
       </c>
       <c r="B4" t="n">
-        <v>58013</v>
+        <v>79830</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,34 +908,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>497202</v>
+        <v>496721</v>
       </c>
       <c r="R4" t="n">
-        <v>6826919</v>
+        <v>6827083</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -967,7 +967,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -992,22 +992,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130252591</v>
+        <v>130252584</v>
       </c>
       <c r="B5" t="n">
-        <v>78968</v>
+        <v>58013</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1015,21 +1015,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>496966</v>
+        <v>497202</v>
       </c>
       <c r="R5" t="n">
-        <v>6826906</v>
+        <v>6826919</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,32 +1111,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130252116</v>
+        <v>130252120</v>
       </c>
       <c r="B6" t="n">
-        <v>79830</v>
+        <v>8451</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1146,10 +1146,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>496721</v>
+        <v>496653</v>
       </c>
       <c r="R6" t="n">
-        <v>6827083</v>
+        <v>6827111</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1218,10 +1218,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130252120</v>
+        <v>130252155</v>
       </c>
       <c r="B7" t="n">
-        <v>8451</v>
+        <v>93047</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1229,21 +1229,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1253,10 +1253,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>496653</v>
+        <v>496725</v>
       </c>
       <c r="R7" t="n">
-        <v>6827111</v>
+        <v>6827084</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1432,32 +1432,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130252156</v>
+        <v>130252126</v>
       </c>
       <c r="B9" t="n">
-        <v>93043</v>
+        <v>78968</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>496675</v>
+        <v>496737</v>
       </c>
       <c r="R9" t="n">
-        <v>6827138</v>
+        <v>6827071</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1512,7 +1512,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1539,10 +1539,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130252138</v>
+        <v>130252592</v>
       </c>
       <c r="B10" t="n">
-        <v>79211</v>
+        <v>78968</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1550,34 +1550,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>497207</v>
+        <v>496950</v>
       </c>
       <c r="R10" t="n">
-        <v>6826726</v>
+        <v>6827038</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1634,22 +1634,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130252126</v>
+        <v>130252115</v>
       </c>
       <c r="B11" t="n">
-        <v>78968</v>
+        <v>79243</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1657,21 +1657,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1681,10 +1681,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>496737</v>
+        <v>496555</v>
       </c>
       <c r="R11" t="n">
-        <v>6827071</v>
+        <v>6826991</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,6 +1735,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1753,10 +1754,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130252592</v>
+        <v>130252138</v>
       </c>
       <c r="B12" t="n">
-        <v>78968</v>
+        <v>79211</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1764,34 +1765,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>496950</v>
+        <v>497207</v>
       </c>
       <c r="R12" t="n">
-        <v>6827038</v>
+        <v>6826726</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1823,7 +1824,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1833,7 +1834,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1848,12 +1849,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1967,32 +1968,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130252115</v>
+        <v>130252156</v>
       </c>
       <c r="B14" t="n">
-        <v>79243</v>
+        <v>93047</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>185</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2002,10 +2003,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>496555</v>
+        <v>496675</v>
       </c>
       <c r="R14" t="n">
-        <v>6826991</v>
+        <v>6827138</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2037,7 +2038,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2047,7 +2048,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2056,7 +2057,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2185,7 +2185,7 @@
         <v>130252154</v>
       </c>
       <c r="B16" t="n">
-        <v>93043</v>
+        <v>93047</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2396,10 +2396,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130252145</v>
+        <v>130252125</v>
       </c>
       <c r="B18" t="n">
-        <v>79211</v>
+        <v>78968</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2407,21 +2407,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2431,10 +2431,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>496870</v>
+        <v>497154</v>
       </c>
       <c r="R18" t="n">
-        <v>6827056</v>
+        <v>6826854</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2476,7 +2476,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2503,10 +2503,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130252603</v>
+        <v>130252594</v>
       </c>
       <c r="B19" t="n">
-        <v>79211</v>
+        <v>78968</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2514,21 +2514,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2538,10 +2538,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>496694</v>
+        <v>496874</v>
       </c>
       <c r="R19" t="n">
-        <v>6827132</v>
+        <v>6827149</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2610,10 +2610,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130252125</v>
+        <v>130252603</v>
       </c>
       <c r="B20" t="n">
-        <v>78968</v>
+        <v>79211</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,34 +2621,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>497154</v>
+        <v>496694</v>
       </c>
       <c r="R20" t="n">
-        <v>6826854</v>
+        <v>6827132</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2705,22 +2705,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130252594</v>
+        <v>130252145</v>
       </c>
       <c r="B21" t="n">
-        <v>78968</v>
+        <v>79211</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2728,34 +2728,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>496874</v>
+        <v>496870</v>
       </c>
       <c r="R21" t="n">
-        <v>6827149</v>
+        <v>6827056</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2812,12 +2812,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2931,10 +2931,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130252124</v>
+        <v>130252142</v>
       </c>
       <c r="B23" t="n">
-        <v>78968</v>
+        <v>79211</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2942,21 +2942,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2966,10 +2966,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>497192</v>
+        <v>496939</v>
       </c>
       <c r="R23" t="n">
-        <v>6826651</v>
+        <v>6827036</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3011,7 +3011,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3038,10 +3038,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130252142</v>
+        <v>130252124</v>
       </c>
       <c r="B24" t="n">
-        <v>79211</v>
+        <v>78968</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3049,21 +3049,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3073,10 +3073,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>496939</v>
+        <v>497192</v>
       </c>
       <c r="R24" t="n">
-        <v>6827036</v>
+        <v>6826651</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3118,7 +3118,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3252,7 +3252,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130252595</v>
+        <v>130252127</v>
       </c>
       <c r="B26" t="n">
         <v>78968</v>
@@ -3283,14 +3283,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>496894</v>
+        <v>496719</v>
       </c>
       <c r="R26" t="n">
-        <v>6827123</v>
+        <v>6827076</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3322,7 +3322,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3347,22 +3347,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130252127</v>
+        <v>130252600</v>
       </c>
       <c r="B27" t="n">
-        <v>78968</v>
+        <v>79211</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3370,34 +3370,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>496719</v>
+        <v>496948</v>
       </c>
       <c r="R27" t="n">
-        <v>6827076</v>
+        <v>6827029</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3429,7 +3429,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3439,7 +3439,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3454,22 +3454,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130252600</v>
+        <v>130252595</v>
       </c>
       <c r="B28" t="n">
-        <v>79211</v>
+        <v>78968</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3477,21 +3477,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3501,10 +3501,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>496948</v>
+        <v>496894</v>
       </c>
       <c r="R28" t="n">
-        <v>6827029</v>
+        <v>6827123</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3536,7 +3536,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3546,7 +3546,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3573,32 +3573,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130252157</v>
+        <v>130252129</v>
       </c>
       <c r="B29" t="n">
-        <v>93043</v>
+        <v>78968</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3608,10 +3608,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>496628</v>
+        <v>496646</v>
       </c>
       <c r="R29" t="n">
-        <v>6827124</v>
+        <v>6827139</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3643,7 +3643,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3680,7 +3680,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130252129</v>
+        <v>130252589</v>
       </c>
       <c r="B30" t="n">
         <v>78968</v>
@@ -3711,14 +3711,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>496646</v>
+        <v>497211</v>
       </c>
       <c r="R30" t="n">
-        <v>6827139</v>
+        <v>6826926</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3750,7 +3750,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3760,7 +3760,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3775,22 +3775,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130252589</v>
+        <v>130252141</v>
       </c>
       <c r="B31" t="n">
-        <v>78968</v>
+        <v>79211</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3798,34 +3798,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>497211</v>
+        <v>496956</v>
       </c>
       <c r="R31" t="n">
-        <v>6826926</v>
+        <v>6827088</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3857,7 +3857,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3867,7 +3867,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3882,44 +3882,44 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130252141</v>
+        <v>130252157</v>
       </c>
       <c r="B32" t="n">
-        <v>79211</v>
+        <v>93047</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3929,10 +3929,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>496956</v>
+        <v>496628</v>
       </c>
       <c r="R32" t="n">
-        <v>6827088</v>
+        <v>6827124</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3964,7 +3964,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3974,7 +3974,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4108,45 +4108,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130252587</v>
+        <v>130252143</v>
       </c>
       <c r="B34" t="n">
-        <v>8451</v>
+        <v>79211</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>496719</v>
+        <v>496877</v>
       </c>
       <c r="R34" t="n">
-        <v>6827112</v>
+        <v>6827056</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4203,57 +4203,57 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130252143</v>
+        <v>130252587</v>
       </c>
       <c r="B35" t="n">
-        <v>79211</v>
+        <v>8451</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>496877</v>
+        <v>496719</v>
       </c>
       <c r="R35" t="n">
-        <v>6827056</v>
+        <v>6827112</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4285,7 +4285,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4295,7 +4295,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4310,12 +4310,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4429,7 +4429,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130252146</v>
+        <v>130252135</v>
       </c>
       <c r="B37" t="n">
         <v>79211</v>
@@ -4464,10 +4464,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>496864</v>
+        <v>496915</v>
       </c>
       <c r="R37" t="n">
-        <v>6827053</v>
+        <v>6826903</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4509,7 +4509,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4536,7 +4536,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130252135</v>
+        <v>130252146</v>
       </c>
       <c r="B38" t="n">
         <v>79211</v>
@@ -4571,10 +4571,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>496915</v>
+        <v>496864</v>
       </c>
       <c r="R38" t="n">
-        <v>6826903</v>
+        <v>6827053</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4750,45 +4750,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130252158</v>
+        <v>130252590</v>
       </c>
       <c r="B40" t="n">
-        <v>93043</v>
+        <v>78968</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>496629</v>
+        <v>496995</v>
       </c>
       <c r="R40" t="n">
-        <v>6827128</v>
+        <v>6826923</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4820,7 +4820,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4845,57 +4845,57 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130252607</v>
+        <v>130252136</v>
       </c>
       <c r="B41" t="n">
-        <v>93043</v>
+        <v>79211</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>496598</v>
+        <v>497002</v>
       </c>
       <c r="R41" t="n">
-        <v>6827085</v>
+        <v>6826879</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4927,7 +4927,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4937,7 +4937,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4946,26 +4946,25 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130252590</v>
+        <v>130252128</v>
       </c>
       <c r="B42" t="n">
         <v>78968</v>
@@ -4996,14 +4995,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>496995</v>
+        <v>496684</v>
       </c>
       <c r="R42" t="n">
-        <v>6826923</v>
+        <v>6827129</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5035,7 +5034,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5045,7 +5044,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5060,22 +5059,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130252136</v>
+        <v>130252585</v>
       </c>
       <c r="B43" t="n">
-        <v>79211</v>
+        <v>57851</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5083,34 +5082,42 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>497002</v>
+        <v>496635</v>
       </c>
       <c r="R43" t="n">
-        <v>6826879</v>
+        <v>6827130</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5142,7 +5149,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5152,7 +5159,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5167,44 +5174,44 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130252128</v>
+        <v>130252158</v>
       </c>
       <c r="B44" t="n">
-        <v>78968</v>
+        <v>93047</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5214,10 +5221,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>496684</v>
+        <v>496629</v>
       </c>
       <c r="R44" t="n">
-        <v>6827129</v>
+        <v>6827128</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5249,7 +5256,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5259,7 +5266,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5286,53 +5293,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130252585</v>
+        <v>130252607</v>
       </c>
       <c r="B45" t="n">
-        <v>57851</v>
+        <v>93047</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>496635</v>
+        <v>496598</v>
       </c>
       <c r="R45" t="n">
-        <v>6827130</v>
+        <v>6827085</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5364,7 +5363,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5374,7 +5373,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5383,6 +5382,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5401,45 +5401,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130252609</v>
+        <v>130252153</v>
       </c>
       <c r="B46" t="n">
-        <v>93043</v>
+        <v>79211</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>496549</v>
+        <v>496564</v>
       </c>
       <c r="R46" t="n">
-        <v>6826988</v>
+        <v>6827012</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5471,7 +5471,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5490,26 +5490,25 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130252602</v>
+        <v>130252598</v>
       </c>
       <c r="B47" t="n">
         <v>79211</v>
@@ -5544,10 +5543,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>496722</v>
+        <v>497202</v>
       </c>
       <c r="R47" t="n">
-        <v>6827107</v>
+        <v>6826911</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5579,7 +5578,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5589,7 +5588,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5616,7 +5615,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130252598</v>
+        <v>130252602</v>
       </c>
       <c r="B48" t="n">
         <v>79211</v>
@@ -5651,10 +5650,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>497202</v>
+        <v>496722</v>
       </c>
       <c r="R48" t="n">
-        <v>6826911</v>
+        <v>6827107</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5686,7 +5685,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5696,7 +5695,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5723,45 +5722,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130252153</v>
+        <v>130252609</v>
       </c>
       <c r="B49" t="n">
-        <v>79211</v>
+        <v>93047</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>496564</v>
+        <v>496549</v>
       </c>
       <c r="R49" t="n">
-        <v>6827012</v>
+        <v>6826988</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5793,7 +5792,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5803,7 +5802,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5812,18 +5811,19 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -6388,32 +6388,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130252606</v>
+        <v>130252596</v>
       </c>
       <c r="B55" t="n">
-        <v>93043</v>
+        <v>78968</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6423,10 +6423,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>496618</v>
+        <v>496771</v>
       </c>
       <c r="R55" t="n">
-        <v>6827114</v>
+        <v>6827069</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6458,7 +6458,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6468,7 +6468,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6477,7 +6477,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6496,10 +6495,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130252596</v>
+        <v>130252137</v>
       </c>
       <c r="B56" t="n">
-        <v>78968</v>
+        <v>79211</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6507,34 +6506,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>496771</v>
+        <v>497206</v>
       </c>
       <c r="R56" t="n">
-        <v>6827069</v>
+        <v>6826638</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6566,7 +6565,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6576,7 +6575,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6591,57 +6590,57 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130252137</v>
+        <v>130252606</v>
       </c>
       <c r="B57" t="n">
-        <v>79211</v>
+        <v>93047</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>497206</v>
+        <v>496618</v>
       </c>
       <c r="R57" t="n">
-        <v>6826638</v>
+        <v>6827114</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6673,7 +6672,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6683,7 +6682,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6692,18 +6691,19 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -7352,10 +7352,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130252114</v>
+        <v>130252139</v>
       </c>
       <c r="B64" t="n">
-        <v>79243</v>
+        <v>79211</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7363,21 +7363,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7387,10 +7387,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>496880</v>
+        <v>497225</v>
       </c>
       <c r="R64" t="n">
-        <v>6827051</v>
+        <v>6826804</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7422,7 +7422,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7432,7 +7432,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7441,7 +7441,6 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7674,10 +7673,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130252139</v>
+        <v>130252114</v>
       </c>
       <c r="B67" t="n">
-        <v>79211</v>
+        <v>79243</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7685,21 +7684,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7709,10 +7708,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>497225</v>
+        <v>496880</v>
       </c>
       <c r="R67" t="n">
-        <v>6826804</v>
+        <v>6827051</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7744,7 +7743,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7754,7 +7753,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7763,6 +7762,7 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7784,7 +7784,7 @@
         <v>130252608</v>
       </c>
       <c r="B68" t="n">
-        <v>93043</v>
+        <v>93047</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7889,7 +7889,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130256379</v>
+        <v>130256388</v>
       </c>
       <c r="B69" t="n">
         <v>79211</v>
@@ -7924,10 +7924,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>496857</v>
+        <v>496665</v>
       </c>
       <c r="R69" t="n">
-        <v>6827067</v>
+        <v>6827143</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7986,7 +7986,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130256388</v>
+        <v>130252149</v>
       </c>
       <c r="B70" t="n">
         <v>79211</v>
@@ -8015,16 +8015,19 @@
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>496665</v>
+        <v>496745</v>
       </c>
       <c r="R70" t="n">
-        <v>6827143</v>
+        <v>6827070</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8054,36 +8057,47 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130256356</v>
+        <v>130256379</v>
       </c>
       <c r="B71" t="n">
         <v>79211</v>
@@ -8118,10 +8132,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>496957</v>
+        <v>496857</v>
       </c>
       <c r="R71" t="n">
-        <v>6826898</v>
+        <v>6827067</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8180,7 +8194,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130252149</v>
+        <v>130256356</v>
       </c>
       <c r="B72" t="n">
         <v>79211</v>
@@ -8209,19 +8223,16 @@
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>496745</v>
+        <v>496957</v>
       </c>
       <c r="R72" t="n">
-        <v>6827070</v>
+        <v>6826898</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8251,40 +8262,29 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
@@ -8816,10 +8816,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>130256376</v>
+        <v>130255797</v>
       </c>
       <c r="B78" t="n">
-        <v>79211</v>
+        <v>78968</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8827,21 +8827,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8851,10 +8851,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>496855</v>
+        <v>497218</v>
       </c>
       <c r="R78" t="n">
-        <v>6827052</v>
+        <v>6826761</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8884,9 +8884,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8901,19 +8911,19 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>130256368</v>
+        <v>130256383</v>
       </c>
       <c r="B79" t="n">
         <v>79211</v>
@@ -8948,10 +8958,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>496902</v>
+        <v>496821</v>
       </c>
       <c r="R79" t="n">
-        <v>6827030</v>
+        <v>6827087</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9010,7 +9020,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>130256365</v>
+        <v>130256376</v>
       </c>
       <c r="B80" t="n">
         <v>79211</v>
@@ -9045,10 +9055,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>496920</v>
+        <v>496855</v>
       </c>
       <c r="R80" t="n">
-        <v>6827003</v>
+        <v>6827052</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9107,7 +9117,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>130256383</v>
+        <v>130256368</v>
       </c>
       <c r="B81" t="n">
         <v>79211</v>
@@ -9142,10 +9152,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>496821</v>
+        <v>496902</v>
       </c>
       <c r="R81" t="n">
-        <v>6827087</v>
+        <v>6827030</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9204,10 +9214,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>130255797</v>
+        <v>130256365</v>
       </c>
       <c r="B82" t="n">
-        <v>78968</v>
+        <v>79211</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9215,21 +9225,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9239,10 +9249,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>497218</v>
+        <v>496920</v>
       </c>
       <c r="R82" t="n">
-        <v>6826761</v>
+        <v>6827003</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9272,19 +9282,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>11:59</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>11:59</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9299,12 +9299,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
@@ -9518,7 +9518,7 @@
         <v>130255839</v>
       </c>
       <c r="B85" t="n">
-        <v>93043</v>
+        <v>93047</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9719,7 +9719,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>130255823</v>
+        <v>130255803</v>
       </c>
       <c r="B87" t="n">
         <v>79211</v>
@@ -9754,10 +9754,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>496757</v>
+        <v>497148</v>
       </c>
       <c r="R87" t="n">
-        <v>6827109</v>
+        <v>6826907</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9789,7 +9789,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9799,7 +9799,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9826,7 +9826,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>130255803</v>
+        <v>130255818</v>
       </c>
       <c r="B88" t="n">
         <v>79211</v>
@@ -9861,10 +9861,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>497148</v>
+        <v>496862</v>
       </c>
       <c r="R88" t="n">
-        <v>6826907</v>
+        <v>6827065</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9896,7 +9896,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -9906,7 +9906,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9933,7 +9933,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>130255818</v>
+        <v>130256387</v>
       </c>
       <c r="B89" t="n">
         <v>79211</v>
@@ -9968,10 +9968,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>496862</v>
+        <v>496715</v>
       </c>
       <c r="R89" t="n">
-        <v>6827065</v>
+        <v>6827126</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10001,19 +10001,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>11:06</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>11:06</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10028,12 +10018,12 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
@@ -10147,7 +10137,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>130256387</v>
+        <v>130255823</v>
       </c>
       <c r="B91" t="n">
         <v>79211</v>
@@ -10182,10 +10172,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>496715</v>
+        <v>496757</v>
       </c>
       <c r="R91" t="n">
-        <v>6827126</v>
+        <v>6827109</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10215,9 +10205,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10232,22 +10232,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>130255798</v>
+        <v>130256370</v>
       </c>
       <c r="B92" t="n">
-        <v>78968</v>
+        <v>79211</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10255,21 +10255,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10279,10 +10279,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>496740</v>
+        <v>496894</v>
       </c>
       <c r="R92" t="n">
-        <v>6827145</v>
+        <v>6827030</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10312,19 +10312,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z92" t="inlineStr">
-        <is>
-          <t>10:45</t>
-        </is>
-      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB92" t="inlineStr">
-        <is>
-          <t>10:45</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10339,22 +10329,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>130255808</v>
+        <v>130255798</v>
       </c>
       <c r="B93" t="n">
-        <v>79211</v>
+        <v>78968</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10362,21 +10352,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10386,10 +10376,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>497167</v>
+        <v>496740</v>
       </c>
       <c r="R93" t="n">
-        <v>6826594</v>
+        <v>6827145</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10421,7 +10411,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10431,7 +10421,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10458,7 +10448,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>130256370</v>
+        <v>130255808</v>
       </c>
       <c r="B94" t="n">
         <v>79211</v>
@@ -10493,10 +10483,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>496894</v>
+        <v>497167</v>
       </c>
       <c r="R94" t="n">
-        <v>6827030</v>
+        <v>6826594</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10526,9 +10516,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10543,12 +10543,12 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
@@ -11167,7 +11167,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>130255825</v>
+        <v>130256391</v>
       </c>
       <c r="B101" t="n">
         <v>79211</v>
@@ -11202,10 +11202,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>496759</v>
+        <v>496588</v>
       </c>
       <c r="R101" t="n">
-        <v>6827133</v>
+        <v>6827066</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11235,19 +11235,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z101" t="inlineStr">
-        <is>
-          <t>10:48</t>
-        </is>
-      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB101" t="inlineStr">
-        <is>
-          <t>10:48</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11262,19 +11252,19 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>130256391</v>
+        <v>130256375</v>
       </c>
       <c r="B102" t="n">
         <v>79211</v>
@@ -11309,10 +11299,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>496588</v>
+        <v>496859</v>
       </c>
       <c r="R102" t="n">
-        <v>6827066</v>
+        <v>6827052</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11371,7 +11361,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>130256375</v>
+        <v>130255825</v>
       </c>
       <c r="B103" t="n">
         <v>79211</v>
@@ -11406,10 +11396,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>496859</v>
+        <v>496759</v>
       </c>
       <c r="R103" t="n">
-        <v>6827052</v>
+        <v>6827133</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11439,9 +11429,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11456,12 +11456,12 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
@@ -11983,7 +11983,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>130256386</v>
+        <v>130256374</v>
       </c>
       <c r="B109" t="n">
         <v>79211</v>
@@ -12018,10 +12018,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>496723</v>
+        <v>496863</v>
       </c>
       <c r="R109" t="n">
-        <v>6827125</v>
+        <v>6827047</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12177,10 +12177,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>130256374</v>
+        <v>130256354</v>
       </c>
       <c r="B111" t="n">
-        <v>79211</v>
+        <v>78968</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12188,21 +12188,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12212,10 +12212,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>496863</v>
+        <v>496654</v>
       </c>
       <c r="R111" t="n">
-        <v>6827047</v>
+        <v>6827171</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12274,10 +12274,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>130256354</v>
+        <v>130255819</v>
       </c>
       <c r="B112" t="n">
-        <v>78968</v>
+        <v>79211</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12285,21 +12285,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12309,10 +12309,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>496654</v>
+        <v>496850</v>
       </c>
       <c r="R112" t="n">
-        <v>6827171</v>
+        <v>6827090</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12342,9 +12342,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12359,19 +12369,19 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>130255819</v>
+        <v>130256386</v>
       </c>
       <c r="B113" t="n">
         <v>79211</v>
@@ -12406,10 +12416,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>496850</v>
+        <v>496723</v>
       </c>
       <c r="R113" t="n">
-        <v>6827090</v>
+        <v>6827125</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12439,19 +12449,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z113" t="inlineStr">
-        <is>
-          <t>11:05</t>
-        </is>
-      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB113" t="inlineStr">
-        <is>
-          <t>11:05</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12466,12 +12466,12 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
@@ -12588,7 +12588,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>130255802</v>
+        <v>130256380</v>
       </c>
       <c r="B115" t="n">
         <v>79211</v>
@@ -12623,10 +12623,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>496785</v>
+        <v>496852</v>
       </c>
       <c r="R115" t="n">
-        <v>6827060</v>
+        <v>6827074</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12656,19 +12656,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z115" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB115" t="inlineStr">
-        <is>
-          <t>12:47</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12683,19 +12673,19 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>130256380</v>
+        <v>130255802</v>
       </c>
       <c r="B116" t="n">
         <v>79211</v>
@@ -12730,10 +12720,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>496852</v>
+        <v>496785</v>
       </c>
       <c r="R116" t="n">
-        <v>6827074</v>
+        <v>6827060</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12763,9 +12753,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12780,12 +12780,12 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
@@ -12889,54 +12889,45 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>130256348</v>
+        <v>130256381</v>
       </c>
       <c r="B118" t="n">
-        <v>8451</v>
+        <v>79211</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="J118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>496864</v>
+        <v>496852</v>
       </c>
       <c r="R118" t="n">
-        <v>6827043</v>
+        <v>6827066</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12977,7 +12968,6 @@
       <c r="AE118" t="b">
         <v>0</v>
       </c>
-      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
@@ -13103,7 +13093,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>130255801</v>
+        <v>130256382</v>
       </c>
       <c r="B120" t="n">
         <v>79211</v>
@@ -13138,10 +13128,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>496702</v>
+        <v>496831</v>
       </c>
       <c r="R120" t="n">
-        <v>6827131</v>
+        <v>6827081</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13171,19 +13161,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z120" t="inlineStr">
-        <is>
-          <t>10:39</t>
-        </is>
-      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB120" t="inlineStr">
-        <is>
-          <t>10:39</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13198,57 +13178,66 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>130256382</v>
+        <v>130256348</v>
       </c>
       <c r="B121" t="n">
-        <v>79211</v>
+        <v>8451</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>496831</v>
+        <v>496864</v>
       </c>
       <c r="R121" t="n">
-        <v>6827081</v>
+        <v>6827043</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13289,6 +13278,7 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
+      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -13307,7 +13297,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>130256381</v>
+        <v>130256363</v>
       </c>
       <c r="B122" t="n">
         <v>79211</v>
@@ -13342,10 +13332,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>496852</v>
+        <v>496897</v>
       </c>
       <c r="R122" t="n">
-        <v>6827066</v>
+        <v>6827002</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13501,7 +13491,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>130256363</v>
+        <v>130256359</v>
       </c>
       <c r="B124" t="n">
         <v>79211</v>
@@ -13536,10 +13526,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>496897</v>
+        <v>496963</v>
       </c>
       <c r="R124" t="n">
-        <v>6827002</v>
+        <v>6826942</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13598,7 +13588,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>130256390</v>
+        <v>130255801</v>
       </c>
       <c r="B125" t="n">
         <v>79211</v>
@@ -13633,10 +13623,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>496581</v>
+        <v>496702</v>
       </c>
       <c r="R125" t="n">
-        <v>6827049</v>
+        <v>6827131</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13666,9 +13656,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13683,19 +13683,19 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>130256359</v>
+        <v>130256390</v>
       </c>
       <c r="B126" t="n">
         <v>79211</v>
@@ -13730,10 +13730,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>496963</v>
+        <v>496581</v>
       </c>
       <c r="R126" t="n">
-        <v>6826942</v>
+        <v>6827049</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13792,45 +13792,54 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>130255834</v>
+        <v>130255793</v>
       </c>
       <c r="B127" t="n">
-        <v>79211</v>
+        <v>8451</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>496582</v>
+        <v>496670</v>
       </c>
       <c r="R127" t="n">
-        <v>6827040</v>
+        <v>6827136</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13862,7 +13871,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -13872,7 +13881,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13881,6 +13890,7 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
+      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
@@ -13899,45 +13909,54 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>130255836</v>
+        <v>130256349</v>
       </c>
       <c r="B128" t="n">
-        <v>79211</v>
+        <v>8451</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>497183</v>
+        <v>496714</v>
       </c>
       <c r="R128" t="n">
-        <v>6826662</v>
+        <v>6827127</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13967,84 +13986,84 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z128" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="AB128" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AD128" t="b">
         <v>0</v>
       </c>
       <c r="AE128" t="b">
         <v>0</v>
       </c>
+      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>130255805</v>
+        <v>130256347</v>
       </c>
       <c r="B129" t="n">
-        <v>79211</v>
+        <v>8451</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>497139</v>
+        <v>496941</v>
       </c>
       <c r="R129" t="n">
-        <v>6826719</v>
+        <v>6826899</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14074,46 +14093,37 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z129" t="inlineStr">
-        <is>
-          <t>12:17</t>
-        </is>
-      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="AB129" t="inlineStr">
-        <is>
-          <t>12:17</t>
-        </is>
-      </c>
       <c r="AD129" t="b">
         <v>0</v>
       </c>
       <c r="AE129" t="b">
         <v>0</v>
       </c>
+      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>130256343</v>
+        <v>130255834</v>
       </c>
       <c r="B130" t="n">
         <v>79211</v>
@@ -14148,10 +14158,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>496851</v>
+        <v>496582</v>
       </c>
       <c r="R130" t="n">
-        <v>6827066</v>
+        <v>6827040</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14181,9 +14191,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14198,66 +14218,57 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>130255793</v>
+        <v>130255836</v>
       </c>
       <c r="B131" t="n">
-        <v>8451</v>
+        <v>79211</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="J131" t="inlineStr"/>
-      <c r="K131" t="inlineStr"/>
-      <c r="L131" t="inlineStr"/>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>496670</v>
+        <v>497183</v>
       </c>
       <c r="R131" t="n">
-        <v>6827136</v>
+        <v>6826662</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14289,7 +14300,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -14299,7 +14310,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14308,7 +14319,6 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
-      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
@@ -14327,54 +14337,45 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>130256349</v>
+        <v>130255805</v>
       </c>
       <c r="B132" t="n">
-        <v>8451</v>
+        <v>79211</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr"/>
-      <c r="K132" t="inlineStr"/>
-      <c r="L132" t="inlineStr"/>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>496714</v>
+        <v>497139</v>
       </c>
       <c r="R132" t="n">
-        <v>6827127</v>
+        <v>6826719</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14404,84 +14405,84 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="AB132" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
       <c r="AD132" t="b">
         <v>0</v>
       </c>
       <c r="AE132" t="b">
         <v>0</v>
       </c>
-      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>130256347</v>
+        <v>130256343</v>
       </c>
       <c r="B133" t="n">
-        <v>8451</v>
+        <v>79211</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
-      <c r="L133" t="inlineStr"/>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>496941</v>
+        <v>496851</v>
       </c>
       <c r="R133" t="n">
-        <v>6826899</v>
+        <v>6827066</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14522,7 +14523,6 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
-      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
@@ -14544,7 +14544,7 @@
         <v>130256392</v>
       </c>
       <c r="B134" t="n">
-        <v>93043</v>
+        <v>93047</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15154,7 +15154,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>130256389</v>
+        <v>130256358</v>
       </c>
       <c r="B140" t="n">
         <v>79211</v>
@@ -15189,10 +15189,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>496578</v>
+        <v>496962</v>
       </c>
       <c r="R140" t="n">
-        <v>6827076</v>
+        <v>6826923</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15348,7 +15348,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>130256358</v>
+        <v>130256389</v>
       </c>
       <c r="B142" t="n">
         <v>79211</v>
@@ -15383,10 +15383,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>496962</v>
+        <v>496578</v>
       </c>
       <c r="R142" t="n">
-        <v>6826923</v>
+        <v>6827076</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15445,10 +15445,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>130255828</v>
+        <v>130256340</v>
       </c>
       <c r="B143" t="n">
-        <v>79211</v>
+        <v>79801</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15456,21 +15456,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15480,10 +15480,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>496658</v>
+        <v>496774</v>
       </c>
       <c r="R143" t="n">
-        <v>6827133</v>
+        <v>6827067</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15513,19 +15513,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z143" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB143" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15540,19 +15530,19 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>130255821</v>
+        <v>130256355</v>
       </c>
       <c r="B144" t="n">
         <v>79211</v>
@@ -15587,10 +15577,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>496839</v>
+        <v>496940</v>
       </c>
       <c r="R144" t="n">
-        <v>6827082</v>
+        <v>6826898</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15620,19 +15610,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z144" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AA144" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB144" t="inlineStr">
-        <is>
-          <t>11:04</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15647,19 +15627,19 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>130256362</v>
+        <v>130256371</v>
       </c>
       <c r="B145" t="n">
         <v>79211</v>
@@ -15694,10 +15674,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>496893</v>
+        <v>496880</v>
       </c>
       <c r="R145" t="n">
-        <v>6826998</v>
+        <v>6827036</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15756,7 +15736,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>130256355</v>
+        <v>130255828</v>
       </c>
       <c r="B146" t="n">
         <v>79211</v>
@@ -15791,10 +15771,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>496940</v>
+        <v>496658</v>
       </c>
       <c r="R146" t="n">
-        <v>6826898</v>
+        <v>6827133</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15824,9 +15804,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z146" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA146" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB146" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15841,19 +15831,19 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>130256371</v>
+        <v>130255821</v>
       </c>
       <c r="B147" t="n">
         <v>79211</v>
@@ -15888,10 +15878,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>496880</v>
+        <v>496839</v>
       </c>
       <c r="R147" t="n">
-        <v>6827036</v>
+        <v>6827082</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15921,9 +15911,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z147" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AA147" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB147" t="inlineStr">
+        <is>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15938,19 +15938,19 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>130256364</v>
+        <v>130256362</v>
       </c>
       <c r="B148" t="n">
         <v>79211</v>
@@ -15985,10 +15985,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>496909</v>
+        <v>496893</v>
       </c>
       <c r="R148" t="n">
-        <v>6827002</v>
+        <v>6826998</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16047,10 +16047,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>130256340</v>
+        <v>130256364</v>
       </c>
       <c r="B149" t="n">
-        <v>79801</v>
+        <v>79211</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16058,21 +16058,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16082,10 +16082,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>496774</v>
+        <v>496909</v>
       </c>
       <c r="R149" t="n">
-        <v>6827067</v>
+        <v>6827002</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16147,7 +16147,7 @@
         <v>130256394</v>
       </c>
       <c r="B150" t="n">
-        <v>93043</v>
+        <v>93047</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16253,7 +16253,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>130255811</v>
+        <v>130256372</v>
       </c>
       <c r="B151" t="n">
         <v>79211</v>
@@ -16288,10 +16288,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>497200</v>
+        <v>496867</v>
       </c>
       <c r="R151" t="n">
-        <v>6826832</v>
+        <v>6827035</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16321,19 +16321,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z151" t="inlineStr">
-        <is>
-          <t>11:53</t>
-        </is>
-      </c>
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB151" t="inlineStr">
-        <is>
-          <t>11:53</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16348,19 +16338,19 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>130255831</v>
+        <v>130255811</v>
       </c>
       <c r="B152" t="n">
         <v>79211</v>
@@ -16395,10 +16385,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>496599</v>
+        <v>497200</v>
       </c>
       <c r="R152" t="n">
-        <v>6827121</v>
+        <v>6826832</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16430,7 +16420,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -16440,7 +16430,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16467,7 +16457,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>130255824</v>
+        <v>130255831</v>
       </c>
       <c r="B153" t="n">
         <v>79211</v>
@@ -16502,10 +16492,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>496752</v>
+        <v>496599</v>
       </c>
       <c r="R153" t="n">
-        <v>6827114</v>
+        <v>6827121</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16537,7 +16527,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -16547,7 +16537,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16574,7 +16564,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>130256372</v>
+        <v>130255824</v>
       </c>
       <c r="B154" t="n">
         <v>79211</v>
@@ -16609,10 +16599,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>496867</v>
+        <v>496752</v>
       </c>
       <c r="R154" t="n">
-        <v>6827035</v>
+        <v>6827114</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16642,9 +16632,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z154" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
       <c r="AA154" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB154" t="inlineStr">
+        <is>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16659,12 +16659,12 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
@@ -16771,7 +16771,7 @@
         <v>130255838</v>
       </c>
       <c r="B156" t="n">
-        <v>93043</v>
+        <v>93047</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17199,7 +17199,7 @@
         <v>130256393</v>
       </c>
       <c r="B160" t="n">
-        <v>93043</v>
+        <v>93047</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>

--- a/artfynd/A 58895-2025 artfynd.xlsx
+++ b/artfynd/A 58895-2025 artfynd.xlsx
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130252591</v>
+        <v>130252584</v>
       </c>
       <c r="B3" t="n">
-        <v>78968</v>
+        <v>58013</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,21 +801,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>496966</v>
+        <v>497202</v>
       </c>
       <c r="R3" t="n">
-        <v>6826906</v>
+        <v>6826919</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,32 +897,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130252116</v>
+        <v>130252120</v>
       </c>
       <c r="B4" t="n">
-        <v>79830</v>
+        <v>8451</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>496721</v>
+        <v>496653</v>
       </c>
       <c r="R4" t="n">
-        <v>6827083</v>
+        <v>6827111</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -967,7 +967,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,10 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130252584</v>
+        <v>130252591</v>
       </c>
       <c r="B5" t="n">
-        <v>58013</v>
+        <v>78968</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1015,21 +1015,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497202</v>
+        <v>496966</v>
       </c>
       <c r="R5" t="n">
-        <v>6826919</v>
+        <v>6826906</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,32 +1111,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130252120</v>
+        <v>130252116</v>
       </c>
       <c r="B6" t="n">
-        <v>8451</v>
+        <v>79830</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1146,10 +1146,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>496653</v>
+        <v>496721</v>
       </c>
       <c r="R6" t="n">
-        <v>6827111</v>
+        <v>6827083</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1432,10 +1432,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130252126</v>
+        <v>130252138</v>
       </c>
       <c r="B9" t="n">
-        <v>78968</v>
+        <v>79211</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1443,21 +1443,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>496737</v>
+        <v>497207</v>
       </c>
       <c r="R9" t="n">
-        <v>6827071</v>
+        <v>6826726</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1512,7 +1512,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1539,7 +1539,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130252592</v>
+        <v>130252126</v>
       </c>
       <c r="B10" t="n">
         <v>78968</v>
@@ -1570,14 +1570,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>496950</v>
+        <v>496737</v>
       </c>
       <c r="R10" t="n">
-        <v>6827038</v>
+        <v>6827071</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1634,22 +1634,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130252115</v>
+        <v>130252592</v>
       </c>
       <c r="B11" t="n">
-        <v>79243</v>
+        <v>78968</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1657,34 +1657,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>496555</v>
+        <v>496950</v>
       </c>
       <c r="R11" t="n">
-        <v>6826991</v>
+        <v>6827038</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,29 +1735,28 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130252138</v>
+        <v>130252588</v>
       </c>
       <c r="B12" t="n">
-        <v>79211</v>
+        <v>78968</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1765,34 +1764,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497207</v>
+        <v>497230</v>
       </c>
       <c r="R12" t="n">
-        <v>6826726</v>
+        <v>6826961</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1824,7 +1823,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1834,7 +1833,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1849,57 +1848,57 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130252588</v>
+        <v>130252156</v>
       </c>
       <c r="B13" t="n">
-        <v>78968</v>
+        <v>93047</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>497230</v>
+        <v>496675</v>
       </c>
       <c r="R13" t="n">
-        <v>6826961</v>
+        <v>6827138</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1931,7 +1930,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1941,7 +1940,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1956,44 +1955,44 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130252156</v>
+        <v>130252115</v>
       </c>
       <c r="B14" t="n">
-        <v>93047</v>
+        <v>79243</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>185</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2003,10 +2002,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>496675</v>
+        <v>496555</v>
       </c>
       <c r="R14" t="n">
-        <v>6827138</v>
+        <v>6826991</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2038,7 +2037,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2048,7 +2047,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2057,6 +2056,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2075,32 +2075,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130252119</v>
+        <v>130252154</v>
       </c>
       <c r="B15" t="n">
-        <v>58013</v>
+        <v>93047</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2110,10 +2110,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>496602</v>
+        <v>496692</v>
       </c>
       <c r="R15" t="n">
-        <v>6827039</v>
+        <v>6827092</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2145,7 +2145,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2182,32 +2182,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130252154</v>
+        <v>130252119</v>
       </c>
       <c r="B16" t="n">
-        <v>93047</v>
+        <v>58013</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2217,10 +2217,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>496692</v>
+        <v>496602</v>
       </c>
       <c r="R16" t="n">
-        <v>6827092</v>
+        <v>6827039</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2396,32 +2396,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130252125</v>
+        <v>130252123</v>
       </c>
       <c r="B18" t="n">
-        <v>78968</v>
+        <v>8451</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2431,10 +2431,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>497154</v>
+        <v>496581</v>
       </c>
       <c r="R18" t="n">
-        <v>6826854</v>
+        <v>6827019</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2476,7 +2476,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2503,7 +2503,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130252594</v>
+        <v>130252125</v>
       </c>
       <c r="B19" t="n">
         <v>78968</v>
@@ -2534,14 +2534,14 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>496874</v>
+        <v>497154</v>
       </c>
       <c r="R19" t="n">
-        <v>6827149</v>
+        <v>6826854</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2598,12 +2598,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2824,45 +2824,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130252123</v>
+        <v>130252594</v>
       </c>
       <c r="B22" t="n">
-        <v>8451</v>
+        <v>78968</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>496581</v>
+        <v>496874</v>
       </c>
       <c r="R22" t="n">
-        <v>6827019</v>
+        <v>6827149</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2904,7 +2904,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2919,12 +2919,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3252,7 +3252,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130252127</v>
+        <v>130252595</v>
       </c>
       <c r="B26" t="n">
         <v>78968</v>
@@ -3283,14 +3283,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>496719</v>
+        <v>496894</v>
       </c>
       <c r="R26" t="n">
-        <v>6827076</v>
+        <v>6827123</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3322,7 +3322,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3347,22 +3347,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130252600</v>
+        <v>130252127</v>
       </c>
       <c r="B27" t="n">
-        <v>79211</v>
+        <v>78968</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3370,34 +3370,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>496948</v>
+        <v>496719</v>
       </c>
       <c r="R27" t="n">
-        <v>6827029</v>
+        <v>6827076</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3429,7 +3429,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3439,7 +3439,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3454,22 +3454,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130252595</v>
+        <v>130252600</v>
       </c>
       <c r="B28" t="n">
-        <v>78968</v>
+        <v>79211</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3477,21 +3477,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3501,10 +3501,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>496894</v>
+        <v>496948</v>
       </c>
       <c r="R28" t="n">
-        <v>6827123</v>
+        <v>6827029</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3536,7 +3536,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3546,7 +3546,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4108,7 +4108,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130252143</v>
+        <v>130252135</v>
       </c>
       <c r="B34" t="n">
         <v>79211</v>
@@ -4143,10 +4143,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>496877</v>
+        <v>496915</v>
       </c>
       <c r="R34" t="n">
-        <v>6827056</v>
+        <v>6826903</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4215,32 +4215,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130252587</v>
+        <v>130252604</v>
       </c>
       <c r="B35" t="n">
-        <v>8451</v>
+        <v>79211</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4250,10 +4250,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>496719</v>
+        <v>496679</v>
       </c>
       <c r="R35" t="n">
-        <v>6827112</v>
+        <v>6827141</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4285,7 +4285,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4295,7 +4295,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4322,7 +4322,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130252604</v>
+        <v>130252146</v>
       </c>
       <c r="B36" t="n">
         <v>79211</v>
@@ -4353,14 +4353,14 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>496679</v>
+        <v>496864</v>
       </c>
       <c r="R36" t="n">
-        <v>6827141</v>
+        <v>6827053</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4417,19 +4417,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130252135</v>
+        <v>130252143</v>
       </c>
       <c r="B37" t="n">
         <v>79211</v>
@@ -4464,10 +4464,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>496915</v>
+        <v>496877</v>
       </c>
       <c r="R37" t="n">
-        <v>6826903</v>
+        <v>6827056</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4509,7 +4509,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4536,7 +4536,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130252146</v>
+        <v>130252605</v>
       </c>
       <c r="B38" t="n">
         <v>79211</v>
@@ -4567,14 +4567,14 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>496864</v>
+        <v>496676</v>
       </c>
       <c r="R38" t="n">
-        <v>6827053</v>
+        <v>6827143</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4631,44 +4631,44 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130252605</v>
+        <v>130252587</v>
       </c>
       <c r="B39" t="n">
-        <v>79211</v>
+        <v>8451</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4678,10 +4678,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>496676</v>
+        <v>496719</v>
       </c>
       <c r="R39" t="n">
-        <v>6827143</v>
+        <v>6827112</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4723,7 +4723,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5071,53 +5071,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130252585</v>
+        <v>130252158</v>
       </c>
       <c r="B43" t="n">
-        <v>57851</v>
+        <v>93047</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>496635</v>
+        <v>496629</v>
       </c>
       <c r="R43" t="n">
-        <v>6827130</v>
+        <v>6827128</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5149,7 +5141,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5159,7 +5151,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5174,19 +5166,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130252158</v>
+        <v>130252607</v>
       </c>
       <c r="B44" t="n">
         <v>93047</v>
@@ -5217,14 +5209,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>496629</v>
+        <v>496598</v>
       </c>
       <c r="R44" t="n">
-        <v>6827128</v>
+        <v>6827085</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5256,7 +5248,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5266,7 +5258,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5275,63 +5267,72 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130252607</v>
+        <v>130252585</v>
       </c>
       <c r="B45" t="n">
-        <v>93047</v>
+        <v>57851</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>496598</v>
+        <v>496635</v>
       </c>
       <c r="R45" t="n">
-        <v>6827085</v>
+        <v>6827130</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5363,7 +5364,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5373,7 +5374,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5382,7 +5383,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5401,45 +5401,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130252153</v>
+        <v>130252609</v>
       </c>
       <c r="B46" t="n">
-        <v>79211</v>
+        <v>93047</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>496564</v>
+        <v>496549</v>
       </c>
       <c r="R46" t="n">
-        <v>6827012</v>
+        <v>6826988</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5471,7 +5471,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5490,18 +5490,19 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5722,45 +5723,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130252609</v>
+        <v>130252153</v>
       </c>
       <c r="B49" t="n">
-        <v>93047</v>
+        <v>79211</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>496549</v>
+        <v>496564</v>
       </c>
       <c r="R49" t="n">
-        <v>6826988</v>
+        <v>6827012</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5792,7 +5793,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5802,7 +5803,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5811,26 +5812,25 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130252140</v>
+        <v>130252147</v>
       </c>
       <c r="B50" t="n">
         <v>79211</v>
@@ -5865,10 +5865,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>497211</v>
+        <v>496781</v>
       </c>
       <c r="R50" t="n">
-        <v>6826809</v>
+        <v>6827069</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5900,7 +5900,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5910,7 +5910,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5937,7 +5937,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130252147</v>
+        <v>130252140</v>
       </c>
       <c r="B51" t="n">
         <v>79211</v>
@@ -5972,10 +5972,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>496781</v>
+        <v>497211</v>
       </c>
       <c r="R51" t="n">
-        <v>6827069</v>
+        <v>6826809</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6007,7 +6007,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6017,7 +6017,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6151,41 +6151,40 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130252130</v>
+        <v>130252118</v>
       </c>
       <c r="B53" t="n">
-        <v>44108</v>
+        <v>57854</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>101735</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
@@ -6195,10 +6194,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>497225</v>
+        <v>496923</v>
       </c>
       <c r="R53" t="n">
-        <v>6826804</v>
+        <v>6826913</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6230,7 +6229,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6240,7 +6239,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6249,7 +6253,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6268,40 +6271,41 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130252118</v>
+        <v>130252130</v>
       </c>
       <c r="B54" t="n">
-        <v>57854</v>
+        <v>44108</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>101735</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
@@ -6311,10 +6315,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>496923</v>
+        <v>497225</v>
       </c>
       <c r="R54" t="n">
-        <v>6826913</v>
+        <v>6826804</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6346,7 +6350,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6356,12 +6360,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:50</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6370,6 +6369,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6388,10 +6388,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130252596</v>
+        <v>130252117</v>
       </c>
       <c r="B55" t="n">
-        <v>78968</v>
+        <v>79801</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6399,34 +6399,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>496771</v>
+        <v>497155</v>
       </c>
       <c r="R55" t="n">
-        <v>6827069</v>
+        <v>6826856</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6458,7 +6458,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6468,7 +6468,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6483,22 +6483,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130252137</v>
+        <v>130252596</v>
       </c>
       <c r="B56" t="n">
-        <v>79211</v>
+        <v>78968</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6506,34 +6506,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>497206</v>
+        <v>496771</v>
       </c>
       <c r="R56" t="n">
-        <v>6826638</v>
+        <v>6827069</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6565,7 +6565,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6575,7 +6575,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6590,57 +6590,57 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130252606</v>
+        <v>130252137</v>
       </c>
       <c r="B57" t="n">
-        <v>93047</v>
+        <v>79211</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>496618</v>
+        <v>497206</v>
       </c>
       <c r="R57" t="n">
-        <v>6827114</v>
+        <v>6826638</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6672,7 +6672,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6682,7 +6682,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6691,64 +6691,63 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130252117</v>
+        <v>130252606</v>
       </c>
       <c r="B58" t="n">
-        <v>79801</v>
+        <v>93047</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>497155</v>
+        <v>496618</v>
       </c>
       <c r="R58" t="n">
-        <v>6826856</v>
+        <v>6827114</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6780,7 +6779,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6790,7 +6789,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6799,18 +6798,19 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -7352,45 +7352,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130252139</v>
+        <v>130252608</v>
       </c>
       <c r="B64" t="n">
-        <v>79211</v>
+        <v>93047</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>497225</v>
+        <v>496576</v>
       </c>
       <c r="R64" t="n">
-        <v>6826804</v>
+        <v>6826998</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7422,7 +7422,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7432,7 +7432,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7441,25 +7441,26 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130252151</v>
+        <v>130252139</v>
       </c>
       <c r="B65" t="n">
         <v>79211</v>
@@ -7494,10 +7495,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>496704</v>
+        <v>497225</v>
       </c>
       <c r="R65" t="n">
-        <v>6827086</v>
+        <v>6826804</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7529,7 +7530,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7539,7 +7540,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7566,7 +7567,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130252597</v>
+        <v>130252151</v>
       </c>
       <c r="B66" t="n">
         <v>79211</v>
@@ -7597,14 +7598,14 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>496922</v>
+        <v>496704</v>
       </c>
       <c r="R66" t="n">
-        <v>6826906</v>
+        <v>6827086</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7636,7 +7637,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7646,7 +7647,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7661,22 +7662,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130252114</v>
+        <v>130252597</v>
       </c>
       <c r="B67" t="n">
-        <v>79243</v>
+        <v>79211</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7684,34 +7685,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>496880</v>
+        <v>496922</v>
       </c>
       <c r="R67" t="n">
-        <v>6827051</v>
+        <v>6826906</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7743,7 +7744,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7753,7 +7754,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7762,64 +7763,63 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130252608</v>
+        <v>130252114</v>
       </c>
       <c r="B68" t="n">
-        <v>93047</v>
+        <v>79243</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4364</v>
+        <v>185</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>496576</v>
+        <v>496880</v>
       </c>
       <c r="R68" t="n">
-        <v>6826998</v>
+        <v>6827051</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7851,7 +7851,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7861,7 +7861,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7877,12 +7877,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
@@ -8505,7 +8505,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130255830</v>
+        <v>130256369</v>
       </c>
       <c r="B75" t="n">
         <v>79211</v>
@@ -8540,10 +8540,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>496649</v>
+        <v>496893</v>
       </c>
       <c r="R75" t="n">
-        <v>6827117</v>
+        <v>6827043</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8573,19 +8573,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>10:23</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>10:23</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8600,19 +8590,19 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>130255820</v>
+        <v>130255830</v>
       </c>
       <c r="B76" t="n">
         <v>79211</v>
@@ -8647,10 +8637,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>496838</v>
+        <v>496649</v>
       </c>
       <c r="R76" t="n">
-        <v>6827085</v>
+        <v>6827117</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8682,7 +8672,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8692,7 +8682,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8719,7 +8709,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>130256369</v>
+        <v>130255820</v>
       </c>
       <c r="B77" t="n">
         <v>79211</v>
@@ -8754,10 +8744,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>496893</v>
+        <v>496838</v>
       </c>
       <c r="R77" t="n">
-        <v>6827043</v>
+        <v>6827085</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8787,9 +8777,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8804,22 +8804,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>130255797</v>
+        <v>130256383</v>
       </c>
       <c r="B78" t="n">
-        <v>78968</v>
+        <v>79211</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8827,21 +8827,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8851,10 +8851,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>497218</v>
+        <v>496821</v>
       </c>
       <c r="R78" t="n">
-        <v>6826761</v>
+        <v>6827087</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8884,19 +8884,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>11:59</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>11:59</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8911,19 +8901,19 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>130256383</v>
+        <v>130256365</v>
       </c>
       <c r="B79" t="n">
         <v>79211</v>
@@ -8958,10 +8948,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>496821</v>
+        <v>496920</v>
       </c>
       <c r="R79" t="n">
-        <v>6827087</v>
+        <v>6827003</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9020,10 +9010,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>130256376</v>
+        <v>130255797</v>
       </c>
       <c r="B80" t="n">
-        <v>79211</v>
+        <v>78968</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9031,21 +9021,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9055,10 +9045,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>496855</v>
+        <v>497218</v>
       </c>
       <c r="R80" t="n">
-        <v>6827052</v>
+        <v>6826761</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9088,9 +9078,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9105,19 +9105,19 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>130256368</v>
+        <v>130256376</v>
       </c>
       <c r="B81" t="n">
         <v>79211</v>
@@ -9152,10 +9152,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>496902</v>
+        <v>496855</v>
       </c>
       <c r="R81" t="n">
-        <v>6827030</v>
+        <v>6827052</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9214,7 +9214,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>130256365</v>
+        <v>130256368</v>
       </c>
       <c r="B82" t="n">
         <v>79211</v>
@@ -9249,10 +9249,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>496920</v>
+        <v>496902</v>
       </c>
       <c r="R82" t="n">
-        <v>6827003</v>
+        <v>6827030</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9311,10 +9311,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>130255837</v>
+        <v>130256346</v>
       </c>
       <c r="B83" t="n">
-        <v>79211</v>
+        <v>78969</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9322,21 +9322,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9346,10 +9346,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>497191</v>
+        <v>496652</v>
       </c>
       <c r="R83" t="n">
-        <v>6826771</v>
+        <v>6827164</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9379,19 +9379,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>12:00</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9406,22 +9396,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>130256346</v>
+        <v>130255837</v>
       </c>
       <c r="B84" t="n">
-        <v>78969</v>
+        <v>79211</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9429,21 +9419,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9453,10 +9443,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>496652</v>
+        <v>497191</v>
       </c>
       <c r="R84" t="n">
-        <v>6827164</v>
+        <v>6826771</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9486,9 +9476,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9503,44 +9503,44 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>130255839</v>
+        <v>130256352</v>
       </c>
       <c r="B85" t="n">
-        <v>93047</v>
+        <v>78968</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9550,10 +9550,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>496787</v>
+        <v>496837</v>
       </c>
       <c r="R85" t="n">
-        <v>6827052</v>
+        <v>6827069</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9583,19 +9583,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9610,44 +9600,44 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>130256352</v>
+        <v>130255839</v>
       </c>
       <c r="B86" t="n">
-        <v>78968</v>
+        <v>93047</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9657,10 +9647,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>496837</v>
+        <v>496787</v>
       </c>
       <c r="R86" t="n">
-        <v>6827069</v>
+        <v>6827052</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9690,9 +9680,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9707,19 +9707,19 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>130255803</v>
+        <v>130255823</v>
       </c>
       <c r="B87" t="n">
         <v>79211</v>
@@ -9754,10 +9754,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>497148</v>
+        <v>496757</v>
       </c>
       <c r="R87" t="n">
-        <v>6826907</v>
+        <v>6827109</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9789,7 +9789,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9799,7 +9799,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9826,7 +9826,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>130255818</v>
+        <v>130255803</v>
       </c>
       <c r="B88" t="n">
         <v>79211</v>
@@ -9861,10 +9861,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>496862</v>
+        <v>497148</v>
       </c>
       <c r="R88" t="n">
-        <v>6827065</v>
+        <v>6826907</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9896,7 +9896,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -9906,7 +9906,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9933,7 +9933,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>130256387</v>
+        <v>130255818</v>
       </c>
       <c r="B89" t="n">
         <v>79211</v>
@@ -9968,10 +9968,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>496715</v>
+        <v>496862</v>
       </c>
       <c r="R89" t="n">
-        <v>6827126</v>
+        <v>6827065</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10001,9 +10001,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10018,19 +10028,19 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>130255814</v>
+        <v>130256387</v>
       </c>
       <c r="B90" t="n">
         <v>79211</v>
@@ -10065,10 +10075,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>497073</v>
+        <v>496715</v>
       </c>
       <c r="R90" t="n">
-        <v>6827132</v>
+        <v>6827126</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10098,19 +10108,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>11:27</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>11:27</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10125,19 +10125,19 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>130255823</v>
+        <v>130255814</v>
       </c>
       <c r="B91" t="n">
         <v>79211</v>
@@ -10172,10 +10172,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>496757</v>
+        <v>497073</v>
       </c>
       <c r="R91" t="n">
-        <v>6827109</v>
+        <v>6827132</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10207,7 +10207,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10217,7 +10217,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -12889,7 +12889,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>130256381</v>
+        <v>130256390</v>
       </c>
       <c r="B118" t="n">
         <v>79211</v>
@@ -12924,10 +12924,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>496852</v>
+        <v>496581</v>
       </c>
       <c r="R118" t="n">
-        <v>6827066</v>
+        <v>6827049</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12986,10 +12986,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>130255796</v>
+        <v>130256363</v>
       </c>
       <c r="B119" t="n">
-        <v>78968</v>
+        <v>79211</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12997,21 +12997,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13021,10 +13021,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>497111</v>
+        <v>496897</v>
       </c>
       <c r="R119" t="n">
-        <v>6826644</v>
+        <v>6827002</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13054,19 +13054,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z119" t="inlineStr">
-        <is>
-          <t>12:13</t>
-        </is>
-      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB119" t="inlineStr">
-        <is>
-          <t>12:13</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13081,19 +13071,19 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>130256382</v>
+        <v>130256381</v>
       </c>
       <c r="B120" t="n">
         <v>79211</v>
@@ -13128,10 +13118,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>496831</v>
+        <v>496852</v>
       </c>
       <c r="R120" t="n">
-        <v>6827081</v>
+        <v>6827066</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13190,54 +13180,45 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>130256348</v>
+        <v>130255796</v>
       </c>
       <c r="B121" t="n">
-        <v>8451</v>
+        <v>78968</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>496864</v>
+        <v>497111</v>
       </c>
       <c r="R121" t="n">
-        <v>6827043</v>
+        <v>6826644</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13267,37 +13248,46 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
       <c r="AD121" t="b">
         <v>0</v>
       </c>
       <c r="AE121" t="b">
         <v>0</v>
       </c>
-      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>130256363</v>
+        <v>130256378</v>
       </c>
       <c r="B122" t="n">
         <v>79211</v>
@@ -13332,10 +13322,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>496897</v>
+        <v>496862</v>
       </c>
       <c r="R122" t="n">
-        <v>6827002</v>
+        <v>6827064</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13394,7 +13384,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>130256378</v>
+        <v>130256382</v>
       </c>
       <c r="B123" t="n">
         <v>79211</v>
@@ -13429,10 +13419,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>496862</v>
+        <v>496831</v>
       </c>
       <c r="R123" t="n">
-        <v>6827064</v>
+        <v>6827081</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13695,45 +13685,54 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>130256390</v>
+        <v>130256348</v>
       </c>
       <c r="B126" t="n">
-        <v>79211</v>
+        <v>8451</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>496581</v>
+        <v>496864</v>
       </c>
       <c r="R126" t="n">
-        <v>6827049</v>
+        <v>6827043</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13774,6 +13773,7 @@
       <c r="AE126" t="b">
         <v>0</v>
       </c>
+      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
@@ -13792,10 +13792,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>130255793</v>
+        <v>130256392</v>
       </c>
       <c r="B127" t="n">
-        <v>8451</v>
+        <v>93047</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13803,43 +13803,34 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
-      <c r="K127" t="inlineStr"/>
-      <c r="L127" t="inlineStr"/>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>496670</v>
+        <v>496581</v>
       </c>
       <c r="R127" t="n">
-        <v>6827136</v>
+        <v>6827082</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13869,19 +13860,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z127" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB127" t="inlineStr">
-        <is>
-          <t>10:30</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13897,19 +13878,19 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>130256349</v>
+        <v>130255793</v>
       </c>
       <c r="B128" t="n">
         <v>8451</v>
@@ -13953,10 +13934,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>496714</v>
+        <v>496670</v>
       </c>
       <c r="R128" t="n">
-        <v>6827127</v>
+        <v>6827136</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13986,9 +13967,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14004,19 +13995,19 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>130256347</v>
+        <v>130256349</v>
       </c>
       <c r="B129" t="n">
         <v>8451</v>
@@ -14060,10 +14051,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>496941</v>
+        <v>496714</v>
       </c>
       <c r="R129" t="n">
-        <v>6826899</v>
+        <v>6827127</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14123,45 +14114,54 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>130255834</v>
+        <v>130256347</v>
       </c>
       <c r="B130" t="n">
-        <v>79211</v>
+        <v>8451</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>496582</v>
+        <v>496941</v>
       </c>
       <c r="R130" t="n">
-        <v>6827040</v>
+        <v>6826899</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14191,46 +14191,37 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z130" t="inlineStr">
-        <is>
-          <t>10:10</t>
-        </is>
-      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="AB130" t="inlineStr">
-        <is>
-          <t>10:10</t>
-        </is>
-      </c>
       <c r="AD130" t="b">
         <v>0</v>
       </c>
       <c r="AE130" t="b">
         <v>0</v>
       </c>
+      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>130255836</v>
+        <v>130255834</v>
       </c>
       <c r="B131" t="n">
         <v>79211</v>
@@ -14265,10 +14256,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>497183</v>
+        <v>496582</v>
       </c>
       <c r="R131" t="n">
-        <v>6826662</v>
+        <v>6827040</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14300,7 +14291,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -14310,7 +14301,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14337,7 +14328,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>130255805</v>
+        <v>130255836</v>
       </c>
       <c r="B132" t="n">
         <v>79211</v>
@@ -14372,10 +14363,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>497139</v>
+        <v>497183</v>
       </c>
       <c r="R132" t="n">
-        <v>6826719</v>
+        <v>6826662</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14407,7 +14398,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14417,7 +14408,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14444,7 +14435,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>130256343</v>
+        <v>130255805</v>
       </c>
       <c r="B133" t="n">
         <v>79211</v>
@@ -14479,10 +14470,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>496851</v>
+        <v>497139</v>
       </c>
       <c r="R133" t="n">
-        <v>6827066</v>
+        <v>6826719</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14512,9 +14503,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z133" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
       <c r="AA133" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB133" t="inlineStr">
+        <is>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14529,44 +14530,44 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>130256392</v>
+        <v>130256343</v>
       </c>
       <c r="B134" t="n">
-        <v>93047</v>
+        <v>79211</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14576,10 +14577,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>496581</v>
+        <v>496851</v>
       </c>
       <c r="R134" t="n">
-        <v>6827082</v>
+        <v>6827066</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14620,7 +14621,6 @@
       <c r="AE134" t="b">
         <v>0</v>
       </c>
-      <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="b">
         <v>0</v>
       </c>
@@ -14639,10 +14639,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>130255806</v>
+        <v>130256345</v>
       </c>
       <c r="B135" t="n">
-        <v>79211</v>
+        <v>78969</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14650,21 +14650,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14674,10 +14674,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>497147</v>
+        <v>496837</v>
       </c>
       <c r="R135" t="n">
-        <v>6826725</v>
+        <v>6827069</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14707,19 +14707,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z135" t="inlineStr">
-        <is>
-          <t>12:17</t>
-        </is>
-      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB135" t="inlineStr">
-        <is>
-          <t>12:17</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14734,22 +14724,22 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>130255810</v>
+        <v>130256344</v>
       </c>
       <c r="B136" t="n">
-        <v>79211</v>
+        <v>78969</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14757,21 +14747,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14781,10 +14771,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>497191</v>
+        <v>496869</v>
       </c>
       <c r="R136" t="n">
-        <v>6826663</v>
+        <v>6827038</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14814,19 +14804,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z136" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB136" t="inlineStr">
-        <is>
-          <t>12:06</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14841,19 +14821,19 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>130255813</v>
+        <v>130255806</v>
       </c>
       <c r="B137" t="n">
         <v>79211</v>
@@ -14888,10 +14868,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>497093</v>
+        <v>497147</v>
       </c>
       <c r="R137" t="n">
-        <v>6827168</v>
+        <v>6826725</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14923,7 +14903,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -14933,7 +14913,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14960,10 +14940,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>130256345</v>
+        <v>130255810</v>
       </c>
       <c r="B138" t="n">
-        <v>78969</v>
+        <v>79211</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14971,21 +14951,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14995,10 +14975,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>496837</v>
+        <v>497191</v>
       </c>
       <c r="R138" t="n">
-        <v>6827069</v>
+        <v>6826663</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15028,9 +15008,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z138" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AA138" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB138" t="inlineStr">
+        <is>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15045,22 +15035,22 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>130256344</v>
+        <v>130255813</v>
       </c>
       <c r="B139" t="n">
-        <v>78969</v>
+        <v>79211</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15068,21 +15058,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15092,10 +15082,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>496869</v>
+        <v>497093</v>
       </c>
       <c r="R139" t="n">
-        <v>6827038</v>
+        <v>6827168</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15125,9 +15115,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB139" t="inlineStr">
+        <is>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15142,12 +15142,12 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
@@ -15445,10 +15445,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>130256340</v>
+        <v>130256364</v>
       </c>
       <c r="B143" t="n">
-        <v>79801</v>
+        <v>79211</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15456,21 +15456,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15480,10 +15480,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>496774</v>
+        <v>496909</v>
       </c>
       <c r="R143" t="n">
-        <v>6827067</v>
+        <v>6827002</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16047,10 +16047,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>130256364</v>
+        <v>130256340</v>
       </c>
       <c r="B149" t="n">
-        <v>79211</v>
+        <v>79801</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16058,21 +16058,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16082,10 +16082,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>496909</v>
+        <v>496774</v>
       </c>
       <c r="R149" t="n">
-        <v>6827002</v>
+        <v>6827067</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16253,7 +16253,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>130256372</v>
+        <v>130255811</v>
       </c>
       <c r="B151" t="n">
         <v>79211</v>
@@ -16288,10 +16288,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>496867</v>
+        <v>497200</v>
       </c>
       <c r="R151" t="n">
-        <v>6827035</v>
+        <v>6826832</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16321,9 +16321,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z151" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB151" t="inlineStr">
+        <is>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16338,19 +16348,19 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>130255811</v>
+        <v>130255831</v>
       </c>
       <c r="B152" t="n">
         <v>79211</v>
@@ -16385,10 +16395,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>497200</v>
+        <v>496599</v>
       </c>
       <c r="R152" t="n">
-        <v>6826832</v>
+        <v>6827121</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16420,7 +16430,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -16430,7 +16440,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16457,7 +16467,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>130255831</v>
+        <v>130256372</v>
       </c>
       <c r="B153" t="n">
         <v>79211</v>
@@ -16492,10 +16502,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>496599</v>
+        <v>496867</v>
       </c>
       <c r="R153" t="n">
-        <v>6827121</v>
+        <v>6827035</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16525,19 +16535,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z153" t="inlineStr">
-        <is>
-          <t>10:18</t>
-        </is>
-      </c>
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB153" t="inlineStr">
-        <is>
-          <t>10:18</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16552,12 +16552,12 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>

--- a/artfynd/A 58895-2025 artfynd.xlsx
+++ b/artfynd/A 58895-2025 artfynd.xlsx
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130252584</v>
+        <v>130252591</v>
       </c>
       <c r="B3" t="n">
-        <v>58013</v>
+        <v>78968</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,21 +801,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>497202</v>
+        <v>496966</v>
       </c>
       <c r="R3" t="n">
-        <v>6826919</v>
+        <v>6826906</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,32 +897,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130252120</v>
+        <v>130252116</v>
       </c>
       <c r="B4" t="n">
-        <v>8451</v>
+        <v>79830</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>496653</v>
+        <v>496721</v>
       </c>
       <c r="R4" t="n">
-        <v>6827111</v>
+        <v>6827083</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -967,7 +967,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,10 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130252591</v>
+        <v>130252584</v>
       </c>
       <c r="B5" t="n">
-        <v>78968</v>
+        <v>58013</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1015,21 +1015,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>496966</v>
+        <v>497202</v>
       </c>
       <c r="R5" t="n">
-        <v>6826906</v>
+        <v>6826919</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,32 +1111,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130252116</v>
+        <v>130252120</v>
       </c>
       <c r="B6" t="n">
-        <v>79830</v>
+        <v>8451</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1146,10 +1146,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>496721</v>
+        <v>496653</v>
       </c>
       <c r="R6" t="n">
-        <v>6827083</v>
+        <v>6827111</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1432,10 +1432,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130252138</v>
+        <v>130252115</v>
       </c>
       <c r="B9" t="n">
-        <v>79211</v>
+        <v>79243</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1443,21 +1443,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>497207</v>
+        <v>496555</v>
       </c>
       <c r="R9" t="n">
-        <v>6826726</v>
+        <v>6826991</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1512,7 +1512,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,6 +1521,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1539,10 +1540,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130252126</v>
+        <v>130252138</v>
       </c>
       <c r="B10" t="n">
-        <v>78968</v>
+        <v>79211</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1550,21 +1551,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1574,10 +1575,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>496737</v>
+        <v>497207</v>
       </c>
       <c r="R10" t="n">
-        <v>6827071</v>
+        <v>6826726</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1609,7 +1610,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1619,7 +1620,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1646,7 +1647,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130252592</v>
+        <v>130252126</v>
       </c>
       <c r="B11" t="n">
         <v>78968</v>
@@ -1677,14 +1678,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>496950</v>
+        <v>496737</v>
       </c>
       <c r="R11" t="n">
-        <v>6827038</v>
+        <v>6827071</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1716,7 +1717,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1726,7 +1727,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1741,19 +1742,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130252588</v>
+        <v>130252592</v>
       </c>
       <c r="B12" t="n">
         <v>78968</v>
@@ -1788,10 +1789,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>497230</v>
+        <v>496950</v>
       </c>
       <c r="R12" t="n">
-        <v>6826961</v>
+        <v>6827038</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1823,7 +1824,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1833,7 +1834,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1860,45 +1861,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130252156</v>
+        <v>130252588</v>
       </c>
       <c r="B13" t="n">
-        <v>93047</v>
+        <v>78968</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>496675</v>
+        <v>497230</v>
       </c>
       <c r="R13" t="n">
-        <v>6827138</v>
+        <v>6826961</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1930,7 +1931,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1940,7 +1941,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1955,44 +1956,44 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130252115</v>
+        <v>130252156</v>
       </c>
       <c r="B14" t="n">
-        <v>79243</v>
+        <v>93047</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>185</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2002,10 +2003,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>496555</v>
+        <v>496675</v>
       </c>
       <c r="R14" t="n">
-        <v>6826991</v>
+        <v>6827138</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2037,7 +2038,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2047,7 +2048,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2056,7 +2057,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2396,32 +2396,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130252123</v>
+        <v>130252125</v>
       </c>
       <c r="B18" t="n">
-        <v>8451</v>
+        <v>78968</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2431,10 +2431,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>496581</v>
+        <v>497154</v>
       </c>
       <c r="R18" t="n">
-        <v>6827019</v>
+        <v>6826854</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2476,7 +2476,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2503,10 +2503,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130252125</v>
+        <v>130252603</v>
       </c>
       <c r="B19" t="n">
-        <v>78968</v>
+        <v>79211</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2514,34 +2514,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>497154</v>
+        <v>496694</v>
       </c>
       <c r="R19" t="n">
-        <v>6826854</v>
+        <v>6827132</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2598,19 +2598,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130252603</v>
+        <v>130252145</v>
       </c>
       <c r="B20" t="n">
         <v>79211</v>
@@ -2641,14 +2641,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>496694</v>
+        <v>496870</v>
       </c>
       <c r="R20" t="n">
-        <v>6827132</v>
+        <v>6827056</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2705,22 +2705,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130252145</v>
+        <v>130252594</v>
       </c>
       <c r="B21" t="n">
-        <v>79211</v>
+        <v>78968</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2728,34 +2728,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>496870</v>
+        <v>496874</v>
       </c>
       <c r="R21" t="n">
-        <v>6827056</v>
+        <v>6827149</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2812,57 +2812,57 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130252594</v>
+        <v>130252123</v>
       </c>
       <c r="B22" t="n">
-        <v>78968</v>
+        <v>8451</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>496874</v>
+        <v>496581</v>
       </c>
       <c r="R22" t="n">
-        <v>6827149</v>
+        <v>6827019</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2904,7 +2904,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2919,12 +2919,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3573,32 +3573,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130252129</v>
+        <v>130252157</v>
       </c>
       <c r="B29" t="n">
-        <v>78968</v>
+        <v>93047</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3608,10 +3608,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>496646</v>
+        <v>496628</v>
       </c>
       <c r="R29" t="n">
-        <v>6827139</v>
+        <v>6827124</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3643,7 +3643,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3680,7 +3680,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130252589</v>
+        <v>130252129</v>
       </c>
       <c r="B30" t="n">
         <v>78968</v>
@@ -3711,14 +3711,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>497211</v>
+        <v>496646</v>
       </c>
       <c r="R30" t="n">
-        <v>6826926</v>
+        <v>6827139</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3750,7 +3750,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3760,7 +3760,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3775,22 +3775,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130252141</v>
+        <v>130252589</v>
       </c>
       <c r="B31" t="n">
-        <v>79211</v>
+        <v>78968</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3798,34 +3798,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>496956</v>
+        <v>497211</v>
       </c>
       <c r="R31" t="n">
-        <v>6827088</v>
+        <v>6826926</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3857,7 +3857,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3867,7 +3867,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3882,44 +3882,44 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130252157</v>
+        <v>130252141</v>
       </c>
       <c r="B32" t="n">
-        <v>93047</v>
+        <v>79211</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3929,10 +3929,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>496628</v>
+        <v>496956</v>
       </c>
       <c r="R32" t="n">
-        <v>6827124</v>
+        <v>6827088</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3964,7 +3964,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3974,7 +3974,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4750,45 +4750,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130252590</v>
+        <v>130252158</v>
       </c>
       <c r="B40" t="n">
-        <v>78968</v>
+        <v>93047</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>496995</v>
+        <v>496629</v>
       </c>
       <c r="R40" t="n">
-        <v>6826923</v>
+        <v>6827128</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4820,7 +4820,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4845,57 +4845,57 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130252136</v>
+        <v>130252607</v>
       </c>
       <c r="B41" t="n">
-        <v>79211</v>
+        <v>93047</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>497002</v>
+        <v>496598</v>
       </c>
       <c r="R41" t="n">
-        <v>6826879</v>
+        <v>6827085</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4927,7 +4927,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4937,7 +4937,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4946,28 +4946,29 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130252128</v>
+        <v>130252585</v>
       </c>
       <c r="B42" t="n">
-        <v>78968</v>
+        <v>57851</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4975,34 +4976,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>496684</v>
+        <v>496635</v>
       </c>
       <c r="R42" t="n">
-        <v>6827129</v>
+        <v>6827130</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5034,7 +5043,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5044,7 +5053,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5059,57 +5068,57 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130252158</v>
+        <v>130252590</v>
       </c>
       <c r="B43" t="n">
-        <v>93047</v>
+        <v>78968</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>496629</v>
+        <v>496995</v>
       </c>
       <c r="R43" t="n">
-        <v>6827128</v>
+        <v>6826923</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5141,7 +5150,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5151,7 +5160,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5166,57 +5175,57 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130252607</v>
+        <v>130252136</v>
       </c>
       <c r="B44" t="n">
-        <v>93047</v>
+        <v>79211</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>496598</v>
+        <v>497002</v>
       </c>
       <c r="R44" t="n">
-        <v>6827085</v>
+        <v>6826879</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5248,7 +5257,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5258,7 +5267,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5267,29 +5276,28 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130252585</v>
+        <v>130252128</v>
       </c>
       <c r="B45" t="n">
-        <v>57851</v>
+        <v>78968</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5297,42 +5305,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>496635</v>
+        <v>496684</v>
       </c>
       <c r="R45" t="n">
-        <v>6827130</v>
+        <v>6827129</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5364,7 +5364,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5374,7 +5374,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5389,12 +5389,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -6044,45 +6044,54 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130252150</v>
+        <v>130252130</v>
       </c>
       <c r="B52" t="n">
-        <v>79211</v>
+        <v>44108</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>101735</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>496701</v>
+        <v>497225</v>
       </c>
       <c r="R52" t="n">
-        <v>6827080</v>
+        <v>6826804</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6114,7 +6123,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6124,7 +6133,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6133,6 +6142,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6151,10 +6161,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130252118</v>
+        <v>130252150</v>
       </c>
       <c r="B53" t="n">
-        <v>57854</v>
+        <v>79211</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6162,42 +6172,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>496923</v>
+        <v>496701</v>
       </c>
       <c r="R53" t="n">
-        <v>6826913</v>
+        <v>6827080</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6229,7 +6231,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6239,12 +6241,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:50</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6271,41 +6268,40 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130252130</v>
+        <v>130252118</v>
       </c>
       <c r="B54" t="n">
-        <v>44108</v>
+        <v>57854</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>101735</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
@@ -6315,10 +6311,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>497225</v>
+        <v>496923</v>
       </c>
       <c r="R54" t="n">
-        <v>6826804</v>
+        <v>6826913</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6350,7 +6346,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6360,7 +6356,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6369,7 +6370,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6388,10 +6388,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130252117</v>
+        <v>130252596</v>
       </c>
       <c r="B55" t="n">
-        <v>79801</v>
+        <v>78968</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6399,34 +6399,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>497155</v>
+        <v>496771</v>
       </c>
       <c r="R55" t="n">
-        <v>6826856</v>
+        <v>6827069</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6458,7 +6458,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6468,7 +6468,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6483,22 +6483,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130252596</v>
+        <v>130252137</v>
       </c>
       <c r="B56" t="n">
-        <v>78968</v>
+        <v>79211</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6506,34 +6506,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>496771</v>
+        <v>497206</v>
       </c>
       <c r="R56" t="n">
-        <v>6827069</v>
+        <v>6826638</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6565,7 +6565,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6575,7 +6575,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6590,57 +6590,57 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130252137</v>
+        <v>130252606</v>
       </c>
       <c r="B57" t="n">
-        <v>79211</v>
+        <v>93047</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>497206</v>
+        <v>496618</v>
       </c>
       <c r="R57" t="n">
-        <v>6826638</v>
+        <v>6827114</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6672,7 +6672,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6682,7 +6682,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6691,63 +6691,64 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130252606</v>
+        <v>130252117</v>
       </c>
       <c r="B58" t="n">
-        <v>93047</v>
+        <v>79801</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>496618</v>
+        <v>497155</v>
       </c>
       <c r="R58" t="n">
-        <v>6827114</v>
+        <v>6826856</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6779,7 +6780,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6789,7 +6790,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6798,19 +6799,18 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -7352,45 +7352,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130252608</v>
+        <v>130252114</v>
       </c>
       <c r="B64" t="n">
-        <v>93047</v>
+        <v>79243</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4364</v>
+        <v>185</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>496576</v>
+        <v>496880</v>
       </c>
       <c r="R64" t="n">
-        <v>6826998</v>
+        <v>6827051</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7422,7 +7422,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7432,7 +7432,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7448,57 +7448,57 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130252139</v>
+        <v>130252608</v>
       </c>
       <c r="B65" t="n">
-        <v>79211</v>
+        <v>93047</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>497225</v>
+        <v>496576</v>
       </c>
       <c r="R65" t="n">
-        <v>6826804</v>
+        <v>6826998</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7549,25 +7549,26 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130252151</v>
+        <v>130252139</v>
       </c>
       <c r="B66" t="n">
         <v>79211</v>
@@ -7602,10 +7603,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>496704</v>
+        <v>497225</v>
       </c>
       <c r="R66" t="n">
-        <v>6827086</v>
+        <v>6826804</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7637,7 +7638,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7647,7 +7648,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7674,7 +7675,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130252597</v>
+        <v>130252151</v>
       </c>
       <c r="B67" t="n">
         <v>79211</v>
@@ -7705,14 +7706,14 @@
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>496922</v>
+        <v>496704</v>
       </c>
       <c r="R67" t="n">
-        <v>6826906</v>
+        <v>6827086</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7744,7 +7745,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7754,7 +7755,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7769,22 +7770,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130252114</v>
+        <v>130252597</v>
       </c>
       <c r="B68" t="n">
-        <v>79243</v>
+        <v>79211</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7792,34 +7793,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>496880</v>
+        <v>496922</v>
       </c>
       <c r="R68" t="n">
-        <v>6827051</v>
+        <v>6826906</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7851,7 +7852,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7861,7 +7862,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7870,19 +7871,18 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
@@ -7986,7 +7986,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130252149</v>
+        <v>130256379</v>
       </c>
       <c r="B70" t="n">
         <v>79211</v>
@@ -8015,19 +8015,16 @@
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>496745</v>
+        <v>496857</v>
       </c>
       <c r="R70" t="n">
-        <v>6827070</v>
+        <v>6827067</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8057,47 +8054,36 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130256379</v>
+        <v>130256356</v>
       </c>
       <c r="B71" t="n">
         <v>79211</v>
@@ -8132,10 +8118,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>496857</v>
+        <v>496957</v>
       </c>
       <c r="R71" t="n">
-        <v>6827067</v>
+        <v>6826898</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8194,7 +8180,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130256356</v>
+        <v>130252149</v>
       </c>
       <c r="B72" t="n">
         <v>79211</v>
@@ -8223,16 +8209,19 @@
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>496957</v>
+        <v>496745</v>
       </c>
       <c r="R72" t="n">
-        <v>6826898</v>
+        <v>6827070</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8262,29 +8251,40 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
@@ -9311,10 +9311,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>130256346</v>
+        <v>130255837</v>
       </c>
       <c r="B83" t="n">
-        <v>78969</v>
+        <v>79211</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9322,21 +9322,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9346,10 +9346,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>496652</v>
+        <v>497191</v>
       </c>
       <c r="R83" t="n">
-        <v>6827164</v>
+        <v>6826771</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9379,9 +9379,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9396,22 +9406,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>130255837</v>
+        <v>130256346</v>
       </c>
       <c r="B84" t="n">
-        <v>79211</v>
+        <v>78969</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9419,21 +9429,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9443,10 +9453,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>497191</v>
+        <v>496652</v>
       </c>
       <c r="R84" t="n">
-        <v>6826771</v>
+        <v>6827164</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9476,19 +9486,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>12:00</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9503,44 +9503,44 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>130256352</v>
+        <v>130255839</v>
       </c>
       <c r="B85" t="n">
-        <v>78968</v>
+        <v>93047</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9550,10 +9550,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>496837</v>
+        <v>496787</v>
       </c>
       <c r="R85" t="n">
-        <v>6827069</v>
+        <v>6827052</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9583,9 +9583,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9600,44 +9610,44 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>130255839</v>
+        <v>130256352</v>
       </c>
       <c r="B86" t="n">
-        <v>93047</v>
+        <v>78968</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9647,10 +9657,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>496787</v>
+        <v>496837</v>
       </c>
       <c r="R86" t="n">
-        <v>6827052</v>
+        <v>6827069</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9680,19 +9690,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9707,12 +9707,12 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
@@ -11983,10 +11983,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>130256374</v>
+        <v>130256342</v>
       </c>
       <c r="B109" t="n">
-        <v>79211</v>
+        <v>57854</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11994,34 +11994,42 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>496863</v>
+        <v>496940</v>
       </c>
       <c r="R109" t="n">
-        <v>6827047</v>
+        <v>6826899</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12054,6 +12062,11 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12080,7 +12093,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>130256360</v>
+        <v>130256374</v>
       </c>
       <c r="B110" t="n">
         <v>79211</v>
@@ -12115,10 +12128,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>496972</v>
+        <v>496863</v>
       </c>
       <c r="R110" t="n">
-        <v>6826953</v>
+        <v>6827047</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12177,10 +12190,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>130256354</v>
+        <v>130256360</v>
       </c>
       <c r="B111" t="n">
-        <v>78968</v>
+        <v>79211</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12188,21 +12201,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12212,10 +12225,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>496654</v>
+        <v>496972</v>
       </c>
       <c r="R111" t="n">
-        <v>6827171</v>
+        <v>6826953</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12274,10 +12287,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>130255819</v>
+        <v>130256354</v>
       </c>
       <c r="B112" t="n">
-        <v>79211</v>
+        <v>78968</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12285,21 +12298,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12309,10 +12322,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>496850</v>
+        <v>496654</v>
       </c>
       <c r="R112" t="n">
-        <v>6827090</v>
+        <v>6827171</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12342,19 +12355,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>11:05</t>
-        </is>
-      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>11:05</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12369,19 +12372,19 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>130256386</v>
+        <v>130255819</v>
       </c>
       <c r="B113" t="n">
         <v>79211</v>
@@ -12416,10 +12419,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>496723</v>
+        <v>496850</v>
       </c>
       <c r="R113" t="n">
-        <v>6827125</v>
+        <v>6827090</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12449,9 +12452,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12466,22 +12479,22 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>130256342</v>
+        <v>130256386</v>
       </c>
       <c r="B114" t="n">
-        <v>57854</v>
+        <v>79211</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12489,42 +12502,34 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>496940</v>
+        <v>496723</v>
       </c>
       <c r="R114" t="n">
-        <v>6826899</v>
+        <v>6827125</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12557,11 +12562,6 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12889,7 +12889,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>130256390</v>
+        <v>130256359</v>
       </c>
       <c r="B118" t="n">
         <v>79211</v>
@@ -12924,10 +12924,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>496581</v>
+        <v>496963</v>
       </c>
       <c r="R118" t="n">
-        <v>6827049</v>
+        <v>6826942</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12986,7 +12986,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>130256363</v>
+        <v>130256390</v>
       </c>
       <c r="B119" t="n">
         <v>79211</v>
@@ -13021,10 +13021,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>496897</v>
+        <v>496581</v>
       </c>
       <c r="R119" t="n">
-        <v>6827002</v>
+        <v>6827049</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13083,7 +13083,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>130256381</v>
+        <v>130256363</v>
       </c>
       <c r="B120" t="n">
         <v>79211</v>
@@ -13118,10 +13118,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>496852</v>
+        <v>496897</v>
       </c>
       <c r="R120" t="n">
-        <v>6827066</v>
+        <v>6827002</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13180,10 +13180,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>130255796</v>
+        <v>130256381</v>
       </c>
       <c r="B121" t="n">
-        <v>78968</v>
+        <v>79211</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13191,21 +13191,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13215,10 +13215,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>497111</v>
+        <v>496852</v>
       </c>
       <c r="R121" t="n">
-        <v>6826644</v>
+        <v>6827066</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13248,19 +13248,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z121" t="inlineStr">
-        <is>
-          <t>12:13</t>
-        </is>
-      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB121" t="inlineStr">
-        <is>
-          <t>12:13</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13275,22 +13265,22 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>130256378</v>
+        <v>130255796</v>
       </c>
       <c r="B122" t="n">
-        <v>79211</v>
+        <v>78968</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13298,21 +13288,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13322,10 +13312,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>496862</v>
+        <v>497111</v>
       </c>
       <c r="R122" t="n">
-        <v>6827064</v>
+        <v>6826644</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13355,9 +13345,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13372,19 +13372,19 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>130256382</v>
+        <v>130256378</v>
       </c>
       <c r="B123" t="n">
         <v>79211</v>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>496831</v>
+        <v>496862</v>
       </c>
       <c r="R123" t="n">
-        <v>6827081</v>
+        <v>6827064</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13481,7 +13481,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>130256359</v>
+        <v>130256382</v>
       </c>
       <c r="B124" t="n">
         <v>79211</v>
@@ -13516,10 +13516,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>496963</v>
+        <v>496831</v>
       </c>
       <c r="R124" t="n">
-        <v>6826942</v>
+        <v>6827081</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13890,54 +13890,45 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>130255793</v>
+        <v>130255834</v>
       </c>
       <c r="B128" t="n">
-        <v>8451</v>
+        <v>79211</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
-      <c r="L128" t="inlineStr"/>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>496670</v>
+        <v>496582</v>
       </c>
       <c r="R128" t="n">
-        <v>6827136</v>
+        <v>6827040</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13969,7 +13960,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -13979,7 +13970,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13988,7 +13979,6 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
-      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
@@ -14007,54 +13997,45 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>130256349</v>
+        <v>130255836</v>
       </c>
       <c r="B129" t="n">
-        <v>8451</v>
+        <v>79211</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
-      <c r="K129" t="inlineStr"/>
-      <c r="L129" t="inlineStr"/>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>496714</v>
+        <v>497183</v>
       </c>
       <c r="R129" t="n">
-        <v>6827127</v>
+        <v>6826662</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14084,84 +14065,84 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AD129" t="b">
         <v>0</v>
       </c>
       <c r="AE129" t="b">
         <v>0</v>
       </c>
-      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>130256347</v>
+        <v>130255805</v>
       </c>
       <c r="B130" t="n">
-        <v>8451</v>
+        <v>79211</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="J130" t="inlineStr"/>
-      <c r="K130" t="inlineStr"/>
-      <c r="L130" t="inlineStr"/>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>496941</v>
+        <v>497139</v>
       </c>
       <c r="R130" t="n">
-        <v>6826899</v>
+        <v>6826719</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14191,37 +14172,46 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
       <c r="AD130" t="b">
         <v>0</v>
       </c>
       <c r="AE130" t="b">
         <v>0</v>
       </c>
-      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>130255834</v>
+        <v>130256343</v>
       </c>
       <c r="B131" t="n">
         <v>79211</v>
@@ -14256,10 +14246,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>496582</v>
+        <v>496851</v>
       </c>
       <c r="R131" t="n">
-        <v>6827040</v>
+        <v>6827066</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14289,19 +14279,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z131" t="inlineStr">
-        <is>
-          <t>10:10</t>
-        </is>
-      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB131" t="inlineStr">
-        <is>
-          <t>10:10</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14316,57 +14296,66 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>130255836</v>
+        <v>130255793</v>
       </c>
       <c r="B132" t="n">
-        <v>79211</v>
+        <v>8451</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>497183</v>
+        <v>496670</v>
       </c>
       <c r="R132" t="n">
-        <v>6826662</v>
+        <v>6827136</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14398,7 +14387,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14408,7 +14397,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14417,6 +14406,7 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
+      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
@@ -14435,45 +14425,54 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>130255805</v>
+        <v>130256349</v>
       </c>
       <c r="B133" t="n">
-        <v>79211</v>
+        <v>8451</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>497139</v>
+        <v>496714</v>
       </c>
       <c r="R133" t="n">
-        <v>6826719</v>
+        <v>6827127</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14503,84 +14502,84 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z133" t="inlineStr">
-        <is>
-          <t>12:17</t>
-        </is>
-      </c>
       <c r="AA133" t="inlineStr">
         <is>
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="AB133" t="inlineStr">
-        <is>
-          <t>12:17</t>
-        </is>
-      </c>
       <c r="AD133" t="b">
         <v>0</v>
       </c>
       <c r="AE133" t="b">
         <v>0</v>
       </c>
+      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>130256343</v>
+        <v>130256347</v>
       </c>
       <c r="B134" t="n">
-        <v>79211</v>
+        <v>8451</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>496851</v>
+        <v>496941</v>
       </c>
       <c r="R134" t="n">
-        <v>6827066</v>
+        <v>6826899</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14621,6 +14620,7 @@
       <c r="AE134" t="b">
         <v>0</v>
       </c>
+      <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="b">
         <v>0</v>
       </c>
@@ -14736,10 +14736,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>130256344</v>
+        <v>130255806</v>
       </c>
       <c r="B136" t="n">
-        <v>78969</v>
+        <v>79211</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14747,21 +14747,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14771,10 +14771,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>496869</v>
+        <v>497147</v>
       </c>
       <c r="R136" t="n">
-        <v>6827038</v>
+        <v>6826725</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14804,9 +14804,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB136" t="inlineStr">
+        <is>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14821,19 +14831,19 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>130255806</v>
+        <v>130255810</v>
       </c>
       <c r="B137" t="n">
         <v>79211</v>
@@ -14868,10 +14878,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>497147</v>
+        <v>497191</v>
       </c>
       <c r="R137" t="n">
-        <v>6826725</v>
+        <v>6826663</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14903,7 +14913,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -14913,7 +14923,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14940,7 +14950,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>130255810</v>
+        <v>130255813</v>
       </c>
       <c r="B138" t="n">
         <v>79211</v>
@@ -14975,10 +14985,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>497191</v>
+        <v>497093</v>
       </c>
       <c r="R138" t="n">
-        <v>6826663</v>
+        <v>6827168</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15010,7 +15020,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -15020,7 +15030,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15047,10 +15057,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>130255813</v>
+        <v>130256344</v>
       </c>
       <c r="B139" t="n">
-        <v>79211</v>
+        <v>78969</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15058,21 +15068,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15082,10 +15092,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>497093</v>
+        <v>496869</v>
       </c>
       <c r="R139" t="n">
-        <v>6827168</v>
+        <v>6827038</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15115,19 +15125,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z139" t="inlineStr">
-        <is>
-          <t>11:31</t>
-        </is>
-      </c>
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB139" t="inlineStr">
-        <is>
-          <t>11:31</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15142,12 +15142,12 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
@@ -16047,45 +16047,56 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>130256340</v>
+        <v>130256394</v>
       </c>
       <c r="B149" t="n">
-        <v>79801</v>
+        <v>93047</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr"/>
+      <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
           <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>496774</v>
+        <v>496581</v>
       </c>
       <c r="R149" t="n">
-        <v>6827067</v>
+        <v>6827079</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16126,6 +16137,7 @@
       <c r="AE149" t="b">
         <v>0</v>
       </c>
+      <c r="AF149" t="inlineStr"/>
       <c r="AG149" t="b">
         <v>0</v>
       </c>
@@ -16144,56 +16156,45 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>130256394</v>
+        <v>130256340</v>
       </c>
       <c r="B150" t="n">
-        <v>93047</v>
+        <v>79801</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J150" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K150" t="inlineStr"/>
-      <c r="N150" t="inlineStr"/>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
           <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>496581</v>
+        <v>496774</v>
       </c>
       <c r="R150" t="n">
-        <v>6827079</v>
+        <v>6827067</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16234,7 +16235,6 @@
       <c r="AE150" t="b">
         <v>0</v>
       </c>
-      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
@@ -16671,32 +16671,32 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>130256385</v>
+        <v>130255838</v>
       </c>
       <c r="B155" t="n">
-        <v>79211</v>
+        <v>93047</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16706,10 +16706,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>496747</v>
+        <v>496571</v>
       </c>
       <c r="R155" t="n">
-        <v>6827065</v>
+        <v>6827076</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16739,9 +16739,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z155" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
       <c r="AA155" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB155" t="inlineStr">
+        <is>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16756,44 +16766,44 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>130255838</v>
+        <v>130256385</v>
       </c>
       <c r="B156" t="n">
-        <v>93047</v>
+        <v>79211</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16803,10 +16813,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>496571</v>
+        <v>496747</v>
       </c>
       <c r="R156" t="n">
-        <v>6827076</v>
+        <v>6827065</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16836,19 +16846,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z156" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB156" t="inlineStr">
-        <is>
-          <t>10:13</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16863,44 +16863,44 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>130255809</v>
+        <v>130256393</v>
       </c>
       <c r="B157" t="n">
-        <v>79211</v>
+        <v>93047</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16910,10 +16910,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>497168</v>
+        <v>496647</v>
       </c>
       <c r="R157" t="n">
-        <v>6826596</v>
+        <v>6827158</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16943,19 +16943,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z157" t="inlineStr">
-        <is>
-          <t>12:09</t>
-        </is>
-      </c>
       <c r="AA157" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB157" t="inlineStr">
-        <is>
-          <t>12:09</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16970,19 +16960,19 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>130255816</v>
+        <v>130255809</v>
       </c>
       <c r="B158" t="n">
         <v>79211</v>
@@ -17017,10 +17007,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>496954</v>
+        <v>497168</v>
       </c>
       <c r="R158" t="n">
-        <v>6827096</v>
+        <v>6826596</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17052,7 +17042,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -17062,7 +17052,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17089,7 +17079,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>130255829</v>
+        <v>130255816</v>
       </c>
       <c r="B159" t="n">
         <v>79211</v>
@@ -17124,10 +17114,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>496643</v>
+        <v>496954</v>
       </c>
       <c r="R159" t="n">
-        <v>6827146</v>
+        <v>6827096</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17159,7 +17149,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -17169,7 +17159,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17196,32 +17186,32 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>130256393</v>
+        <v>130255829</v>
       </c>
       <c r="B160" t="n">
-        <v>93047</v>
+        <v>79211</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17231,10 +17221,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>496647</v>
+        <v>496643</v>
       </c>
       <c r="R160" t="n">
-        <v>6827158</v>
+        <v>6827146</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17264,9 +17254,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z160" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB160" t="inlineStr">
+        <is>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17281,12 +17281,12 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>

--- a/artfynd/A 58895-2025 artfynd.xlsx
+++ b/artfynd/A 58895-2025 artfynd.xlsx
@@ -790,45 +790,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130252591</v>
+        <v>130252155</v>
       </c>
       <c r="B3" t="n">
-        <v>78968</v>
+        <v>93047</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>496966</v>
+        <v>496725</v>
       </c>
       <c r="R3" t="n">
-        <v>6826906</v>
+        <v>6827084</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,22 +885,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130252116</v>
+        <v>130252591</v>
       </c>
       <c r="B4" t="n">
-        <v>79830</v>
+        <v>78968</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,34 +908,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>496721</v>
+        <v>496966</v>
       </c>
       <c r="R4" t="n">
-        <v>6827083</v>
+        <v>6826906</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -967,7 +967,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -992,22 +992,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130252584</v>
+        <v>130252116</v>
       </c>
       <c r="B5" t="n">
-        <v>58013</v>
+        <v>79830</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1015,34 +1015,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>497202</v>
+        <v>496721</v>
       </c>
       <c r="R5" t="n">
-        <v>6826919</v>
+        <v>6827083</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1099,57 +1099,57 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130252120</v>
+        <v>130252584</v>
       </c>
       <c r="B6" t="n">
-        <v>8451</v>
+        <v>58013</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>496653</v>
+        <v>497202</v>
       </c>
       <c r="R6" t="n">
-        <v>6827111</v>
+        <v>6826919</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1206,22 +1206,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130252155</v>
+        <v>130252120</v>
       </c>
       <c r="B7" t="n">
-        <v>93047</v>
+        <v>8451</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1229,21 +1229,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1253,10 +1253,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>496725</v>
+        <v>496653</v>
       </c>
       <c r="R7" t="n">
-        <v>6827084</v>
+        <v>6827111</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1647,32 +1647,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130252126</v>
+        <v>130252156</v>
       </c>
       <c r="B11" t="n">
-        <v>78968</v>
+        <v>93047</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1682,10 +1682,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>496737</v>
+        <v>496675</v>
       </c>
       <c r="R11" t="n">
-        <v>6827071</v>
+        <v>6827138</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1717,7 +1717,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1727,7 +1727,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1754,7 +1754,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130252592</v>
+        <v>130252126</v>
       </c>
       <c r="B12" t="n">
         <v>78968</v>
@@ -1785,14 +1785,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>496950</v>
+        <v>496737</v>
       </c>
       <c r="R12" t="n">
-        <v>6827038</v>
+        <v>6827071</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1849,19 +1849,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130252588</v>
+        <v>130252592</v>
       </c>
       <c r="B13" t="n">
         <v>78968</v>
@@ -1896,10 +1896,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>497230</v>
+        <v>496950</v>
       </c>
       <c r="R13" t="n">
-        <v>6826961</v>
+        <v>6827038</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1931,7 +1931,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1968,45 +1968,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130252156</v>
+        <v>130252588</v>
       </c>
       <c r="B14" t="n">
-        <v>93047</v>
+        <v>78968</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>496675</v>
+        <v>497230</v>
       </c>
       <c r="R14" t="n">
-        <v>6827138</v>
+        <v>6826961</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2038,7 +2038,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2063,22 +2063,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130252154</v>
+        <v>130252122</v>
       </c>
       <c r="B15" t="n">
-        <v>93047</v>
+        <v>8451</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2086,21 +2086,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2110,10 +2110,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>496692</v>
+        <v>496640</v>
       </c>
       <c r="R15" t="n">
-        <v>6827092</v>
+        <v>6827137</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2145,7 +2145,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2182,32 +2182,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130252119</v>
+        <v>130252154</v>
       </c>
       <c r="B16" t="n">
-        <v>58013</v>
+        <v>93047</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2217,10 +2217,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>496602</v>
+        <v>496692</v>
       </c>
       <c r="R16" t="n">
-        <v>6827039</v>
+        <v>6827092</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2289,32 +2289,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130252122</v>
+        <v>130252119</v>
       </c>
       <c r="B17" t="n">
-        <v>8451</v>
+        <v>58013</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2324,10 +2324,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>496640</v>
+        <v>496602</v>
       </c>
       <c r="R17" t="n">
-        <v>6827137</v>
+        <v>6827039</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2396,32 +2396,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130252125</v>
+        <v>130252123</v>
       </c>
       <c r="B18" t="n">
-        <v>78968</v>
+        <v>8451</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2431,10 +2431,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>497154</v>
+        <v>496581</v>
       </c>
       <c r="R18" t="n">
-        <v>6826854</v>
+        <v>6827019</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2476,7 +2476,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2610,10 +2610,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130252145</v>
+        <v>130252125</v>
       </c>
       <c r="B20" t="n">
-        <v>79211</v>
+        <v>78968</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,21 +2621,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2645,10 +2645,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>496870</v>
+        <v>497154</v>
       </c>
       <c r="R20" t="n">
-        <v>6827056</v>
+        <v>6826854</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2717,10 +2717,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130252594</v>
+        <v>130252145</v>
       </c>
       <c r="B21" t="n">
-        <v>78968</v>
+        <v>79211</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2728,34 +2728,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>496874</v>
+        <v>496870</v>
       </c>
       <c r="R21" t="n">
-        <v>6827149</v>
+        <v>6827056</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2812,57 +2812,57 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130252123</v>
+        <v>130252594</v>
       </c>
       <c r="B22" t="n">
-        <v>8451</v>
+        <v>78968</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>496581</v>
+        <v>496874</v>
       </c>
       <c r="R22" t="n">
-        <v>6827019</v>
+        <v>6827149</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2904,7 +2904,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2919,12 +2919,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3252,10 +3252,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130252595</v>
+        <v>130252600</v>
       </c>
       <c r="B26" t="n">
-        <v>78968</v>
+        <v>79211</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3263,21 +3263,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3287,10 +3287,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>496894</v>
+        <v>496948</v>
       </c>
       <c r="R26" t="n">
-        <v>6827123</v>
+        <v>6827029</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3322,7 +3322,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3359,7 +3359,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130252127</v>
+        <v>130252595</v>
       </c>
       <c r="B27" t="n">
         <v>78968</v>
@@ -3390,14 +3390,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>496719</v>
+        <v>496894</v>
       </c>
       <c r="R27" t="n">
-        <v>6827076</v>
+        <v>6827123</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3429,7 +3429,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3439,7 +3439,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3454,22 +3454,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130252600</v>
+        <v>130252127</v>
       </c>
       <c r="B28" t="n">
-        <v>79211</v>
+        <v>78968</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3477,34 +3477,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>496948</v>
+        <v>496719</v>
       </c>
       <c r="R28" t="n">
-        <v>6827029</v>
+        <v>6827076</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3536,7 +3536,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3546,7 +3546,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3561,12 +3561,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3680,10 +3680,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130252129</v>
+        <v>130252141</v>
       </c>
       <c r="B30" t="n">
-        <v>78968</v>
+        <v>79211</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3691,21 +3691,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3715,10 +3715,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>496646</v>
+        <v>496956</v>
       </c>
       <c r="R30" t="n">
-        <v>6827139</v>
+        <v>6827088</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3750,7 +3750,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3760,7 +3760,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3787,7 +3787,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130252589</v>
+        <v>130252129</v>
       </c>
       <c r="B31" t="n">
         <v>78968</v>
@@ -3818,14 +3818,14 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>497211</v>
+        <v>496646</v>
       </c>
       <c r="R31" t="n">
-        <v>6826926</v>
+        <v>6827139</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3857,7 +3857,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3867,7 +3867,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3882,22 +3882,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130252141</v>
+        <v>130252589</v>
       </c>
       <c r="B32" t="n">
-        <v>79211</v>
+        <v>78968</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3905,34 +3905,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>496956</v>
+        <v>497211</v>
       </c>
       <c r="R32" t="n">
-        <v>6827088</v>
+        <v>6826926</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3964,7 +3964,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3974,7 +3974,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3989,12 +3989,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4108,7 +4108,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130252135</v>
+        <v>130252604</v>
       </c>
       <c r="B34" t="n">
         <v>79211</v>
@@ -4139,14 +4139,14 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>496915</v>
+        <v>496679</v>
       </c>
       <c r="R34" t="n">
-        <v>6826903</v>
+        <v>6827141</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4203,19 +4203,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130252604</v>
+        <v>130252605</v>
       </c>
       <c r="B35" t="n">
         <v>79211</v>
@@ -4250,10 +4250,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>496679</v>
+        <v>496676</v>
       </c>
       <c r="R35" t="n">
-        <v>6827141</v>
+        <v>6827143</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4322,7 +4322,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130252146</v>
+        <v>130252135</v>
       </c>
       <c r="B36" t="n">
         <v>79211</v>
@@ -4357,10 +4357,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>496864</v>
+        <v>496915</v>
       </c>
       <c r="R36" t="n">
-        <v>6827053</v>
+        <v>6826903</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4429,7 +4429,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130252143</v>
+        <v>130252146</v>
       </c>
       <c r="B37" t="n">
         <v>79211</v>
@@ -4464,10 +4464,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>496877</v>
+        <v>496864</v>
       </c>
       <c r="R37" t="n">
-        <v>6827056</v>
+        <v>6827053</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4509,7 +4509,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4536,7 +4536,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130252605</v>
+        <v>130252143</v>
       </c>
       <c r="B38" t="n">
         <v>79211</v>
@@ -4567,14 +4567,14 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>496676</v>
+        <v>496877</v>
       </c>
       <c r="R38" t="n">
-        <v>6827143</v>
+        <v>6827056</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4631,12 +4631,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4965,10 +4965,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130252585</v>
+        <v>130252590</v>
       </c>
       <c r="B42" t="n">
-        <v>57851</v>
+        <v>78968</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4976,42 +4976,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>496635</v>
+        <v>496995</v>
       </c>
       <c r="R42" t="n">
-        <v>6827130</v>
+        <v>6826923</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5043,7 +5035,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5053,7 +5045,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5080,10 +5072,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130252590</v>
+        <v>130252136</v>
       </c>
       <c r="B43" t="n">
-        <v>78968</v>
+        <v>79211</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5091,34 +5083,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>496995</v>
+        <v>497002</v>
       </c>
       <c r="R43" t="n">
-        <v>6826923</v>
+        <v>6826879</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5150,7 +5142,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5160,7 +5152,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5175,22 +5167,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130252136</v>
+        <v>130252128</v>
       </c>
       <c r="B44" t="n">
-        <v>79211</v>
+        <v>78968</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5198,21 +5190,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5222,10 +5214,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>497002</v>
+        <v>496684</v>
       </c>
       <c r="R44" t="n">
-        <v>6826879</v>
+        <v>6827129</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5257,7 +5249,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5267,7 +5259,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5294,10 +5286,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130252128</v>
+        <v>130252585</v>
       </c>
       <c r="B45" t="n">
-        <v>78968</v>
+        <v>57851</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5305,34 +5297,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>496684</v>
+        <v>496635</v>
       </c>
       <c r="R45" t="n">
-        <v>6827129</v>
+        <v>6827130</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5364,7 +5364,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5374,7 +5374,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5389,44 +5389,44 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130252609</v>
+        <v>130252598</v>
       </c>
       <c r="B46" t="n">
-        <v>93047</v>
+        <v>79211</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5436,10 +5436,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>496549</v>
+        <v>497202</v>
       </c>
       <c r="R46" t="n">
-        <v>6826988</v>
+        <v>6826911</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5471,7 +5471,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5490,7 +5490,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5509,7 +5508,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130252598</v>
+        <v>130252602</v>
       </c>
       <c r="B47" t="n">
         <v>79211</v>
@@ -5544,10 +5543,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>497202</v>
+        <v>496722</v>
       </c>
       <c r="R47" t="n">
-        <v>6826911</v>
+        <v>6827107</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5579,7 +5578,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5589,7 +5588,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5616,32 +5615,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130252602</v>
+        <v>130252609</v>
       </c>
       <c r="B48" t="n">
-        <v>79211</v>
+        <v>93047</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5651,10 +5650,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>496722</v>
+        <v>496549</v>
       </c>
       <c r="R48" t="n">
-        <v>6827107</v>
+        <v>6826988</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5686,7 +5685,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5696,7 +5695,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5705,6 +5704,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6044,54 +6044,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130252130</v>
+        <v>130252150</v>
       </c>
       <c r="B52" t="n">
-        <v>44108</v>
+        <v>79211</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>101735</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>497225</v>
+        <v>496701</v>
       </c>
       <c r="R52" t="n">
-        <v>6826804</v>
+        <v>6827080</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6123,7 +6114,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6133,7 +6124,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6142,7 +6133,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6161,45 +6151,54 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130252150</v>
+        <v>130252130</v>
       </c>
       <c r="B53" t="n">
-        <v>79211</v>
+        <v>44108</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>101735</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>496701</v>
+        <v>497225</v>
       </c>
       <c r="R53" t="n">
-        <v>6827080</v>
+        <v>6826804</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6231,7 +6230,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6241,7 +6240,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6250,6 +6249,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6388,10 +6388,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130252596</v>
+        <v>130252117</v>
       </c>
       <c r="B55" t="n">
-        <v>78968</v>
+        <v>79801</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6399,34 +6399,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>496771</v>
+        <v>497155</v>
       </c>
       <c r="R55" t="n">
-        <v>6827069</v>
+        <v>6826856</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6458,7 +6458,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6468,7 +6468,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6483,12 +6483,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6710,10 +6710,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130252117</v>
+        <v>130252596</v>
       </c>
       <c r="B58" t="n">
-        <v>79801</v>
+        <v>78968</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6721,34 +6721,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>497155</v>
+        <v>496771</v>
       </c>
       <c r="R58" t="n">
-        <v>6826856</v>
+        <v>6827069</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6780,7 +6780,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6790,7 +6790,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6805,12 +6805,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -7031,7 +7031,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130252131</v>
+        <v>130252152</v>
       </c>
       <c r="B61" t="n">
         <v>79211</v>
@@ -7066,10 +7066,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>496656</v>
+        <v>496591</v>
       </c>
       <c r="R61" t="n">
-        <v>6827109</v>
+        <v>6827054</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7101,7 +7101,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7111,7 +7111,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7138,7 +7138,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130252152</v>
+        <v>130252133</v>
       </c>
       <c r="B62" t="n">
         <v>79211</v>
@@ -7173,10 +7173,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>496591</v>
+        <v>496799</v>
       </c>
       <c r="R62" t="n">
-        <v>6827054</v>
+        <v>6827050</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7208,7 +7208,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7218,7 +7218,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7245,7 +7245,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130252133</v>
+        <v>130252131</v>
       </c>
       <c r="B63" t="n">
         <v>79211</v>
@@ -7280,10 +7280,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>496799</v>
+        <v>496656</v>
       </c>
       <c r="R63" t="n">
-        <v>6827050</v>
+        <v>6827109</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7315,7 +7315,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7325,7 +7325,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7460,45 +7460,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130252608</v>
+        <v>130252139</v>
       </c>
       <c r="B65" t="n">
-        <v>93047</v>
+        <v>79211</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>496576</v>
+        <v>497225</v>
       </c>
       <c r="R65" t="n">
-        <v>6826998</v>
+        <v>6826804</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7549,64 +7549,63 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130252139</v>
+        <v>130252608</v>
       </c>
       <c r="B66" t="n">
-        <v>79211</v>
+        <v>93047</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>497225</v>
+        <v>496576</v>
       </c>
       <c r="R66" t="n">
-        <v>6826804</v>
+        <v>6826998</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7638,7 +7637,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7648,7 +7647,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7657,25 +7656,26 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130252151</v>
+        <v>130252597</v>
       </c>
       <c r="B67" t="n">
         <v>79211</v>
@@ -7706,14 +7706,14 @@
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>496704</v>
+        <v>496922</v>
       </c>
       <c r="R67" t="n">
-        <v>6827086</v>
+        <v>6826906</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7745,7 +7745,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7755,7 +7755,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7770,19 +7770,19 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130252597</v>
+        <v>130252151</v>
       </c>
       <c r="B68" t="n">
         <v>79211</v>
@@ -7813,14 +7813,14 @@
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>496922</v>
+        <v>496704</v>
       </c>
       <c r="R68" t="n">
-        <v>6826906</v>
+        <v>6827086</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7852,7 +7852,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7862,7 +7862,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7877,19 +7877,19 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130256388</v>
+        <v>130256379</v>
       </c>
       <c r="B69" t="n">
         <v>79211</v>
@@ -7924,10 +7924,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>496665</v>
+        <v>496857</v>
       </c>
       <c r="R69" t="n">
-        <v>6827143</v>
+        <v>6827067</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7986,7 +7986,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130256379</v>
+        <v>130256356</v>
       </c>
       <c r="B70" t="n">
         <v>79211</v>
@@ -8021,10 +8021,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>496857</v>
+        <v>496957</v>
       </c>
       <c r="R70" t="n">
-        <v>6827067</v>
+        <v>6826898</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8083,7 +8083,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130256356</v>
+        <v>130256388</v>
       </c>
       <c r="B71" t="n">
         <v>79211</v>
@@ -8118,10 +8118,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>496957</v>
+        <v>496665</v>
       </c>
       <c r="R71" t="n">
-        <v>6826898</v>
+        <v>6827143</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8291,7 +8291,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130255817</v>
+        <v>130255832</v>
       </c>
       <c r="B73" t="n">
         <v>79211</v>
@@ -8326,10 +8326,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>496872</v>
+        <v>496578</v>
       </c>
       <c r="R73" t="n">
-        <v>6827052</v>
+        <v>6827044</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8361,7 +8361,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8371,7 +8371,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8398,7 +8398,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130255832</v>
+        <v>130255820</v>
       </c>
       <c r="B74" t="n">
         <v>79211</v>
@@ -8433,10 +8433,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>496578</v>
+        <v>496838</v>
       </c>
       <c r="R74" t="n">
-        <v>6827044</v>
+        <v>6827085</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8468,7 +8468,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8478,7 +8478,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8505,7 +8505,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130256369</v>
+        <v>130255830</v>
       </c>
       <c r="B75" t="n">
         <v>79211</v>
@@ -8540,10 +8540,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>496893</v>
+        <v>496649</v>
       </c>
       <c r="R75" t="n">
-        <v>6827043</v>
+        <v>6827117</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8573,9 +8573,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8590,19 +8600,19 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>130255830</v>
+        <v>130255817</v>
       </c>
       <c r="B76" t="n">
         <v>79211</v>
@@ -8637,10 +8647,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>496649</v>
+        <v>496872</v>
       </c>
       <c r="R76" t="n">
-        <v>6827117</v>
+        <v>6827052</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8672,7 +8682,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8682,7 +8692,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8709,7 +8719,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>130255820</v>
+        <v>130256369</v>
       </c>
       <c r="B77" t="n">
         <v>79211</v>
@@ -8744,10 +8754,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>496838</v>
+        <v>496893</v>
       </c>
       <c r="R77" t="n">
-        <v>6827085</v>
+        <v>6827043</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8777,19 +8787,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>11:04</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8804,12 +8804,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -10040,7 +10040,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>130256387</v>
+        <v>130255814</v>
       </c>
       <c r="B90" t="n">
         <v>79211</v>
@@ -10075,10 +10075,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>496715</v>
+        <v>497073</v>
       </c>
       <c r="R90" t="n">
-        <v>6827126</v>
+        <v>6827132</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10108,9 +10108,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10125,19 +10135,19 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>130255814</v>
+        <v>130256387</v>
       </c>
       <c r="B91" t="n">
         <v>79211</v>
@@ -10172,10 +10182,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>497073</v>
+        <v>496715</v>
       </c>
       <c r="R91" t="n">
-        <v>6827132</v>
+        <v>6827126</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10205,19 +10215,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>11:27</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>11:27</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10232,19 +10232,19 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>130256370</v>
+        <v>130255808</v>
       </c>
       <c r="B92" t="n">
         <v>79211</v>
@@ -10279,10 +10279,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>496894</v>
+        <v>497167</v>
       </c>
       <c r="R92" t="n">
-        <v>6827030</v>
+        <v>6826594</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10312,9 +10312,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10329,22 +10339,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>130255798</v>
+        <v>130256370</v>
       </c>
       <c r="B93" t="n">
-        <v>78968</v>
+        <v>79211</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10352,21 +10362,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10376,10 +10386,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>496740</v>
+        <v>496894</v>
       </c>
       <c r="R93" t="n">
-        <v>6827145</v>
+        <v>6827030</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10409,19 +10419,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>10:45</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>10:45</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10436,22 +10436,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>130255808</v>
+        <v>130255798</v>
       </c>
       <c r="B94" t="n">
-        <v>79211</v>
+        <v>78968</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10459,21 +10459,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10483,10 +10483,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>497167</v>
+        <v>496740</v>
       </c>
       <c r="R94" t="n">
-        <v>6826594</v>
+        <v>6827145</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10518,7 +10518,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10528,7 +10528,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10856,10 +10856,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>130256350</v>
+        <v>130255807</v>
       </c>
       <c r="B98" t="n">
-        <v>78968</v>
+        <v>79211</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10867,21 +10867,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10891,10 +10891,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>496962</v>
+        <v>497130</v>
       </c>
       <c r="R98" t="n">
-        <v>6826909</v>
+        <v>6826601</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10924,9 +10924,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10941,19 +10951,19 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>130255807</v>
+        <v>130255812</v>
       </c>
       <c r="B99" t="n">
         <v>79211</v>
@@ -10988,10 +10998,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>497130</v>
+        <v>497186</v>
       </c>
       <c r="R99" t="n">
-        <v>6826601</v>
+        <v>6826839</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11023,7 +11033,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11033,7 +11043,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11060,7 +11070,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>130255812</v>
+        <v>130256391</v>
       </c>
       <c r="B100" t="n">
         <v>79211</v>
@@ -11095,10 +11105,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>497186</v>
+        <v>496588</v>
       </c>
       <c r="R100" t="n">
-        <v>6826839</v>
+        <v>6827066</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11128,19 +11138,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>11:52</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>11:52</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11155,19 +11155,19 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>130256391</v>
+        <v>130256375</v>
       </c>
       <c r="B101" t="n">
         <v>79211</v>
@@ -11202,10 +11202,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>496588</v>
+        <v>496859</v>
       </c>
       <c r="R101" t="n">
-        <v>6827066</v>
+        <v>6827052</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11264,10 +11264,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>130256375</v>
+        <v>130256350</v>
       </c>
       <c r="B102" t="n">
-        <v>79211</v>
+        <v>78968</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11275,21 +11275,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11299,10 +11299,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>496859</v>
+        <v>496962</v>
       </c>
       <c r="R102" t="n">
-        <v>6827052</v>
+        <v>6826909</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11468,7 +11468,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>130255833</v>
+        <v>130255804</v>
       </c>
       <c r="B104" t="n">
         <v>79211</v>
@@ -11503,10 +11503,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>496579</v>
+        <v>497012</v>
       </c>
       <c r="R104" t="n">
-        <v>6827030</v>
+        <v>6826898</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11538,7 +11538,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11575,10 +11575,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>130256351</v>
+        <v>130255833</v>
       </c>
       <c r="B105" t="n">
-        <v>78968</v>
+        <v>79211</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11586,21 +11586,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11610,10 +11610,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>496898</v>
+        <v>496579</v>
       </c>
       <c r="R105" t="n">
-        <v>6827000</v>
+        <v>6827030</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11643,9 +11643,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11660,22 +11670,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>130255826</v>
+        <v>130256351</v>
       </c>
       <c r="B106" t="n">
-        <v>79211</v>
+        <v>78968</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11683,21 +11693,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11707,10 +11717,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>496694</v>
+        <v>496898</v>
       </c>
       <c r="R106" t="n">
-        <v>6827122</v>
+        <v>6827000</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11740,19 +11750,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z106" t="inlineStr">
-        <is>
-          <t>10:34</t>
-        </is>
-      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB106" t="inlineStr">
-        <is>
-          <t>10:34</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11767,22 +11767,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>130256353</v>
+        <v>130255826</v>
       </c>
       <c r="B107" t="n">
-        <v>78968</v>
+        <v>79211</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11790,21 +11790,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11814,10 +11814,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>496827</v>
+        <v>496694</v>
       </c>
       <c r="R107" t="n">
-        <v>6827089</v>
+        <v>6827122</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11847,9 +11847,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11864,22 +11874,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>130255804</v>
+        <v>130256353</v>
       </c>
       <c r="B108" t="n">
-        <v>79211</v>
+        <v>78968</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11887,21 +11897,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11911,10 +11921,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>497012</v>
+        <v>496827</v>
       </c>
       <c r="R108" t="n">
-        <v>6826898</v>
+        <v>6827089</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11944,19 +11954,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z108" t="inlineStr">
-        <is>
-          <t>12:22</t>
-        </is>
-      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB108" t="inlineStr">
-        <is>
-          <t>12:22</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11971,22 +11971,22 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>130256342</v>
+        <v>130256374</v>
       </c>
       <c r="B109" t="n">
-        <v>57854</v>
+        <v>79211</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11994,42 +11994,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>496940</v>
+        <v>496863</v>
       </c>
       <c r="R109" t="n">
-        <v>6826899</v>
+        <v>6827047</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12062,11 +12054,6 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12093,7 +12080,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>130256374</v>
+        <v>130256360</v>
       </c>
       <c r="B110" t="n">
         <v>79211</v>
@@ -12128,10 +12115,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>496863</v>
+        <v>496972</v>
       </c>
       <c r="R110" t="n">
-        <v>6827047</v>
+        <v>6826953</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12190,7 +12177,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>130256360</v>
+        <v>130255819</v>
       </c>
       <c r="B111" t="n">
         <v>79211</v>
@@ -12225,10 +12212,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>496972</v>
+        <v>496850</v>
       </c>
       <c r="R111" t="n">
-        <v>6826953</v>
+        <v>6827090</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12258,9 +12245,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12275,12 +12272,12 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
@@ -12384,7 +12381,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>130255819</v>
+        <v>130256386</v>
       </c>
       <c r="B113" t="n">
         <v>79211</v>
@@ -12419,10 +12416,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>496850</v>
+        <v>496723</v>
       </c>
       <c r="R113" t="n">
-        <v>6827090</v>
+        <v>6827125</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12452,19 +12449,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z113" t="inlineStr">
-        <is>
-          <t>11:05</t>
-        </is>
-      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB113" t="inlineStr">
-        <is>
-          <t>11:05</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12479,22 +12466,22 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>130256386</v>
+        <v>130256342</v>
       </c>
       <c r="B114" t="n">
-        <v>79211</v>
+        <v>57854</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12502,34 +12489,42 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>496723</v>
+        <v>496940</v>
       </c>
       <c r="R114" t="n">
-        <v>6827125</v>
+        <v>6826899</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12562,6 +12557,11 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12889,45 +12889,54 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>130256359</v>
+        <v>130256348</v>
       </c>
       <c r="B118" t="n">
-        <v>79211</v>
+        <v>8451</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>496963</v>
+        <v>496864</v>
       </c>
       <c r="R118" t="n">
-        <v>6826942</v>
+        <v>6827043</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12968,6 +12977,7 @@
       <c r="AE118" t="b">
         <v>0</v>
       </c>
+      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
@@ -13578,7 +13588,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>130255801</v>
+        <v>130256359</v>
       </c>
       <c r="B125" t="n">
         <v>79211</v>
@@ -13613,10 +13623,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>496702</v>
+        <v>496963</v>
       </c>
       <c r="R125" t="n">
-        <v>6827131</v>
+        <v>6826942</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13646,19 +13656,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z125" t="inlineStr">
-        <is>
-          <t>10:39</t>
-        </is>
-      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB125" t="inlineStr">
-        <is>
-          <t>10:39</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13673,66 +13673,57 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>130256348</v>
+        <v>130255801</v>
       </c>
       <c r="B126" t="n">
-        <v>8451</v>
+        <v>79211</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr"/>
-      <c r="K126" t="inlineStr"/>
-      <c r="L126" t="inlineStr"/>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>496864</v>
+        <v>496702</v>
       </c>
       <c r="R126" t="n">
-        <v>6827043</v>
+        <v>6827131</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13762,62 +13753,71 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
       <c r="AD126" t="b">
         <v>0</v>
       </c>
       <c r="AE126" t="b">
         <v>0</v>
       </c>
-      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>130256392</v>
+        <v>130255834</v>
       </c>
       <c r="B127" t="n">
-        <v>93047</v>
+        <v>79211</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13827,10 +13827,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>496581</v>
+        <v>496582</v>
       </c>
       <c r="R127" t="n">
-        <v>6827082</v>
+        <v>6827040</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13860,62 +13860,71 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
       <c r="AD127" t="b">
         <v>0</v>
       </c>
       <c r="AE127" t="b">
         <v>0</v>
       </c>
-      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>130255834</v>
+        <v>130256392</v>
       </c>
       <c r="B128" t="n">
-        <v>79211</v>
+        <v>93047</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13925,10 +13934,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>496582</v>
+        <v>496581</v>
       </c>
       <c r="R128" t="n">
-        <v>6827040</v>
+        <v>6827082</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13958,39 +13967,30 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z128" t="inlineStr">
-        <is>
-          <t>10:10</t>
-        </is>
-      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="AB128" t="inlineStr">
-        <is>
-          <t>10:10</t>
-        </is>
-      </c>
       <c r="AD128" t="b">
         <v>0</v>
       </c>
       <c r="AE128" t="b">
         <v>0</v>
       </c>
+      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
@@ -14211,45 +14211,54 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>130256343</v>
+        <v>130255793</v>
       </c>
       <c r="B131" t="n">
-        <v>79211</v>
+        <v>8451</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>496851</v>
+        <v>496670</v>
       </c>
       <c r="R131" t="n">
-        <v>6827066</v>
+        <v>6827136</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14279,83 +14288,85 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AD131" t="b">
         <v>0</v>
       </c>
       <c r="AE131" t="b">
         <v>0</v>
       </c>
+      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>130255793</v>
+        <v>130256343</v>
       </c>
       <c r="B132" t="n">
-        <v>8451</v>
+        <v>79211</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr"/>
-      <c r="K132" t="inlineStr"/>
-      <c r="L132" t="inlineStr"/>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>496670</v>
+        <v>496851</v>
       </c>
       <c r="R132" t="n">
-        <v>6827136</v>
+        <v>6827066</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14385,40 +14396,29 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z132" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="AB132" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AD132" t="b">
         <v>0</v>
       </c>
       <c r="AE132" t="b">
         <v>0</v>
       </c>
-      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
@@ -14639,10 +14639,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>130256345</v>
+        <v>130255810</v>
       </c>
       <c r="B135" t="n">
-        <v>78969</v>
+        <v>79211</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14650,21 +14650,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14674,10 +14674,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>496837</v>
+        <v>497191</v>
       </c>
       <c r="R135" t="n">
-        <v>6827069</v>
+        <v>6826663</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14707,9 +14707,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB135" t="inlineStr">
+        <is>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14724,19 +14734,19 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>130255806</v>
+        <v>130255813</v>
       </c>
       <c r="B136" t="n">
         <v>79211</v>
@@ -14771,10 +14781,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>497147</v>
+        <v>497093</v>
       </c>
       <c r="R136" t="n">
-        <v>6826725</v>
+        <v>6827168</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14806,7 +14816,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -14816,7 +14826,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14843,10 +14853,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>130255810</v>
+        <v>130256345</v>
       </c>
       <c r="B137" t="n">
-        <v>79211</v>
+        <v>78969</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14854,21 +14864,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14878,10 +14888,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>497191</v>
+        <v>496837</v>
       </c>
       <c r="R137" t="n">
-        <v>6826663</v>
+        <v>6827069</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14911,19 +14921,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z137" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AA137" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB137" t="inlineStr">
-        <is>
-          <t>12:06</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14938,22 +14938,22 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>130255813</v>
+        <v>130256344</v>
       </c>
       <c r="B138" t="n">
-        <v>79211</v>
+        <v>78969</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14961,21 +14961,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14985,10 +14985,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>497093</v>
+        <v>496869</v>
       </c>
       <c r="R138" t="n">
-        <v>6827168</v>
+        <v>6827038</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15018,19 +15018,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z138" t="inlineStr">
-        <is>
-          <t>11:31</t>
-        </is>
-      </c>
       <c r="AA138" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB138" t="inlineStr">
-        <is>
-          <t>11:31</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15045,22 +15035,22 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>130256344</v>
+        <v>130255806</v>
       </c>
       <c r="B139" t="n">
-        <v>78969</v>
+        <v>79211</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15068,21 +15058,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15092,10 +15082,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>496869</v>
+        <v>497147</v>
       </c>
       <c r="R139" t="n">
-        <v>6827038</v>
+        <v>6826725</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15125,9 +15115,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB139" t="inlineStr">
+        <is>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15142,19 +15142,19 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>130256358</v>
+        <v>130256361</v>
       </c>
       <c r="B140" t="n">
         <v>79211</v>
@@ -15189,10 +15189,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>496962</v>
+        <v>496893</v>
       </c>
       <c r="R140" t="n">
-        <v>6826923</v>
+        <v>6826989</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15251,7 +15251,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>130256361</v>
+        <v>130256389</v>
       </c>
       <c r="B141" t="n">
         <v>79211</v>
@@ -15286,10 +15286,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>496893</v>
+        <v>496578</v>
       </c>
       <c r="R141" t="n">
-        <v>6826989</v>
+        <v>6827076</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15348,7 +15348,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>130256389</v>
+        <v>130256358</v>
       </c>
       <c r="B142" t="n">
         <v>79211</v>
@@ -15383,10 +15383,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>496578</v>
+        <v>496962</v>
       </c>
       <c r="R142" t="n">
-        <v>6827076</v>
+        <v>6826923</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15445,7 +15445,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>130256364</v>
+        <v>130256355</v>
       </c>
       <c r="B143" t="n">
         <v>79211</v>
@@ -15480,10 +15480,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>496909</v>
+        <v>496940</v>
       </c>
       <c r="R143" t="n">
-        <v>6827002</v>
+        <v>6826898</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15542,7 +15542,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>130256355</v>
+        <v>130256362</v>
       </c>
       <c r="B144" t="n">
         <v>79211</v>
@@ -15577,10 +15577,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>496940</v>
+        <v>496893</v>
       </c>
       <c r="R144" t="n">
-        <v>6826898</v>
+        <v>6826998</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15639,7 +15639,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>130256371</v>
+        <v>130256364</v>
       </c>
       <c r="B145" t="n">
         <v>79211</v>
@@ -15674,10 +15674,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>496880</v>
+        <v>496909</v>
       </c>
       <c r="R145" t="n">
-        <v>6827036</v>
+        <v>6827002</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15736,7 +15736,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>130255828</v>
+        <v>130256371</v>
       </c>
       <c r="B146" t="n">
         <v>79211</v>
@@ -15771,10 +15771,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>496658</v>
+        <v>496880</v>
       </c>
       <c r="R146" t="n">
-        <v>6827133</v>
+        <v>6827036</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15804,19 +15804,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z146" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA146" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB146" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15831,19 +15821,19 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>130255821</v>
+        <v>130255828</v>
       </c>
       <c r="B147" t="n">
         <v>79211</v>
@@ -15878,10 +15868,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>496839</v>
+        <v>496658</v>
       </c>
       <c r="R147" t="n">
-        <v>6827082</v>
+        <v>6827133</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15913,7 +15903,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -15923,7 +15913,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15950,7 +15940,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>130256362</v>
+        <v>130255821</v>
       </c>
       <c r="B148" t="n">
         <v>79211</v>
@@ -15985,10 +15975,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>496893</v>
+        <v>496839</v>
       </c>
       <c r="R148" t="n">
-        <v>6826998</v>
+        <v>6827082</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16018,9 +16008,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z148" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB148" t="inlineStr">
+        <is>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16035,12 +16035,12 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
@@ -16253,7 +16253,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>130255811</v>
+        <v>130255831</v>
       </c>
       <c r="B151" t="n">
         <v>79211</v>
@@ -16288,10 +16288,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>497200</v>
+        <v>496599</v>
       </c>
       <c r="R151" t="n">
-        <v>6826832</v>
+        <v>6827121</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16323,7 +16323,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -16333,7 +16333,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16360,7 +16360,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>130255831</v>
+        <v>130256372</v>
       </c>
       <c r="B152" t="n">
         <v>79211</v>
@@ -16395,10 +16395,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>496599</v>
+        <v>496867</v>
       </c>
       <c r="R152" t="n">
-        <v>6827121</v>
+        <v>6827035</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16428,19 +16428,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z152" t="inlineStr">
-        <is>
-          <t>10:18</t>
-        </is>
-      </c>
       <c r="AA152" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB152" t="inlineStr">
-        <is>
-          <t>10:18</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16455,19 +16445,19 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>130256372</v>
+        <v>130255811</v>
       </c>
       <c r="B153" t="n">
         <v>79211</v>
@@ -16502,10 +16492,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>496867</v>
+        <v>497200</v>
       </c>
       <c r="R153" t="n">
-        <v>6827035</v>
+        <v>6826832</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16535,9 +16525,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z153" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB153" t="inlineStr">
+        <is>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16552,12 +16552,12 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
@@ -16671,32 +16671,32 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>130255838</v>
+        <v>130256385</v>
       </c>
       <c r="B155" t="n">
-        <v>93047</v>
+        <v>79211</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16706,10 +16706,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>496571</v>
+        <v>496747</v>
       </c>
       <c r="R155" t="n">
-        <v>6827076</v>
+        <v>6827065</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16739,19 +16739,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z155" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
       <c r="AA155" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB155" t="inlineStr">
-        <is>
-          <t>10:13</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16766,44 +16756,44 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>130256385</v>
+        <v>130255838</v>
       </c>
       <c r="B156" t="n">
-        <v>79211</v>
+        <v>93047</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16813,10 +16803,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>496747</v>
+        <v>496571</v>
       </c>
       <c r="R156" t="n">
-        <v>6827065</v>
+        <v>6827076</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16846,9 +16836,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z156" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB156" t="inlineStr">
+        <is>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16863,44 +16863,44 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>130256393</v>
+        <v>130255809</v>
       </c>
       <c r="B157" t="n">
-        <v>93047</v>
+        <v>79211</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16910,10 +16910,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>496647</v>
+        <v>497168</v>
       </c>
       <c r="R157" t="n">
-        <v>6827158</v>
+        <v>6826596</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16943,9 +16943,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
       <c r="AA157" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB157" t="inlineStr">
+        <is>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16960,19 +16970,19 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>130255809</v>
+        <v>130255816</v>
       </c>
       <c r="B158" t="n">
         <v>79211</v>
@@ -17007,10 +17017,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>497168</v>
+        <v>496954</v>
       </c>
       <c r="R158" t="n">
-        <v>6826596</v>
+        <v>6827096</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17042,7 +17052,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -17052,7 +17062,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17079,7 +17089,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>130255816</v>
+        <v>130255829</v>
       </c>
       <c r="B159" t="n">
         <v>79211</v>
@@ -17114,10 +17124,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>496954</v>
+        <v>496643</v>
       </c>
       <c r="R159" t="n">
-        <v>6827096</v>
+        <v>6827146</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17149,7 +17159,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -17159,7 +17169,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17186,32 +17196,32 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>130255829</v>
+        <v>130256393</v>
       </c>
       <c r="B160" t="n">
-        <v>79211</v>
+        <v>93047</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17221,10 +17231,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>496643</v>
+        <v>496647</v>
       </c>
       <c r="R160" t="n">
-        <v>6827146</v>
+        <v>6827158</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17254,19 +17264,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z160" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB160" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17281,12 +17281,12 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>

--- a/artfynd/A 58895-2025 artfynd.xlsx
+++ b/artfynd/A 58895-2025 artfynd.xlsx
@@ -7892,7 +7892,7 @@
         <v>130256379</v>
       </c>
       <c r="B69" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7986,10 +7986,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130256356</v>
+        <v>130252149</v>
       </c>
       <c r="B70" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8015,16 +8015,19 @@
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Bergtallstjärnarna, Dlr</t>
+          <t>Bergfallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>496957</v>
+        <v>496745</v>
       </c>
       <c r="R70" t="n">
-        <v>6826898</v>
+        <v>6827070</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8054,29 +8057,40 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -8086,7 +8100,7 @@
         <v>130256388</v>
       </c>
       <c r="B71" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8180,10 +8194,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130252149</v>
+        <v>130256356</v>
       </c>
       <c r="B72" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8209,19 +8223,16 @@
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Bergfallstjärnarna, Dlr</t>
+          <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>496745</v>
+        <v>496957</v>
       </c>
       <c r="R72" t="n">
-        <v>6827070</v>
+        <v>6826898</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8251,50 +8262,39 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>10:56</t>
-        </is>
-      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130255832</v>
+        <v>130256369</v>
       </c>
       <c r="B73" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8326,10 +8326,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>496578</v>
+        <v>496893</v>
       </c>
       <c r="R73" t="n">
-        <v>6827044</v>
+        <v>6827043</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8359,19 +8359,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>10:11</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>10:11</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8386,22 +8376,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130255820</v>
+        <v>130255830</v>
       </c>
       <c r="B74" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8433,10 +8423,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>496838</v>
+        <v>496649</v>
       </c>
       <c r="R74" t="n">
-        <v>6827085</v>
+        <v>6827117</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8468,7 +8458,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8478,7 +8468,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8505,10 +8495,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130255830</v>
+        <v>130255820</v>
       </c>
       <c r="B75" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8540,10 +8530,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>496649</v>
+        <v>496838</v>
       </c>
       <c r="R75" t="n">
-        <v>6827117</v>
+        <v>6827085</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8575,7 +8565,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8585,7 +8575,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8615,7 +8605,7 @@
         <v>130255817</v>
       </c>
       <c r="B76" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8719,10 +8709,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>130256369</v>
+        <v>130255832</v>
       </c>
       <c r="B77" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8754,10 +8744,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>496893</v>
+        <v>496578</v>
       </c>
       <c r="R77" t="n">
-        <v>6827043</v>
+        <v>6827044</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8787,9 +8777,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8804,22 +8804,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>130256383</v>
+        <v>130256376</v>
       </c>
       <c r="B78" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8851,10 +8851,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>496821</v>
+        <v>496855</v>
       </c>
       <c r="R78" t="n">
-        <v>6827087</v>
+        <v>6827052</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8913,10 +8913,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>130256365</v>
+        <v>130256368</v>
       </c>
       <c r="B79" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8948,10 +8948,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>496920</v>
+        <v>496902</v>
       </c>
       <c r="R79" t="n">
-        <v>6827003</v>
+        <v>6827030</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9010,10 +9010,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>130255797</v>
+        <v>130256365</v>
       </c>
       <c r="B80" t="n">
-        <v>78968</v>
+        <v>79219</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9021,21 +9021,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9045,10 +9045,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>497218</v>
+        <v>496920</v>
       </c>
       <c r="R80" t="n">
-        <v>6826761</v>
+        <v>6827003</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9078,19 +9078,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>11:59</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>11:59</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9105,22 +9095,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>130256376</v>
+        <v>130255797</v>
       </c>
       <c r="B81" t="n">
-        <v>79211</v>
+        <v>78976</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9128,21 +9118,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9152,10 +9142,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>496855</v>
+        <v>497218</v>
       </c>
       <c r="R81" t="n">
-        <v>6827052</v>
+        <v>6826761</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9185,9 +9175,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9202,22 +9202,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>130256368</v>
+        <v>130256383</v>
       </c>
       <c r="B82" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9249,10 +9249,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>496902</v>
+        <v>496821</v>
       </c>
       <c r="R82" t="n">
-        <v>6827030</v>
+        <v>6827087</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9314,7 +9314,7 @@
         <v>130255837</v>
       </c>
       <c r="B83" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9421,7 +9421,7 @@
         <v>130256346</v>
       </c>
       <c r="B84" t="n">
-        <v>78969</v>
+        <v>78977</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9515,32 +9515,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>130255839</v>
+        <v>130256352</v>
       </c>
       <c r="B85" t="n">
-        <v>93047</v>
+        <v>78976</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9550,10 +9550,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>496787</v>
+        <v>496837</v>
       </c>
       <c r="R85" t="n">
-        <v>6827052</v>
+        <v>6827069</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9583,19 +9583,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>11:02</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9610,44 +9600,44 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>130256352</v>
+        <v>130255839</v>
       </c>
       <c r="B86" t="n">
-        <v>78968</v>
+        <v>93060</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9657,10 +9647,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>496837</v>
+        <v>496787</v>
       </c>
       <c r="R86" t="n">
-        <v>6827069</v>
+        <v>6827052</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9690,9 +9680,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9707,22 +9707,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>130255823</v>
+        <v>130255818</v>
       </c>
       <c r="B87" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9754,10 +9754,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>496757</v>
+        <v>496862</v>
       </c>
       <c r="R87" t="n">
-        <v>6827109</v>
+        <v>6827065</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9789,7 +9789,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9799,7 +9799,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9826,10 +9826,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>130255803</v>
+        <v>130255823</v>
       </c>
       <c r="B88" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9861,10 +9861,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>497148</v>
+        <v>496757</v>
       </c>
       <c r="R88" t="n">
-        <v>6826907</v>
+        <v>6827109</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9896,7 +9896,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -9906,7 +9906,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9933,10 +9933,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>130255818</v>
+        <v>130256387</v>
       </c>
       <c r="B89" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9968,10 +9968,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>496862</v>
+        <v>496715</v>
       </c>
       <c r="R89" t="n">
-        <v>6827065</v>
+        <v>6827126</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10001,19 +10001,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>11:06</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>11:06</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10028,22 +10018,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>130255814</v>
+        <v>130255803</v>
       </c>
       <c r="B90" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10075,10 +10065,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>497073</v>
+        <v>497148</v>
       </c>
       <c r="R90" t="n">
-        <v>6827132</v>
+        <v>6826907</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10110,7 +10100,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10120,7 +10110,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10147,10 +10137,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>130256387</v>
+        <v>130255814</v>
       </c>
       <c r="B91" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10182,10 +10172,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>496715</v>
+        <v>497073</v>
       </c>
       <c r="R91" t="n">
-        <v>6827126</v>
+        <v>6827132</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10215,9 +10205,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10232,12 +10232,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
@@ -10247,7 +10247,7 @@
         <v>130255808</v>
       </c>
       <c r="B92" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10351,10 +10351,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>130256370</v>
+        <v>130255798</v>
       </c>
       <c r="B93" t="n">
-        <v>79211</v>
+        <v>78976</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10362,21 +10362,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10386,10 +10386,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>496894</v>
+        <v>496740</v>
       </c>
       <c r="R93" t="n">
-        <v>6827030</v>
+        <v>6827145</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10419,9 +10419,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10436,22 +10446,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>130255798</v>
+        <v>130256370</v>
       </c>
       <c r="B94" t="n">
-        <v>78968</v>
+        <v>79219</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10459,21 +10469,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10483,10 +10493,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>496740</v>
+        <v>496894</v>
       </c>
       <c r="R94" t="n">
-        <v>6827145</v>
+        <v>6827030</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10516,19 +10526,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>10:45</t>
-        </is>
-      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>10:45</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10543,12 +10543,12 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
@@ -10558,7 +10558,7 @@
         <v>130256367</v>
       </c>
       <c r="B95" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10655,7 +10655,7 @@
         <v>130256373</v>
       </c>
       <c r="B96" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10749,10 +10749,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>130255827</v>
+        <v>130256350</v>
       </c>
       <c r="B97" t="n">
-        <v>79211</v>
+        <v>78976</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10760,21 +10760,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10784,10 +10784,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>496658</v>
+        <v>496962</v>
       </c>
       <c r="R97" t="n">
-        <v>6827164</v>
+        <v>6826909</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10817,19 +10817,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>10:27</t>
-        </is>
-      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>10:27</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10844,22 +10834,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>130255807</v>
+        <v>130255827</v>
       </c>
       <c r="B98" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10891,10 +10881,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>497130</v>
+        <v>496658</v>
       </c>
       <c r="R98" t="n">
-        <v>6826601</v>
+        <v>6827164</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10926,7 +10916,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -10936,7 +10926,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10963,10 +10953,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>130255812</v>
+        <v>130256391</v>
       </c>
       <c r="B99" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10998,10 +10988,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>497186</v>
+        <v>496588</v>
       </c>
       <c r="R99" t="n">
-        <v>6826839</v>
+        <v>6827066</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11031,19 +11021,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>11:52</t>
-        </is>
-      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>11:52</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11058,22 +11038,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>130256391</v>
+        <v>130256375</v>
       </c>
       <c r="B100" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11105,10 +11085,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>496588</v>
+        <v>496859</v>
       </c>
       <c r="R100" t="n">
-        <v>6827066</v>
+        <v>6827052</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11167,10 +11147,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>130256375</v>
+        <v>130255812</v>
       </c>
       <c r="B101" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11202,10 +11182,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>496859</v>
+        <v>497186</v>
       </c>
       <c r="R101" t="n">
-        <v>6827052</v>
+        <v>6826839</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11235,9 +11215,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11252,22 +11242,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>130256350</v>
+        <v>130255825</v>
       </c>
       <c r="B102" t="n">
-        <v>78968</v>
+        <v>79219</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11275,21 +11265,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11299,10 +11289,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>496962</v>
+        <v>496759</v>
       </c>
       <c r="R102" t="n">
-        <v>6826909</v>
+        <v>6827133</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11332,9 +11322,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11349,22 +11349,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>130255825</v>
+        <v>130255807</v>
       </c>
       <c r="B103" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11396,10 +11396,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>496759</v>
+        <v>497130</v>
       </c>
       <c r="R103" t="n">
-        <v>6827133</v>
+        <v>6826601</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11431,7 +11431,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11441,7 +11441,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11468,10 +11468,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>130255804</v>
+        <v>130255833</v>
       </c>
       <c r="B104" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11503,10 +11503,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>497012</v>
+        <v>496579</v>
       </c>
       <c r="R104" t="n">
-        <v>6826898</v>
+        <v>6827030</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11538,7 +11538,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11575,10 +11575,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>130255833</v>
+        <v>130256351</v>
       </c>
       <c r="B105" t="n">
-        <v>79211</v>
+        <v>78976</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11586,21 +11586,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11610,10 +11610,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>496579</v>
+        <v>496898</v>
       </c>
       <c r="R105" t="n">
-        <v>6827030</v>
+        <v>6827000</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11643,19 +11643,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z105" t="inlineStr">
-        <is>
-          <t>10:11</t>
-        </is>
-      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB105" t="inlineStr">
-        <is>
-          <t>10:11</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11670,22 +11660,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>130256351</v>
+        <v>130255804</v>
       </c>
       <c r="B106" t="n">
-        <v>78968</v>
+        <v>79219</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11693,21 +11683,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11717,10 +11707,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>496898</v>
+        <v>497012</v>
       </c>
       <c r="R106" t="n">
-        <v>6827000</v>
+        <v>6826898</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11750,9 +11740,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11767,22 +11767,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>130255826</v>
+        <v>130256353</v>
       </c>
       <c r="B107" t="n">
-        <v>79211</v>
+        <v>78976</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11790,21 +11790,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11814,10 +11814,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>496694</v>
+        <v>496827</v>
       </c>
       <c r="R107" t="n">
-        <v>6827122</v>
+        <v>6827089</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11847,19 +11847,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z107" t="inlineStr">
-        <is>
-          <t>10:34</t>
-        </is>
-      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB107" t="inlineStr">
-        <is>
-          <t>10:34</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11874,22 +11864,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>130256353</v>
+        <v>130255826</v>
       </c>
       <c r="B108" t="n">
-        <v>78968</v>
+        <v>79219</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11897,21 +11887,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11921,10 +11911,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>496827</v>
+        <v>496694</v>
       </c>
       <c r="R108" t="n">
-        <v>6827089</v>
+        <v>6827122</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11954,9 +11944,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11971,22 +11971,22 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>130256374</v>
+        <v>130256386</v>
       </c>
       <c r="B109" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12018,10 +12018,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>496863</v>
+        <v>496723</v>
       </c>
       <c r="R109" t="n">
-        <v>6827047</v>
+        <v>6827125</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12080,10 +12080,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>130256360</v>
+        <v>130256354</v>
       </c>
       <c r="B110" t="n">
-        <v>79211</v>
+        <v>78976</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12091,21 +12091,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>496972</v>
+        <v>496654</v>
       </c>
       <c r="R110" t="n">
-        <v>6826953</v>
+        <v>6827171</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12180,7 +12180,7 @@
         <v>130255819</v>
       </c>
       <c r="B111" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12284,10 +12284,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>130256354</v>
+        <v>130256360</v>
       </c>
       <c r="B112" t="n">
-        <v>78968</v>
+        <v>79219</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12295,21 +12295,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12319,10 +12319,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>496654</v>
+        <v>496972</v>
       </c>
       <c r="R112" t="n">
-        <v>6827171</v>
+        <v>6826953</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12381,10 +12381,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>130256386</v>
+        <v>130256374</v>
       </c>
       <c r="B113" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12416,10 +12416,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>496723</v>
+        <v>496863</v>
       </c>
       <c r="R113" t="n">
-        <v>6827125</v>
+        <v>6827047</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12481,7 +12481,7 @@
         <v>130256342</v>
       </c>
       <c r="B114" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12591,7 +12591,7 @@
         <v>130256380</v>
       </c>
       <c r="B115" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12685,10 +12685,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>130255802</v>
+        <v>130256357</v>
       </c>
       <c r="B116" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12720,10 +12720,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>496785</v>
+        <v>496964</v>
       </c>
       <c r="R116" t="n">
-        <v>6827060</v>
+        <v>6826912</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12753,19 +12753,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z116" t="inlineStr">
-        <is>
-          <t>12:47</t>
-        </is>
-      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB116" t="inlineStr">
-        <is>
-          <t>12:47</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12780,22 +12770,22 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>130256357</v>
+        <v>130255802</v>
       </c>
       <c r="B117" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12827,10 +12817,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>496964</v>
+        <v>496785</v>
       </c>
       <c r="R117" t="n">
-        <v>6826912</v>
+        <v>6827060</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12860,9 +12850,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12877,12 +12877,12 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
@@ -12996,10 +12996,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>130256390</v>
+        <v>130256382</v>
       </c>
       <c r="B119" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13031,10 +13031,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>496581</v>
+        <v>496831</v>
       </c>
       <c r="R119" t="n">
-        <v>6827049</v>
+        <v>6827081</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13093,10 +13093,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>130256363</v>
+        <v>130256381</v>
       </c>
       <c r="B120" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13128,10 +13128,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>496897</v>
+        <v>496852</v>
       </c>
       <c r="R120" t="n">
-        <v>6827002</v>
+        <v>6827066</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13190,10 +13190,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>130256381</v>
+        <v>130255801</v>
       </c>
       <c r="B121" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13225,10 +13225,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>496852</v>
+        <v>496702</v>
       </c>
       <c r="R121" t="n">
-        <v>6827066</v>
+        <v>6827131</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13258,9 +13258,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13275,22 +13285,22 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>130255796</v>
+        <v>130256378</v>
       </c>
       <c r="B122" t="n">
-        <v>78968</v>
+        <v>79219</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13298,21 +13308,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13322,10 +13332,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>497111</v>
+        <v>496862</v>
       </c>
       <c r="R122" t="n">
-        <v>6826644</v>
+        <v>6827064</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13355,19 +13365,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z122" t="inlineStr">
-        <is>
-          <t>12:13</t>
-        </is>
-      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB122" t="inlineStr">
-        <is>
-          <t>12:13</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13382,22 +13382,22 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>130256378</v>
+        <v>130255796</v>
       </c>
       <c r="B123" t="n">
-        <v>79211</v>
+        <v>78976</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13405,21 +13405,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13429,10 +13429,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>496862</v>
+        <v>497111</v>
       </c>
       <c r="R123" t="n">
-        <v>6827064</v>
+        <v>6826644</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13462,9 +13462,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13479,22 +13489,22 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>130256382</v>
+        <v>130256363</v>
       </c>
       <c r="B124" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13526,10 +13536,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>496831</v>
+        <v>496897</v>
       </c>
       <c r="R124" t="n">
-        <v>6827081</v>
+        <v>6827002</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13588,10 +13598,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>130256359</v>
+        <v>130256390</v>
       </c>
       <c r="B125" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13623,10 +13633,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>496963</v>
+        <v>496581</v>
       </c>
       <c r="R125" t="n">
-        <v>6826942</v>
+        <v>6827049</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13685,10 +13695,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>130255801</v>
+        <v>130256359</v>
       </c>
       <c r="B126" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13720,10 +13730,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>496702</v>
+        <v>496963</v>
       </c>
       <c r="R126" t="n">
-        <v>6827131</v>
+        <v>6826942</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13753,19 +13763,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z126" t="inlineStr">
-        <is>
-          <t>10:39</t>
-        </is>
-      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB126" t="inlineStr">
-        <is>
-          <t>10:39</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13780,12 +13780,12 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
@@ -13795,7 +13795,7 @@
         <v>130255834</v>
       </c>
       <c r="B127" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13899,32 +13899,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>130256392</v>
+        <v>130255805</v>
       </c>
       <c r="B128" t="n">
-        <v>93047</v>
+        <v>79219</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13934,10 +13934,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>496581</v>
+        <v>497139</v>
       </c>
       <c r="R128" t="n">
-        <v>6827082</v>
+        <v>6826719</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13967,40 +13967,49 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
       <c r="AD128" t="b">
         <v>0</v>
       </c>
       <c r="AE128" t="b">
         <v>0</v>
       </c>
-      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>130255836</v>
+        <v>130256343</v>
       </c>
       <c r="B129" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14032,10 +14041,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>497183</v>
+        <v>496851</v>
       </c>
       <c r="R129" t="n">
-        <v>6826662</v>
+        <v>6827066</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14065,19 +14074,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z129" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB129" t="inlineStr">
-        <is>
-          <t>12:06</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14092,22 +14091,22 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>130255805</v>
+        <v>130255836</v>
       </c>
       <c r="B130" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14139,10 +14138,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>497139</v>
+        <v>497183</v>
       </c>
       <c r="R130" t="n">
-        <v>6826719</v>
+        <v>6826662</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14174,7 +14173,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -14184,7 +14183,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14211,10 +14210,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>130255793</v>
+        <v>130256392</v>
       </c>
       <c r="B131" t="n">
-        <v>8451</v>
+        <v>93060</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14222,43 +14221,34 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="J131" t="inlineStr"/>
-      <c r="K131" t="inlineStr"/>
-      <c r="L131" t="inlineStr"/>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>496670</v>
+        <v>496581</v>
       </c>
       <c r="R131" t="n">
-        <v>6827136</v>
+        <v>6827082</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14288,19 +14278,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z131" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB131" t="inlineStr">
-        <is>
-          <t>10:30</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14316,57 +14296,66 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>130256343</v>
+        <v>130255793</v>
       </c>
       <c r="B132" t="n">
-        <v>79211</v>
+        <v>8451</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>496851</v>
+        <v>496670</v>
       </c>
       <c r="R132" t="n">
-        <v>6827066</v>
+        <v>6827136</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14396,29 +14385,40 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="AB132" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AD132" t="b">
         <v>0</v>
       </c>
       <c r="AE132" t="b">
         <v>0</v>
       </c>
+      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
@@ -14639,10 +14639,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>130255810</v>
+        <v>130255806</v>
       </c>
       <c r="B135" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14674,10 +14674,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>497191</v>
+        <v>497147</v>
       </c>
       <c r="R135" t="n">
-        <v>6826663</v>
+        <v>6826725</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14709,7 +14709,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -14719,7 +14719,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14749,7 +14749,7 @@
         <v>130255813</v>
       </c>
       <c r="B136" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14853,10 +14853,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>130256345</v>
+        <v>130255810</v>
       </c>
       <c r="B137" t="n">
-        <v>78969</v>
+        <v>79219</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14864,21 +14864,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14888,10 +14888,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>496837</v>
+        <v>497191</v>
       </c>
       <c r="R137" t="n">
-        <v>6827069</v>
+        <v>6826663</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14921,9 +14921,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AA137" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB137" t="inlineStr">
+        <is>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14938,12 +14948,12 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
@@ -14953,7 +14963,7 @@
         <v>130256344</v>
       </c>
       <c r="B138" t="n">
-        <v>78969</v>
+        <v>78977</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15047,10 +15057,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>130255806</v>
+        <v>130256345</v>
       </c>
       <c r="B139" t="n">
-        <v>79211</v>
+        <v>78977</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15058,21 +15068,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15082,10 +15092,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>497147</v>
+        <v>496837</v>
       </c>
       <c r="R139" t="n">
-        <v>6826725</v>
+        <v>6827069</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15115,19 +15125,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z139" t="inlineStr">
-        <is>
-          <t>12:17</t>
-        </is>
-      </c>
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB139" t="inlineStr">
-        <is>
-          <t>12:17</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15142,22 +15142,22 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>130256361</v>
+        <v>130256389</v>
       </c>
       <c r="B140" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15189,10 +15189,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>496893</v>
+        <v>496578</v>
       </c>
       <c r="R140" t="n">
-        <v>6826989</v>
+        <v>6827076</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15251,10 +15251,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>130256389</v>
+        <v>130256361</v>
       </c>
       <c r="B141" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15286,10 +15286,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>496578</v>
+        <v>496893</v>
       </c>
       <c r="R141" t="n">
-        <v>6827076</v>
+        <v>6826989</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15351,7 +15351,7 @@
         <v>130256358</v>
       </c>
       <c r="B142" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15445,10 +15445,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>130256355</v>
+        <v>130256340</v>
       </c>
       <c r="B143" t="n">
-        <v>79211</v>
+        <v>79809</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15456,21 +15456,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15480,10 +15480,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>496940</v>
+        <v>496774</v>
       </c>
       <c r="R143" t="n">
-        <v>6826898</v>
+        <v>6827067</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15545,7 +15545,7 @@
         <v>130256362</v>
       </c>
       <c r="B144" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15639,10 +15639,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>130256364</v>
+        <v>130256355</v>
       </c>
       <c r="B145" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15674,10 +15674,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>496909</v>
+        <v>496940</v>
       </c>
       <c r="R145" t="n">
-        <v>6827002</v>
+        <v>6826898</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15739,7 +15739,7 @@
         <v>130256371</v>
       </c>
       <c r="B146" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15833,10 +15833,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>130255828</v>
+        <v>130256364</v>
       </c>
       <c r="B147" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15868,10 +15868,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>496658</v>
+        <v>496909</v>
       </c>
       <c r="R147" t="n">
-        <v>6827133</v>
+        <v>6827002</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15901,19 +15901,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z147" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA147" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB147" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15928,22 +15918,22 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>130255821</v>
+        <v>130255828</v>
       </c>
       <c r="B148" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15975,10 +15965,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>496839</v>
+        <v>496658</v>
       </c>
       <c r="R148" t="n">
-        <v>6827082</v>
+        <v>6827133</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16010,7 +16000,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -16020,7 +16010,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16047,56 +16037,45 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>130256394</v>
+        <v>130255821</v>
       </c>
       <c r="B149" t="n">
-        <v>93047</v>
+        <v>79219</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J149" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K149" t="inlineStr"/>
-      <c r="N149" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
           <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>496581</v>
+        <v>496839</v>
       </c>
       <c r="R149" t="n">
-        <v>6827079</v>
+        <v>6827082</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16126,75 +16105,95 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z149" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AA149" t="inlineStr">
         <is>
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="AB149" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
       <c r="AD149" t="b">
         <v>0</v>
       </c>
       <c r="AE149" t="b">
         <v>0</v>
       </c>
-      <c r="AF149" t="inlineStr"/>
       <c r="AG149" t="b">
         <v>0</v>
       </c>
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>130256340</v>
+        <v>130256394</v>
       </c>
       <c r="B150" t="n">
-        <v>79801</v>
+        <v>93060</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr"/>
+      <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
           <t>Bergtallstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>496774</v>
+        <v>496581</v>
       </c>
       <c r="R150" t="n">
-        <v>6827067</v>
+        <v>6827079</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16235,6 +16234,7 @@
       <c r="AE150" t="b">
         <v>0</v>
       </c>
+      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
@@ -16253,10 +16253,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>130255831</v>
+        <v>130256372</v>
       </c>
       <c r="B151" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16288,10 +16288,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>496599</v>
+        <v>496867</v>
       </c>
       <c r="R151" t="n">
-        <v>6827121</v>
+        <v>6827035</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16321,19 +16321,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z151" t="inlineStr">
-        <is>
-          <t>10:18</t>
-        </is>
-      </c>
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB151" t="inlineStr">
-        <is>
-          <t>10:18</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16348,22 +16338,22 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>130256372</v>
+        <v>130255811</v>
       </c>
       <c r="B152" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16395,10 +16385,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>496867</v>
+        <v>497200</v>
       </c>
       <c r="R152" t="n">
-        <v>6827035</v>
+        <v>6826832</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16428,9 +16418,19 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z152" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
       <c r="AA152" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB152" t="inlineStr">
+        <is>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16445,22 +16445,22 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>130255811</v>
+        <v>130255824</v>
       </c>
       <c r="B153" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16492,10 +16492,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>497200</v>
+        <v>496752</v>
       </c>
       <c r="R153" t="n">
-        <v>6826832</v>
+        <v>6827114</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16527,7 +16527,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -16537,7 +16537,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16564,10 +16564,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>130255824</v>
+        <v>130255831</v>
       </c>
       <c r="B154" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16599,10 +16599,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>496752</v>
+        <v>496599</v>
       </c>
       <c r="R154" t="n">
-        <v>6827114</v>
+        <v>6827121</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16634,7 +16634,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -16644,7 +16644,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16674,7 +16674,7 @@
         <v>130256385</v>
       </c>
       <c r="B155" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16771,7 +16771,7 @@
         <v>130255838</v>
       </c>
       <c r="B156" t="n">
-        <v>93047</v>
+        <v>93060</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16875,10 +16875,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>130255809</v>
+        <v>130255816</v>
       </c>
       <c r="B157" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16910,10 +16910,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>497168</v>
+        <v>496954</v>
       </c>
       <c r="R157" t="n">
-        <v>6826596</v>
+        <v>6827096</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16945,7 +16945,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -16955,7 +16955,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16982,10 +16982,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>130255816</v>
+        <v>130255809</v>
       </c>
       <c r="B158" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17017,10 +17017,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>496954</v>
+        <v>497168</v>
       </c>
       <c r="R158" t="n">
-        <v>6827096</v>
+        <v>6826596</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17052,7 +17052,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -17062,7 +17062,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17092,7 +17092,7 @@
         <v>130255829</v>
       </c>
       <c r="B159" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17199,7 +17199,7 @@
         <v>130256393</v>
       </c>
       <c r="B160" t="n">
-        <v>93047</v>
+        <v>93060</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>

--- a/artfynd/A 58895-2025 artfynd.xlsx
+++ b/artfynd/A 58895-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY167"/>
+  <dimension ref="A1:AZ167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252114</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,6 +898,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252115</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -995,6 +1010,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252154</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1102,6 +1122,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252155</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1209,6 +1234,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252156</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1316,6 +1346,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252157</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1423,6 +1458,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252158</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1531,6 +1571,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252606</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1639,6 +1684,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252607</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1747,6 +1797,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252608</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1855,6 +1910,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252609</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1962,6 +2022,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130255838</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2069,6 +2134,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130255839</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2167,6 +2237,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256392</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2264,6 +2339,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256393</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2373,6 +2453,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256394</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2480,6 +2565,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252131</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2587,6 +2677,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252132</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2694,6 +2789,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252133</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2801,6 +2901,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252134</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2908,6 +3013,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252135</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3015,6 +3125,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252136</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3122,6 +3237,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252137</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3229,6 +3349,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252138</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3336,6 +3461,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252139</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3443,6 +3573,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252140</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3550,6 +3685,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252141</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3657,6 +3797,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252142</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3764,6 +3909,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252143</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3871,6 +4021,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252144</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3978,6 +4133,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252145</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4085,6 +4245,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252146</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4192,6 +4357,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252147</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4299,6 +4469,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252148</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4410,6 +4585,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252149</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4517,6 +4697,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252150</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4624,6 +4809,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252151</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4731,6 +4921,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252152</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4838,6 +5033,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252153</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4945,6 +5145,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252597</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5052,6 +5257,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252598</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5159,6 +5369,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252599</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5266,6 +5481,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252600</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5373,6 +5593,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252601</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5480,6 +5705,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252602</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5587,6 +5817,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252603</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5694,6 +5929,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252604</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5801,6 +6041,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252605</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5908,6 +6153,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130255800</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6015,6 +6265,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130255801</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6122,6 +6377,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130255802</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6229,6 +6489,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130255803</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6336,6 +6601,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130255804</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6443,6 +6713,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130255805</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6550,6 +6825,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130255806</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6657,6 +6937,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130255807</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6764,6 +7049,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130255808</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6871,6 +7161,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130255809</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6978,6 +7273,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130255810</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7085,6 +7385,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130255811</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7192,6 +7497,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130255812</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7299,6 +7609,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130255813</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7406,6 +7721,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130255814</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7513,6 +7833,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130255816</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7620,6 +7945,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130255817</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7727,6 +8057,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130255818</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7834,6 +8169,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130255819</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7941,6 +8281,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130255820</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8048,6 +8393,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130255821</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8155,6 +8505,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130255822</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8262,6 +8617,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130255823</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8369,6 +8729,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130255824</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8476,6 +8841,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130255825</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8583,6 +8953,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130255826</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8690,6 +9065,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130255827</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8797,6 +9177,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130255828</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8904,6 +9289,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130255829</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9011,6 +9401,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130255830</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9118,6 +9513,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130255831</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9225,6 +9625,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130255832</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9332,6 +9737,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130255833</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9439,6 +9849,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130255834</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9546,6 +9961,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130255835</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9653,6 +10073,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130255836</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9760,6 +10185,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130255837</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9857,6 +10287,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256343</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9954,6 +10389,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256355</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10051,6 +10491,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256356</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10148,6 +10593,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256357</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10245,6 +10695,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256358</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10342,6 +10797,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256359</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10439,6 +10899,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256360</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10536,6 +11001,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256361</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10633,6 +11103,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256362</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10730,6 +11205,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256363</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10827,6 +11307,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256364</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10924,6 +11409,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256365</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11021,6 +11511,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256367</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11118,6 +11613,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256368</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11215,6 +11715,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256369</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11312,6 +11817,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256370</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11409,6 +11919,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256371</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11506,6 +12021,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256372</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11603,6 +12123,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256373</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11700,6 +12225,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256374</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11797,6 +12327,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256375</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11894,6 +12429,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256376</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11991,6 +12531,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256378</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12088,6 +12633,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256379</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12185,6 +12735,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256380</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12282,6 +12837,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256381</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12379,6 +12939,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256382</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12476,6 +13041,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256383</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12573,6 +13143,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256384</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12670,6 +13245,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256385</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12767,6 +13347,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256386</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12864,6 +13449,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256387</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12961,6 +13551,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256388</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -13058,6 +13653,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256389</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13155,6 +13755,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256390</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13252,6 +13857,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256391</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13359,6 +13969,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252124</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13466,6 +14081,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252125</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13573,6 +14193,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252126</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13680,6 +14305,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252127</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13787,6 +14417,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252128</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13894,6 +14529,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252129</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -14001,6 +14641,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252588</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -14108,6 +14753,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252589</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -14215,6 +14865,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252590</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -14322,6 +14977,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252591</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -14429,6 +15089,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252592</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -14536,6 +15201,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252594</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -14643,6 +15313,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252595</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -14750,6 +15425,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252596</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -14857,6 +15537,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130255796</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -14964,6 +15649,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130255797</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -15071,6 +15761,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130255798</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -15168,6 +15863,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256350</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -15265,6 +15965,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256351</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -15362,6 +16067,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256352</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -15459,6 +16169,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256353</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -15556,6 +16271,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256354</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -15663,6 +16383,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252116</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -15778,6 +16503,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252585</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -15898,6 +16628,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252118</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -16008,6 +16743,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256342</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -16125,6 +16865,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252130</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -16232,6 +16977,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252119</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -16339,6 +17089,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252584</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -16446,6 +17201,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252120</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -16553,6 +17313,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252121</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -16660,6 +17425,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252122</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -16767,6 +17537,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252123</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -16874,6 +17649,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252586</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -16981,6 +17761,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252587</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -17098,6 +17883,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130255793</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -17205,6 +17995,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256347</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -17312,6 +18107,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256348</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -17419,6 +18219,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256349</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -17534,6 +18339,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129846986</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -17631,6 +18441,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256344</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -17728,6 +18543,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256345</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -17825,6 +18645,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256346</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -17932,6 +18757,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130252117</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -18029,8 +18859,181 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130256340</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>